--- a/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
+++ b/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E8A516-5AFE-4C02-AFB8-4E006C6AEA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82103BD-568D-4F11-BDC3-68F7F1956363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1229,9 +1229,6 @@
     <t>Redondeo mes de FEBRERO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Mes de FEBRERO Fc. 00000244</t>
-  </si>
-  <si>
     <t>Grey Brick - Fc. 0000007595 - Certificacion de obra pavimento correspondiente a FEBRERO</t>
   </si>
   <si>
@@ -1540,6 +1537,9 @@
   </si>
   <si>
     <t>TOTAL AL 02/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - Mes de FEBRERO </t>
   </si>
 </sst>
 </file>
@@ -2912,6 +2912,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2924,36 +2937,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2987,50 +2981,46 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3089,7 +3079,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3117,12 +3124,6 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3134,6 +3135,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3165,13 +3172,6 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -3604,34 +3604,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="403"/>
-      <c r="B1" s="398" t="s">
+      <c r="A1" s="405"/>
+      <c r="B1" s="400" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="399"/>
-      <c r="D1" s="399"/>
-      <c r="E1" s="400"/>
+      <c r="C1" s="401"/>
+      <c r="D1" s="401"/>
+      <c r="E1" s="402"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="404"/>
-      <c r="B2" s="398" t="s">
+      <c r="A2" s="406"/>
+      <c r="B2" s="400" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="399"/>
-      <c r="D2" s="399"/>
-      <c r="E2" s="400"/>
+      <c r="C2" s="401"/>
+      <c r="D2" s="401"/>
+      <c r="E2" s="402"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="404"/>
-      <c r="B3" s="395" t="s">
+      <c r="A3" s="406"/>
+      <c r="B3" s="397" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="396"/>
-      <c r="D3" s="396"/>
-      <c r="E3" s="397"/>
+      <c r="C3" s="398"/>
+      <c r="D3" s="398"/>
+      <c r="E3" s="399"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="404"/>
+      <c r="A4" s="406"/>
       <c r="B4" s="47" t="s">
         <v>156</v>
       </c>
@@ -3640,7 +3640,7 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="404"/>
+      <c r="A5" s="406"/>
       <c r="B5" s="50" t="s">
         <v>392</v>
       </c>
@@ -3649,7 +3649,7 @@
       <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="404"/>
+      <c r="A6" s="406"/>
       <c r="B6" s="51" t="s">
         <v>287</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="404"/>
+      <c r="A7" s="406"/>
       <c r="B7" s="51" t="s">
         <v>286</v>
       </c>
@@ -3667,36 +3667,36 @@
       <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="405"/>
-      <c r="B8" s="401" t="s">
+      <c r="A8" s="407"/>
+      <c r="B8" s="403" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="401"/>
-      <c r="D8" s="401"/>
-      <c r="E8" s="402"/>
+      <c r="C8" s="403"/>
+      <c r="D8" s="403"/>
+      <c r="E8" s="404"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="406" t="s">
-        <v>496</v>
-      </c>
-      <c r="B10" s="406"/>
-      <c r="C10" s="406"/>
-      <c r="D10" s="406"/>
-      <c r="E10" s="406"/>
+      <c r="A10" s="392" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" s="392"/>
+      <c r="C10" s="392"/>
+      <c r="D10" s="392"/>
+      <c r="E10" s="392"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="406"/>
-      <c r="B11" s="406"/>
-      <c r="C11" s="406"/>
-      <c r="D11" s="406"/>
-      <c r="E11" s="406"/>
+      <c r="A11" s="392"/>
+      <c r="B11" s="392"/>
+      <c r="C11" s="392"/>
+      <c r="D11" s="392"/>
+      <c r="E11" s="392"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="406"/>
-      <c r="B12" s="406"/>
-      <c r="C12" s="406"/>
-      <c r="D12" s="406"/>
-      <c r="E12" s="406"/>
+      <c r="A12" s="392"/>
+      <c r="B12" s="392"/>
+      <c r="C12" s="392"/>
+      <c r="D12" s="392"/>
+      <c r="E12" s="392"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="32"/>
@@ -3713,34 +3713,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="407" t="s">
+      <c r="A15" s="393" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="407"/>
-      <c r="C15" s="407"/>
-      <c r="D15" s="407"/>
-      <c r="E15" s="407"/>
+      <c r="B15" s="393"/>
+      <c r="C15" s="393"/>
+      <c r="D15" s="393"/>
+      <c r="E15" s="393"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="407"/>
-      <c r="B16" s="407"/>
-      <c r="C16" s="407"/>
-      <c r="D16" s="407"/>
-      <c r="E16" s="407"/>
+      <c r="A16" s="393"/>
+      <c r="B16" s="393"/>
+      <c r="C16" s="393"/>
+      <c r="D16" s="393"/>
+      <c r="E16" s="393"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="407"/>
-      <c r="B17" s="407"/>
-      <c r="C17" s="407"/>
-      <c r="D17" s="407"/>
-      <c r="E17" s="407"/>
+      <c r="A17" s="393"/>
+      <c r="B17" s="393"/>
+      <c r="C17" s="393"/>
+      <c r="D17" s="393"/>
+      <c r="E17" s="393"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="407"/>
-      <c r="B18" s="407"/>
-      <c r="C18" s="407"/>
-      <c r="D18" s="407"/>
-      <c r="E18" s="407"/>
+      <c r="A18" s="393"/>
+      <c r="B18" s="393"/>
+      <c r="C18" s="393"/>
+      <c r="D18" s="393"/>
+      <c r="E18" s="393"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32"/>
@@ -3787,33 +3787,33 @@
       </c>
       <c r="B24" s="182"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="469">
+      <c r="D24" s="382">
         <v>2001463.53</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="409" t="s">
+      <c r="A25" s="395" t="s">
         <v>394</v>
       </c>
-      <c r="B25" s="410"/>
+      <c r="B25" s="396"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="469">
+      <c r="D25" s="382">
         <v>-435318.34</v>
       </c>
       <c r="E25" s="24"/>
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="411" t="s">
+      <c r="A26" s="386" t="s">
         <v>395</v>
       </c>
-      <c r="B26" s="412"/>
+      <c r="B26" s="387"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="469">
+      <c r="D26" s="382">
         <v>0.81</v>
       </c>
       <c r="E26" s="24"/>
@@ -3839,12 +3839,12 @@
       <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="383" t="s">
+      <c r="A28" s="390" t="s">
         <v>315</v>
       </c>
-      <c r="B28" s="384"/>
+      <c r="B28" s="391"/>
       <c r="C28" s="24"/>
-      <c r="D28" s="469">
+      <c r="D28" s="382">
         <v>920000</v>
       </c>
       <c r="E28" s="24" t="s">
@@ -3889,31 +3889,31 @@
     </row>
     <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="108"/>
-      <c r="D32" s="470">
+      <c r="D32" s="383">
         <v>933473.93</v>
       </c>
       <c r="E32" s="84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G32" s="42"/>
     </row>
     <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="109" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="108"/>
-      <c r="D33" s="470">
+      <c r="D33" s="383">
         <v>92048.38</v>
       </c>
       <c r="E33" s="84" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G33" s="42"/>
     </row>
@@ -3926,7 +3926,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="108"/>
-      <c r="D34" s="470">
+      <c r="D34" s="383">
         <v>213869.17</v>
       </c>
       <c r="E34" s="84" t="str">
@@ -3944,7 +3944,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="108"/>
-      <c r="D35" s="471">
+      <c r="D35" s="384">
         <v>10227.6</v>
       </c>
       <c r="E35" s="84" t="str">
@@ -3975,49 +3975,49 @@
       <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="381" t="s">
+      <c r="A38" s="388" t="s">
         <v>273</v>
       </c>
-      <c r="B38" s="382"/>
+      <c r="B38" s="389"/>
       <c r="C38" s="24"/>
       <c r="D38" s="231">
         <v>148964</v>
       </c>
       <c r="E38" s="85" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="381" t="s">
+      <c r="A39" s="388" t="s">
         <v>274</v>
       </c>
-      <c r="B39" s="382"/>
+      <c r="B39" s="389"/>
       <c r="C39" s="24"/>
       <c r="D39" s="231">
         <v>6160</v>
       </c>
       <c r="E39" s="85" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="381" t="s">
+      <c r="A40" s="388" t="s">
         <v>318</v>
       </c>
-      <c r="B40" s="382"/>
+      <c r="B40" s="389"/>
       <c r="C40" s="24"/>
       <c r="D40" s="231">
         <v>23596</v>
       </c>
       <c r="E40" s="85" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="381" t="s">
+      <c r="A41" s="388" t="s">
         <v>317</v>
       </c>
-      <c r="B41" s="382"/>
+      <c r="B41" s="389"/>
       <c r="C41" s="24"/>
       <c r="D41" s="231"/>
       <c r="E41" s="85"/>
@@ -4044,31 +4044,31 @@
       <c r="E43" s="29"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="381" t="s">
-        <v>400</v>
-      </c>
-      <c r="B44" s="408"/>
+      <c r="A44" s="388" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="394"/>
       <c r="C44" s="112"/>
       <c r="D44" s="231">
         <v>44907682.960000001</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G44" s="13"/>
       <c r="I44" s="40"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="381" t="s">
-        <v>401</v>
-      </c>
-      <c r="B45" s="408"/>
+      <c r="A45" s="388" t="s">
+        <v>400</v>
+      </c>
+      <c r="B45" s="394"/>
       <c r="C45" s="112"/>
       <c r="D45" s="231">
         <v>4773198.96</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="13"/>
     </row>
@@ -4096,10 +4096,10 @@
       <c r="E47" s="72"/>
     </row>
     <row r="48" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="381" t="s">
+      <c r="A48" s="388" t="s">
         <v>330</v>
       </c>
-      <c r="B48" s="408"/>
+      <c r="B48" s="394"/>
       <c r="C48" s="112"/>
       <c r="D48" s="231">
         <v>1212341.6499999999</v>
@@ -4109,10 +4109,10 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="381" t="s">
+      <c r="A49" s="388" t="s">
         <v>383</v>
       </c>
-      <c r="B49" s="408"/>
+      <c r="B49" s="394"/>
       <c r="C49" s="112"/>
       <c r="D49" s="231">
         <v>1512500</v>
@@ -4122,23 +4122,23 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="381" t="s">
-        <v>415</v>
-      </c>
-      <c r="B50" s="408"/>
+      <c r="A50" s="388" t="s">
+        <v>414</v>
+      </c>
+      <c r="B50" s="394"/>
       <c r="C50" s="112"/>
       <c r="D50" s="231">
         <v>5445000</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="381" t="s">
+      <c r="A51" s="388" t="s">
         <v>384</v>
       </c>
-      <c r="B51" s="382"/>
+      <c r="B51" s="389"/>
       <c r="C51" s="113"/>
       <c r="D51" s="231">
         <v>480000</v>
@@ -4149,23 +4149,23 @@
       <c r="G51" s="36"/>
     </row>
     <row r="52" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="381" t="s">
-        <v>425</v>
-      </c>
-      <c r="B52" s="382"/>
+      <c r="A52" s="388" t="s">
+        <v>424</v>
+      </c>
+      <c r="B52" s="389"/>
       <c r="C52" s="113"/>
       <c r="D52" s="231">
         <v>6300000</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="381" t="s">
+      <c r="A53" s="388" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="382"/>
+      <c r="B53" s="389"/>
       <c r="C53" s="113"/>
       <c r="D53" s="231">
         <v>228690</v>
@@ -4175,10 +4175,10 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="381" t="s">
+      <c r="A54" s="388" t="s">
         <v>386</v>
       </c>
-      <c r="B54" s="382"/>
+      <c r="B54" s="389"/>
       <c r="C54" s="113"/>
       <c r="D54" s="231">
         <v>228690</v>
@@ -4188,10 +4188,10 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="381" t="s">
-        <v>411</v>
-      </c>
-      <c r="B55" s="382"/>
+      <c r="A55" s="388" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" s="389"/>
       <c r="C55" s="113"/>
       <c r="D55" s="231">
         <v>943800</v>
@@ -4201,10 +4201,10 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="381" t="s">
-        <v>410</v>
-      </c>
-      <c r="B56" s="382"/>
+      <c r="A56" s="388" t="s">
+        <v>409</v>
+      </c>
+      <c r="B56" s="389"/>
       <c r="C56" s="113"/>
       <c r="D56" s="231">
         <v>943800</v>
@@ -4214,62 +4214,62 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="381" t="s">
+      <c r="A57" s="388" t="s">
         <v>376</v>
       </c>
-      <c r="B57" s="382"/>
+      <c r="B57" s="389"/>
       <c r="C57" s="113"/>
       <c r="D57" s="231">
         <v>820380</v>
       </c>
       <c r="E57" s="86" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="381" t="s">
+      <c r="A58" s="388" t="s">
         <v>377</v>
       </c>
-      <c r="B58" s="382"/>
+      <c r="B58" s="389"/>
       <c r="C58" s="113"/>
       <c r="D58" s="231">
         <v>820380</v>
       </c>
       <c r="E58" s="86" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="381" t="s">
+      <c r="A59" s="388" t="s">
         <v>379</v>
       </c>
-      <c r="B59" s="382"/>
+      <c r="B59" s="389"/>
       <c r="C59" s="113"/>
       <c r="D59" s="231">
         <v>100000</v>
       </c>
       <c r="E59" s="86" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="381" t="s">
-        <v>417</v>
-      </c>
-      <c r="B60" s="382"/>
+      <c r="A60" s="388" t="s">
+        <v>416</v>
+      </c>
+      <c r="B60" s="389"/>
       <c r="C60" s="113"/>
       <c r="D60" s="231">
         <v>100000</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="381" t="s">
-        <v>430</v>
-      </c>
-      <c r="B61" s="382"/>
+      <c r="A61" s="388" t="s">
+        <v>429</v>
+      </c>
+      <c r="B61" s="389"/>
       <c r="C61" s="24"/>
       <c r="D61" s="149">
         <v>200000</v>
@@ -4281,31 +4281,31 @@
       <c r="H61" s="97"/>
     </row>
     <row r="62" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="381" t="s">
-        <v>405</v>
-      </c>
-      <c r="B62" s="382"/>
+      <c r="A62" s="388" t="s">
+        <v>404</v>
+      </c>
+      <c r="B62" s="389"/>
       <c r="C62" s="24"/>
       <c r="D62" s="231">
         <v>2459883</v>
       </c>
       <c r="E62" s="86" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G62" s="97"/>
       <c r="H62" s="97"/>
     </row>
     <row r="63" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="381" t="s">
+      <c r="A63" s="388" t="s">
         <v>288</v>
       </c>
-      <c r="B63" s="382"/>
+      <c r="B63" s="389"/>
       <c r="C63" s="24"/>
       <c r="D63" s="231">
         <v>350000</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G63" s="97"/>
       <c r="H63" s="97"/>
@@ -4332,10 +4332,10 @@
       <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="383" t="s">
-        <v>429</v>
-      </c>
-      <c r="B66" s="384"/>
+      <c r="A66" s="390" t="s">
+        <v>428</v>
+      </c>
+      <c r="B66" s="391"/>
       <c r="C66" s="24"/>
       <c r="D66" s="149">
         <v>280000</v>
@@ -4345,10 +4345,10 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="383" t="s">
+      <c r="A67" s="390" t="s">
         <v>380</v>
       </c>
-      <c r="B67" s="384"/>
+      <c r="B67" s="391"/>
       <c r="C67" s="24"/>
       <c r="D67" s="149">
         <v>250000</v>
@@ -4358,10 +4358,10 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="383" t="s">
+      <c r="A68" s="390" t="s">
         <v>382</v>
       </c>
-      <c r="B68" s="384"/>
+      <c r="B68" s="391"/>
       <c r="C68" s="24"/>
       <c r="D68" s="149">
         <v>150000</v>
@@ -4371,29 +4371,29 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="123.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="381" t="s">
-        <v>426</v>
-      </c>
-      <c r="B69" s="382"/>
+      <c r="A69" s="388" t="s">
+        <v>425</v>
+      </c>
+      <c r="B69" s="389"/>
       <c r="C69" s="109"/>
       <c r="D69" s="149">
         <v>2130000</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="381" t="s">
-        <v>493</v>
-      </c>
-      <c r="B70" s="382"/>
+      <c r="A70" s="388" t="s">
+        <v>492</v>
+      </c>
+      <c r="B70" s="389"/>
       <c r="C70" s="109"/>
       <c r="D70" s="149">
         <v>150000</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G70" s="97">
         <f>D69+D70+D71+D72</f>
@@ -4401,36 +4401,36 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="381" t="s">
-        <v>406</v>
-      </c>
-      <c r="B71" s="382"/>
+      <c r="A71" s="388" t="s">
+        <v>405</v>
+      </c>
+      <c r="B71" s="389"/>
       <c r="C71" s="109"/>
       <c r="D71" s="149">
         <v>2200000</v>
       </c>
       <c r="E71" s="156" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="381" t="s">
-        <v>434</v>
-      </c>
-      <c r="B72" s="382"/>
+      <c r="A72" s="388" t="s">
+        <v>433</v>
+      </c>
+      <c r="B72" s="389"/>
       <c r="C72" s="24"/>
       <c r="D72" s="149">
         <v>320000</v>
       </c>
       <c r="E72" s="87" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="381" t="s">
-        <v>427</v>
-      </c>
-      <c r="B73" s="382"/>
+      <c r="A73" s="388" t="s">
+        <v>426</v>
+      </c>
+      <c r="B73" s="389"/>
       <c r="C73" s="109"/>
       <c r="D73" s="149">
         <v>1050000</v>
@@ -4441,10 +4441,10 @@
       <c r="F73" s="97"/>
     </row>
     <row r="74" spans="1:7" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="381" t="s">
-        <v>428</v>
-      </c>
-      <c r="B74" s="382"/>
+      <c r="A74" s="388" t="s">
+        <v>427</v>
+      </c>
+      <c r="B74" s="389"/>
       <c r="C74" s="109"/>
       <c r="D74" s="149">
         <v>1390000</v>
@@ -4454,141 +4454,141 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="381" t="s">
-        <v>441</v>
-      </c>
-      <c r="B75" s="382"/>
+      <c r="A75" s="388" t="s">
+        <v>440</v>
+      </c>
+      <c r="B75" s="389"/>
       <c r="C75" s="109"/>
       <c r="D75" s="149">
         <v>3000000</v>
       </c>
       <c r="E75" s="156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="381" t="s">
-        <v>418</v>
-      </c>
-      <c r="B76" s="382"/>
+      <c r="A76" s="388" t="s">
+        <v>417</v>
+      </c>
+      <c r="B76" s="389"/>
       <c r="C76" s="109"/>
       <c r="D76" s="149">
         <v>319377.61</v>
       </c>
       <c r="E76" s="96" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="381" t="s">
-        <v>494</v>
-      </c>
-      <c r="B77" s="382"/>
+      <c r="A77" s="388" t="s">
+        <v>493</v>
+      </c>
+      <c r="B77" s="389"/>
       <c r="C77" s="109"/>
       <c r="D77" s="149">
         <v>112180.05</v>
       </c>
       <c r="E77" s="96" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="381" t="s">
-        <v>443</v>
-      </c>
-      <c r="B78" s="382"/>
+      <c r="A78" s="388" t="s">
+        <v>442</v>
+      </c>
+      <c r="B78" s="389"/>
       <c r="C78" s="109"/>
       <c r="D78" s="149">
         <v>73716.19</v>
       </c>
       <c r="E78" s="156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="381" t="s">
-        <v>444</v>
-      </c>
-      <c r="B79" s="382"/>
+      <c r="A79" s="388" t="s">
+        <v>443</v>
+      </c>
+      <c r="B79" s="389"/>
       <c r="C79" s="109"/>
       <c r="D79" s="149">
         <v>588090.9</v>
       </c>
       <c r="E79" s="156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F79" s="97"/>
     </row>
     <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="381" t="s">
-        <v>445</v>
-      </c>
-      <c r="B80" s="382"/>
+      <c r="A80" s="388" t="s">
+        <v>444</v>
+      </c>
+      <c r="B80" s="389"/>
       <c r="C80" s="109"/>
       <c r="D80" s="149">
         <v>54497.599999999999</v>
       </c>
       <c r="E80" s="156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="381" t="s">
-        <v>446</v>
-      </c>
-      <c r="B81" s="382"/>
+      <c r="A81" s="388" t="s">
+        <v>445</v>
+      </c>
+      <c r="B81" s="389"/>
       <c r="C81" s="109"/>
       <c r="D81" s="149">
         <v>160307.04</v>
       </c>
       <c r="E81" s="156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="381" t="s">
-        <v>449</v>
-      </c>
-      <c r="B82" s="382"/>
+      <c r="A82" s="388" t="s">
+        <v>448</v>
+      </c>
+      <c r="B82" s="389"/>
       <c r="C82" s="109"/>
       <c r="D82" s="149">
         <v>12</v>
       </c>
       <c r="E82" s="156" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="381" t="s">
+      <c r="A83" s="388" t="s">
         <v>390</v>
       </c>
-      <c r="B83" s="382"/>
+      <c r="B83" s="389"/>
       <c r="C83" s="109"/>
       <c r="D83" s="149">
         <v>97200</v>
       </c>
       <c r="E83" s="96" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="381" t="s">
-        <v>433</v>
-      </c>
-      <c r="B84" s="382"/>
+      <c r="A84" s="388" t="s">
+        <v>432</v>
+      </c>
+      <c r="B84" s="389"/>
       <c r="C84" s="109"/>
       <c r="D84" s="149">
         <v>146099</v>
       </c>
       <c r="E84" s="96" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="381" t="s">
-        <v>452</v>
-      </c>
-      <c r="B85" s="382"/>
+      <c r="A85" s="388" t="s">
+        <v>451</v>
+      </c>
+      <c r="B85" s="389"/>
       <c r="C85" s="109"/>
       <c r="D85" s="149">
         <v>681000</v>
@@ -4598,10 +4598,10 @@
       </c>
     </row>
     <row r="86" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="381" t="s">
+      <c r="A86" s="388" t="s">
         <v>388</v>
       </c>
-      <c r="B86" s="382"/>
+      <c r="B86" s="389"/>
       <c r="C86" s="109"/>
       <c r="D86" s="149">
         <v>481000</v>
@@ -4632,19 +4632,19 @@
       <c r="E88" s="26"/>
     </row>
     <row r="89" spans="1:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="381" t="s">
-        <v>396</v>
-      </c>
-      <c r="B89" s="382"/>
+      <c r="A89" s="388" t="s">
+        <v>497</v>
+      </c>
+      <c r="B89" s="389"/>
       <c r="C89" s="24"/>
       <c r="D89" s="365"/>
       <c r="E89" s="96"/>
     </row>
-    <row r="90" spans="1:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="381" t="s">
-        <v>412</v>
-      </c>
-      <c r="B90" s="382"/>
+    <row r="90" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="388" t="s">
+        <v>411</v>
+      </c>
+      <c r="B90" s="389"/>
       <c r="C90" s="24"/>
       <c r="D90" s="365">
         <v>1900000</v>
@@ -4762,10 +4762,10 @@
       <c r="E101" s="44"/>
     </row>
     <row r="102" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="381" t="s">
+      <c r="A102" s="388" t="s">
         <v>389</v>
       </c>
-      <c r="B102" s="382"/>
+      <c r="B102" s="389"/>
       <c r="C102" s="24"/>
       <c r="D102" s="231">
         <v>452107.07</v>
@@ -4775,23 +4775,23 @@
       </c>
     </row>
     <row r="103" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="381" t="s">
+      <c r="A103" s="388" t="s">
         <v>331</v>
       </c>
-      <c r="B103" s="382"/>
+      <c r="B103" s="389"/>
       <c r="C103" s="24"/>
       <c r="D103" s="231">
         <v>74126.81</v>
       </c>
       <c r="E103" s="212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="381" t="s">
+      <c r="A104" s="388" t="s">
         <v>332</v>
       </c>
-      <c r="B104" s="382"/>
+      <c r="B104" s="389"/>
       <c r="C104" s="24"/>
       <c r="D104" s="231">
         <v>74126.81</v>
@@ -4802,10 +4802,10 @@
       </c>
     </row>
     <row r="105" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="381" t="s">
+      <c r="A105" s="388" t="s">
         <v>333</v>
       </c>
-      <c r="B105" s="382"/>
+      <c r="B105" s="389"/>
       <c r="C105" s="24"/>
       <c r="D105" s="231">
         <v>75556.14</v>
@@ -4816,10 +4816,10 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="383" t="s">
+      <c r="A106" s="390" t="s">
         <v>378</v>
       </c>
-      <c r="B106" s="384"/>
+      <c r="B106" s="391"/>
       <c r="C106" s="24"/>
       <c r="D106" s="231">
         <v>1114493.6200000001</v>
@@ -4829,10 +4829,10 @@
       </c>
     </row>
     <row r="107" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="383" t="s">
+      <c r="A107" s="390" t="s">
         <v>192</v>
       </c>
-      <c r="B107" s="384"/>
+      <c r="B107" s="391"/>
       <c r="C107" s="24"/>
       <c r="D107" s="231">
         <v>6056.84</v>
@@ -4843,17 +4843,17 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="383" t="s">
+      <c r="A108" s="390" t="s">
         <v>306</v>
       </c>
-      <c r="B108" s="384"/>
+      <c r="B108" s="391"/>
       <c r="C108" s="24"/>
       <c r="D108" s="231"/>
       <c r="E108" s="24" t="s">
         <v>275</v>
       </c>
       <c r="G108" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4885,21 +4885,21 @@
       <c r="E111" s="52"/>
     </row>
     <row r="112" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="383" t="s">
-        <v>397</v>
-      </c>
-      <c r="B112" s="384"/>
+      <c r="A112" s="390" t="s">
+        <v>396</v>
+      </c>
+      <c r="B112" s="391"/>
       <c r="C112" s="24"/>
-      <c r="D112" s="472">
+      <c r="D112" s="385">
         <v>5816279.9100000001</v>
       </c>
       <c r="E112" s="86" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="383"/>
-      <c r="B113" s="384"/>
+      <c r="A113" s="390"/>
+      <c r="B113" s="391"/>
       <c r="C113" s="24"/>
       <c r="D113" s="149"/>
       <c r="E113" s="86"/>
@@ -4966,10 +4966,10 @@
       <c r="E120" s="59"/>
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="392" t="s">
-        <v>402</v>
-      </c>
-      <c r="B121" s="392"/>
+      <c r="A121" s="415" t="s">
+        <v>401</v>
+      </c>
+      <c r="B121" s="415"/>
       <c r="C121" s="24"/>
       <c r="D121" s="231">
         <f>1500871-920000</f>
@@ -4981,10 +4981,10 @@
       </c>
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="381" t="s">
-        <v>404</v>
-      </c>
-      <c r="B122" s="382"/>
+      <c r="A122" s="388" t="s">
+        <v>403</v>
+      </c>
+      <c r="B122" s="389"/>
       <c r="C122" s="109"/>
       <c r="D122" s="231">
         <v>91169.89</v>
@@ -5103,24 +5103,24 @@
       <c r="E133" s="32"/>
     </row>
     <row r="134" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="385" t="s">
-        <v>403</v>
-      </c>
-      <c r="B134" s="386"/>
+      <c r="A134" s="408" t="s">
+        <v>402</v>
+      </c>
+      <c r="B134" s="409"/>
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32"/>
     </row>
     <row r="135" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="387"/>
-      <c r="B135" s="388"/>
+      <c r="A135" s="410"/>
+      <c r="B135" s="411"/>
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32"/>
     </row>
     <row r="136" spans="1:5" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="389"/>
-      <c r="B136" s="390"/>
+      <c r="A136" s="412"/>
+      <c r="B136" s="413"/>
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32"/>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="140" spans="1:5" s="163" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="165" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B140" s="166">
         <v>850000</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="143" spans="1:5" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="144" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B143" s="169">
         <v>-767817</v>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="144" spans="1:5" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="144" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B144" s="169">
         <v>-23703</v>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="145" spans="1:6" s="163" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="144" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B145" s="169">
         <v>-1520000</v>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="146" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="144" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B146" s="169">
         <f>-{43790}</f>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="147" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B147" s="169">
         <v>-23204</v>
@@ -5237,7 +5237,7 @@
     </row>
     <row r="148" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="144" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B148" s="169">
         <v>-23442</v>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="149" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="144" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B149" s="169">
         <v>-23442</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="150" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="144" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B150" s="169">
         <v>-750500</v>
@@ -5267,7 +5267,7 @@
     </row>
     <row r="151" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="144" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B151" s="169">
         <f>-28259-29121-48822</f>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="152" spans="1:6" s="163" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="34" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B152" s="169">
         <v>-305367.8</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="153" spans="1:6" s="163" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="357" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B153" s="355">
         <v>-1500000</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="154" spans="1:6" s="163" customFormat="1" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="357" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B154" s="355">
         <v>-1500000</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="155" spans="1:6" s="163" customFormat="1" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="357" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B155" s="355">
         <v>-7500000</v>
@@ -5318,7 +5318,7 @@
     </row>
     <row r="156" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="356" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B156" s="355">
         <v>-127445</v>
@@ -5395,10 +5395,10 @@
       <c r="F162" s="83"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="393" t="s">
+      <c r="A163" s="416" t="s">
         <v>298</v>
       </c>
-      <c r="B163" s="394"/>
+      <c r="B163" s="417"/>
       <c r="C163" s="6"/>
       <c r="D163" s="13"/>
       <c r="E163" s="37"/>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="173" spans="1:7" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="99" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B173" s="145">
         <v>-57120</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="174" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="99" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B174" s="145">
         <v>-46999</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="175" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="99" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B175" s="145">
         <v>-7999</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="176" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="99" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B176" s="145">
         <v>-51999</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="182" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="134" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B182" s="225">
         <v>39090069.299999997</v>
@@ -5670,16 +5670,16 @@
       <c r="F185" s="38"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A186" s="391" t="s">
+      <c r="A186" s="414" t="s">
         <v>17</v>
       </c>
-      <c r="B186" s="391"/>
-      <c r="C186" s="391"/>
+      <c r="B186" s="414"/>
+      <c r="C186" s="414"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A187" s="391"/>
-      <c r="B187" s="391"/>
-      <c r="C187" s="391"/>
+      <c r="A187" s="414"/>
+      <c r="B187" s="414"/>
+      <c r="C187" s="414"/>
     </row>
     <row r="188" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="71"/>
@@ -5706,19 +5706,44 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A134:B136"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A186:C187"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
     <mergeCell ref="A10:E12"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A15:E18"/>
@@ -5735,46 +5760,21 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A134:B136"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A186:C187"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -5816,7 +5816,7 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="426" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D1" s="427"/>
       <c r="E1" s="427"/>
@@ -5855,20 +5855,20 @@
       <c r="D2" s="425"/>
       <c r="E2" s="425"/>
       <c r="F2" s="155"/>
-      <c r="G2" s="420">
+      <c r="G2" s="422">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="420"/>
+      <c r="H2" s="422"/>
       <c r="I2" s="155" t="s">
         <v>279</v>
       </c>
       <c r="J2" s="155"/>
-      <c r="K2" s="420">
+      <c r="K2" s="422">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="420"/>
+      <c r="L2" s="422"/>
       <c r="M2" s="361"/>
       <c r="N2" s="362" t="s">
         <v>265</v>
@@ -5927,7 +5927,7 @@
       <c r="D4" s="438" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="421" t="s">
+      <c r="E4" s="418" t="s">
         <v>184</v>
       </c>
       <c r="F4" s="438" t="s">
@@ -5936,26 +5936,26 @@
       <c r="G4" s="440" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="421" t="s">
+      <c r="H4" s="418" t="s">
         <v>235</v>
       </c>
-      <c r="I4" s="421" t="s">
+      <c r="I4" s="418" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="421"/>
-      <c r="K4" s="421" t="s">
+      <c r="J4" s="418"/>
+      <c r="K4" s="418" t="s">
         <v>185</v>
       </c>
-      <c r="L4" s="421" t="s">
+      <c r="L4" s="418" t="s">
         <v>148</v>
       </c>
-      <c r="M4" s="421" t="s">
+      <c r="M4" s="418" t="s">
         <v>187</v>
       </c>
-      <c r="N4" s="421" t="s">
+      <c r="N4" s="418" t="s">
         <v>186</v>
       </c>
-      <c r="O4" s="421" t="s">
+      <c r="O4" s="418" t="s">
         <v>261</v>
       </c>
       <c r="P4" s="429" t="s">
@@ -5966,7 +5966,7 @@
         <v>326</v>
       </c>
       <c r="S4" s="430"/>
-      <c r="T4" s="421" t="s">
+      <c r="T4" s="418" t="s">
         <v>263</v>
       </c>
       <c r="U4" s="13"/>
@@ -5976,17 +5976,17 @@
       <c r="B5" s="439"/>
       <c r="C5" s="439"/>
       <c r="D5" s="439"/>
-      <c r="E5" s="422"/>
+      <c r="E5" s="419"/>
       <c r="F5" s="439"/>
       <c r="G5" s="441"/>
-      <c r="H5" s="422"/>
-      <c r="I5" s="422"/>
-      <c r="J5" s="422"/>
-      <c r="K5" s="422"/>
-      <c r="L5" s="422"/>
-      <c r="M5" s="422"/>
-      <c r="N5" s="422"/>
-      <c r="O5" s="422"/>
+      <c r="H5" s="419"/>
+      <c r="I5" s="419"/>
+      <c r="J5" s="419"/>
+      <c r="K5" s="419"/>
+      <c r="L5" s="419"/>
+      <c r="M5" s="419"/>
+      <c r="N5" s="419"/>
+      <c r="O5" s="419"/>
       <c r="P5" s="431" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  16/03</v>
@@ -5994,7 +5994,7 @@
       <c r="Q5" s="432"/>
       <c r="R5" s="431"/>
       <c r="S5" s="432"/>
-      <c r="T5" s="422"/>
+      <c r="T5" s="419"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="204"/>
@@ -6043,11 +6043,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="209"/>
-      <c r="P6" s="442">
+      <c r="P6" s="420">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>1518529.01</v>
       </c>
-      <c r="Q6" s="442"/>
+      <c r="Q6" s="420"/>
       <c r="R6" s="363">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>1564586.01</v>
@@ -6112,11 +6112,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="74"/>
-      <c r="P7" s="413">
+      <c r="P7" s="421">
         <f t="shared" si="2"/>
         <v>1542558.02</v>
       </c>
-      <c r="Q7" s="413"/>
+      <c r="Q7" s="421"/>
       <c r="R7" s="363">
         <f t="shared" si="3"/>
         <v>1589344.02</v>
@@ -6180,11 +6180,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="74"/>
-      <c r="P8" s="413">
+      <c r="P8" s="421">
         <f t="shared" si="2"/>
         <v>736705.03</v>
       </c>
-      <c r="Q8" s="413"/>
+      <c r="Q8" s="421"/>
       <c r="R8" s="363">
         <f t="shared" si="3"/>
         <v>759049.03</v>
@@ -6249,11 +6249,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="74"/>
-      <c r="P9" s="413">
+      <c r="P9" s="421">
         <f t="shared" si="2"/>
         <v>3222835.04</v>
       </c>
-      <c r="Q9" s="413"/>
+      <c r="Q9" s="421"/>
       <c r="R9" s="363">
         <f t="shared" si="3"/>
         <v>3320584.04</v>
@@ -6321,11 +6321,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="74"/>
-      <c r="P10" s="413">
+      <c r="P10" s="421">
         <f t="shared" si="2"/>
         <v>744528.05</v>
       </c>
-      <c r="Q10" s="413"/>
+      <c r="Q10" s="421"/>
       <c r="R10" s="363">
         <f t="shared" si="3"/>
         <v>767110.05</v>
@@ -6391,11 +6391,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="74"/>
-      <c r="P11" s="413">
+      <c r="P11" s="421">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="413"/>
+      <c r="Q11" s="421"/>
       <c r="R11" s="363">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6462,11 +6462,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="74"/>
-      <c r="P12" s="413">
+      <c r="P12" s="421">
         <f t="shared" si="2"/>
         <v>744299.07</v>
       </c>
-      <c r="Q12" s="413"/>
+      <c r="Q12" s="421"/>
       <c r="R12" s="363">
         <f t="shared" si="3"/>
         <v>766874.07</v>
@@ -6533,11 +6533,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="74"/>
-      <c r="P13" s="413">
+      <c r="P13" s="421">
         <f t="shared" si="2"/>
         <v>744514.08</v>
       </c>
-      <c r="Q13" s="413"/>
+      <c r="Q13" s="421"/>
       <c r="R13" s="363">
         <f t="shared" si="3"/>
         <v>767095.08</v>
@@ -6602,11 +6602,11 @@
         <v>379177.030424</v>
       </c>
       <c r="O14" s="74"/>
-      <c r="P14" s="413">
+      <c r="P14" s="421">
         <f t="shared" si="2"/>
         <v>3509954.09</v>
       </c>
-      <c r="Q14" s="413"/>
+      <c r="Q14" s="421"/>
       <c r="R14" s="363">
         <f t="shared" si="3"/>
         <v>3616411.09</v>
@@ -6670,11 +6670,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="74"/>
-      <c r="P15" s="413">
+      <c r="P15" s="421">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="413"/>
+      <c r="Q15" s="421"/>
       <c r="R15" s="363">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -6740,11 +6740,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="36"/>
-      <c r="P16" s="413">
+      <c r="P16" s="421">
         <f t="shared" si="2"/>
         <v>744528.11</v>
       </c>
-      <c r="Q16" s="413"/>
+      <c r="Q16" s="421"/>
       <c r="R16" s="363">
         <f t="shared" si="3"/>
         <v>767110.11</v>
@@ -6808,11 +6808,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="74"/>
-      <c r="P17" s="413">
+      <c r="P17" s="421">
         <f t="shared" si="2"/>
         <v>4420303.12</v>
       </c>
-      <c r="Q17" s="413"/>
+      <c r="Q17" s="421"/>
       <c r="R17" s="363">
         <f t="shared" si="3"/>
         <v>4554371.12</v>
@@ -6877,11 +6877,11 @@
       </c>
       <c r="N18" s="74"/>
       <c r="O18" s="74"/>
-      <c r="P18" s="413">
+      <c r="P18" s="421">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="413"/>
+      <c r="Q18" s="421"/>
       <c r="R18" s="363">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -6945,11 +6945,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="74"/>
-      <c r="P19" s="413">
+      <c r="P19" s="421">
         <f t="shared" si="2"/>
         <v>720435.14</v>
       </c>
-      <c r="Q19" s="413"/>
+      <c r="Q19" s="421"/>
       <c r="R19" s="363">
         <f t="shared" si="3"/>
         <v>742286.14</v>
@@ -6963,7 +6963,7 @@
         <v>14</v>
       </c>
       <c r="U19" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7016,11 +7016,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="74"/>
-      <c r="P20" s="413">
+      <c r="P20" s="421">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="413"/>
+      <c r="Q20" s="421"/>
       <c r="R20" s="363">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7085,11 +7085,11 @@
       </c>
       <c r="N21" s="74"/>
       <c r="O21" s="74"/>
-      <c r="P21" s="413">
+      <c r="P21" s="421">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="413"/>
+      <c r="Q21" s="421"/>
       <c r="R21" s="363">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7150,11 +7150,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="74"/>
-      <c r="P22" s="413">
+      <c r="P22" s="421">
         <f t="shared" si="2"/>
         <v>2350329.17</v>
       </c>
-      <c r="Q22" s="413"/>
+      <c r="Q22" s="421"/>
       <c r="R22" s="363">
         <f t="shared" si="3"/>
         <v>2421615.17</v>
@@ -7220,11 +7220,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="88"/>
-      <c r="P23" s="413">
+      <c r="P23" s="421">
         <f t="shared" si="2"/>
         <v>736705.18</v>
       </c>
-      <c r="Q23" s="413"/>
+      <c r="Q23" s="421"/>
       <c r="R23" s="363">
         <f t="shared" si="3"/>
         <v>759049.18</v>
@@ -7290,11 +7290,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="88"/>
-      <c r="P24" s="413">
+      <c r="P24" s="421">
         <f t="shared" si="2"/>
         <v>744528.19</v>
       </c>
-      <c r="Q24" s="413"/>
+      <c r="Q24" s="421"/>
       <c r="R24" s="363">
         <f t="shared" si="3"/>
         <v>767110.19</v>
@@ -7357,11 +7357,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="88"/>
-      <c r="P25" s="413">
+      <c r="P25" s="421">
         <f t="shared" si="2"/>
         <v>744528.2</v>
       </c>
-      <c r="Q25" s="413"/>
+      <c r="Q25" s="421"/>
       <c r="R25" s="363">
         <f t="shared" si="3"/>
         <v>767110.2</v>
@@ -7422,11 +7422,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="88"/>
-      <c r="P26" s="413">
+      <c r="P26" s="421">
         <f t="shared" si="2"/>
         <v>1559335.21</v>
       </c>
-      <c r="Q26" s="413"/>
+      <c r="Q26" s="421"/>
       <c r="R26" s="363">
         <f t="shared" si="3"/>
         <v>1606630.21</v>
@@ -7495,11 +7495,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="88"/>
-      <c r="P27" s="413">
+      <c r="P27" s="421">
         <f t="shared" si="2"/>
         <v>744528.22</v>
       </c>
-      <c r="Q27" s="413"/>
+      <c r="Q27" s="421"/>
       <c r="R27" s="363">
         <f t="shared" si="3"/>
         <v>767110.22</v>
@@ -7565,11 +7565,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="88"/>
-      <c r="P28" s="413">
+      <c r="P28" s="421">
         <f t="shared" si="2"/>
         <v>767815.23</v>
       </c>
-      <c r="Q28" s="413"/>
+      <c r="Q28" s="421"/>
       <c r="R28" s="363">
         <f t="shared" si="3"/>
         <v>791103.23</v>
@@ -7635,11 +7635,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="88"/>
-      <c r="P29" s="413">
+      <c r="P29" s="421">
         <f t="shared" si="2"/>
         <v>744528.24</v>
       </c>
-      <c r="Q29" s="413"/>
+      <c r="Q29" s="421"/>
       <c r="R29" s="363">
         <f t="shared" si="3"/>
         <v>767110.24</v>
@@ -7706,11 +7706,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="88"/>
-      <c r="P30" s="413">
+      <c r="P30" s="421">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="413"/>
+      <c r="Q30" s="421"/>
       <c r="R30" s="363">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -7776,11 +7776,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="88"/>
-      <c r="P31" s="413">
+      <c r="P31" s="421">
         <f t="shared" si="2"/>
         <v>752356.26</v>
       </c>
-      <c r="Q31" s="413"/>
+      <c r="Q31" s="421"/>
       <c r="R31" s="363">
         <f t="shared" si="3"/>
         <v>775175.26</v>
@@ -7847,11 +7847,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="88"/>
-      <c r="P32" s="413">
+      <c r="P32" s="421">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="413"/>
+      <c r="Q32" s="421"/>
       <c r="R32" s="363">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -7917,11 +7917,11 @@
         <f>I33/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P33" s="413">
+      <c r="P33" s="421">
         <f t="shared" si="2"/>
         <v>923797.28</v>
       </c>
-      <c r="Q33" s="413"/>
+      <c r="Q33" s="421"/>
       <c r="R33" s="363">
         <f t="shared" si="3"/>
         <v>951816.28</v>
@@ -7987,11 +7987,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="88"/>
-      <c r="P34" s="413">
+      <c r="P34" s="421">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="413"/>
+      <c r="Q34" s="421"/>
       <c r="R34" s="363">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8058,11 +8058,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="88"/>
-      <c r="P35" s="413">
+      <c r="P35" s="421">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="413"/>
+      <c r="Q35" s="421"/>
       <c r="R35" s="363">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8126,11 +8126,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="88"/>
-      <c r="P36" s="413">
+      <c r="P36" s="421">
         <f t="shared" si="2"/>
         <v>2643433.31</v>
       </c>
-      <c r="Q36" s="413"/>
+      <c r="Q36" s="421"/>
       <c r="R36" s="363">
         <f t="shared" si="3"/>
         <v>2723609.31</v>
@@ -8197,11 +8197,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="88"/>
-      <c r="P37" s="413">
+      <c r="P37" s="421">
         <f t="shared" si="2"/>
         <v>573720.31999999995</v>
       </c>
-      <c r="Q37" s="413"/>
+      <c r="Q37" s="421"/>
       <c r="R37" s="363">
         <f t="shared" si="3"/>
         <v>591121.31999999995</v>
@@ -8264,11 +8264,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="88"/>
-      <c r="P38" s="413">
+      <c r="P38" s="421">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="413"/>
+      <c r="Q38" s="421"/>
       <c r="R38" s="363">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8328,11 +8328,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="88"/>
-      <c r="P39" s="413">
+      <c r="P39" s="421">
         <f t="shared" si="14"/>
         <v>2473411.34</v>
       </c>
-      <c r="Q39" s="413"/>
+      <c r="Q39" s="421"/>
       <c r="R39" s="363">
         <f t="shared" si="15"/>
         <v>2548430.34</v>
@@ -8399,11 +8399,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="88"/>
-      <c r="P40" s="413">
+      <c r="P40" s="421">
         <f t="shared" si="14"/>
         <v>736704.35</v>
       </c>
-      <c r="Q40" s="413"/>
+      <c r="Q40" s="421"/>
       <c r="R40" s="363">
         <f t="shared" si="15"/>
         <v>759049.35</v>
@@ -8471,11 +8471,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="88"/>
-      <c r="P41" s="413">
+      <c r="P41" s="421">
         <f t="shared" si="14"/>
         <v>748020.36</v>
       </c>
-      <c r="Q41" s="413"/>
+      <c r="Q41" s="421"/>
       <c r="R41" s="363">
         <f t="shared" si="15"/>
         <v>770708.36</v>
@@ -8538,11 +8538,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="88"/>
-      <c r="P42" s="413">
+      <c r="P42" s="421">
         <f t="shared" si="14"/>
         <v>1526106.37</v>
       </c>
-      <c r="Q42" s="413"/>
+      <c r="Q42" s="421"/>
       <c r="R42" s="363">
         <f t="shared" si="15"/>
         <v>1572393.37</v>
@@ -8608,11 +8608,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="88"/>
-      <c r="P43" s="413">
+      <c r="P43" s="421">
         <f t="shared" si="14"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="413"/>
+      <c r="Q43" s="421"/>
       <c r="R43" s="363">
         <f t="shared" si="15"/>
         <v>774480.38</v>
@@ -8680,11 +8680,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="88"/>
-      <c r="P44" s="413">
+      <c r="P44" s="421">
         <f t="shared" si="14"/>
         <v>872758.39</v>
       </c>
-      <c r="Q44" s="413"/>
+      <c r="Q44" s="421"/>
       <c r="R44" s="363">
         <f t="shared" si="15"/>
         <v>899229.39</v>
@@ -8751,11 +8751,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="88"/>
-      <c r="P45" s="413">
+      <c r="P45" s="421">
         <f t="shared" si="14"/>
         <v>728593.4</v>
       </c>
-      <c r="Q45" s="413"/>
+      <c r="Q45" s="421"/>
       <c r="R45" s="363">
         <f t="shared" si="15"/>
         <v>750692.4</v>
@@ -8819,11 +8819,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="88"/>
-      <c r="P46" s="413">
+      <c r="P46" s="421">
         <f t="shared" si="14"/>
         <v>728882.41</v>
       </c>
-      <c r="Q46" s="413"/>
+      <c r="Q46" s="421"/>
       <c r="R46" s="363">
         <f t="shared" si="15"/>
         <v>750989.41</v>
@@ -8890,11 +8890,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="88"/>
-      <c r="P47" s="413">
+      <c r="P47" s="421">
         <f t="shared" si="14"/>
         <v>728882.42</v>
       </c>
-      <c r="Q47" s="413"/>
+      <c r="Q47" s="421"/>
       <c r="R47" s="363">
         <f t="shared" si="15"/>
         <v>750989.42</v>
@@ -8962,11 +8962,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="88"/>
-      <c r="P48" s="413">
+      <c r="P48" s="421">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="413"/>
+      <c r="Q48" s="421"/>
       <c r="R48" s="363">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9030,11 +9030,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="88"/>
-      <c r="P49" s="413">
+      <c r="P49" s="421">
         <f t="shared" si="14"/>
         <v>895905.44</v>
       </c>
-      <c r="Q49" s="413"/>
+      <c r="Q49" s="421"/>
       <c r="R49" s="363">
         <f t="shared" si="15"/>
         <v>923078.44</v>
@@ -9100,11 +9100,11 @@
         <v>395312.22320800001</v>
       </c>
       <c r="O50" s="88"/>
-      <c r="P50" s="413">
+      <c r="P50" s="421">
         <f t="shared" si="14"/>
         <v>1987415.45</v>
       </c>
-      <c r="Q50" s="413"/>
+      <c r="Q50" s="421"/>
       <c r="R50" s="363">
         <f t="shared" si="15"/>
         <v>2047694.45</v>
@@ -9168,11 +9168,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="88"/>
-      <c r="P51" s="413">
+      <c r="P51" s="421">
         <f t="shared" si="14"/>
         <v>1451367.46</v>
       </c>
-      <c r="Q51" s="413"/>
+      <c r="Q51" s="421"/>
       <c r="R51" s="363">
         <f t="shared" si="15"/>
         <v>1495387.46</v>
@@ -9237,11 +9237,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="88"/>
-      <c r="P52" s="413">
+      <c r="P52" s="421">
         <f t="shared" si="14"/>
         <v>3158183.47</v>
       </c>
-      <c r="Q52" s="413"/>
+      <c r="Q52" s="421"/>
       <c r="R52" s="363">
         <f t="shared" si="15"/>
         <v>3253971.47</v>
@@ -9312,11 +9312,11 @@
         <f>I53*0.1</f>
         <v>36304.183764000001</v>
       </c>
-      <c r="P53" s="413">
+      <c r="P53" s="421">
         <f t="shared" si="14"/>
         <v>1053230.48</v>
       </c>
-      <c r="Q53" s="413"/>
+      <c r="Q53" s="421"/>
       <c r="R53" s="363">
         <f t="shared" si="15"/>
         <v>1085175.48</v>
@@ -9381,11 +9381,11 @@
         <v>0</v>
       </c>
       <c r="O54" s="88"/>
-      <c r="P54" s="413">
+      <c r="P54" s="421">
         <f t="shared" si="14"/>
         <v>728882.49</v>
       </c>
-      <c r="Q54" s="413"/>
+      <c r="Q54" s="421"/>
       <c r="R54" s="363">
         <f t="shared" si="15"/>
         <v>750989.49</v>
@@ -9452,11 +9452,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="88"/>
-      <c r="P55" s="413">
+      <c r="P55" s="421">
         <f t="shared" si="14"/>
         <v>728882.5</v>
       </c>
-      <c r="Q55" s="413"/>
+      <c r="Q55" s="421"/>
       <c r="R55" s="363">
         <f t="shared" si="15"/>
         <v>750990.5</v>
@@ -9522,11 +9522,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O56" s="88"/>
-      <c r="P56" s="413">
+      <c r="P56" s="421">
         <f t="shared" si="14"/>
         <v>2172571.5099999998</v>
       </c>
-      <c r="Q56" s="413"/>
+      <c r="Q56" s="421"/>
       <c r="R56" s="363">
         <f t="shared" si="15"/>
         <v>2238466.5099999998</v>
@@ -9594,11 +9594,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="88"/>
-      <c r="P57" s="413">
+      <c r="P57" s="421">
         <f t="shared" si="14"/>
         <v>712950.52</v>
       </c>
-      <c r="Q57" s="413"/>
+      <c r="Q57" s="421"/>
       <c r="R57" s="363">
         <f t="shared" si="15"/>
         <v>734574.52</v>
@@ -9663,11 +9663,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="88"/>
-      <c r="P58" s="413">
+      <c r="P58" s="421">
         <f t="shared" si="14"/>
         <v>3399941.53</v>
       </c>
-      <c r="Q58" s="413"/>
+      <c r="Q58" s="421"/>
       <c r="R58" s="363">
         <f t="shared" si="15"/>
         <v>3503062.53</v>
@@ -9732,11 +9732,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="88"/>
-      <c r="P59" s="413">
+      <c r="P59" s="421">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="413"/>
+      <c r="Q59" s="421"/>
       <c r="R59" s="363">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -9803,11 +9803,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="88"/>
-      <c r="P60" s="413">
+      <c r="P60" s="421">
         <f t="shared" si="14"/>
         <v>728882.55</v>
       </c>
-      <c r="Q60" s="413"/>
+      <c r="Q60" s="421"/>
       <c r="R60" s="363">
         <f t="shared" si="15"/>
         <v>750990.55</v>
@@ -9878,11 +9878,11 @@
         <f>(I61*0.1)*2</f>
         <v>72608.367528000002</v>
       </c>
-      <c r="P61" s="413">
+      <c r="P61" s="421">
         <f t="shared" si="14"/>
         <v>1152903.56</v>
       </c>
-      <c r="Q61" s="413"/>
+      <c r="Q61" s="421"/>
       <c r="R61" s="363">
         <f t="shared" si="15"/>
         <v>1187871.56</v>
@@ -9947,11 +9947,11 @@
         <v>0</v>
       </c>
       <c r="O62" s="88"/>
-      <c r="P62" s="413">
+      <c r="P62" s="421">
         <f t="shared" si="14"/>
         <v>1526567.57</v>
       </c>
-      <c r="Q62" s="413"/>
+      <c r="Q62" s="421"/>
       <c r="R62" s="363">
         <f t="shared" si="15"/>
         <v>1572868.57</v>
@@ -10015,11 +10015,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="88"/>
-      <c r="P63" s="413">
+      <c r="P63" s="421">
         <f t="shared" si="14"/>
         <v>728882.58</v>
       </c>
-      <c r="Q63" s="413"/>
+      <c r="Q63" s="421"/>
       <c r="R63" s="363">
         <f t="shared" si="15"/>
         <v>750990.58</v>
@@ -10083,11 +10083,11 @@
         <v>0</v>
       </c>
       <c r="O64" s="88"/>
-      <c r="P64" s="413">
+      <c r="P64" s="421">
         <f t="shared" si="14"/>
         <v>691468.59</v>
       </c>
-      <c r="Q64" s="413"/>
+      <c r="Q64" s="421"/>
       <c r="R64" s="363">
         <f t="shared" si="15"/>
         <v>712441.59</v>
@@ -10154,11 +10154,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="88"/>
-      <c r="P65" s="413">
+      <c r="P65" s="421">
         <f t="shared" si="14"/>
         <v>750827.6</v>
       </c>
-      <c r="Q65" s="413"/>
+      <c r="Q65" s="421"/>
       <c r="R65" s="363">
         <f t="shared" si="15"/>
         <v>773600.6</v>
@@ -10226,11 +10226,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="88"/>
-      <c r="P66" s="413">
+      <c r="P66" s="421">
         <f t="shared" si="14"/>
         <v>751038.61</v>
       </c>
-      <c r="Q66" s="413"/>
+      <c r="Q66" s="421"/>
       <c r="R66" s="363">
         <f t="shared" si="15"/>
         <v>773818.61</v>
@@ -10301,11 +10301,11 @@
         <f>I67/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P67" s="413">
+      <c r="P67" s="421">
         <f t="shared" si="14"/>
         <v>855140.62</v>
       </c>
-      <c r="Q67" s="413"/>
+      <c r="Q67" s="421"/>
       <c r="R67" s="363">
         <f t="shared" si="15"/>
         <v>881077.62</v>
@@ -10370,11 +10370,11 @@
         <v>0</v>
       </c>
       <c r="O68" s="88"/>
-      <c r="P68" s="413">
+      <c r="P68" s="421">
         <f t="shared" si="14"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="413"/>
+      <c r="Q68" s="421"/>
       <c r="R68" s="363">
         <f t="shared" si="15"/>
         <v>774480.63</v>
@@ -10442,11 +10442,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="88"/>
-      <c r="P69" s="413">
+      <c r="P69" s="421">
         <f t="shared" si="14"/>
         <v>706943.64</v>
       </c>
-      <c r="Q69" s="413"/>
+      <c r="Q69" s="421"/>
       <c r="R69" s="363">
         <f t="shared" si="15"/>
         <v>728385.64</v>
@@ -10514,11 +10514,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="88"/>
-      <c r="P70" s="413">
+      <c r="P70" s="421">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="413"/>
+      <c r="Q70" s="421"/>
       <c r="R70" s="363">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10582,11 +10582,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="88"/>
-      <c r="P71" s="413">
+      <c r="P71" s="421">
         <f t="shared" si="22"/>
         <v>728882.66</v>
       </c>
-      <c r="Q71" s="413"/>
+      <c r="Q71" s="421"/>
       <c r="R71" s="363">
         <f t="shared" si="23"/>
         <v>750990.66</v>
@@ -10651,11 +10651,11 @@
         <v>0</v>
       </c>
       <c r="O72" s="88"/>
-      <c r="P72" s="413">
+      <c r="P72" s="421">
         <f t="shared" si="22"/>
         <v>1518273.67</v>
       </c>
-      <c r="Q72" s="413"/>
+      <c r="Q72" s="421"/>
       <c r="R72" s="363">
         <f t="shared" si="23"/>
         <v>1564323.67</v>
@@ -10720,11 +10720,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O73" s="88"/>
-      <c r="P73" s="413">
+      <c r="P73" s="421">
         <f t="shared" si="22"/>
         <v>4486656.68</v>
       </c>
-      <c r="Q73" s="413"/>
+      <c r="Q73" s="421"/>
       <c r="R73" s="363">
         <f t="shared" si="23"/>
         <v>4622737.68</v>
@@ -10787,11 +10787,11 @@
         <v>0</v>
       </c>
       <c r="O74" s="36"/>
-      <c r="P74" s="413">
+      <c r="P74" s="421">
         <f t="shared" si="22"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="413"/>
+      <c r="Q74" s="421"/>
       <c r="R74" s="363">
         <f t="shared" si="23"/>
         <v>678447.69</v>
@@ -10857,11 +10857,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="88"/>
-      <c r="P75" s="413">
+      <c r="P75" s="421">
         <f t="shared" si="22"/>
         <v>1372860.7</v>
       </c>
-      <c r="Q75" s="413"/>
+      <c r="Q75" s="421"/>
       <c r="R75" s="363">
         <f t="shared" si="23"/>
         <v>1414500.7</v>
@@ -10925,11 +10925,11 @@
         <v>0</v>
       </c>
       <c r="O76" s="88"/>
-      <c r="P76" s="413">
+      <c r="P76" s="421">
         <f t="shared" si="22"/>
         <v>4028209.71</v>
       </c>
-      <c r="Q76" s="413"/>
+      <c r="Q76" s="421"/>
       <c r="R76" s="363">
         <f t="shared" si="23"/>
         <v>4150385.71</v>
@@ -10995,11 +10995,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="88"/>
-      <c r="P77" s="413">
+      <c r="P77" s="421">
         <f t="shared" si="22"/>
         <v>690051.72</v>
       </c>
-      <c r="Q77" s="413"/>
+      <c r="Q77" s="421"/>
       <c r="R77" s="363">
         <f t="shared" si="23"/>
         <v>710981.72</v>
@@ -11066,11 +11066,11 @@
         <v>0</v>
       </c>
       <c r="O78" s="88"/>
-      <c r="P78" s="413">
+      <c r="P78" s="421">
         <f t="shared" si="22"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="413"/>
+      <c r="Q78" s="421"/>
       <c r="R78" s="363">
         <f t="shared" si="23"/>
         <v>732919.73</v>
@@ -11134,11 +11134,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="88"/>
-      <c r="P79" s="413">
+      <c r="P79" s="421">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="413"/>
+      <c r="Q79" s="421"/>
       <c r="R79" s="363">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11205,11 +11205,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="413">
+      <c r="P80" s="421">
         <f t="shared" si="22"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="413"/>
+      <c r="Q80" s="421"/>
       <c r="R80" s="363">
         <f t="shared" si="23"/>
         <v>911633.75</v>
@@ -11276,11 +11276,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="88"/>
-      <c r="P81" s="413">
+      <c r="P81" s="421">
         <f t="shared" si="22"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="413"/>
+      <c r="Q81" s="421"/>
       <c r="R81" s="363">
         <f t="shared" si="23"/>
         <v>774480.76</v>
@@ -11343,11 +11343,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="88"/>
-      <c r="P82" s="413">
+      <c r="P82" s="421">
         <f t="shared" si="22"/>
         <v>854048.77</v>
       </c>
-      <c r="Q82" s="413"/>
+      <c r="Q82" s="421"/>
       <c r="R82" s="363">
         <f t="shared" si="23"/>
         <v>879952.77</v>
@@ -11413,11 +11413,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="88"/>
-      <c r="P83" s="413">
+      <c r="P83" s="421">
         <f t="shared" si="22"/>
         <v>751480.78</v>
       </c>
-      <c r="Q83" s="413"/>
+      <c r="Q83" s="421"/>
       <c r="R83" s="363">
         <f t="shared" si="23"/>
         <v>774273.78</v>
@@ -11484,11 +11484,11 @@
         <v>0</v>
       </c>
       <c r="O84" s="88"/>
-      <c r="P84" s="413">
+      <c r="P84" s="421">
         <f t="shared" si="22"/>
         <v>1089017.79</v>
       </c>
-      <c r="Q84" s="413"/>
+      <c r="Q84" s="421"/>
       <c r="R84" s="363">
         <f t="shared" si="23"/>
         <v>1122048.79</v>
@@ -11557,11 +11557,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="88"/>
-      <c r="P85" s="413">
+      <c r="P85" s="421">
         <f t="shared" si="22"/>
         <v>728063.8</v>
       </c>
-      <c r="Q85" s="413"/>
+      <c r="Q85" s="421"/>
       <c r="R85" s="363">
         <f t="shared" si="23"/>
         <v>750146.8</v>
@@ -11628,11 +11628,11 @@
         <v>0</v>
       </c>
       <c r="O86" s="88"/>
-      <c r="P86" s="413">
+      <c r="P86" s="421">
         <f t="shared" si="22"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="413"/>
+      <c r="Q86" s="421"/>
       <c r="R86" s="363">
         <f t="shared" si="23"/>
         <v>774480.81</v>
@@ -11698,11 +11698,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="74"/>
-      <c r="P87" s="413">
+      <c r="P87" s="421">
         <f t="shared" si="22"/>
         <v>682667.82</v>
       </c>
-      <c r="Q87" s="413"/>
+      <c r="Q87" s="421"/>
       <c r="R87" s="363">
         <f t="shared" si="23"/>
         <v>703373.82</v>
@@ -11769,11 +11769,11 @@
         <v>0</v>
       </c>
       <c r="O88" s="88"/>
-      <c r="P88" s="413">
+      <c r="P88" s="421">
         <f t="shared" si="22"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="413"/>
+      <c r="Q88" s="421"/>
       <c r="R88" s="363">
         <f t="shared" si="23"/>
         <v>775171.83</v>
@@ -11836,11 +11836,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="88"/>
-      <c r="P89" s="413">
+      <c r="P89" s="421">
         <f t="shared" si="22"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="413"/>
+      <c r="Q89" s="421"/>
       <c r="R89" s="363">
         <f t="shared" si="23"/>
         <v>775171.84</v>
@@ -11904,11 +11904,11 @@
         <v>0</v>
       </c>
       <c r="O90" s="88"/>
-      <c r="P90" s="413">
+      <c r="P90" s="421">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="413"/>
+      <c r="Q90" s="421"/>
       <c r="R90" s="363">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -11976,11 +11976,11 @@
         <v>387244.62681599997</v>
       </c>
       <c r="O91" s="88"/>
-      <c r="P91" s="413">
+      <c r="P91" s="421">
         <f t="shared" si="22"/>
         <v>1163128.8600000001</v>
       </c>
-      <c r="Q91" s="413"/>
+      <c r="Q91" s="421"/>
       <c r="R91" s="363">
         <f t="shared" si="23"/>
         <v>1198407.8600000001</v>
@@ -12043,11 +12043,11 @@
         <v>0</v>
       </c>
       <c r="O92" s="88"/>
-      <c r="P92" s="413">
+      <c r="P92" s="421">
         <f t="shared" si="22"/>
         <v>752351.87</v>
       </c>
-      <c r="Q92" s="413"/>
+      <c r="Q92" s="421"/>
       <c r="R92" s="363">
         <f t="shared" si="23"/>
         <v>775171.87</v>
@@ -12111,11 +12111,11 @@
         <v>0</v>
       </c>
       <c r="O93" s="88"/>
-      <c r="P93" s="413">
+      <c r="P93" s="421">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="413"/>
+      <c r="Q93" s="421"/>
       <c r="R93" s="363">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12178,11 +12178,11 @@
         <v>0</v>
       </c>
       <c r="O94" s="88"/>
-      <c r="P94" s="413">
+      <c r="P94" s="421">
         <f t="shared" si="22"/>
         <v>752351.89</v>
       </c>
-      <c r="Q94" s="413"/>
+      <c r="Q94" s="421"/>
       <c r="R94" s="363">
         <f t="shared" si="23"/>
         <v>775171.89</v>
@@ -12248,11 +12248,11 @@
         <v>0</v>
       </c>
       <c r="O95" s="88"/>
-      <c r="P95" s="413">
+      <c r="P95" s="421">
         <f t="shared" si="22"/>
         <v>743876.9</v>
       </c>
-      <c r="Q95" s="413"/>
+      <c r="Q95" s="421"/>
       <c r="R95" s="363">
         <f t="shared" si="23"/>
         <v>766439.9</v>
@@ -12318,11 +12318,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="88"/>
-      <c r="P96" s="413">
+      <c r="P96" s="421">
         <f t="shared" si="22"/>
         <v>752351.91</v>
       </c>
-      <c r="Q96" s="413"/>
+      <c r="Q96" s="421"/>
       <c r="R96" s="363">
         <f t="shared" si="23"/>
         <v>775171.91</v>
@@ -12387,15 +12387,15 @@
       <c r="N97" s="74">
         <v>0</v>
       </c>
-      <c r="O97" s="468">
+      <c r="O97" s="381">
         <f>1780*100</f>
         <v>178000</v>
       </c>
-      <c r="P97" s="413">
+      <c r="P97" s="421">
         <f t="shared" si="22"/>
         <v>1840080.92</v>
       </c>
-      <c r="Q97" s="413"/>
+      <c r="Q97" s="421"/>
       <c r="R97" s="363">
         <f t="shared" si="23"/>
         <v>1895891.92</v>
@@ -12461,11 +12461,11 @@
         <v>0</v>
       </c>
       <c r="O98" s="60"/>
-      <c r="P98" s="413">
+      <c r="P98" s="421">
         <f t="shared" si="22"/>
         <v>238871.93</v>
       </c>
-      <c r="Q98" s="413"/>
+      <c r="Q98" s="421"/>
       <c r="R98" s="363">
         <f t="shared" si="23"/>
         <v>246117.93</v>
@@ -12532,11 +12532,11 @@
         <v>0</v>
       </c>
       <c r="O99" s="60"/>
-      <c r="P99" s="413">
+      <c r="P99" s="421">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="413"/>
+      <c r="Q99" s="421"/>
       <c r="R99" s="363">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -12602,11 +12602,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="88"/>
-      <c r="P100" s="413">
+      <c r="P100" s="421">
         <f t="shared" si="22"/>
         <v>4049080.95</v>
       </c>
-      <c r="Q100" s="413"/>
+      <c r="Q100" s="421"/>
       <c r="R100" s="363">
         <f t="shared" si="23"/>
         <v>4171890.95</v>
@@ -12669,11 +12669,11 @@
         <v>0</v>
       </c>
       <c r="O101" s="88"/>
-      <c r="P101" s="413">
+      <c r="P101" s="421">
         <f t="shared" si="22"/>
         <v>752388.96</v>
       </c>
-      <c r="Q101" s="413"/>
+      <c r="Q101" s="421"/>
       <c r="R101" s="363">
         <f t="shared" si="23"/>
         <v>775209.96</v>
@@ -12739,11 +12739,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="88"/>
-      <c r="P102" s="413">
+      <c r="P102" s="421">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752269.97</v>
       </c>
-      <c r="Q102" s="413"/>
+      <c r="Q102" s="421"/>
       <c r="R102" s="363">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775086.97</v>
@@ -12809,11 +12809,11 @@
         <v>0</v>
       </c>
       <c r="O103" s="88"/>
-      <c r="P103" s="413">
+      <c r="P103" s="421">
         <f t="shared" si="32"/>
         <v>752350.98</v>
       </c>
-      <c r="Q103" s="413"/>
+      <c r="Q103" s="421"/>
       <c r="R103" s="363">
         <f t="shared" si="33"/>
         <v>775170.98</v>
@@ -12877,11 +12877,11 @@
         <v>0</v>
       </c>
       <c r="O104" s="88"/>
-      <c r="P104" s="413">
+      <c r="P104" s="421">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="413"/>
+      <c r="Q104" s="421"/>
       <c r="R104" s="363">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -12947,11 +12947,11 @@
         <v>0</v>
       </c>
       <c r="O105" s="88"/>
-      <c r="P105" s="413">
+      <c r="P105" s="421">
         <f t="shared" si="32"/>
         <v>752351</v>
       </c>
-      <c r="Q105" s="413"/>
+      <c r="Q105" s="421"/>
       <c r="R105" s="363">
         <f t="shared" si="33"/>
         <v>775171</v>
@@ -13014,11 +13014,11 @@
         <v>0</v>
       </c>
       <c r="O106" s="88"/>
-      <c r="P106" s="413">
+      <c r="P106" s="421">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="413"/>
+      <c r="Q106" s="421"/>
       <c r="R106" s="363">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13081,11 +13081,11 @@
         <v>0</v>
       </c>
       <c r="O107" s="88"/>
-      <c r="P107" s="413">
+      <c r="P107" s="421">
         <f t="shared" si="32"/>
         <v>775118.02</v>
       </c>
-      <c r="Q107" s="413"/>
+      <c r="Q107" s="421"/>
       <c r="R107" s="363">
         <f t="shared" si="33"/>
         <v>798628.02</v>
@@ -13151,11 +13151,11 @@
         <v>0</v>
       </c>
       <c r="O108" s="88"/>
-      <c r="P108" s="413">
+      <c r="P108" s="421">
         <f t="shared" si="32"/>
         <v>728092.03</v>
       </c>
-      <c r="Q108" s="413"/>
+      <c r="Q108" s="421"/>
       <c r="R108" s="363">
         <f t="shared" si="33"/>
         <v>750176.03</v>
@@ -13219,11 +13219,11 @@
         <v>0</v>
       </c>
       <c r="O109" s="88"/>
-      <c r="P109" s="413">
+      <c r="P109" s="421">
         <f t="shared" si="32"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="413"/>
+      <c r="Q109" s="421"/>
       <c r="R109" s="363">
         <f t="shared" si="33"/>
         <v>791106.04</v>
@@ -13237,7 +13237,7 @@
         <v>104</v>
       </c>
       <c r="U109" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13289,11 +13289,11 @@
         <v>0</v>
       </c>
       <c r="O110" s="88"/>
-      <c r="P110" s="413">
+      <c r="P110" s="421">
         <f t="shared" si="32"/>
         <v>705414.05</v>
       </c>
-      <c r="Q110" s="413"/>
+      <c r="Q110" s="421"/>
       <c r="R110" s="363">
         <f t="shared" si="33"/>
         <v>726810.05</v>
@@ -13362,11 +13362,11 @@
         <v>270455.26692913822</v>
       </c>
       <c r="O111" s="88"/>
-      <c r="P111" s="413">
+      <c r="P111" s="421">
         <f t="shared" si="32"/>
         <v>1698531.06</v>
       </c>
-      <c r="Q111" s="413"/>
+      <c r="Q111" s="421"/>
       <c r="R111" s="363">
         <f t="shared" si="33"/>
         <v>1750049.06</v>
@@ -13432,11 +13432,11 @@
         <v>0</v>
       </c>
       <c r="O112" s="88"/>
-      <c r="P112" s="413">
+      <c r="P112" s="421">
         <f t="shared" si="32"/>
         <v>766866.07</v>
       </c>
-      <c r="Q112" s="413"/>
+      <c r="Q112" s="421"/>
       <c r="R112" s="363">
         <f t="shared" si="33"/>
         <v>790126.07</v>
@@ -13502,11 +13502,11 @@
         <v>0</v>
       </c>
       <c r="O113" s="88"/>
-      <c r="P113" s="413">
+      <c r="P113" s="421">
         <f t="shared" si="32"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="413"/>
+      <c r="Q113" s="421"/>
       <c r="R113" s="363">
         <f t="shared" si="33"/>
         <v>742930.08</v>
@@ -13569,11 +13569,11 @@
         <v>0</v>
       </c>
       <c r="O114" s="88"/>
-      <c r="P114" s="413">
+      <c r="P114" s="421">
         <f t="shared" si="32"/>
         <v>1511441.09</v>
       </c>
-      <c r="Q114" s="413"/>
+      <c r="Q114" s="421"/>
       <c r="R114" s="363">
         <f t="shared" si="33"/>
         <v>1557284.09</v>
@@ -13639,11 +13639,11 @@
         <v>0</v>
       </c>
       <c r="O115" s="88"/>
-      <c r="P115" s="413">
+      <c r="P115" s="421">
         <f t="shared" si="32"/>
         <v>1524957.1</v>
       </c>
-      <c r="Q115" s="413"/>
+      <c r="Q115" s="421"/>
       <c r="R115" s="363">
         <f t="shared" si="33"/>
         <v>1571210.1</v>
@@ -13711,11 +13711,11 @@
         <v>0</v>
       </c>
       <c r="O116" s="88"/>
-      <c r="P116" s="413">
+      <c r="P116" s="421">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="413"/>
+      <c r="Q116" s="421"/>
       <c r="R116" s="363">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -13778,11 +13778,11 @@
         <v>0</v>
       </c>
       <c r="O117" s="88"/>
-      <c r="P117" s="413">
+      <c r="P117" s="421">
         <f t="shared" si="32"/>
         <v>725114.12</v>
       </c>
-      <c r="Q117" s="413"/>
+      <c r="Q117" s="421"/>
       <c r="R117" s="363">
         <f t="shared" si="33"/>
         <v>747108.12</v>
@@ -13848,11 +13848,11 @@
         <v>0</v>
       </c>
       <c r="O118" s="88"/>
-      <c r="P118" s="413">
+      <c r="P118" s="421">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="413"/>
+      <c r="Q118" s="421"/>
       <c r="R118" s="363">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -13915,11 +13915,11 @@
         <v>0</v>
       </c>
       <c r="O119" s="88"/>
-      <c r="P119" s="413">
+      <c r="P119" s="421">
         <f t="shared" si="32"/>
         <v>728882.14</v>
       </c>
-      <c r="Q119" s="413"/>
+      <c r="Q119" s="421"/>
       <c r="R119" s="363">
         <f t="shared" si="33"/>
         <v>750990.14</v>
@@ -13983,11 +13983,11 @@
         <v>0</v>
       </c>
       <c r="O120" s="88"/>
-      <c r="P120" s="413">
+      <c r="P120" s="421">
         <f t="shared" si="32"/>
         <v>849222.15</v>
       </c>
-      <c r="Q120" s="413"/>
+      <c r="Q120" s="421"/>
       <c r="R120" s="363">
         <f t="shared" si="33"/>
         <v>874980.15</v>
@@ -14054,11 +14054,11 @@
         <v>0</v>
       </c>
       <c r="O121" s="88"/>
-      <c r="P121" s="413">
+      <c r="P121" s="421">
         <f t="shared" si="32"/>
         <v>803799.16</v>
       </c>
-      <c r="Q121" s="413"/>
+      <c r="Q121" s="421"/>
       <c r="R121" s="363">
         <f t="shared" si="33"/>
         <v>828179.16</v>
@@ -14121,11 +14121,11 @@
         <v>0</v>
       </c>
       <c r="O122" s="88"/>
-      <c r="P122" s="413">
+      <c r="P122" s="421">
         <f t="shared" si="32"/>
         <v>854048.17</v>
       </c>
-      <c r="Q122" s="413"/>
+      <c r="Q122" s="421"/>
       <c r="R122" s="363">
         <f t="shared" si="33"/>
         <v>879952.17</v>
@@ -14192,11 +14192,11 @@
         <v>0</v>
       </c>
       <c r="O123" s="88"/>
-      <c r="P123" s="413">
+      <c r="P123" s="421">
         <f t="shared" si="32"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="413"/>
+      <c r="Q123" s="421"/>
       <c r="R123" s="363">
         <f t="shared" si="33"/>
         <v>882540.18</v>
@@ -14262,11 +14262,11 @@
         <v>0</v>
       </c>
       <c r="O124" s="88"/>
-      <c r="P124" s="413">
+      <c r="P124" s="421">
         <f t="shared" si="32"/>
         <v>827956.19</v>
       </c>
-      <c r="Q124" s="413"/>
+      <c r="Q124" s="421"/>
       <c r="R124" s="363">
         <f t="shared" si="33"/>
         <v>853069.19</v>
@@ -14333,11 +14333,11 @@
         <v>0</v>
       </c>
       <c r="O125" s="88"/>
-      <c r="P125" s="413">
+      <c r="P125" s="421">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="413"/>
+      <c r="Q125" s="421"/>
       <c r="R125" s="363">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -14404,11 +14404,11 @@
         <v>0</v>
       </c>
       <c r="O126" s="88"/>
-      <c r="P126" s="413">
+      <c r="P126" s="421">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="413"/>
+      <c r="Q126" s="421"/>
       <c r="R126" s="363">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -14474,11 +14474,11 @@
         <v>0</v>
       </c>
       <c r="O127" s="74"/>
-      <c r="P127" s="413">
+      <c r="P127" s="421">
         <f t="shared" si="32"/>
         <v>736705.22</v>
       </c>
-      <c r="Q127" s="413"/>
+      <c r="Q127" s="421"/>
       <c r="R127" s="363">
         <f t="shared" si="33"/>
         <v>759050.22</v>
@@ -14542,11 +14542,11 @@
         <v>0</v>
       </c>
       <c r="O128" s="88"/>
-      <c r="P128" s="413">
+      <c r="P128" s="421">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="413"/>
+      <c r="Q128" s="421"/>
       <c r="R128" s="363">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -14612,11 +14612,11 @@
         <v>0</v>
       </c>
       <c r="O129" s="88"/>
-      <c r="P129" s="413">
+      <c r="P129" s="421">
         <f t="shared" si="32"/>
         <v>736705.24</v>
       </c>
-      <c r="Q129" s="413"/>
+      <c r="Q129" s="421"/>
       <c r="R129" s="363">
         <f t="shared" si="33"/>
         <v>759051.24</v>
@@ -14680,11 +14680,11 @@
         <v>0</v>
       </c>
       <c r="O130" s="88"/>
-      <c r="P130" s="413">
+      <c r="P130" s="421">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="413"/>
+      <c r="Q130" s="421"/>
       <c r="R130" s="363">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -14751,11 +14751,11 @@
         <v>0</v>
       </c>
       <c r="O131" s="88"/>
-      <c r="P131" s="413">
+      <c r="P131" s="421">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="413"/>
+      <c r="Q131" s="421"/>
       <c r="R131" s="363">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -14816,11 +14816,11 @@
         <v>0</v>
       </c>
       <c r="O132" s="88"/>
-      <c r="P132" s="413">
+      <c r="P132" s="421">
         <f t="shared" si="32"/>
         <v>1680082.27</v>
       </c>
-      <c r="Q132" s="413"/>
+      <c r="Q132" s="421"/>
       <c r="R132" s="363">
         <f t="shared" si="33"/>
         <v>1731040.27</v>
@@ -14887,11 +14887,11 @@
         <v>339029.8362611382</v>
       </c>
       <c r="O133" s="88"/>
-      <c r="P133" s="413">
+      <c r="P133" s="421">
         <f t="shared" si="32"/>
         <v>9465986.2799999993</v>
       </c>
-      <c r="Q133" s="413"/>
+      <c r="Q133" s="421"/>
       <c r="R133" s="363">
         <f t="shared" si="33"/>
         <v>9753091.2799999993</v>
@@ -14954,11 +14954,11 @@
         <v>0</v>
       </c>
       <c r="O134" s="88"/>
-      <c r="P134" s="413">
+      <c r="P134" s="421">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>854048.29</v>
       </c>
-      <c r="Q134" s="413"/>
+      <c r="Q134" s="421"/>
       <c r="R134" s="363">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>879953.29</v>
@@ -15024,11 +15024,11 @@
         <v>0</v>
       </c>
       <c r="O135" s="88"/>
-      <c r="P135" s="413">
+      <c r="P135" s="421">
         <f t="shared" si="39"/>
         <v>847809.3</v>
       </c>
-      <c r="Q135" s="413"/>
+      <c r="Q135" s="421"/>
       <c r="R135" s="363">
         <f t="shared" si="40"/>
         <v>873524.3</v>
@@ -15095,11 +15095,11 @@
         <v>0</v>
       </c>
       <c r="O136" s="88"/>
-      <c r="P136" s="413">
+      <c r="P136" s="421">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="413"/>
+      <c r="Q136" s="421"/>
       <c r="R136" s="363">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15165,11 +15165,11 @@
         <v>0</v>
       </c>
       <c r="O137" s="88"/>
-      <c r="P137" s="413">
+      <c r="P137" s="421">
         <f t="shared" si="39"/>
         <v>846226.32</v>
       </c>
-      <c r="Q137" s="413"/>
+      <c r="Q137" s="421"/>
       <c r="R137" s="363">
         <f t="shared" si="40"/>
         <v>871893.32</v>
@@ -15236,11 +15236,11 @@
         <v>0</v>
       </c>
       <c r="O138" s="88"/>
-      <c r="P138" s="413">
+      <c r="P138" s="421">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="413"/>
+      <c r="Q138" s="421"/>
       <c r="R138" s="363">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -15306,11 +15306,11 @@
         <v>0</v>
       </c>
       <c r="O139" s="88"/>
-      <c r="P139" s="413">
+      <c r="P139" s="421">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="413"/>
+      <c r="Q139" s="421"/>
       <c r="R139" s="363">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -15376,11 +15376,11 @@
         <v>0</v>
       </c>
       <c r="O140" s="88"/>
-      <c r="P140" s="413">
+      <c r="P140" s="421">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="413"/>
+      <c r="Q140" s="421"/>
       <c r="R140" s="363">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -15444,11 +15444,11 @@
         <v>0</v>
       </c>
       <c r="O141" s="88"/>
-      <c r="P141" s="413">
+      <c r="P141" s="421">
         <f t="shared" si="39"/>
         <v>3751757.36</v>
       </c>
-      <c r="Q141" s="413"/>
+      <c r="Q141" s="421"/>
       <c r="R141" s="363">
         <f t="shared" si="40"/>
         <v>3865549.36</v>
@@ -15514,11 +15514,11 @@
         <v>0</v>
       </c>
       <c r="O142" s="88"/>
-      <c r="P142" s="413">
+      <c r="P142" s="421">
         <f t="shared" si="39"/>
         <v>799288.37</v>
       </c>
-      <c r="Q142" s="413"/>
+      <c r="Q142" s="421"/>
       <c r="R142" s="363">
         <f t="shared" si="40"/>
         <v>823532.37</v>
@@ -15581,11 +15581,11 @@
         <v>0</v>
       </c>
       <c r="O143" s="88"/>
-      <c r="P143" s="413">
+      <c r="P143" s="421">
         <f t="shared" si="39"/>
         <v>885340.38</v>
       </c>
-      <c r="Q143" s="413"/>
+      <c r="Q143" s="421"/>
       <c r="R143" s="363">
         <f t="shared" si="40"/>
         <v>912194.38</v>
@@ -15651,11 +15651,11 @@
         <v>0</v>
       </c>
       <c r="O144" s="88"/>
-      <c r="P144" s="413">
+      <c r="P144" s="421">
         <f t="shared" si="39"/>
         <v>880691.39</v>
       </c>
-      <c r="Q144" s="413"/>
+      <c r="Q144" s="421"/>
       <c r="R144" s="363">
         <f t="shared" si="40"/>
         <v>907404.39</v>
@@ -15695,8 +15695,8 @@
       <c r="M145" s="74"/>
       <c r="N145" s="74"/>
       <c r="O145" s="88"/>
-      <c r="P145" s="413"/>
-      <c r="Q145" s="413"/>
+      <c r="P145" s="421"/>
+      <c r="Q145" s="421"/>
       <c r="R145" s="364"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -15730,8 +15730,8 @@
       <c r="M146" s="74"/>
       <c r="N146" s="74"/>
       <c r="O146" s="88"/>
-      <c r="P146" s="413"/>
-      <c r="Q146" s="413"/>
+      <c r="P146" s="421"/>
+      <c r="Q146" s="421"/>
       <c r="R146" s="364"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -15758,8 +15758,8 @@
       <c r="M147" s="74"/>
       <c r="N147" s="74"/>
       <c r="O147" s="88"/>
-      <c r="P147" s="413"/>
-      <c r="Q147" s="413"/>
+      <c r="P147" s="421"/>
+      <c r="Q147" s="421"/>
       <c r="R147" s="364"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -15786,8 +15786,8 @@
       <c r="M148" s="74"/>
       <c r="N148" s="74"/>
       <c r="O148" s="88"/>
-      <c r="P148" s="413"/>
-      <c r="Q148" s="413"/>
+      <c r="P148" s="421"/>
+      <c r="Q148" s="421"/>
       <c r="R148" s="364"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -15847,11 +15847,11 @@
         <v>246252.47775313823</v>
       </c>
       <c r="O149" s="88"/>
-      <c r="P149" s="413">
+      <c r="P149" s="421">
         <f t="shared" ref="P149:P158" si="49">ROUND(SUM(G149:O149),0) + S149</f>
         <v>882923.46</v>
       </c>
-      <c r="Q149" s="413"/>
+      <c r="Q149" s="421"/>
       <c r="R149" s="363">
         <f t="shared" ref="R149:R158" si="50">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>909704.46</v>
@@ -15912,11 +15912,11 @@
         <v>0</v>
       </c>
       <c r="O150" s="88"/>
-      <c r="P150" s="413">
+      <c r="P150" s="421">
         <f t="shared" si="49"/>
         <v>707760.55</v>
       </c>
-      <c r="Q150" s="413"/>
+      <c r="Q150" s="421"/>
       <c r="R150" s="363">
         <f t="shared" si="50"/>
         <v>729228.55</v>
@@ -15983,11 +15983,11 @@
         <v>0</v>
       </c>
       <c r="O151" s="74"/>
-      <c r="P151" s="413">
+      <c r="P151" s="421">
         <f t="shared" si="49"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="413"/>
+      <c r="Q151" s="421"/>
       <c r="R151" s="363">
         <f t="shared" si="50"/>
         <v>782794.58</v>
@@ -16051,11 +16051,11 @@
         <v>0</v>
       </c>
       <c r="O152" s="74"/>
-      <c r="P152" s="413">
+      <c r="P152" s="421">
         <f t="shared" si="49"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="413"/>
+      <c r="Q152" s="421"/>
       <c r="R152" s="363">
         <f t="shared" si="50"/>
         <v>782794.59</v>
@@ -16119,11 +16119,11 @@
         <v>0</v>
       </c>
       <c r="O153" s="74"/>
-      <c r="P153" s="413">
+      <c r="P153" s="421">
         <f t="shared" si="49"/>
         <v>759750.63</v>
       </c>
-      <c r="Q153" s="413"/>
+      <c r="Q153" s="421"/>
       <c r="R153" s="363">
         <f t="shared" si="50"/>
         <v>782795.63</v>
@@ -16187,11 +16187,11 @@
         <v>0</v>
       </c>
       <c r="O154" s="74"/>
-      <c r="P154" s="413">
+      <c r="P154" s="421">
         <f t="shared" si="49"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="413"/>
+      <c r="Q154" s="421"/>
       <c r="R154" s="363">
         <f t="shared" si="50"/>
         <v>766170.68</v>
@@ -16254,11 +16254,11 @@
         <v>0</v>
       </c>
       <c r="O155" s="74"/>
-      <c r="P155" s="413">
+      <c r="P155" s="421">
         <f t="shared" si="49"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="413"/>
+      <c r="Q155" s="421"/>
       <c r="R155" s="363">
         <f t="shared" si="50"/>
         <v>759050.73</v>
@@ -16324,11 +16324,11 @@
         <v>0</v>
       </c>
       <c r="O156" s="74"/>
-      <c r="P156" s="413">
+      <c r="P156" s="421">
         <f t="shared" si="49"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="413"/>
+      <c r="Q156" s="421"/>
       <c r="R156" s="363">
         <f t="shared" si="50"/>
         <v>759050.75</v>
@@ -16395,11 +16395,11 @@
         <v>0</v>
       </c>
       <c r="O157" s="74"/>
-      <c r="P157" s="413">
+      <c r="P157" s="421">
         <f t="shared" si="49"/>
         <v>759750.76</v>
       </c>
-      <c r="Q157" s="413"/>
+      <c r="Q157" s="421"/>
       <c r="R157" s="363">
         <f t="shared" si="50"/>
         <v>782795.76</v>
@@ -16463,11 +16463,11 @@
         <v>0</v>
       </c>
       <c r="O158" s="74"/>
-      <c r="P158" s="413">
+      <c r="P158" s="421">
         <f t="shared" si="49"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="413"/>
+      <c r="Q158" s="421"/>
       <c r="R158" s="363">
         <f t="shared" si="50"/>
         <v>807732.04</v>
@@ -16500,8 +16500,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="74"/>
-      <c r="P159" s="418"/>
-      <c r="Q159" s="418"/>
+      <c r="P159" s="446"/>
+      <c r="Q159" s="446"/>
       <c r="R159" s="183"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -16522,8 +16522,8 @@
       <c r="M160" s="194"/>
       <c r="N160" s="194"/>
       <c r="O160" s="360"/>
-      <c r="P160" s="419"/>
-      <c r="Q160" s="419"/>
+      <c r="P160" s="447"/>
+      <c r="Q160" s="447"/>
       <c r="R160" s="186"/>
       <c r="S160" s="13"/>
       <c r="T160" s="195"/>
@@ -16577,173 +16577,288 @@
         <f t="shared" si="54"/>
         <v>799204.92218400002</v>
       </c>
-      <c r="P161" s="416">
+      <c r="P161" s="444">
         <f>SUM(P6:P160)</f>
         <v>168716264.07000002</v>
       </c>
-      <c r="Q161" s="417"/>
+      <c r="Q161" s="445"/>
       <c r="R161" s="187">
         <f>SUM(R6:R160)</f>
         <v>173833550.07000002</v>
       </c>
-      <c r="S161" s="416"/>
-      <c r="T161" s="417"/>
+      <c r="S161" s="444"/>
+      <c r="T161" s="445"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="414" t="s">
+      <c r="B162" s="442" t="s">
         <v>327</v>
       </c>
-      <c r="C162" s="414"/>
-      <c r="D162" s="414"/>
-      <c r="E162" s="414"/>
-      <c r="F162" s="414"/>
-      <c r="G162" s="414"/>
-      <c r="H162" s="414"/>
-      <c r="I162" s="414"/>
-      <c r="J162" s="414"/>
-      <c r="K162" s="414"/>
-      <c r="L162" s="414"/>
-      <c r="M162" s="414"/>
-      <c r="N162" s="414"/>
-      <c r="O162" s="414"/>
-      <c r="P162" s="414"/>
-      <c r="Q162" s="414"/>
-      <c r="R162" s="414"/>
-      <c r="S162" s="414"/>
-      <c r="T162" s="414"/>
+      <c r="C162" s="442"/>
+      <c r="D162" s="442"/>
+      <c r="E162" s="442"/>
+      <c r="F162" s="442"/>
+      <c r="G162" s="442"/>
+      <c r="H162" s="442"/>
+      <c r="I162" s="442"/>
+      <c r="J162" s="442"/>
+      <c r="K162" s="442"/>
+      <c r="L162" s="442"/>
+      <c r="M162" s="442"/>
+      <c r="N162" s="442"/>
+      <c r="O162" s="442"/>
+      <c r="P162" s="442"/>
+      <c r="Q162" s="442"/>
+      <c r="R162" s="442"/>
+      <c r="S162" s="442"/>
+      <c r="T162" s="442"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="415"/>
-      <c r="C163" s="415"/>
-      <c r="D163" s="415"/>
-      <c r="E163" s="415"/>
-      <c r="F163" s="415"/>
-      <c r="G163" s="415"/>
-      <c r="H163" s="415"/>
-      <c r="I163" s="415"/>
-      <c r="J163" s="415"/>
-      <c r="K163" s="415"/>
-      <c r="L163" s="415"/>
-      <c r="M163" s="415"/>
-      <c r="N163" s="415"/>
-      <c r="O163" s="415"/>
-      <c r="P163" s="415"/>
-      <c r="Q163" s="415"/>
-      <c r="R163" s="415"/>
-      <c r="S163" s="415"/>
-      <c r="T163" s="415"/>
+      <c r="B163" s="443"/>
+      <c r="C163" s="443"/>
+      <c r="D163" s="443"/>
+      <c r="E163" s="443"/>
+      <c r="F163" s="443"/>
+      <c r="G163" s="443"/>
+      <c r="H163" s="443"/>
+      <c r="I163" s="443"/>
+      <c r="J163" s="443"/>
+      <c r="K163" s="443"/>
+      <c r="L163" s="443"/>
+      <c r="M163" s="443"/>
+      <c r="N163" s="443"/>
+      <c r="O163" s="443"/>
+      <c r="P163" s="443"/>
+      <c r="Q163" s="443"/>
+      <c r="R163" s="443"/>
+      <c r="S163" s="443"/>
+      <c r="T163" s="443"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="415" t="s">
+      <c r="B164" s="443" t="s">
         <v>264</v>
       </c>
-      <c r="C164" s="415"/>
-      <c r="D164" s="415"/>
-      <c r="E164" s="415"/>
-      <c r="F164" s="415"/>
-      <c r="G164" s="415"/>
-      <c r="H164" s="415"/>
-      <c r="I164" s="415"/>
-      <c r="J164" s="415"/>
-      <c r="K164" s="415"/>
-      <c r="L164" s="415"/>
-      <c r="M164" s="415"/>
-      <c r="N164" s="415"/>
-      <c r="O164" s="415"/>
-      <c r="P164" s="415"/>
-      <c r="Q164" s="415"/>
-      <c r="R164" s="415"/>
-      <c r="S164" s="415"/>
-      <c r="T164" s="415"/>
+      <c r="C164" s="443"/>
+      <c r="D164" s="443"/>
+      <c r="E164" s="443"/>
+      <c r="F164" s="443"/>
+      <c r="G164" s="443"/>
+      <c r="H164" s="443"/>
+      <c r="I164" s="443"/>
+      <c r="J164" s="443"/>
+      <c r="K164" s="443"/>
+      <c r="L164" s="443"/>
+      <c r="M164" s="443"/>
+      <c r="N164" s="443"/>
+      <c r="O164" s="443"/>
+      <c r="P164" s="443"/>
+      <c r="Q164" s="443"/>
+      <c r="R164" s="443"/>
+      <c r="S164" s="443"/>
+      <c r="T164" s="443"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="415"/>
-      <c r="C165" s="415"/>
-      <c r="D165" s="415"/>
-      <c r="E165" s="415"/>
-      <c r="F165" s="415"/>
-      <c r="G165" s="415"/>
-      <c r="H165" s="415"/>
-      <c r="I165" s="415"/>
-      <c r="J165" s="415"/>
-      <c r="K165" s="415"/>
-      <c r="L165" s="415"/>
-      <c r="M165" s="415"/>
-      <c r="N165" s="415"/>
-      <c r="O165" s="415"/>
-      <c r="P165" s="415"/>
-      <c r="Q165" s="415"/>
-      <c r="R165" s="415"/>
-      <c r="S165" s="415"/>
-      <c r="T165" s="415"/>
+      <c r="B165" s="443"/>
+      <c r="C165" s="443"/>
+      <c r="D165" s="443"/>
+      <c r="E165" s="443"/>
+      <c r="F165" s="443"/>
+      <c r="G165" s="443"/>
+      <c r="H165" s="443"/>
+      <c r="I165" s="443"/>
+      <c r="J165" s="443"/>
+      <c r="K165" s="443"/>
+      <c r="L165" s="443"/>
+      <c r="M165" s="443"/>
+      <c r="N165" s="443"/>
+      <c r="O165" s="443"/>
+      <c r="P165" s="443"/>
+      <c r="Q165" s="443"/>
+      <c r="R165" s="443"/>
+      <c r="S165" s="443"/>
+      <c r="T165" s="443"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="415"/>
-      <c r="C166" s="415"/>
-      <c r="D166" s="415"/>
-      <c r="E166" s="415"/>
-      <c r="F166" s="415"/>
-      <c r="G166" s="415"/>
-      <c r="H166" s="415"/>
-      <c r="I166" s="415"/>
-      <c r="J166" s="415"/>
-      <c r="K166" s="415"/>
-      <c r="L166" s="415"/>
-      <c r="M166" s="415"/>
-      <c r="N166" s="415"/>
-      <c r="O166" s="415"/>
-      <c r="P166" s="415"/>
-      <c r="Q166" s="415"/>
-      <c r="R166" s="415"/>
-      <c r="S166" s="415"/>
-      <c r="T166" s="415"/>
+      <c r="B166" s="443"/>
+      <c r="C166" s="443"/>
+      <c r="D166" s="443"/>
+      <c r="E166" s="443"/>
+      <c r="F166" s="443"/>
+      <c r="G166" s="443"/>
+      <c r="H166" s="443"/>
+      <c r="I166" s="443"/>
+      <c r="J166" s="443"/>
+      <c r="K166" s="443"/>
+      <c r="L166" s="443"/>
+      <c r="M166" s="443"/>
+      <c r="N166" s="443"/>
+      <c r="O166" s="443"/>
+      <c r="P166" s="443"/>
+      <c r="Q166" s="443"/>
+      <c r="R166" s="443"/>
+      <c r="S166" s="443"/>
+      <c r="T166" s="443"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="415"/>
-      <c r="C167" s="415"/>
-      <c r="D167" s="415"/>
-      <c r="E167" s="415"/>
-      <c r="F167" s="415"/>
-      <c r="G167" s="415"/>
-      <c r="H167" s="415"/>
-      <c r="I167" s="415"/>
-      <c r="J167" s="415"/>
-      <c r="K167" s="415"/>
-      <c r="L167" s="415"/>
-      <c r="M167" s="415"/>
-      <c r="N167" s="415"/>
-      <c r="O167" s="415"/>
-      <c r="P167" s="415"/>
-      <c r="Q167" s="415"/>
-      <c r="R167" s="415"/>
-      <c r="S167" s="415"/>
-      <c r="T167" s="415"/>
+      <c r="B167" s="443"/>
+      <c r="C167" s="443"/>
+      <c r="D167" s="443"/>
+      <c r="E167" s="443"/>
+      <c r="F167" s="443"/>
+      <c r="G167" s="443"/>
+      <c r="H167" s="443"/>
+      <c r="I167" s="443"/>
+      <c r="J167" s="443"/>
+      <c r="K167" s="443"/>
+      <c r="L167" s="443"/>
+      <c r="M167" s="443"/>
+      <c r="N167" s="443"/>
+      <c r="O167" s="443"/>
+      <c r="P167" s="443"/>
+      <c r="Q167" s="443"/>
+      <c r="R167" s="443"/>
+      <c r="S167" s="443"/>
+      <c r="T167" s="443"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="P1:Q1"/>
@@ -16768,145 +16883,30 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -16942,12 +16942,12 @@
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
       <c r="J3" s="66"/>
-      <c r="K3" s="454" t="s">
+      <c r="K3" s="457" t="s">
         <v>337</v>
       </c>
-      <c r="L3" s="455"/>
-      <c r="M3" s="455"/>
-      <c r="N3" s="455"/>
+      <c r="L3" s="458"/>
+      <c r="M3" s="458"/>
+      <c r="N3" s="458"/>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C4" s="147" t="s">
@@ -16966,10 +16966,10 @@
       </c>
       <c r="I4" s="67"/>
       <c r="J4" s="68"/>
-      <c r="K4" s="454"/>
-      <c r="L4" s="455"/>
-      <c r="M4" s="455"/>
-      <c r="N4" s="455"/>
+      <c r="K4" s="457"/>
+      <c r="L4" s="458"/>
+      <c r="M4" s="458"/>
+      <c r="N4" s="458"/>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C5" s="147" t="s">
@@ -16990,10 +16990,10 @@
       </c>
       <c r="I5" s="67"/>
       <c r="J5" s="68"/>
-      <c r="K5" s="454"/>
-      <c r="L5" s="455"/>
-      <c r="M5" s="455"/>
-      <c r="N5" s="455"/>
+      <c r="K5" s="457"/>
+      <c r="L5" s="458"/>
+      <c r="M5" s="458"/>
+      <c r="N5" s="458"/>
     </row>
     <row r="6" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" s="147" t="s">
@@ -17006,56 +17006,56 @@
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
       <c r="J6" s="69"/>
-      <c r="K6" s="454"/>
-      <c r="L6" s="455"/>
-      <c r="M6" s="455"/>
-      <c r="N6" s="455"/>
+      <c r="K6" s="457"/>
+      <c r="L6" s="458"/>
+      <c r="M6" s="458"/>
+      <c r="N6" s="458"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="443" t="s">
+      <c r="C7" s="448" t="s">
         <v>322</v>
       </c>
-      <c r="D7" s="444"/>
-      <c r="E7" s="444"/>
-      <c r="F7" s="444"/>
-      <c r="G7" s="444"/>
-      <c r="H7" s="444"/>
-      <c r="I7" s="444"/>
-      <c r="J7" s="445"/>
-      <c r="K7" s="456" t="s">
+      <c r="D7" s="449"/>
+      <c r="E7" s="449"/>
+      <c r="F7" s="449"/>
+      <c r="G7" s="449"/>
+      <c r="H7" s="449"/>
+      <c r="I7" s="449"/>
+      <c r="J7" s="450"/>
+      <c r="K7" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="L7" s="457"/>
-      <c r="M7" s="457"/>
-      <c r="N7" s="457"/>
+      <c r="L7" s="460"/>
+      <c r="M7" s="460"/>
+      <c r="N7" s="460"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="446"/>
-      <c r="D8" s="447"/>
-      <c r="E8" s="447"/>
-      <c r="F8" s="447"/>
-      <c r="G8" s="447"/>
-      <c r="H8" s="447"/>
-      <c r="I8" s="447"/>
-      <c r="J8" s="448"/>
-      <c r="K8" s="456"/>
-      <c r="L8" s="457"/>
-      <c r="M8" s="457"/>
-      <c r="N8" s="457"/>
+      <c r="C8" s="451"/>
+      <c r="D8" s="452"/>
+      <c r="E8" s="452"/>
+      <c r="F8" s="452"/>
+      <c r="G8" s="452"/>
+      <c r="H8" s="452"/>
+      <c r="I8" s="452"/>
+      <c r="J8" s="453"/>
+      <c r="K8" s="459"/>
+      <c r="L8" s="460"/>
+      <c r="M8" s="460"/>
+      <c r="N8" s="460"/>
     </row>
     <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="449"/>
-      <c r="D9" s="450"/>
-      <c r="E9" s="450"/>
-      <c r="F9" s="450"/>
-      <c r="G9" s="450"/>
-      <c r="H9" s="450"/>
-      <c r="I9" s="450"/>
-      <c r="J9" s="451"/>
-      <c r="K9" s="456"/>
-      <c r="L9" s="457"/>
-      <c r="M9" s="457"/>
-      <c r="N9" s="457"/>
+      <c r="C9" s="454"/>
+      <c r="D9" s="455"/>
+      <c r="E9" s="455"/>
+      <c r="F9" s="455"/>
+      <c r="G9" s="455"/>
+      <c r="H9" s="455"/>
+      <c r="I9" s="455"/>
+      <c r="J9" s="456"/>
+      <c r="K9" s="459"/>
+      <c r="L9" s="460"/>
+      <c r="M9" s="460"/>
+      <c r="N9" s="460"/>
     </row>
     <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:14" x14ac:dyDescent="0.25">
@@ -17136,42 +17136,42 @@
       <c r="M15" s="347"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="443" t="s">
+      <c r="C16" s="448" t="s">
         <v>341</v>
       </c>
-      <c r="D16" s="444"/>
-      <c r="E16" s="444"/>
-      <c r="F16" s="444"/>
-      <c r="G16" s="444"/>
-      <c r="H16" s="444"/>
-      <c r="I16" s="444"/>
-      <c r="J16" s="445"/>
+      <c r="D16" s="449"/>
+      <c r="E16" s="449"/>
+      <c r="F16" s="449"/>
+      <c r="G16" s="449"/>
+      <c r="H16" s="449"/>
+      <c r="I16" s="449"/>
+      <c r="J16" s="450"/>
       <c r="K16" s="347"/>
       <c r="L16" s="347"/>
       <c r="M16" s="347"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C17" s="446"/>
-      <c r="D17" s="447"/>
-      <c r="E17" s="447"/>
-      <c r="F17" s="447"/>
-      <c r="G17" s="447"/>
-      <c r="H17" s="447"/>
-      <c r="I17" s="447"/>
-      <c r="J17" s="448"/>
+      <c r="C17" s="451"/>
+      <c r="D17" s="452"/>
+      <c r="E17" s="452"/>
+      <c r="F17" s="452"/>
+      <c r="G17" s="452"/>
+      <c r="H17" s="452"/>
+      <c r="I17" s="452"/>
+      <c r="J17" s="453"/>
       <c r="K17" s="347"/>
       <c r="L17" s="347"/>
       <c r="M17" s="347"/>
     </row>
     <row r="18" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="449"/>
-      <c r="D18" s="450"/>
-      <c r="E18" s="450"/>
-      <c r="F18" s="450"/>
-      <c r="G18" s="450"/>
-      <c r="H18" s="450"/>
-      <c r="I18" s="450"/>
-      <c r="J18" s="451"/>
+      <c r="C18" s="454"/>
+      <c r="D18" s="455"/>
+      <c r="E18" s="455"/>
+      <c r="F18" s="455"/>
+      <c r="G18" s="455"/>
+      <c r="H18" s="455"/>
+      <c r="I18" s="455"/>
+      <c r="J18" s="456"/>
     </row>
     <row r="20" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="256"/>
@@ -17251,40 +17251,40 @@
       <c r="L24" s="347"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="443" t="s">
+      <c r="C25" s="448" t="s">
         <v>371</v>
       </c>
-      <c r="D25" s="444"/>
-      <c r="E25" s="444"/>
-      <c r="F25" s="444"/>
-      <c r="G25" s="444"/>
-      <c r="H25" s="444"/>
-      <c r="I25" s="444"/>
-      <c r="J25" s="445"/>
+      <c r="D25" s="449"/>
+      <c r="E25" s="449"/>
+      <c r="F25" s="449"/>
+      <c r="G25" s="449"/>
+      <c r="H25" s="449"/>
+      <c r="I25" s="449"/>
+      <c r="J25" s="450"/>
       <c r="K25" s="347"/>
       <c r="L25" s="347"/>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="446"/>
-      <c r="D26" s="447"/>
-      <c r="E26" s="447"/>
-      <c r="F26" s="447"/>
-      <c r="G26" s="447"/>
-      <c r="H26" s="447"/>
-      <c r="I26" s="447"/>
-      <c r="J26" s="448"/>
+      <c r="C26" s="451"/>
+      <c r="D26" s="452"/>
+      <c r="E26" s="452"/>
+      <c r="F26" s="452"/>
+      <c r="G26" s="452"/>
+      <c r="H26" s="452"/>
+      <c r="I26" s="452"/>
+      <c r="J26" s="453"/>
       <c r="K26" s="347"/>
       <c r="L26" s="347"/>
     </row>
     <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="449"/>
-      <c r="D27" s="450"/>
-      <c r="E27" s="450"/>
-      <c r="F27" s="450"/>
-      <c r="G27" s="450"/>
-      <c r="H27" s="450"/>
-      <c r="I27" s="450"/>
-      <c r="J27" s="451"/>
+      <c r="C27" s="454"/>
+      <c r="D27" s="455"/>
+      <c r="E27" s="455"/>
+      <c r="F27" s="455"/>
+      <c r="G27" s="455"/>
+      <c r="H27" s="455"/>
+      <c r="I27" s="455"/>
+      <c r="J27" s="456"/>
       <c r="K27" s="347"/>
       <c r="L27" s="347"/>
     </row>
@@ -17371,42 +17371,42 @@
       <c r="M33" s="347"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C34" s="443" t="s">
+      <c r="C34" s="448" t="s">
         <v>344</v>
       </c>
-      <c r="D34" s="444"/>
-      <c r="E34" s="444"/>
-      <c r="F34" s="444"/>
-      <c r="G34" s="444"/>
-      <c r="H34" s="444"/>
-      <c r="I34" s="444"/>
-      <c r="J34" s="445"/>
+      <c r="D34" s="449"/>
+      <c r="E34" s="449"/>
+      <c r="F34" s="449"/>
+      <c r="G34" s="449"/>
+      <c r="H34" s="449"/>
+      <c r="I34" s="449"/>
+      <c r="J34" s="450"/>
       <c r="K34" s="347"/>
       <c r="L34" s="347"/>
       <c r="M34" s="347"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C35" s="446"/>
-      <c r="D35" s="447"/>
-      <c r="E35" s="447"/>
-      <c r="F35" s="447"/>
-      <c r="G35" s="447"/>
-      <c r="H35" s="447"/>
-      <c r="I35" s="447"/>
-      <c r="J35" s="448"/>
+      <c r="C35" s="451"/>
+      <c r="D35" s="452"/>
+      <c r="E35" s="452"/>
+      <c r="F35" s="452"/>
+      <c r="G35" s="452"/>
+      <c r="H35" s="452"/>
+      <c r="I35" s="452"/>
+      <c r="J35" s="453"/>
       <c r="K35" s="347"/>
       <c r="L35" s="347"/>
       <c r="M35" s="347"/>
     </row>
     <row r="36" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="449"/>
-      <c r="D36" s="450"/>
-      <c r="E36" s="450"/>
-      <c r="F36" s="450"/>
-      <c r="G36" s="450"/>
-      <c r="H36" s="450"/>
-      <c r="I36" s="450"/>
-      <c r="J36" s="451"/>
+      <c r="C36" s="454"/>
+      <c r="D36" s="455"/>
+      <c r="E36" s="455"/>
+      <c r="F36" s="455"/>
+      <c r="G36" s="455"/>
+      <c r="H36" s="455"/>
+      <c r="I36" s="455"/>
+      <c r="J36" s="456"/>
       <c r="K36" s="347"/>
       <c r="L36" s="347"/>
       <c r="M36" s="347"/>
@@ -17487,42 +17487,42 @@
       <c r="M42" s="347"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C43" s="443" t="s">
+      <c r="C43" s="448" t="s">
         <v>359</v>
       </c>
-      <c r="D43" s="444"/>
-      <c r="E43" s="444"/>
-      <c r="F43" s="444"/>
-      <c r="G43" s="444"/>
-      <c r="H43" s="444"/>
-      <c r="I43" s="444"/>
-      <c r="J43" s="445"/>
+      <c r="D43" s="449"/>
+      <c r="E43" s="449"/>
+      <c r="F43" s="449"/>
+      <c r="G43" s="449"/>
+      <c r="H43" s="449"/>
+      <c r="I43" s="449"/>
+      <c r="J43" s="450"/>
       <c r="K43" s="347"/>
       <c r="L43" s="347"/>
       <c r="M43" s="347"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="446"/>
-      <c r="D44" s="447"/>
-      <c r="E44" s="447"/>
-      <c r="F44" s="447"/>
-      <c r="G44" s="447"/>
-      <c r="H44" s="447"/>
-      <c r="I44" s="447"/>
-      <c r="J44" s="448"/>
+      <c r="C44" s="451"/>
+      <c r="D44" s="452"/>
+      <c r="E44" s="452"/>
+      <c r="F44" s="452"/>
+      <c r="G44" s="452"/>
+      <c r="H44" s="452"/>
+      <c r="I44" s="452"/>
+      <c r="J44" s="453"/>
       <c r="K44" s="347"/>
       <c r="L44" s="347"/>
       <c r="M44" s="347"/>
     </row>
     <row r="45" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="449"/>
-      <c r="D45" s="450"/>
-      <c r="E45" s="450"/>
-      <c r="F45" s="450"/>
-      <c r="G45" s="450"/>
-      <c r="H45" s="450"/>
-      <c r="I45" s="450"/>
-      <c r="J45" s="451"/>
+      <c r="C45" s="454"/>
+      <c r="D45" s="455"/>
+      <c r="E45" s="455"/>
+      <c r="F45" s="455"/>
+      <c r="G45" s="455"/>
+      <c r="H45" s="455"/>
+      <c r="I45" s="455"/>
+      <c r="J45" s="456"/>
     </row>
     <row r="47" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="3:13" x14ac:dyDescent="0.25">
@@ -17597,40 +17597,40 @@
       <c r="L51" s="347"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="443" t="s">
+      <c r="C52" s="448" t="s">
         <v>357</v>
       </c>
-      <c r="D52" s="444"/>
-      <c r="E52" s="444"/>
-      <c r="F52" s="444"/>
-      <c r="G52" s="444"/>
-      <c r="H52" s="444"/>
-      <c r="I52" s="444"/>
-      <c r="J52" s="445"/>
+      <c r="D52" s="449"/>
+      <c r="E52" s="449"/>
+      <c r="F52" s="449"/>
+      <c r="G52" s="449"/>
+      <c r="H52" s="449"/>
+      <c r="I52" s="449"/>
+      <c r="J52" s="450"/>
       <c r="K52" s="347"/>
       <c r="L52" s="347"/>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C53" s="446"/>
-      <c r="D53" s="447"/>
-      <c r="E53" s="447"/>
-      <c r="F53" s="447"/>
-      <c r="G53" s="447"/>
-      <c r="H53" s="447"/>
-      <c r="I53" s="447"/>
-      <c r="J53" s="448"/>
+      <c r="C53" s="451"/>
+      <c r="D53" s="452"/>
+      <c r="E53" s="452"/>
+      <c r="F53" s="452"/>
+      <c r="G53" s="452"/>
+      <c r="H53" s="452"/>
+      <c r="I53" s="452"/>
+      <c r="J53" s="453"/>
       <c r="K53" s="347"/>
       <c r="L53" s="347"/>
     </row>
     <row r="54" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="449"/>
-      <c r="D54" s="450"/>
-      <c r="E54" s="450"/>
-      <c r="F54" s="450"/>
-      <c r="G54" s="450"/>
-      <c r="H54" s="450"/>
-      <c r="I54" s="450"/>
-      <c r="J54" s="451"/>
+      <c r="C54" s="454"/>
+      <c r="D54" s="455"/>
+      <c r="E54" s="455"/>
+      <c r="F54" s="455"/>
+      <c r="G54" s="455"/>
+      <c r="H54" s="455"/>
+      <c r="I54" s="455"/>
+      <c r="J54" s="456"/>
       <c r="K54" s="347"/>
       <c r="L54" s="347"/>
     </row>
@@ -17705,40 +17705,40 @@
       <c r="L60" s="347"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C61" s="443" t="s">
+      <c r="C61" s="448" t="s">
         <v>358</v>
       </c>
-      <c r="D61" s="444"/>
-      <c r="E61" s="444"/>
-      <c r="F61" s="444"/>
-      <c r="G61" s="444"/>
-      <c r="H61" s="444"/>
-      <c r="I61" s="444"/>
-      <c r="J61" s="445"/>
+      <c r="D61" s="449"/>
+      <c r="E61" s="449"/>
+      <c r="F61" s="449"/>
+      <c r="G61" s="449"/>
+      <c r="H61" s="449"/>
+      <c r="I61" s="449"/>
+      <c r="J61" s="450"/>
       <c r="K61" s="347"/>
       <c r="L61" s="347"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C62" s="446"/>
-      <c r="D62" s="447"/>
-      <c r="E62" s="447"/>
-      <c r="F62" s="447"/>
-      <c r="G62" s="447"/>
-      <c r="H62" s="447"/>
-      <c r="I62" s="447"/>
-      <c r="J62" s="448"/>
+      <c r="C62" s="451"/>
+      <c r="D62" s="452"/>
+      <c r="E62" s="452"/>
+      <c r="F62" s="452"/>
+      <c r="G62" s="452"/>
+      <c r="H62" s="452"/>
+      <c r="I62" s="452"/>
+      <c r="J62" s="453"/>
       <c r="K62" s="347"/>
       <c r="L62" s="347"/>
     </row>
     <row r="63" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="449"/>
-      <c r="D63" s="450"/>
-      <c r="E63" s="450"/>
-      <c r="F63" s="450"/>
-      <c r="G63" s="450"/>
-      <c r="H63" s="450"/>
-      <c r="I63" s="450"/>
-      <c r="J63" s="451"/>
+      <c r="C63" s="454"/>
+      <c r="D63" s="455"/>
+      <c r="E63" s="455"/>
+      <c r="F63" s="455"/>
+      <c r="G63" s="455"/>
+      <c r="H63" s="455"/>
+      <c r="I63" s="455"/>
+      <c r="J63" s="456"/>
     </row>
     <row r="65" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="66" spans="3:12" x14ac:dyDescent="0.25">
@@ -17813,40 +17813,40 @@
       <c r="L69" s="347"/>
     </row>
     <row r="70" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C70" s="443" t="s">
+      <c r="C70" s="448" t="s">
         <v>346</v>
       </c>
-      <c r="D70" s="444"/>
-      <c r="E70" s="444"/>
-      <c r="F70" s="444"/>
-      <c r="G70" s="444"/>
-      <c r="H70" s="444"/>
-      <c r="I70" s="444"/>
-      <c r="J70" s="445"/>
+      <c r="D70" s="449"/>
+      <c r="E70" s="449"/>
+      <c r="F70" s="449"/>
+      <c r="G70" s="449"/>
+      <c r="H70" s="449"/>
+      <c r="I70" s="449"/>
+      <c r="J70" s="450"/>
       <c r="K70" s="347"/>
       <c r="L70" s="347"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C71" s="446"/>
-      <c r="D71" s="447"/>
-      <c r="E71" s="447"/>
-      <c r="F71" s="447"/>
-      <c r="G71" s="447"/>
-      <c r="H71" s="447"/>
-      <c r="I71" s="447"/>
-      <c r="J71" s="448"/>
+      <c r="C71" s="451"/>
+      <c r="D71" s="452"/>
+      <c r="E71" s="452"/>
+      <c r="F71" s="452"/>
+      <c r="G71" s="452"/>
+      <c r="H71" s="452"/>
+      <c r="I71" s="452"/>
+      <c r="J71" s="453"/>
       <c r="K71" s="347"/>
       <c r="L71" s="347"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="449"/>
-      <c r="D72" s="450"/>
-      <c r="E72" s="450"/>
-      <c r="F72" s="450"/>
-      <c r="G72" s="450"/>
-      <c r="H72" s="450"/>
-      <c r="I72" s="450"/>
-      <c r="J72" s="451"/>
+      <c r="C72" s="454"/>
+      <c r="D72" s="455"/>
+      <c r="E72" s="455"/>
+      <c r="F72" s="455"/>
+      <c r="G72" s="455"/>
+      <c r="H72" s="455"/>
+      <c r="I72" s="455"/>
+      <c r="J72" s="456"/>
     </row>
     <row r="74" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="3:12" x14ac:dyDescent="0.25">
@@ -17921,40 +17921,40 @@
       <c r="L78" s="347"/>
     </row>
     <row r="79" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C79" s="443" t="s">
+      <c r="C79" s="448" t="s">
         <v>347</v>
       </c>
-      <c r="D79" s="444"/>
-      <c r="E79" s="444"/>
-      <c r="F79" s="444"/>
-      <c r="G79" s="444"/>
-      <c r="H79" s="444"/>
-      <c r="I79" s="444"/>
-      <c r="J79" s="445"/>
+      <c r="D79" s="449"/>
+      <c r="E79" s="449"/>
+      <c r="F79" s="449"/>
+      <c r="G79" s="449"/>
+      <c r="H79" s="449"/>
+      <c r="I79" s="449"/>
+      <c r="J79" s="450"/>
       <c r="K79" s="347"/>
       <c r="L79" s="347"/>
     </row>
     <row r="80" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C80" s="446"/>
-      <c r="D80" s="447"/>
-      <c r="E80" s="447"/>
-      <c r="F80" s="447"/>
-      <c r="G80" s="447"/>
-      <c r="H80" s="447"/>
-      <c r="I80" s="447"/>
-      <c r="J80" s="448"/>
+      <c r="C80" s="451"/>
+      <c r="D80" s="452"/>
+      <c r="E80" s="452"/>
+      <c r="F80" s="452"/>
+      <c r="G80" s="452"/>
+      <c r="H80" s="452"/>
+      <c r="I80" s="452"/>
+      <c r="J80" s="453"/>
       <c r="K80" s="347"/>
       <c r="L80" s="347"/>
     </row>
     <row r="81" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="449"/>
-      <c r="D81" s="450"/>
-      <c r="E81" s="450"/>
-      <c r="F81" s="450"/>
-      <c r="G81" s="450"/>
-      <c r="H81" s="450"/>
-      <c r="I81" s="450"/>
-      <c r="J81" s="451"/>
+      <c r="C81" s="454"/>
+      <c r="D81" s="455"/>
+      <c r="E81" s="455"/>
+      <c r="F81" s="455"/>
+      <c r="G81" s="455"/>
+      <c r="H81" s="455"/>
+      <c r="I81" s="455"/>
+      <c r="J81" s="456"/>
       <c r="K81" s="347"/>
       <c r="L81" s="347"/>
     </row>
@@ -18029,40 +18029,40 @@
       <c r="L87" s="347"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C88" s="443" t="s">
+      <c r="C88" s="448" t="s">
         <v>348</v>
       </c>
-      <c r="D88" s="444"/>
-      <c r="E88" s="444"/>
-      <c r="F88" s="444"/>
-      <c r="G88" s="444"/>
-      <c r="H88" s="444"/>
-      <c r="I88" s="444"/>
-      <c r="J88" s="445"/>
+      <c r="D88" s="449"/>
+      <c r="E88" s="449"/>
+      <c r="F88" s="449"/>
+      <c r="G88" s="449"/>
+      <c r="H88" s="449"/>
+      <c r="I88" s="449"/>
+      <c r="J88" s="450"/>
       <c r="K88" s="347"/>
       <c r="L88" s="347"/>
     </row>
     <row r="89" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C89" s="446"/>
-      <c r="D89" s="447"/>
-      <c r="E89" s="447"/>
-      <c r="F89" s="447"/>
-      <c r="G89" s="447"/>
-      <c r="H89" s="447"/>
-      <c r="I89" s="447"/>
-      <c r="J89" s="448"/>
+      <c r="C89" s="451"/>
+      <c r="D89" s="452"/>
+      <c r="E89" s="452"/>
+      <c r="F89" s="452"/>
+      <c r="G89" s="452"/>
+      <c r="H89" s="452"/>
+      <c r="I89" s="452"/>
+      <c r="J89" s="453"/>
       <c r="K89" s="347"/>
       <c r="L89" s="347"/>
     </row>
     <row r="90" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="449"/>
-      <c r="D90" s="450"/>
-      <c r="E90" s="450"/>
-      <c r="F90" s="450"/>
-      <c r="G90" s="450"/>
-      <c r="H90" s="450"/>
-      <c r="I90" s="450"/>
-      <c r="J90" s="451"/>
+      <c r="C90" s="454"/>
+      <c r="D90" s="455"/>
+      <c r="E90" s="455"/>
+      <c r="F90" s="455"/>
+      <c r="G90" s="455"/>
+      <c r="H90" s="455"/>
+      <c r="I90" s="455"/>
+      <c r="J90" s="456"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C91" s="320"/>
@@ -18157,16 +18157,16 @@
       <c r="L99" s="347"/>
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C100" s="443" t="s">
+      <c r="C100" s="448" t="s">
         <v>360</v>
       </c>
-      <c r="D100" s="444"/>
-      <c r="E100" s="444"/>
-      <c r="F100" s="444"/>
-      <c r="G100" s="444"/>
-      <c r="H100" s="444"/>
-      <c r="I100" s="444"/>
-      <c r="J100" s="445"/>
+      <c r="D100" s="449"/>
+      <c r="E100" s="449"/>
+      <c r="F100" s="449"/>
+      <c r="G100" s="449"/>
+      <c r="H100" s="449"/>
+      <c r="I100" s="449"/>
+      <c r="J100" s="450"/>
       <c r="K100" s="347"/>
       <c r="L100" s="347"/>
       <c r="O100">
@@ -18175,14 +18175,14 @@
       </c>
     </row>
     <row r="101" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C101" s="446"/>
-      <c r="D101" s="447"/>
-      <c r="E101" s="447"/>
-      <c r="F101" s="447"/>
-      <c r="G101" s="447"/>
-      <c r="H101" s="447"/>
-      <c r="I101" s="447"/>
-      <c r="J101" s="448"/>
+      <c r="C101" s="451"/>
+      <c r="D101" s="452"/>
+      <c r="E101" s="452"/>
+      <c r="F101" s="452"/>
+      <c r="G101" s="452"/>
+      <c r="H101" s="452"/>
+      <c r="I101" s="452"/>
+      <c r="J101" s="453"/>
       <c r="K101" s="347"/>
       <c r="L101" s="347"/>
       <c r="O101">
@@ -18191,14 +18191,14 @@
       </c>
     </row>
     <row r="102" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="449"/>
-      <c r="D102" s="450"/>
-      <c r="E102" s="450"/>
-      <c r="F102" s="450"/>
-      <c r="G102" s="450"/>
-      <c r="H102" s="450"/>
-      <c r="I102" s="450"/>
-      <c r="J102" s="451"/>
+      <c r="C102" s="454"/>
+      <c r="D102" s="455"/>
+      <c r="E102" s="455"/>
+      <c r="F102" s="455"/>
+      <c r="G102" s="455"/>
+      <c r="H102" s="455"/>
+      <c r="I102" s="455"/>
+      <c r="J102" s="456"/>
       <c r="K102" s="347"/>
       <c r="L102" s="347"/>
     </row>
@@ -18287,40 +18287,40 @@
       <c r="L108" s="347"/>
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C109" s="443" t="s">
+      <c r="C109" s="448" t="s">
         <v>350</v>
       </c>
-      <c r="D109" s="444"/>
-      <c r="E109" s="444"/>
-      <c r="F109" s="444"/>
-      <c r="G109" s="444"/>
-      <c r="H109" s="444"/>
-      <c r="I109" s="444"/>
-      <c r="J109" s="445"/>
+      <c r="D109" s="449"/>
+      <c r="E109" s="449"/>
+      <c r="F109" s="449"/>
+      <c r="G109" s="449"/>
+      <c r="H109" s="449"/>
+      <c r="I109" s="449"/>
+      <c r="J109" s="450"/>
       <c r="K109" s="347"/>
       <c r="L109" s="347"/>
     </row>
     <row r="110" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C110" s="446"/>
-      <c r="D110" s="447"/>
-      <c r="E110" s="447"/>
-      <c r="F110" s="447"/>
-      <c r="G110" s="447"/>
-      <c r="H110" s="447"/>
-      <c r="I110" s="447"/>
-      <c r="J110" s="448"/>
+      <c r="C110" s="451"/>
+      <c r="D110" s="452"/>
+      <c r="E110" s="452"/>
+      <c r="F110" s="452"/>
+      <c r="G110" s="452"/>
+      <c r="H110" s="452"/>
+      <c r="I110" s="452"/>
+      <c r="J110" s="453"/>
       <c r="K110" s="347"/>
       <c r="L110" s="347"/>
     </row>
     <row r="111" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="449"/>
-      <c r="D111" s="450"/>
-      <c r="E111" s="450"/>
-      <c r="F111" s="450"/>
-      <c r="G111" s="450"/>
-      <c r="H111" s="450"/>
-      <c r="I111" s="450"/>
-      <c r="J111" s="451"/>
+      <c r="C111" s="454"/>
+      <c r="D111" s="455"/>
+      <c r="E111" s="455"/>
+      <c r="F111" s="455"/>
+      <c r="G111" s="455"/>
+      <c r="H111" s="455"/>
+      <c r="I111" s="455"/>
+      <c r="J111" s="456"/>
     </row>
     <row r="113" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="3:12" x14ac:dyDescent="0.25">
@@ -18393,40 +18393,40 @@
       <c r="L117" s="347"/>
     </row>
     <row r="118" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C118" s="443" t="s">
+      <c r="C118" s="448" t="s">
         <v>351</v>
       </c>
-      <c r="D118" s="444"/>
-      <c r="E118" s="444"/>
-      <c r="F118" s="444"/>
-      <c r="G118" s="444"/>
-      <c r="H118" s="444"/>
-      <c r="I118" s="444"/>
-      <c r="J118" s="445"/>
+      <c r="D118" s="449"/>
+      <c r="E118" s="449"/>
+      <c r="F118" s="449"/>
+      <c r="G118" s="449"/>
+      <c r="H118" s="449"/>
+      <c r="I118" s="449"/>
+      <c r="J118" s="450"/>
       <c r="K118" s="347"/>
       <c r="L118" s="347"/>
     </row>
     <row r="119" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C119" s="446"/>
-      <c r="D119" s="447"/>
-      <c r="E119" s="447"/>
-      <c r="F119" s="447"/>
-      <c r="G119" s="447"/>
-      <c r="H119" s="447"/>
-      <c r="I119" s="447"/>
-      <c r="J119" s="448"/>
+      <c r="C119" s="451"/>
+      <c r="D119" s="452"/>
+      <c r="E119" s="452"/>
+      <c r="F119" s="452"/>
+      <c r="G119" s="452"/>
+      <c r="H119" s="452"/>
+      <c r="I119" s="452"/>
+      <c r="J119" s="453"/>
       <c r="K119" s="347"/>
       <c r="L119" s="347"/>
     </row>
     <row r="120" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C120" s="449"/>
-      <c r="D120" s="450"/>
-      <c r="E120" s="450"/>
-      <c r="F120" s="450"/>
-      <c r="G120" s="450"/>
-      <c r="H120" s="450"/>
-      <c r="I120" s="450"/>
-      <c r="J120" s="451"/>
+      <c r="C120" s="454"/>
+      <c r="D120" s="455"/>
+      <c r="E120" s="455"/>
+      <c r="F120" s="455"/>
+      <c r="G120" s="455"/>
+      <c r="H120" s="455"/>
+      <c r="I120" s="455"/>
+      <c r="J120" s="456"/>
     </row>
     <row r="122" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="123" spans="3:12" x14ac:dyDescent="0.25">
@@ -18499,40 +18499,40 @@
       <c r="L126" s="347"/>
     </row>
     <row r="127" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C127" s="443" t="s">
+      <c r="C127" s="448" t="s">
         <v>352</v>
       </c>
-      <c r="D127" s="444"/>
-      <c r="E127" s="444"/>
-      <c r="F127" s="444"/>
-      <c r="G127" s="444"/>
-      <c r="H127" s="444"/>
-      <c r="I127" s="444"/>
-      <c r="J127" s="445"/>
+      <c r="D127" s="449"/>
+      <c r="E127" s="449"/>
+      <c r="F127" s="449"/>
+      <c r="G127" s="449"/>
+      <c r="H127" s="449"/>
+      <c r="I127" s="449"/>
+      <c r="J127" s="450"/>
       <c r="K127" s="347"/>
       <c r="L127" s="347"/>
     </row>
     <row r="128" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C128" s="446"/>
-      <c r="D128" s="447"/>
-      <c r="E128" s="447"/>
-      <c r="F128" s="447"/>
-      <c r="G128" s="447"/>
-      <c r="H128" s="447"/>
-      <c r="I128" s="447"/>
-      <c r="J128" s="448"/>
+      <c r="C128" s="451"/>
+      <c r="D128" s="452"/>
+      <c r="E128" s="452"/>
+      <c r="F128" s="452"/>
+      <c r="G128" s="452"/>
+      <c r="H128" s="452"/>
+      <c r="I128" s="452"/>
+      <c r="J128" s="453"/>
       <c r="K128" s="347"/>
       <c r="L128" s="347"/>
     </row>
     <row r="129" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="449"/>
-      <c r="D129" s="450"/>
-      <c r="E129" s="450"/>
-      <c r="F129" s="450"/>
-      <c r="G129" s="450"/>
-      <c r="H129" s="450"/>
-      <c r="I129" s="450"/>
-      <c r="J129" s="451"/>
+      <c r="C129" s="454"/>
+      <c r="D129" s="455"/>
+      <c r="E129" s="455"/>
+      <c r="F129" s="455"/>
+      <c r="G129" s="455"/>
+      <c r="H129" s="455"/>
+      <c r="I129" s="455"/>
+      <c r="J129" s="456"/>
     </row>
     <row r="131" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="132" spans="3:12" x14ac:dyDescent="0.25">
@@ -18605,40 +18605,40 @@
       <c r="L135" s="347"/>
     </row>
     <row r="136" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C136" s="443" t="s">
+      <c r="C136" s="448" t="s">
         <v>353</v>
       </c>
-      <c r="D136" s="444"/>
-      <c r="E136" s="444"/>
-      <c r="F136" s="444"/>
-      <c r="G136" s="444"/>
-      <c r="H136" s="444"/>
-      <c r="I136" s="444"/>
-      <c r="J136" s="445"/>
+      <c r="D136" s="449"/>
+      <c r="E136" s="449"/>
+      <c r="F136" s="449"/>
+      <c r="G136" s="449"/>
+      <c r="H136" s="449"/>
+      <c r="I136" s="449"/>
+      <c r="J136" s="450"/>
       <c r="K136" s="347"/>
       <c r="L136" s="347"/>
     </row>
     <row r="137" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C137" s="446"/>
-      <c r="D137" s="447"/>
-      <c r="E137" s="447"/>
-      <c r="F137" s="447"/>
-      <c r="G137" s="447"/>
-      <c r="H137" s="447"/>
-      <c r="I137" s="447"/>
-      <c r="J137" s="448"/>
+      <c r="C137" s="451"/>
+      <c r="D137" s="452"/>
+      <c r="E137" s="452"/>
+      <c r="F137" s="452"/>
+      <c r="G137" s="452"/>
+      <c r="H137" s="452"/>
+      <c r="I137" s="452"/>
+      <c r="J137" s="453"/>
       <c r="K137" s="347"/>
       <c r="L137" s="347"/>
     </row>
     <row r="138" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C138" s="449"/>
-      <c r="D138" s="450"/>
-      <c r="E138" s="450"/>
-      <c r="F138" s="450"/>
-      <c r="G138" s="450"/>
-      <c r="H138" s="450"/>
-      <c r="I138" s="450"/>
-      <c r="J138" s="451"/>
+      <c r="C138" s="454"/>
+      <c r="D138" s="455"/>
+      <c r="E138" s="455"/>
+      <c r="F138" s="455"/>
+      <c r="G138" s="455"/>
+      <c r="H138" s="455"/>
+      <c r="I138" s="455"/>
+      <c r="J138" s="456"/>
     </row>
     <row r="140" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="141" spans="3:12" x14ac:dyDescent="0.25">
@@ -18711,40 +18711,40 @@
       <c r="L144" s="347"/>
     </row>
     <row r="145" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C145" s="443" t="s">
+      <c r="C145" s="448" t="s">
         <v>354</v>
       </c>
-      <c r="D145" s="444"/>
-      <c r="E145" s="444"/>
-      <c r="F145" s="444"/>
-      <c r="G145" s="444"/>
-      <c r="H145" s="444"/>
-      <c r="I145" s="444"/>
-      <c r="J145" s="445"/>
+      <c r="D145" s="449"/>
+      <c r="E145" s="449"/>
+      <c r="F145" s="449"/>
+      <c r="G145" s="449"/>
+      <c r="H145" s="449"/>
+      <c r="I145" s="449"/>
+      <c r="J145" s="450"/>
       <c r="K145" s="347"/>
       <c r="L145" s="347"/>
     </row>
     <row r="146" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C146" s="446"/>
-      <c r="D146" s="447"/>
-      <c r="E146" s="447"/>
-      <c r="F146" s="447"/>
-      <c r="G146" s="447"/>
-      <c r="H146" s="447"/>
-      <c r="I146" s="447"/>
-      <c r="J146" s="448"/>
+      <c r="C146" s="451"/>
+      <c r="D146" s="452"/>
+      <c r="E146" s="452"/>
+      <c r="F146" s="452"/>
+      <c r="G146" s="452"/>
+      <c r="H146" s="452"/>
+      <c r="I146" s="452"/>
+      <c r="J146" s="453"/>
       <c r="K146" s="347"/>
       <c r="L146" s="347"/>
     </row>
     <row r="147" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="449"/>
-      <c r="D147" s="450"/>
-      <c r="E147" s="450"/>
-      <c r="F147" s="450"/>
-      <c r="G147" s="450"/>
-      <c r="H147" s="450"/>
-      <c r="I147" s="450"/>
-      <c r="J147" s="451"/>
+      <c r="C147" s="454"/>
+      <c r="D147" s="455"/>
+      <c r="E147" s="455"/>
+      <c r="F147" s="455"/>
+      <c r="G147" s="455"/>
+      <c r="H147" s="455"/>
+      <c r="I147" s="455"/>
+      <c r="J147" s="456"/>
     </row>
     <row r="148" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="149" spans="3:12" x14ac:dyDescent="0.25">
@@ -18796,11 +18796,11 @@
       <c r="G151" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H151" s="452" t="s">
+      <c r="H151" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="I151" s="452"/>
-      <c r="J151" s="453"/>
+      <c r="I151" s="461"/>
+      <c r="J151" s="462"/>
       <c r="K151" s="347"/>
       <c r="L151" s="347"/>
     </row>
@@ -18819,40 +18819,40 @@
       <c r="L152" s="347"/>
     </row>
     <row r="153" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C153" s="443" t="s">
+      <c r="C153" s="448" t="s">
         <v>355</v>
       </c>
-      <c r="D153" s="444"/>
-      <c r="E153" s="444"/>
-      <c r="F153" s="444"/>
-      <c r="G153" s="444"/>
-      <c r="H153" s="444"/>
-      <c r="I153" s="444"/>
-      <c r="J153" s="445"/>
+      <c r="D153" s="449"/>
+      <c r="E153" s="449"/>
+      <c r="F153" s="449"/>
+      <c r="G153" s="449"/>
+      <c r="H153" s="449"/>
+      <c r="I153" s="449"/>
+      <c r="J153" s="450"/>
       <c r="K153" s="347"/>
       <c r="L153" s="347"/>
     </row>
     <row r="154" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C154" s="446"/>
-      <c r="D154" s="447"/>
-      <c r="E154" s="447"/>
-      <c r="F154" s="447"/>
-      <c r="G154" s="447"/>
-      <c r="H154" s="447"/>
-      <c r="I154" s="447"/>
-      <c r="J154" s="448"/>
+      <c r="C154" s="451"/>
+      <c r="D154" s="452"/>
+      <c r="E154" s="452"/>
+      <c r="F154" s="452"/>
+      <c r="G154" s="452"/>
+      <c r="H154" s="452"/>
+      <c r="I154" s="452"/>
+      <c r="J154" s="453"/>
       <c r="K154" s="347"/>
       <c r="L154" s="347"/>
     </row>
     <row r="155" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C155" s="449"/>
-      <c r="D155" s="450"/>
-      <c r="E155" s="450"/>
-      <c r="F155" s="450"/>
-      <c r="G155" s="450"/>
-      <c r="H155" s="450"/>
-      <c r="I155" s="450"/>
-      <c r="J155" s="451"/>
+      <c r="C155" s="454"/>
+      <c r="D155" s="455"/>
+      <c r="E155" s="455"/>
+      <c r="F155" s="455"/>
+      <c r="G155" s="455"/>
+      <c r="H155" s="455"/>
+      <c r="I155" s="455"/>
+      <c r="J155" s="456"/>
       <c r="K155" s="347"/>
       <c r="L155" s="347"/>
     </row>
@@ -18925,11 +18925,11 @@
       <c r="G160" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H160" s="452">
+      <c r="H160" s="461">
         <v>119</v>
       </c>
-      <c r="I160" s="452"/>
-      <c r="J160" s="453"/>
+      <c r="I160" s="461"/>
+      <c r="J160" s="462"/>
       <c r="K160" s="347"/>
       <c r="L160" s="347"/>
     </row>
@@ -18948,40 +18948,40 @@
       <c r="L161" s="347"/>
     </row>
     <row r="162" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C162" s="443" t="s">
+      <c r="C162" s="448" t="s">
         <v>363</v>
       </c>
-      <c r="D162" s="444"/>
-      <c r="E162" s="444"/>
-      <c r="F162" s="444"/>
-      <c r="G162" s="444"/>
-      <c r="H162" s="444"/>
-      <c r="I162" s="444"/>
-      <c r="J162" s="445"/>
+      <c r="D162" s="449"/>
+      <c r="E162" s="449"/>
+      <c r="F162" s="449"/>
+      <c r="G162" s="449"/>
+      <c r="H162" s="449"/>
+      <c r="I162" s="449"/>
+      <c r="J162" s="450"/>
       <c r="K162" s="347"/>
       <c r="L162" s="347"/>
     </row>
     <row r="163" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C163" s="446"/>
-      <c r="D163" s="447"/>
-      <c r="E163" s="447"/>
-      <c r="F163" s="447"/>
-      <c r="G163" s="447"/>
-      <c r="H163" s="447"/>
-      <c r="I163" s="447"/>
-      <c r="J163" s="448"/>
+      <c r="C163" s="451"/>
+      <c r="D163" s="452"/>
+      <c r="E163" s="452"/>
+      <c r="F163" s="452"/>
+      <c r="G163" s="452"/>
+      <c r="H163" s="452"/>
+      <c r="I163" s="452"/>
+      <c r="J163" s="453"/>
       <c r="K163" s="347"/>
       <c r="L163" s="347"/>
     </row>
     <row r="164" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C164" s="449"/>
-      <c r="D164" s="450"/>
-      <c r="E164" s="450"/>
-      <c r="F164" s="450"/>
-      <c r="G164" s="450"/>
-      <c r="H164" s="450"/>
-      <c r="I164" s="450"/>
-      <c r="J164" s="451"/>
+      <c r="C164" s="454"/>
+      <c r="D164" s="455"/>
+      <c r="E164" s="455"/>
+      <c r="F164" s="455"/>
+      <c r="G164" s="455"/>
+      <c r="H164" s="455"/>
+      <c r="I164" s="455"/>
+      <c r="J164" s="456"/>
     </row>
     <row r="165" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C165" s="320"/>
@@ -19052,11 +19052,11 @@
       <c r="G169" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H169" s="452">
+      <c r="H169" s="461">
         <v>80</v>
       </c>
-      <c r="I169" s="452"/>
-      <c r="J169" s="453"/>
+      <c r="I169" s="461"/>
+      <c r="J169" s="462"/>
       <c r="K169" s="347"/>
       <c r="L169" s="347"/>
     </row>
@@ -19075,40 +19075,40 @@
       <c r="L170" s="347"/>
     </row>
     <row r="171" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C171" s="443" t="s">
+      <c r="C171" s="448" t="s">
         <v>364</v>
       </c>
-      <c r="D171" s="444"/>
-      <c r="E171" s="444"/>
-      <c r="F171" s="444"/>
-      <c r="G171" s="444"/>
-      <c r="H171" s="444"/>
-      <c r="I171" s="444"/>
-      <c r="J171" s="445"/>
+      <c r="D171" s="449"/>
+      <c r="E171" s="449"/>
+      <c r="F171" s="449"/>
+      <c r="G171" s="449"/>
+      <c r="H171" s="449"/>
+      <c r="I171" s="449"/>
+      <c r="J171" s="450"/>
       <c r="K171" s="347"/>
       <c r="L171" s="347"/>
     </row>
     <row r="172" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C172" s="446"/>
-      <c r="D172" s="447"/>
-      <c r="E172" s="447"/>
-      <c r="F172" s="447"/>
-      <c r="G172" s="447"/>
-      <c r="H172" s="447"/>
-      <c r="I172" s="447"/>
-      <c r="J172" s="448"/>
+      <c r="C172" s="451"/>
+      <c r="D172" s="452"/>
+      <c r="E172" s="452"/>
+      <c r="F172" s="452"/>
+      <c r="G172" s="452"/>
+      <c r="H172" s="452"/>
+      <c r="I172" s="452"/>
+      <c r="J172" s="453"/>
       <c r="K172" s="347"/>
       <c r="L172" s="347"/>
     </row>
     <row r="173" spans="3:12" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C173" s="449"/>
-      <c r="D173" s="450"/>
-      <c r="E173" s="450"/>
-      <c r="F173" s="450"/>
-      <c r="G173" s="450"/>
-      <c r="H173" s="450"/>
-      <c r="I173" s="450"/>
-      <c r="J173" s="451"/>
+      <c r="C173" s="454"/>
+      <c r="D173" s="455"/>
+      <c r="E173" s="455"/>
+      <c r="F173" s="455"/>
+      <c r="G173" s="455"/>
+      <c r="H173" s="455"/>
+      <c r="I173" s="455"/>
+      <c r="J173" s="456"/>
       <c r="K173" s="347"/>
       <c r="L173" s="347"/>
     </row>
@@ -19162,11 +19162,11 @@
       <c r="G177" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H177" s="452">
+      <c r="H177" s="461">
         <v>64</v>
       </c>
-      <c r="I177" s="452"/>
-      <c r="J177" s="453"/>
+      <c r="I177" s="461"/>
+      <c r="J177" s="462"/>
       <c r="K177" s="347"/>
       <c r="L177" s="347"/>
     </row>
@@ -19185,40 +19185,40 @@
       <c r="L178" s="347"/>
     </row>
     <row r="179" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C179" s="443" t="s">
+      <c r="C179" s="448" t="s">
         <v>361</v>
       </c>
-      <c r="D179" s="444"/>
-      <c r="E179" s="444"/>
-      <c r="F179" s="444"/>
-      <c r="G179" s="444"/>
-      <c r="H179" s="444"/>
-      <c r="I179" s="444"/>
-      <c r="J179" s="445"/>
+      <c r="D179" s="449"/>
+      <c r="E179" s="449"/>
+      <c r="F179" s="449"/>
+      <c r="G179" s="449"/>
+      <c r="H179" s="449"/>
+      <c r="I179" s="449"/>
+      <c r="J179" s="450"/>
       <c r="K179" s="347"/>
       <c r="L179" s="347"/>
     </row>
     <row r="180" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C180" s="446"/>
-      <c r="D180" s="447"/>
-      <c r="E180" s="447"/>
-      <c r="F180" s="447"/>
-      <c r="G180" s="447"/>
-      <c r="H180" s="447"/>
-      <c r="I180" s="447"/>
-      <c r="J180" s="448"/>
+      <c r="C180" s="451"/>
+      <c r="D180" s="452"/>
+      <c r="E180" s="452"/>
+      <c r="F180" s="452"/>
+      <c r="G180" s="452"/>
+      <c r="H180" s="452"/>
+      <c r="I180" s="452"/>
+      <c r="J180" s="453"/>
       <c r="K180" s="347"/>
       <c r="L180" s="347"/>
     </row>
     <row r="181" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C181" s="449"/>
-      <c r="D181" s="450"/>
-      <c r="E181" s="450"/>
-      <c r="F181" s="450"/>
-      <c r="G181" s="450"/>
-      <c r="H181" s="450"/>
-      <c r="I181" s="450"/>
-      <c r="J181" s="451"/>
+      <c r="C181" s="454"/>
+      <c r="D181" s="455"/>
+      <c r="E181" s="455"/>
+      <c r="F181" s="455"/>
+      <c r="G181" s="455"/>
+      <c r="H181" s="455"/>
+      <c r="I181" s="455"/>
+      <c r="J181" s="456"/>
       <c r="K181" s="347"/>
       <c r="L181" s="347"/>
     </row>
@@ -19272,11 +19272,11 @@
       <c r="G186" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H186" s="452">
+      <c r="H186" s="461">
         <v>28</v>
       </c>
-      <c r="I186" s="452"/>
-      <c r="J186" s="453"/>
+      <c r="I186" s="461"/>
+      <c r="J186" s="462"/>
       <c r="K186" s="347"/>
       <c r="L186" s="347"/>
     </row>
@@ -19295,40 +19295,40 @@
       <c r="L187" s="347"/>
     </row>
     <row r="188" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C188" s="443" t="s">
+      <c r="C188" s="448" t="s">
         <v>365</v>
       </c>
-      <c r="D188" s="444"/>
-      <c r="E188" s="444"/>
-      <c r="F188" s="444"/>
-      <c r="G188" s="444"/>
-      <c r="H188" s="444"/>
-      <c r="I188" s="444"/>
-      <c r="J188" s="445"/>
+      <c r="D188" s="449"/>
+      <c r="E188" s="449"/>
+      <c r="F188" s="449"/>
+      <c r="G188" s="449"/>
+      <c r="H188" s="449"/>
+      <c r="I188" s="449"/>
+      <c r="J188" s="450"/>
       <c r="K188" s="347"/>
       <c r="L188" s="347"/>
     </row>
     <row r="189" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C189" s="446"/>
-      <c r="D189" s="447"/>
-      <c r="E189" s="447"/>
-      <c r="F189" s="447"/>
-      <c r="G189" s="447"/>
-      <c r="H189" s="447"/>
-      <c r="I189" s="447"/>
-      <c r="J189" s="448"/>
+      <c r="C189" s="451"/>
+      <c r="D189" s="452"/>
+      <c r="E189" s="452"/>
+      <c r="F189" s="452"/>
+      <c r="G189" s="452"/>
+      <c r="H189" s="452"/>
+      <c r="I189" s="452"/>
+      <c r="J189" s="453"/>
       <c r="K189" s="347"/>
       <c r="L189" s="347"/>
     </row>
     <row r="190" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C190" s="449"/>
-      <c r="D190" s="450"/>
-      <c r="E190" s="450"/>
-      <c r="F190" s="450"/>
-      <c r="G190" s="450"/>
-      <c r="H190" s="450"/>
-      <c r="I190" s="450"/>
-      <c r="J190" s="451"/>
+      <c r="C190" s="454"/>
+      <c r="D190" s="455"/>
+      <c r="E190" s="455"/>
+      <c r="F190" s="455"/>
+      <c r="G190" s="455"/>
+      <c r="H190" s="455"/>
+      <c r="I190" s="455"/>
+      <c r="J190" s="456"/>
       <c r="K190" s="347"/>
       <c r="L190" s="347"/>
     </row>
@@ -19382,11 +19382,11 @@
       <c r="G195" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H195" s="452">
+      <c r="H195" s="461">
         <v>61</v>
       </c>
-      <c r="I195" s="452"/>
-      <c r="J195" s="453"/>
+      <c r="I195" s="461"/>
+      <c r="J195" s="462"/>
       <c r="K195" s="347"/>
       <c r="L195" s="347"/>
     </row>
@@ -19405,40 +19405,40 @@
       <c r="L196" s="347"/>
     </row>
     <row r="197" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C197" s="443" t="s">
+      <c r="C197" s="448" t="s">
         <v>366</v>
       </c>
-      <c r="D197" s="444"/>
-      <c r="E197" s="444"/>
-      <c r="F197" s="444"/>
-      <c r="G197" s="444"/>
-      <c r="H197" s="444"/>
-      <c r="I197" s="444"/>
-      <c r="J197" s="445"/>
+      <c r="D197" s="449"/>
+      <c r="E197" s="449"/>
+      <c r="F197" s="449"/>
+      <c r="G197" s="449"/>
+      <c r="H197" s="449"/>
+      <c r="I197" s="449"/>
+      <c r="J197" s="450"/>
       <c r="K197" s="347"/>
       <c r="L197" s="347"/>
     </row>
     <row r="198" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C198" s="446"/>
-      <c r="D198" s="447"/>
-      <c r="E198" s="447"/>
-      <c r="F198" s="447"/>
-      <c r="G198" s="447"/>
-      <c r="H198" s="447"/>
-      <c r="I198" s="447"/>
-      <c r="J198" s="448"/>
+      <c r="C198" s="451"/>
+      <c r="D198" s="452"/>
+      <c r="E198" s="452"/>
+      <c r="F198" s="452"/>
+      <c r="G198" s="452"/>
+      <c r="H198" s="452"/>
+      <c r="I198" s="452"/>
+      <c r="J198" s="453"/>
       <c r="K198" s="347"/>
       <c r="L198" s="347"/>
     </row>
     <row r="199" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C199" s="449"/>
-      <c r="D199" s="450"/>
-      <c r="E199" s="450"/>
-      <c r="F199" s="450"/>
-      <c r="G199" s="450"/>
-      <c r="H199" s="450"/>
-      <c r="I199" s="450"/>
-      <c r="J199" s="451"/>
+      <c r="C199" s="454"/>
+      <c r="D199" s="455"/>
+      <c r="E199" s="455"/>
+      <c r="F199" s="455"/>
+      <c r="G199" s="455"/>
+      <c r="H199" s="455"/>
+      <c r="I199" s="455"/>
+      <c r="J199" s="456"/>
       <c r="K199" s="347"/>
       <c r="L199" s="347"/>
     </row>
@@ -19489,11 +19489,11 @@
       <c r="G204" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H204" s="452">
+      <c r="H204" s="461">
         <v>97</v>
       </c>
-      <c r="I204" s="452"/>
-      <c r="J204" s="453"/>
+      <c r="I204" s="461"/>
+      <c r="J204" s="462"/>
       <c r="K204" s="347"/>
     </row>
     <row r="205" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19510,38 +19510,38 @@
       <c r="K205" s="347"/>
     </row>
     <row r="206" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C206" s="443" t="s">
+      <c r="C206" s="448" t="s">
         <v>367</v>
       </c>
-      <c r="D206" s="444"/>
-      <c r="E206" s="444"/>
-      <c r="F206" s="444"/>
-      <c r="G206" s="444"/>
-      <c r="H206" s="444"/>
-      <c r="I206" s="444"/>
-      <c r="J206" s="445"/>
+      <c r="D206" s="449"/>
+      <c r="E206" s="449"/>
+      <c r="F206" s="449"/>
+      <c r="G206" s="449"/>
+      <c r="H206" s="449"/>
+      <c r="I206" s="449"/>
+      <c r="J206" s="450"/>
       <c r="K206" s="347"/>
     </row>
     <row r="207" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C207" s="446"/>
-      <c r="D207" s="447"/>
-      <c r="E207" s="447"/>
-      <c r="F207" s="447"/>
-      <c r="G207" s="447"/>
-      <c r="H207" s="447"/>
-      <c r="I207" s="447"/>
-      <c r="J207" s="448"/>
+      <c r="C207" s="451"/>
+      <c r="D207" s="452"/>
+      <c r="E207" s="452"/>
+      <c r="F207" s="452"/>
+      <c r="G207" s="452"/>
+      <c r="H207" s="452"/>
+      <c r="I207" s="452"/>
+      <c r="J207" s="453"/>
       <c r="K207" s="347"/>
     </row>
     <row r="208" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C208" s="449"/>
-      <c r="D208" s="450"/>
-      <c r="E208" s="450"/>
-      <c r="F208" s="450"/>
-      <c r="G208" s="450"/>
-      <c r="H208" s="450"/>
-      <c r="I208" s="450"/>
-      <c r="J208" s="451"/>
+      <c r="C208" s="454"/>
+      <c r="D208" s="455"/>
+      <c r="E208" s="455"/>
+      <c r="F208" s="455"/>
+      <c r="G208" s="455"/>
+      <c r="H208" s="455"/>
+      <c r="I208" s="455"/>
+      <c r="J208" s="456"/>
     </row>
     <row r="209" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C209" s="347"/>
@@ -19617,40 +19617,40 @@
       <c r="L214" s="347"/>
     </row>
     <row r="215" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C215" s="443" t="s">
+      <c r="C215" s="448" t="s">
         <v>368</v>
       </c>
-      <c r="D215" s="444"/>
-      <c r="E215" s="444"/>
-      <c r="F215" s="444"/>
-      <c r="G215" s="444"/>
-      <c r="H215" s="444"/>
-      <c r="I215" s="444"/>
-      <c r="J215" s="445"/>
+      <c r="D215" s="449"/>
+      <c r="E215" s="449"/>
+      <c r="F215" s="449"/>
+      <c r="G215" s="449"/>
+      <c r="H215" s="449"/>
+      <c r="I215" s="449"/>
+      <c r="J215" s="450"/>
       <c r="K215" s="347"/>
       <c r="L215" s="347"/>
     </row>
     <row r="216" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C216" s="446"/>
-      <c r="D216" s="447"/>
-      <c r="E216" s="447"/>
-      <c r="F216" s="447"/>
-      <c r="G216" s="447"/>
-      <c r="H216" s="447"/>
-      <c r="I216" s="447"/>
-      <c r="J216" s="448"/>
+      <c r="C216" s="451"/>
+      <c r="D216" s="452"/>
+      <c r="E216" s="452"/>
+      <c r="F216" s="452"/>
+      <c r="G216" s="452"/>
+      <c r="H216" s="452"/>
+      <c r="I216" s="452"/>
+      <c r="J216" s="453"/>
       <c r="K216" s="347"/>
       <c r="L216" s="347"/>
     </row>
     <row r="217" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C217" s="449"/>
-      <c r="D217" s="450"/>
-      <c r="E217" s="450"/>
-      <c r="F217" s="450"/>
-      <c r="G217" s="450"/>
-      <c r="H217" s="450"/>
-      <c r="I217" s="450"/>
-      <c r="J217" s="451"/>
+      <c r="C217" s="454"/>
+      <c r="D217" s="455"/>
+      <c r="E217" s="455"/>
+      <c r="F217" s="455"/>
+      <c r="G217" s="455"/>
+      <c r="H217" s="455"/>
+      <c r="I217" s="455"/>
+      <c r="J217" s="456"/>
     </row>
     <row r="219" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="220" spans="3:12" x14ac:dyDescent="0.25">
@@ -19725,40 +19725,40 @@
       <c r="L223" s="347"/>
     </row>
     <row r="224" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C224" s="443" t="s">
+      <c r="C224" s="448" t="s">
         <v>370</v>
       </c>
-      <c r="D224" s="444"/>
-      <c r="E224" s="444"/>
-      <c r="F224" s="444"/>
-      <c r="G224" s="444"/>
-      <c r="H224" s="444"/>
-      <c r="I224" s="444"/>
-      <c r="J224" s="445"/>
+      <c r="D224" s="449"/>
+      <c r="E224" s="449"/>
+      <c r="F224" s="449"/>
+      <c r="G224" s="449"/>
+      <c r="H224" s="449"/>
+      <c r="I224" s="449"/>
+      <c r="J224" s="450"/>
       <c r="K224" s="347"/>
       <c r="L224" s="347"/>
     </row>
     <row r="225" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C225" s="446"/>
-      <c r="D225" s="447"/>
-      <c r="E225" s="447"/>
-      <c r="F225" s="447"/>
-      <c r="G225" s="447"/>
-      <c r="H225" s="447"/>
-      <c r="I225" s="447"/>
-      <c r="J225" s="448"/>
+      <c r="C225" s="451"/>
+      <c r="D225" s="452"/>
+      <c r="E225" s="452"/>
+      <c r="F225" s="452"/>
+      <c r="G225" s="452"/>
+      <c r="H225" s="452"/>
+      <c r="I225" s="452"/>
+      <c r="J225" s="453"/>
       <c r="K225" s="347"/>
       <c r="L225" s="347"/>
     </row>
     <row r="226" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C226" s="449"/>
-      <c r="D226" s="450"/>
-      <c r="E226" s="450"/>
-      <c r="F226" s="450"/>
-      <c r="G226" s="450"/>
-      <c r="H226" s="450"/>
-      <c r="I226" s="450"/>
-      <c r="J226" s="451"/>
+      <c r="C226" s="454"/>
+      <c r="D226" s="455"/>
+      <c r="E226" s="455"/>
+      <c r="F226" s="455"/>
+      <c r="G226" s="455"/>
+      <c r="H226" s="455"/>
+      <c r="I226" s="455"/>
+      <c r="J226" s="456"/>
       <c r="K226" s="347"/>
       <c r="L226" s="347"/>
     </row>
@@ -19835,40 +19835,40 @@
       <c r="L232" s="347"/>
     </row>
     <row r="233" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C233" s="443" t="s">
+      <c r="C233" s="448" t="s">
         <v>373</v>
       </c>
-      <c r="D233" s="444"/>
-      <c r="E233" s="444"/>
-      <c r="F233" s="444"/>
-      <c r="G233" s="444"/>
-      <c r="H233" s="444"/>
-      <c r="I233" s="444"/>
-      <c r="J233" s="445"/>
+      <c r="D233" s="449"/>
+      <c r="E233" s="449"/>
+      <c r="F233" s="449"/>
+      <c r="G233" s="449"/>
+      <c r="H233" s="449"/>
+      <c r="I233" s="449"/>
+      <c r="J233" s="450"/>
       <c r="K233" s="347"/>
       <c r="L233" s="347"/>
     </row>
     <row r="234" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C234" s="446"/>
-      <c r="D234" s="447"/>
-      <c r="E234" s="447"/>
-      <c r="F234" s="447"/>
-      <c r="G234" s="447"/>
-      <c r="H234" s="447"/>
-      <c r="I234" s="447"/>
-      <c r="J234" s="448"/>
+      <c r="C234" s="451"/>
+      <c r="D234" s="452"/>
+      <c r="E234" s="452"/>
+      <c r="F234" s="452"/>
+      <c r="G234" s="452"/>
+      <c r="H234" s="452"/>
+      <c r="I234" s="452"/>
+      <c r="J234" s="453"/>
       <c r="K234" s="347"/>
       <c r="L234" s="347"/>
     </row>
     <row r="235" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C235" s="449"/>
-      <c r="D235" s="450"/>
-      <c r="E235" s="450"/>
-      <c r="F235" s="450"/>
-      <c r="G235" s="450"/>
-      <c r="H235" s="450"/>
-      <c r="I235" s="450"/>
-      <c r="J235" s="451"/>
+      <c r="C235" s="454"/>
+      <c r="D235" s="455"/>
+      <c r="E235" s="455"/>
+      <c r="F235" s="455"/>
+      <c r="G235" s="455"/>
+      <c r="H235" s="455"/>
+      <c r="I235" s="455"/>
+      <c r="J235" s="456"/>
       <c r="K235" s="347"/>
       <c r="L235" s="347"/>
     </row>
@@ -19940,38 +19940,38 @@
       <c r="K241" s="347"/>
     </row>
     <row r="242" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C242" s="443" t="s">
+      <c r="C242" s="448" t="s">
         <v>374</v>
       </c>
-      <c r="D242" s="444"/>
-      <c r="E242" s="444"/>
-      <c r="F242" s="444"/>
-      <c r="G242" s="444"/>
-      <c r="H242" s="444"/>
-      <c r="I242" s="444"/>
-      <c r="J242" s="445"/>
+      <c r="D242" s="449"/>
+      <c r="E242" s="449"/>
+      <c r="F242" s="449"/>
+      <c r="G242" s="449"/>
+      <c r="H242" s="449"/>
+      <c r="I242" s="449"/>
+      <c r="J242" s="450"/>
       <c r="K242" s="347"/>
     </row>
     <row r="243" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C243" s="446"/>
-      <c r="D243" s="447"/>
-      <c r="E243" s="447"/>
-      <c r="F243" s="447"/>
-      <c r="G243" s="447"/>
-      <c r="H243" s="447"/>
-      <c r="I243" s="447"/>
-      <c r="J243" s="448"/>
+      <c r="C243" s="451"/>
+      <c r="D243" s="452"/>
+      <c r="E243" s="452"/>
+      <c r="F243" s="452"/>
+      <c r="G243" s="452"/>
+      <c r="H243" s="452"/>
+      <c r="I243" s="452"/>
+      <c r="J243" s="453"/>
       <c r="K243" s="347"/>
     </row>
     <row r="244" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C244" s="449"/>
-      <c r="D244" s="450"/>
-      <c r="E244" s="450"/>
-      <c r="F244" s="450"/>
-      <c r="G244" s="450"/>
-      <c r="H244" s="450"/>
-      <c r="I244" s="450"/>
-      <c r="J244" s="451"/>
+      <c r="C244" s="454"/>
+      <c r="D244" s="455"/>
+      <c r="E244" s="455"/>
+      <c r="F244" s="455"/>
+      <c r="G244" s="455"/>
+      <c r="H244" s="455"/>
+      <c r="I244" s="455"/>
+      <c r="J244" s="456"/>
     </row>
     <row r="246" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="247" spans="3:12" x14ac:dyDescent="0.25">
@@ -20044,45 +20044,66 @@
       <c r="L250" s="347"/>
     </row>
     <row r="251" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C251" s="443" t="s">
+      <c r="C251" s="448" t="s">
         <v>375</v>
       </c>
-      <c r="D251" s="444"/>
-      <c r="E251" s="444"/>
-      <c r="F251" s="444"/>
-      <c r="G251" s="444"/>
-      <c r="H251" s="444"/>
-      <c r="I251" s="444"/>
-      <c r="J251" s="445"/>
+      <c r="D251" s="449"/>
+      <c r="E251" s="449"/>
+      <c r="F251" s="449"/>
+      <c r="G251" s="449"/>
+      <c r="H251" s="449"/>
+      <c r="I251" s="449"/>
+      <c r="J251" s="450"/>
       <c r="K251" s="347"/>
       <c r="L251" s="347"/>
     </row>
     <row r="252" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C252" s="446"/>
-      <c r="D252" s="447"/>
-      <c r="E252" s="447"/>
-      <c r="F252" s="447"/>
-      <c r="G252" s="447"/>
-      <c r="H252" s="447"/>
-      <c r="I252" s="447"/>
-      <c r="J252" s="448"/>
+      <c r="C252" s="451"/>
+      <c r="D252" s="452"/>
+      <c r="E252" s="452"/>
+      <c r="F252" s="452"/>
+      <c r="G252" s="452"/>
+      <c r="H252" s="452"/>
+      <c r="I252" s="452"/>
+      <c r="J252" s="453"/>
       <c r="K252" s="347"/>
       <c r="L252" s="347"/>
     </row>
     <row r="253" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C253" s="449"/>
-      <c r="D253" s="450"/>
-      <c r="E253" s="450"/>
-      <c r="F253" s="450"/>
-      <c r="G253" s="450"/>
-      <c r="H253" s="450"/>
-      <c r="I253" s="450"/>
-      <c r="J253" s="451"/>
+      <c r="C253" s="454"/>
+      <c r="D253" s="455"/>
+      <c r="E253" s="455"/>
+      <c r="F253" s="455"/>
+      <c r="G253" s="455"/>
+      <c r="H253" s="455"/>
+      <c r="I253" s="455"/>
+      <c r="J253" s="456"/>
       <c r="K253" s="347"/>
       <c r="L253" s="347"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C242:J244"/>
+    <mergeCell ref="C206:J208"/>
+    <mergeCell ref="C215:J217"/>
+    <mergeCell ref="C224:J226"/>
+    <mergeCell ref="H186:J186"/>
+    <mergeCell ref="C188:J190"/>
+    <mergeCell ref="H195:J195"/>
+    <mergeCell ref="C197:J199"/>
+    <mergeCell ref="H204:J204"/>
+    <mergeCell ref="C233:J235"/>
+    <mergeCell ref="H160:J160"/>
+    <mergeCell ref="C162:J164"/>
+    <mergeCell ref="H169:J169"/>
+    <mergeCell ref="C171:J173"/>
+    <mergeCell ref="H177:J177"/>
+    <mergeCell ref="C118:J120"/>
+    <mergeCell ref="C127:J129"/>
+    <mergeCell ref="C136:J138"/>
+    <mergeCell ref="C145:J147"/>
+    <mergeCell ref="C153:J155"/>
+    <mergeCell ref="H151:J151"/>
     <mergeCell ref="C251:J253"/>
     <mergeCell ref="C109:J111"/>
     <mergeCell ref="C100:J102"/>
@@ -20099,27 +20120,6 @@
     <mergeCell ref="C52:J54"/>
     <mergeCell ref="K7:N9"/>
     <mergeCell ref="C179:J181"/>
-    <mergeCell ref="C118:J120"/>
-    <mergeCell ref="C127:J129"/>
-    <mergeCell ref="C136:J138"/>
-    <mergeCell ref="C145:J147"/>
-    <mergeCell ref="C153:J155"/>
-    <mergeCell ref="H151:J151"/>
-    <mergeCell ref="H160:J160"/>
-    <mergeCell ref="C162:J164"/>
-    <mergeCell ref="H169:J169"/>
-    <mergeCell ref="C171:J173"/>
-    <mergeCell ref="H177:J177"/>
-    <mergeCell ref="C242:J244"/>
-    <mergeCell ref="C206:J208"/>
-    <mergeCell ref="C215:J217"/>
-    <mergeCell ref="C224:J226"/>
-    <mergeCell ref="H186:J186"/>
-    <mergeCell ref="C188:J190"/>
-    <mergeCell ref="H195:J195"/>
-    <mergeCell ref="C197:J199"/>
-    <mergeCell ref="H204:J204"/>
-    <mergeCell ref="C233:J235"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20139,36 +20139,36 @@
   <sheetData>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="135" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F6" s="135" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D7" s="11">
         <v>2700000</v>
       </c>
       <c r="F7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G7" s="13">
         <f>D11</f>
         <v>969506.92</v>
       </c>
       <c r="I7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J7" s="13">
         <f>G13</f>
@@ -20177,19 +20177,19 @@
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D8" s="11">
         <v>2700000</v>
       </c>
       <c r="F8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G8" s="11">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J8" s="13">
         <f>D11</f>
@@ -20198,20 +20198,20 @@
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D9" s="11">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G9" s="13">
         <f>G7</f>
         <v>969506.92</v>
       </c>
       <c r="I9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J9" s="13">
         <f>J7-J8</f>
@@ -20220,17 +20220,17 @@
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D10" s="11"/>
       <c r="F10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G10" s="11">
         <v>29928.678620400002</v>
       </c>
       <c r="I10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J10" s="11">
         <v>26537.673329999998</v>
@@ -20238,50 +20238,50 @@
     </row>
     <row r="11" spans="3:10" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D11" s="11">
         <v>969506.92</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G11" s="11">
         <f>387244.626816+185936.292610276+202702.7028</f>
         <v>775883.62222627597</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D12" s="13">
         <f>D11</f>
         <v>969506.92</v>
       </c>
       <c r="F12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G12" s="13">
         <f>G11+G10+G9</f>
         <v>1775319.220846676</v>
       </c>
       <c r="I12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J12" s="368" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G13" s="11">
         <v>1829165.92</v>
@@ -20291,89 +20291,89 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="458" t="s">
-        <v>476</v>
-      </c>
-      <c r="G15" s="458"/>
-      <c r="I15" s="458" t="s">
-        <v>482</v>
-      </c>
-      <c r="J15" s="458"/>
+      <c r="F15" s="463" t="s">
+        <v>475</v>
+      </c>
+      <c r="G15" s="463"/>
+      <c r="I15" s="463" t="s">
+        <v>481</v>
+      </c>
+      <c r="J15" s="463"/>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F16" s="458"/>
-      <c r="G16" s="458"/>
-      <c r="I16" s="458"/>
-      <c r="J16" s="458"/>
+      <c r="F16" s="463"/>
+      <c r="G16" s="463"/>
+      <c r="I16" s="463"/>
+      <c r="J16" s="463"/>
     </row>
     <row r="17" spans="3:10" ht="37.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="458"/>
-      <c r="G17" s="458"/>
-      <c r="I17" s="458"/>
-      <c r="J17" s="458"/>
+      <c r="F17" s="463"/>
+      <c r="G17" s="463"/>
+      <c r="I17" s="463"/>
+      <c r="J17" s="463"/>
     </row>
     <row r="18" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="372" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D19" s="373"/>
       <c r="E19" s="373"/>
       <c r="F19" s="374"/>
-      <c r="G19" s="459" t="s">
-        <v>489</v>
-      </c>
-      <c r="H19" s="460"/>
-      <c r="I19" s="460"/>
-      <c r="J19" s="461"/>
+      <c r="G19" s="464" t="s">
+        <v>488</v>
+      </c>
+      <c r="H19" s="465"/>
+      <c r="I19" s="465"/>
+      <c r="J19" s="466"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="375" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F20" s="376">
         <v>859658.99999999988</v>
       </c>
-      <c r="G20" s="462"/>
-      <c r="H20" s="463"/>
-      <c r="I20" s="463"/>
-      <c r="J20" s="464"/>
+      <c r="G20" s="467"/>
+      <c r="H20" s="468"/>
+      <c r="I20" s="468"/>
+      <c r="J20" s="469"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="375" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F21" s="376">
         <v>26537.673329999998</v>
       </c>
-      <c r="G21" s="462"/>
-      <c r="H21" s="463"/>
-      <c r="I21" s="463"/>
-      <c r="J21" s="464"/>
+      <c r="G21" s="467"/>
+      <c r="H21" s="468"/>
+      <c r="I21" s="468"/>
+      <c r="J21" s="469"/>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="375" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F22" s="377">
         <v>850000</v>
       </c>
-      <c r="G22" s="462"/>
-      <c r="H22" s="463"/>
-      <c r="I22" s="463"/>
-      <c r="J22" s="464"/>
+      <c r="G22" s="467"/>
+      <c r="H22" s="468"/>
+      <c r="I22" s="468"/>
+      <c r="J22" s="469"/>
     </row>
     <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="375"/>
       <c r="F23" s="378"/>
-      <c r="G23" s="462"/>
-      <c r="H23" s="463"/>
-      <c r="I23" s="463"/>
-      <c r="J23" s="464"/>
+      <c r="G23" s="467"/>
+      <c r="H23" s="468"/>
+      <c r="I23" s="468"/>
+      <c r="J23" s="469"/>
     </row>
     <row r="24" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C24" s="369" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D24" s="370"/>
       <c r="E24" s="370"/>
@@ -20381,10 +20381,10 @@
         <f>SUM(F20:F23)</f>
         <v>1736196.6733299999</v>
       </c>
-      <c r="G24" s="465"/>
-      <c r="H24" s="466"/>
-      <c r="I24" s="466"/>
-      <c r="J24" s="467"/>
+      <c r="G24" s="470"/>
+      <c r="H24" s="471"/>
+      <c r="I24" s="471"/>
+      <c r="J24" s="472"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
+++ b/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82103BD-568D-4F11-BDC3-68F7F1956363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB875B8-CD9E-4174-895E-6040CF1BD9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -823,9 +823,6 @@
     <t>Daniela Cabral</t>
   </si>
   <si>
-    <t>Gastos particulares / Multas / SUM</t>
-  </si>
-  <si>
     <t>Egresos extraordinarios</t>
   </si>
   <si>
@@ -1540,6 +1537,9 @@
   </si>
   <si>
     <t xml:space="preserve">Honorarios administracion - Mes de FEBRERO </t>
+  </si>
+  <si>
+    <t>Gastos particulares / Seguridad de SUM / Multas / Uso de SUM</t>
   </si>
 </sst>
 </file>
@@ -2416,7 +2416,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="473">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2919,12 +2919,6 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2937,17 +2931,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2981,46 +2994,50 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3079,24 +3096,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3124,6 +3124,12 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3135,12 +3141,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3172,6 +3172,7 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -3604,34 +3605,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="405"/>
-      <c r="B1" s="400" t="s">
+      <c r="A1" s="408"/>
+      <c r="B1" s="403" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="401"/>
-      <c r="D1" s="401"/>
-      <c r="E1" s="402"/>
+      <c r="C1" s="404"/>
+      <c r="D1" s="404"/>
+      <c r="E1" s="405"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="406"/>
-      <c r="B2" s="400" t="s">
+      <c r="A2" s="409"/>
+      <c r="B2" s="403" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="401"/>
-      <c r="D2" s="401"/>
-      <c r="E2" s="402"/>
+      <c r="C2" s="404"/>
+      <c r="D2" s="404"/>
+      <c r="E2" s="405"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="406"/>
-      <c r="B3" s="397" t="s">
+      <c r="A3" s="409"/>
+      <c r="B3" s="400" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="398"/>
-      <c r="D3" s="398"/>
-      <c r="E3" s="399"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="402"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="406"/>
+      <c r="A4" s="409"/>
       <c r="B4" s="47" t="s">
         <v>156</v>
       </c>
@@ -3640,63 +3641,63 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="406"/>
+      <c r="A5" s="409"/>
       <c r="B5" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C5" s="48"/>
       <c r="D5" s="48"/>
       <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="406"/>
+      <c r="A6" s="409"/>
       <c r="B6" s="51" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
       <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="406"/>
+      <c r="A7" s="409"/>
       <c r="B7" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
       <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="407"/>
-      <c r="B8" s="403" t="s">
+      <c r="A8" s="410"/>
+      <c r="B8" s="406" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="403"/>
-      <c r="D8" s="403"/>
-      <c r="E8" s="404"/>
+      <c r="C8" s="406"/>
+      <c r="D8" s="406"/>
+      <c r="E8" s="407"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="392" t="s">
-        <v>495</v>
-      </c>
-      <c r="B10" s="392"/>
-      <c r="C10" s="392"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="392"/>
+      <c r="A10" s="411" t="s">
+        <v>494</v>
+      </c>
+      <c r="B10" s="411"/>
+      <c r="C10" s="411"/>
+      <c r="D10" s="411"/>
+      <c r="E10" s="411"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="392"/>
-      <c r="B11" s="392"/>
-      <c r="C11" s="392"/>
-      <c r="D11" s="392"/>
-      <c r="E11" s="392"/>
+      <c r="A11" s="411"/>
+      <c r="B11" s="411"/>
+      <c r="C11" s="411"/>
+      <c r="D11" s="411"/>
+      <c r="E11" s="411"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="392"/>
-      <c r="B12" s="392"/>
-      <c r="C12" s="392"/>
-      <c r="D12" s="392"/>
-      <c r="E12" s="392"/>
+      <c r="A12" s="411"/>
+      <c r="B12" s="411"/>
+      <c r="C12" s="411"/>
+      <c r="D12" s="411"/>
+      <c r="E12" s="411"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="32"/>
@@ -3713,34 +3714,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="393" t="s">
+      <c r="A15" s="412" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="393"/>
-      <c r="C15" s="393"/>
-      <c r="D15" s="393"/>
-      <c r="E15" s="393"/>
+      <c r="B15" s="412"/>
+      <c r="C15" s="412"/>
+      <c r="D15" s="412"/>
+      <c r="E15" s="412"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="393"/>
-      <c r="B16" s="393"/>
-      <c r="C16" s="393"/>
-      <c r="D16" s="393"/>
-      <c r="E16" s="393"/>
+      <c r="A16" s="412"/>
+      <c r="B16" s="412"/>
+      <c r="C16" s="412"/>
+      <c r="D16" s="412"/>
+      <c r="E16" s="412"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="393"/>
-      <c r="B17" s="393"/>
-      <c r="C17" s="393"/>
-      <c r="D17" s="393"/>
-      <c r="E17" s="393"/>
+      <c r="A17" s="412"/>
+      <c r="B17" s="412"/>
+      <c r="C17" s="412"/>
+      <c r="D17" s="412"/>
+      <c r="E17" s="412"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="393"/>
-      <c r="B18" s="393"/>
-      <c r="C18" s="393"/>
-      <c r="D18" s="393"/>
-      <c r="E18" s="393"/>
+      <c r="A18" s="412"/>
+      <c r="B18" s="412"/>
+      <c r="C18" s="412"/>
+      <c r="D18" s="412"/>
+      <c r="E18" s="412"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32"/>
@@ -3783,7 +3784,7 @@
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="211" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B24" s="182"/>
       <c r="C24" s="24"/>
@@ -3791,15 +3792,15 @@
         <v>2001463.53</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="395" t="s">
-        <v>394</v>
-      </c>
-      <c r="B25" s="396"/>
+      <c r="A25" s="414" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" s="415"/>
       <c r="C25" s="24"/>
       <c r="D25" s="382">
         <v>-435318.34</v>
@@ -3808,10 +3809,10 @@
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="386" t="s">
-        <v>395</v>
-      </c>
-      <c r="B26" s="387"/>
+      <c r="A26" s="416" t="s">
+        <v>394</v>
+      </c>
+      <c r="B26" s="417"/>
       <c r="C26" s="24"/>
       <c r="D26" s="382">
         <v>0.81</v>
@@ -3839,16 +3840,16 @@
       <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="390" t="s">
-        <v>315</v>
-      </c>
-      <c r="B28" s="391"/>
+      <c r="A28" s="388" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" s="389"/>
       <c r="C28" s="24"/>
       <c r="D28" s="382">
         <v>920000</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -3889,7 +3890,7 @@
     </row>
     <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="108"/>
@@ -3897,13 +3898,13 @@
         <v>933473.93</v>
       </c>
       <c r="E32" s="84" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G32" s="42"/>
     </row>
     <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="109" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>11</v>
@@ -3913,7 +3914,7 @@
         <v>92048.38</v>
       </c>
       <c r="E33" s="84" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G33" s="42"/>
     </row>
@@ -3975,49 +3976,49 @@
       <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="388" t="s">
-        <v>273</v>
-      </c>
-      <c r="B38" s="389"/>
+      <c r="A38" s="386" t="s">
+        <v>272</v>
+      </c>
+      <c r="B38" s="387"/>
       <c r="C38" s="24"/>
       <c r="D38" s="231">
         <v>148964</v>
       </c>
       <c r="E38" s="85" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="388" t="s">
-        <v>274</v>
-      </c>
-      <c r="B39" s="389"/>
+      <c r="A39" s="386" t="s">
+        <v>273</v>
+      </c>
+      <c r="B39" s="387"/>
       <c r="C39" s="24"/>
       <c r="D39" s="231">
         <v>6160</v>
       </c>
       <c r="E39" s="85" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="388" t="s">
-        <v>318</v>
-      </c>
-      <c r="B40" s="389"/>
+      <c r="A40" s="386" t="s">
+        <v>317</v>
+      </c>
+      <c r="B40" s="387"/>
       <c r="C40" s="24"/>
       <c r="D40" s="231">
         <v>23596</v>
       </c>
       <c r="E40" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="388" t="s">
-        <v>317</v>
-      </c>
-      <c r="B41" s="389"/>
+      <c r="A41" s="386" t="s">
+        <v>316</v>
+      </c>
+      <c r="B41" s="387"/>
       <c r="C41" s="24"/>
       <c r="D41" s="231"/>
       <c r="E41" s="85"/>
@@ -4044,31 +4045,31 @@
       <c r="E43" s="29"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="388" t="s">
-        <v>399</v>
-      </c>
-      <c r="B44" s="394"/>
+      <c r="A44" s="386" t="s">
+        <v>398</v>
+      </c>
+      <c r="B44" s="413"/>
       <c r="C44" s="112"/>
       <c r="D44" s="231">
         <v>44907682.960000001</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G44" s="13"/>
       <c r="I44" s="40"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="388" t="s">
-        <v>400</v>
-      </c>
-      <c r="B45" s="394"/>
+      <c r="A45" s="386" t="s">
+        <v>399</v>
+      </c>
+      <c r="B45" s="413"/>
       <c r="C45" s="112"/>
       <c r="D45" s="231">
         <v>4773198.96</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="13"/>
     </row>
@@ -4096,216 +4097,216 @@
       <c r="E47" s="72"/>
     </row>
     <row r="48" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="388" t="s">
-        <v>330</v>
-      </c>
-      <c r="B48" s="394"/>
+      <c r="A48" s="386" t="s">
+        <v>329</v>
+      </c>
+      <c r="B48" s="413"/>
       <c r="C48" s="112"/>
       <c r="D48" s="231">
         <v>1212341.6499999999</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="388" t="s">
-        <v>383</v>
-      </c>
-      <c r="B49" s="394"/>
+      <c r="A49" s="386" t="s">
+        <v>382</v>
+      </c>
+      <c r="B49" s="413"/>
       <c r="C49" s="112"/>
       <c r="D49" s="231">
         <v>1512500</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="388" t="s">
-        <v>414</v>
-      </c>
-      <c r="B50" s="394"/>
+      <c r="A50" s="386" t="s">
+        <v>413</v>
+      </c>
+      <c r="B50" s="413"/>
       <c r="C50" s="112"/>
       <c r="D50" s="231">
         <v>5445000</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="388" t="s">
-        <v>384</v>
-      </c>
-      <c r="B51" s="389"/>
+      <c r="A51" s="386" t="s">
+        <v>383</v>
+      </c>
+      <c r="B51" s="387"/>
       <c r="C51" s="113"/>
       <c r="D51" s="231">
         <v>480000</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G51" s="36"/>
     </row>
     <row r="52" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="388" t="s">
-        <v>424</v>
-      </c>
-      <c r="B52" s="389"/>
+      <c r="A52" s="386" t="s">
+        <v>423</v>
+      </c>
+      <c r="B52" s="387"/>
       <c r="C52" s="113"/>
       <c r="D52" s="231">
         <v>6300000</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="388" t="s">
-        <v>385</v>
-      </c>
-      <c r="B53" s="389"/>
+      <c r="A53" s="386" t="s">
+        <v>384</v>
+      </c>
+      <c r="B53" s="387"/>
       <c r="C53" s="113"/>
       <c r="D53" s="231">
         <v>228690</v>
       </c>
       <c r="E53" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="388" t="s">
-        <v>386</v>
-      </c>
-      <c r="B54" s="389"/>
+      <c r="A54" s="386" t="s">
+        <v>385</v>
+      </c>
+      <c r="B54" s="387"/>
       <c r="C54" s="113"/>
       <c r="D54" s="231">
         <v>228690</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="388" t="s">
-        <v>410</v>
-      </c>
-      <c r="B55" s="389"/>
+      <c r="A55" s="386" t="s">
+        <v>409</v>
+      </c>
+      <c r="B55" s="387"/>
       <c r="C55" s="113"/>
       <c r="D55" s="231">
         <v>943800</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="388" t="s">
-        <v>409</v>
-      </c>
-      <c r="B56" s="389"/>
+      <c r="A56" s="386" t="s">
+        <v>408</v>
+      </c>
+      <c r="B56" s="387"/>
       <c r="C56" s="113"/>
       <c r="D56" s="231">
         <v>943800</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="388" t="s">
-        <v>376</v>
-      </c>
-      <c r="B57" s="389"/>
+      <c r="A57" s="386" t="s">
+        <v>375</v>
+      </c>
+      <c r="B57" s="387"/>
       <c r="C57" s="113"/>
       <c r="D57" s="231">
         <v>820380</v>
       </c>
       <c r="E57" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="388" t="s">
-        <v>377</v>
-      </c>
-      <c r="B58" s="389"/>
+      <c r="A58" s="386" t="s">
+        <v>376</v>
+      </c>
+      <c r="B58" s="387"/>
       <c r="C58" s="113"/>
       <c r="D58" s="231">
         <v>820380</v>
       </c>
       <c r="E58" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="388" t="s">
-        <v>379</v>
-      </c>
-      <c r="B59" s="389"/>
+      <c r="A59" s="386" t="s">
+        <v>378</v>
+      </c>
+      <c r="B59" s="387"/>
       <c r="C59" s="113"/>
       <c r="D59" s="231">
         <v>100000</v>
       </c>
       <c r="E59" s="86" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="388" t="s">
-        <v>416</v>
-      </c>
-      <c r="B60" s="389"/>
+      <c r="A60" s="386" t="s">
+        <v>415</v>
+      </c>
+      <c r="B60" s="387"/>
       <c r="C60" s="113"/>
       <c r="D60" s="231">
         <v>100000</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="388" t="s">
-        <v>429</v>
-      </c>
-      <c r="B61" s="389"/>
+      <c r="A61" s="386" t="s">
+        <v>428</v>
+      </c>
+      <c r="B61" s="387"/>
       <c r="C61" s="24"/>
       <c r="D61" s="149">
         <v>200000</v>
       </c>
       <c r="E61" s="86" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G61" s="97"/>
       <c r="H61" s="97"/>
     </row>
     <row r="62" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="388" t="s">
-        <v>404</v>
-      </c>
-      <c r="B62" s="389"/>
+      <c r="A62" s="386" t="s">
+        <v>403</v>
+      </c>
+      <c r="B62" s="387"/>
       <c r="C62" s="24"/>
       <c r="D62" s="231">
         <v>2459883</v>
       </c>
       <c r="E62" s="86" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G62" s="97"/>
       <c r="H62" s="97"/>
     </row>
     <row r="63" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="388" t="s">
-        <v>288</v>
-      </c>
-      <c r="B63" s="389"/>
+      <c r="A63" s="386" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" s="387"/>
       <c r="C63" s="24"/>
       <c r="D63" s="231">
         <v>350000</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G63" s="97"/>
       <c r="H63" s="97"/>
@@ -4332,68 +4333,68 @@
       <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="390" t="s">
-        <v>428</v>
-      </c>
-      <c r="B66" s="391"/>
+      <c r="A66" s="388" t="s">
+        <v>427</v>
+      </c>
+      <c r="B66" s="389"/>
       <c r="C66" s="24"/>
       <c r="D66" s="149">
         <v>280000</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="390" t="s">
-        <v>380</v>
-      </c>
-      <c r="B67" s="391"/>
+      <c r="A67" s="388" t="s">
+        <v>379</v>
+      </c>
+      <c r="B67" s="389"/>
       <c r="C67" s="24"/>
       <c r="D67" s="149">
         <v>250000</v>
       </c>
       <c r="E67" s="87" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="388" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="390" t="s">
-        <v>382</v>
-      </c>
-      <c r="B68" s="391"/>
+      <c r="B68" s="389"/>
       <c r="C68" s="24"/>
       <c r="D68" s="149">
         <v>150000</v>
       </c>
       <c r="E68" s="87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="123.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="388" t="s">
-        <v>425</v>
-      </c>
-      <c r="B69" s="389"/>
+      <c r="A69" s="386" t="s">
+        <v>424</v>
+      </c>
+      <c r="B69" s="387"/>
       <c r="C69" s="109"/>
       <c r="D69" s="149">
         <v>2130000</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="388" t="s">
-        <v>492</v>
-      </c>
-      <c r="B70" s="389"/>
+      <c r="A70" s="386" t="s">
+        <v>491</v>
+      </c>
+      <c r="B70" s="387"/>
       <c r="C70" s="109"/>
       <c r="D70" s="149">
         <v>150000</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G70" s="97">
         <f>D69+D70+D71+D72</f>
@@ -4401,213 +4402,213 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="388" t="s">
-        <v>405</v>
-      </c>
-      <c r="B71" s="389"/>
+      <c r="A71" s="386" t="s">
+        <v>404</v>
+      </c>
+      <c r="B71" s="387"/>
       <c r="C71" s="109"/>
       <c r="D71" s="149">
         <v>2200000</v>
       </c>
       <c r="E71" s="156" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="388" t="s">
-        <v>433</v>
-      </c>
-      <c r="B72" s="389"/>
+      <c r="A72" s="386" t="s">
+        <v>432</v>
+      </c>
+      <c r="B72" s="387"/>
       <c r="C72" s="24"/>
       <c r="D72" s="149">
         <v>320000</v>
       </c>
       <c r="E72" s="87" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="388" t="s">
-        <v>426</v>
-      </c>
-      <c r="B73" s="389"/>
+      <c r="A73" s="386" t="s">
+        <v>425</v>
+      </c>
+      <c r="B73" s="387"/>
       <c r="C73" s="109"/>
       <c r="D73" s="149">
         <v>1050000</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F73" s="97"/>
     </row>
     <row r="74" spans="1:7" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="388" t="s">
-        <v>427</v>
-      </c>
-      <c r="B74" s="389"/>
+      <c r="A74" s="386" t="s">
+        <v>426</v>
+      </c>
+      <c r="B74" s="387"/>
       <c r="C74" s="109"/>
       <c r="D74" s="149">
         <v>1390000</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="388" t="s">
-        <v>440</v>
-      </c>
-      <c r="B75" s="389"/>
+      <c r="A75" s="386" t="s">
+        <v>439</v>
+      </c>
+      <c r="B75" s="387"/>
       <c r="C75" s="109"/>
       <c r="D75" s="149">
         <v>3000000</v>
       </c>
       <c r="E75" s="156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="388" t="s">
-        <v>417</v>
-      </c>
-      <c r="B76" s="389"/>
+      <c r="A76" s="386" t="s">
+        <v>416</v>
+      </c>
+      <c r="B76" s="387"/>
       <c r="C76" s="109"/>
       <c r="D76" s="149">
         <v>319377.61</v>
       </c>
       <c r="E76" s="96" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="388" t="s">
-        <v>493</v>
-      </c>
-      <c r="B77" s="389"/>
+      <c r="A77" s="386" t="s">
+        <v>492</v>
+      </c>
+      <c r="B77" s="387"/>
       <c r="C77" s="109"/>
       <c r="D77" s="149">
         <v>112180.05</v>
       </c>
       <c r="E77" s="96" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="388" t="s">
-        <v>442</v>
-      </c>
-      <c r="B78" s="389"/>
+      <c r="A78" s="386" t="s">
+        <v>441</v>
+      </c>
+      <c r="B78" s="387"/>
       <c r="C78" s="109"/>
       <c r="D78" s="149">
         <v>73716.19</v>
       </c>
       <c r="E78" s="156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="388" t="s">
-        <v>443</v>
-      </c>
-      <c r="B79" s="389"/>
+      <c r="A79" s="386" t="s">
+        <v>442</v>
+      </c>
+      <c r="B79" s="387"/>
       <c r="C79" s="109"/>
       <c r="D79" s="149">
         <v>588090.9</v>
       </c>
       <c r="E79" s="156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F79" s="97"/>
     </row>
     <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="388" t="s">
-        <v>444</v>
-      </c>
-      <c r="B80" s="389"/>
+      <c r="A80" s="386" t="s">
+        <v>443</v>
+      </c>
+      <c r="B80" s="387"/>
       <c r="C80" s="109"/>
       <c r="D80" s="149">
         <v>54497.599999999999</v>
       </c>
       <c r="E80" s="156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="388" t="s">
-        <v>445</v>
-      </c>
-      <c r="B81" s="389"/>
+      <c r="A81" s="386" t="s">
+        <v>444</v>
+      </c>
+      <c r="B81" s="387"/>
       <c r="C81" s="109"/>
       <c r="D81" s="149">
         <v>160307.04</v>
       </c>
       <c r="E81" s="156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="388" t="s">
-        <v>448</v>
-      </c>
-      <c r="B82" s="389"/>
+      <c r="A82" s="386" t="s">
+        <v>447</v>
+      </c>
+      <c r="B82" s="387"/>
       <c r="C82" s="109"/>
       <c r="D82" s="149">
         <v>12</v>
       </c>
       <c r="E82" s="156" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="388" t="s">
-        <v>390</v>
-      </c>
-      <c r="B83" s="389"/>
+      <c r="A83" s="386" t="s">
+        <v>389</v>
+      </c>
+      <c r="B83" s="387"/>
       <c r="C83" s="109"/>
       <c r="D83" s="149">
         <v>97200</v>
       </c>
       <c r="E83" s="96" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="388" t="s">
-        <v>432</v>
-      </c>
-      <c r="B84" s="389"/>
+      <c r="A84" s="386" t="s">
+        <v>431</v>
+      </c>
+      <c r="B84" s="387"/>
       <c r="C84" s="109"/>
       <c r="D84" s="149">
         <v>146099</v>
       </c>
       <c r="E84" s="96" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="388" t="s">
-        <v>451</v>
-      </c>
-      <c r="B85" s="389"/>
+      <c r="A85" s="386" t="s">
+        <v>450</v>
+      </c>
+      <c r="B85" s="387"/>
       <c r="C85" s="109"/>
       <c r="D85" s="149">
         <v>681000</v>
       </c>
       <c r="E85" s="87" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="388" t="s">
-        <v>388</v>
-      </c>
-      <c r="B86" s="389"/>
+      <c r="A86" s="386" t="s">
+        <v>387</v>
+      </c>
+      <c r="B86" s="387"/>
       <c r="C86" s="109"/>
       <c r="D86" s="149">
         <v>481000</v>
       </c>
       <c r="E86" s="87" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4632,25 +4633,25 @@
       <c r="E88" s="26"/>
     </row>
     <row r="89" spans="1:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="388" t="s">
-        <v>497</v>
-      </c>
-      <c r="B89" s="389"/>
+      <c r="A89" s="386" t="s">
+        <v>496</v>
+      </c>
+      <c r="B89" s="387"/>
       <c r="C89" s="24"/>
       <c r="D89" s="365"/>
       <c r="E89" s="96"/>
     </row>
     <row r="90" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="388" t="s">
-        <v>411</v>
-      </c>
-      <c r="B90" s="389"/>
+      <c r="A90" s="386" t="s">
+        <v>410</v>
+      </c>
+      <c r="B90" s="387"/>
       <c r="C90" s="24"/>
       <c r="D90" s="365">
         <v>1900000</v>
       </c>
       <c r="E90" s="96" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4762,36 +4763,36 @@
       <c r="E101" s="44"/>
     </row>
     <row r="102" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="388" t="s">
-        <v>389</v>
-      </c>
-      <c r="B102" s="389"/>
+      <c r="A102" s="386" t="s">
+        <v>388</v>
+      </c>
+      <c r="B102" s="387"/>
       <c r="C102" s="24"/>
       <c r="D102" s="231">
         <v>452107.07</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="388" t="s">
-        <v>331</v>
-      </c>
-      <c r="B103" s="389"/>
+      <c r="A103" s="386" t="s">
+        <v>330</v>
+      </c>
+      <c r="B103" s="387"/>
       <c r="C103" s="24"/>
       <c r="D103" s="231">
         <v>74126.81</v>
       </c>
       <c r="E103" s="212" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="388" t="s">
-        <v>332</v>
-      </c>
-      <c r="B104" s="389"/>
+      <c r="A104" s="386" t="s">
+        <v>331</v>
+      </c>
+      <c r="B104" s="387"/>
       <c r="C104" s="24"/>
       <c r="D104" s="231">
         <v>74126.81</v>
@@ -4802,10 +4803,10 @@
       </c>
     </row>
     <row r="105" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="388" t="s">
-        <v>333</v>
-      </c>
-      <c r="B105" s="389"/>
+      <c r="A105" s="386" t="s">
+        <v>332</v>
+      </c>
+      <c r="B105" s="387"/>
       <c r="C105" s="24"/>
       <c r="D105" s="231">
         <v>75556.14</v>
@@ -4816,23 +4817,23 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="390" t="s">
-        <v>378</v>
-      </c>
-      <c r="B106" s="391"/>
+      <c r="A106" s="388" t="s">
+        <v>377</v>
+      </c>
+      <c r="B106" s="389"/>
       <c r="C106" s="24"/>
       <c r="D106" s="231">
         <v>1114493.6200000001</v>
       </c>
       <c r="E106" s="87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="390" t="s">
+      <c r="A107" s="388" t="s">
         <v>192</v>
       </c>
-      <c r="B107" s="391"/>
+      <c r="B107" s="389"/>
       <c r="C107" s="24"/>
       <c r="D107" s="231">
         <v>6056.84</v>
@@ -4843,17 +4844,17 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="390" t="s">
-        <v>306</v>
-      </c>
-      <c r="B108" s="391"/>
+      <c r="A108" s="388" t="s">
+        <v>305</v>
+      </c>
+      <c r="B108" s="389"/>
       <c r="C108" s="24"/>
       <c r="D108" s="231"/>
       <c r="E108" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G108" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4885,21 +4886,21 @@
       <c r="E111" s="52"/>
     </row>
     <row r="112" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="390" t="s">
-        <v>396</v>
-      </c>
-      <c r="B112" s="391"/>
+      <c r="A112" s="388" t="s">
+        <v>395</v>
+      </c>
+      <c r="B112" s="389"/>
       <c r="C112" s="24"/>
       <c r="D112" s="385">
         <v>5816279.9100000001</v>
       </c>
       <c r="E112" s="86" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="390"/>
-      <c r="B113" s="391"/>
+      <c r="A113" s="388"/>
+      <c r="B113" s="389"/>
       <c r="C113" s="24"/>
       <c r="D113" s="149"/>
       <c r="E113" s="86"/>
@@ -4966,10 +4967,10 @@
       <c r="E120" s="59"/>
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="415" t="s">
-        <v>401</v>
-      </c>
-      <c r="B121" s="415"/>
+      <c r="A121" s="397" t="s">
+        <v>400</v>
+      </c>
+      <c r="B121" s="397"/>
       <c r="C121" s="24"/>
       <c r="D121" s="231">
         <f>1500871-920000</f>
@@ -4981,10 +4982,10 @@
       </c>
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="388" t="s">
-        <v>403</v>
-      </c>
-      <c r="B122" s="389"/>
+      <c r="A122" s="386" t="s">
+        <v>402</v>
+      </c>
+      <c r="B122" s="387"/>
       <c r="C122" s="109"/>
       <c r="D122" s="231">
         <v>91169.89</v>
@@ -5103,24 +5104,24 @@
       <c r="E133" s="32"/>
     </row>
     <row r="134" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="408" t="s">
-        <v>402</v>
-      </c>
-      <c r="B134" s="409"/>
+      <c r="A134" s="390" t="s">
+        <v>401</v>
+      </c>
+      <c r="B134" s="391"/>
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32"/>
     </row>
     <row r="135" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="410"/>
-      <c r="B135" s="411"/>
+      <c r="A135" s="392"/>
+      <c r="B135" s="393"/>
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32"/>
     </row>
     <row r="136" spans="1:5" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="412"/>
-      <c r="B136" s="413"/>
+      <c r="A136" s="394"/>
+      <c r="B136" s="395"/>
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32"/>
@@ -5154,7 +5155,7 @@
     </row>
     <row r="140" spans="1:5" s="163" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="165" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B140" s="166">
         <v>850000</v>
@@ -5175,7 +5176,7 @@
     </row>
     <row r="142" spans="1:5" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="144" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B142" s="169">
         <f>-B165</f>
@@ -5186,7 +5187,7 @@
     </row>
     <row r="143" spans="1:5" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="144" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B143" s="169">
         <v>-767817</v>
@@ -5196,7 +5197,7 @@
     </row>
     <row r="144" spans="1:5" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="144" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B144" s="169">
         <v>-23703</v>
@@ -5206,7 +5207,7 @@
     </row>
     <row r="145" spans="1:6" s="163" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="144" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B145" s="169">
         <v>-1520000</v>
@@ -5216,7 +5217,7 @@
     </row>
     <row r="146" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="144" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B146" s="169">
         <f>-{43790}</f>
@@ -5227,7 +5228,7 @@
     </row>
     <row r="147" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="144" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B147" s="169">
         <v>-23204</v>
@@ -5237,7 +5238,7 @@
     </row>
     <row r="148" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B148" s="169">
         <v>-23442</v>
@@ -5247,7 +5248,7 @@
     </row>
     <row r="149" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="144" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B149" s="169">
         <v>-23442</v>
@@ -5257,7 +5258,7 @@
     </row>
     <row r="150" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="144" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B150" s="169">
         <v>-750500</v>
@@ -5267,7 +5268,7 @@
     </row>
     <row r="151" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="144" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B151" s="169">
         <f>-28259-29121-48822</f>
@@ -5278,7 +5279,7 @@
     </row>
     <row r="152" spans="1:6" s="163" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="34" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B152" s="169">
         <v>-305367.8</v>
@@ -5288,7 +5289,7 @@
     </row>
     <row r="153" spans="1:6" s="163" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="357" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B153" s="355">
         <v>-1500000</v>
@@ -5298,7 +5299,7 @@
     </row>
     <row r="154" spans="1:6" s="163" customFormat="1" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="357" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B154" s="355">
         <v>-1500000</v>
@@ -5308,7 +5309,7 @@
     </row>
     <row r="155" spans="1:6" s="163" customFormat="1" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="357" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B155" s="355">
         <v>-7500000</v>
@@ -5318,7 +5319,7 @@
     </row>
     <row r="156" spans="1:6" s="163" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="356" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B156" s="355">
         <v>-127445</v>
@@ -5363,7 +5364,7 @@
     </row>
     <row r="160" spans="1:6" s="163" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B160" s="169">
         <f>-E118</f>
@@ -5395,10 +5396,10 @@
       <c r="F162" s="83"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="416" t="s">
-        <v>298</v>
-      </c>
-      <c r="B163" s="417"/>
+      <c r="A163" s="398" t="s">
+        <v>297</v>
+      </c>
+      <c r="B163" s="399"/>
       <c r="C163" s="6"/>
       <c r="D163" s="13"/>
       <c r="E163" s="37"/>
@@ -5407,7 +5408,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="137" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B164" s="138">
         <v>2207004.5940999999</v>
@@ -5419,7 +5420,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="137" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B165" s="219">
         <v>185555</v>
@@ -5460,7 +5461,7 @@
     </row>
     <row r="169" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="153" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B169" s="152">
         <f>B167+B161</f>
@@ -5490,7 +5491,7 @@
     </row>
     <row r="172" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="99" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B172" s="145">
         <v>518026</v>
@@ -5502,7 +5503,7 @@
     </row>
     <row r="173" spans="1:7" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="99" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B173" s="145">
         <v>-57120</v>
@@ -5514,7 +5515,7 @@
     </row>
     <row r="174" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="99" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B174" s="145">
         <v>-46999</v>
@@ -5526,7 +5527,7 @@
     </row>
     <row r="175" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="99" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B175" s="145">
         <v>-7999</v>
@@ -5538,7 +5539,7 @@
     </row>
     <row r="176" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="99" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B176" s="145">
         <v>-51999</v>
@@ -5550,7 +5551,7 @@
     </row>
     <row r="177" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="99" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B177" s="145"/>
       <c r="C177" s="6"/>
@@ -5620,7 +5621,7 @@
     </row>
     <row r="182" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="134" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B182" s="225">
         <v>39090069.299999997</v>
@@ -5670,16 +5671,16 @@
       <c r="F185" s="38"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A186" s="414" t="s">
+      <c r="A186" s="396" t="s">
         <v>17</v>
       </c>
-      <c r="B186" s="414"/>
-      <c r="C186" s="414"/>
+      <c r="B186" s="396"/>
+      <c r="C186" s="396"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A187" s="414"/>
-      <c r="B187" s="414"/>
-      <c r="C187" s="414"/>
+      <c r="A187" s="396"/>
+      <c r="B187" s="396"/>
+      <c r="C187" s="396"/>
     </row>
     <row r="188" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="71"/>
@@ -5706,23 +5707,42 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
     <mergeCell ref="A134:B136"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A186:C187"/>
@@ -5739,42 +5759,23 @@
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A103:B103"/>
     <mergeCell ref="A104:B104"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -5799,9 +5800,8 @@
     <col min="10" max="10" width="6" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="15" width="13.85546875" customWidth="1"/>
     <col min="16" max="16" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="23.42578125" customWidth="1"/>
@@ -5815,27 +5815,27 @@
     <row r="1" spans="1:24" ht="182.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="426" t="s">
-        <v>464</v>
-      </c>
-      <c r="D1" s="427"/>
-      <c r="E1" s="427"/>
-      <c r="F1" s="427"/>
-      <c r="G1" s="427"/>
-      <c r="H1" s="427"/>
-      <c r="I1" s="427"/>
-      <c r="J1" s="427"/>
-      <c r="K1" s="427"/>
-      <c r="L1" s="427"/>
+      <c r="C1" s="431" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="432"/>
+      <c r="E1" s="432"/>
+      <c r="F1" s="432"/>
+      <c r="G1" s="432"/>
+      <c r="H1" s="432"/>
+      <c r="I1" s="432"/>
+      <c r="J1" s="432"/>
+      <c r="K1" s="432"/>
+      <c r="L1" s="432"/>
       <c r="M1" s="155"/>
-      <c r="N1" s="428" t="s">
-        <v>320</v>
-      </c>
-      <c r="O1" s="428"/>
-      <c r="P1" s="423">
+      <c r="N1" s="433" t="s">
+        <v>319</v>
+      </c>
+      <c r="O1" s="433"/>
+      <c r="P1" s="428">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="423"/>
+      <c r="Q1" s="428"/>
       <c r="R1" s="184"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -5849,35 +5849,35 @@
     <row r="2" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="425" t="s">
+      <c r="C2" s="430" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="425"/>
-      <c r="E2" s="425"/>
+      <c r="D2" s="430"/>
+      <c r="E2" s="430"/>
       <c r="F2" s="155"/>
-      <c r="G2" s="422">
+      <c r="G2" s="425">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="422"/>
+      <c r="H2" s="425"/>
       <c r="I2" s="155" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J2" s="155"/>
-      <c r="K2" s="422">
+      <c r="K2" s="425">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="422"/>
+      <c r="L2" s="425"/>
       <c r="M2" s="361"/>
       <c r="N2" s="362" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O2" s="361"/>
-      <c r="P2" s="424">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="424"/>
+      <c r="P2" s="429">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="429"/>
       <c r="R2" s="185"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -5889,112 +5889,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="76.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="433" t="str">
+      <c r="A3" s="438" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  16/03, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="434"/>
-      <c r="C3" s="434"/>
-      <c r="D3" s="434"/>
-      <c r="E3" s="434"/>
-      <c r="F3" s="434"/>
-      <c r="G3" s="434"/>
-      <c r="H3" s="434"/>
-      <c r="I3" s="434"/>
-      <c r="J3" s="434"/>
-      <c r="K3" s="434"/>
-      <c r="L3" s="434"/>
-      <c r="M3" s="434"/>
-      <c r="N3" s="434"/>
-      <c r="O3" s="434"/>
-      <c r="P3" s="434"/>
-      <c r="Q3" s="434"/>
-      <c r="R3" s="434"/>
-      <c r="S3" s="434"/>
-      <c r="T3" s="435"/>
+      <c r="B3" s="439"/>
+      <c r="C3" s="439"/>
+      <c r="D3" s="439"/>
+      <c r="E3" s="439"/>
+      <c r="F3" s="439"/>
+      <c r="G3" s="439"/>
+      <c r="H3" s="439"/>
+      <c r="I3" s="439"/>
+      <c r="J3" s="439"/>
+      <c r="K3" s="439"/>
+      <c r="L3" s="439"/>
+      <c r="M3" s="439"/>
+      <c r="N3" s="439"/>
+      <c r="O3" s="439"/>
+      <c r="P3" s="439"/>
+      <c r="Q3" s="439"/>
+      <c r="R3" s="439"/>
+      <c r="S3" s="439"/>
+      <c r="T3" s="440"/>
       <c r="X3" s="40"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="436" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="438" t="s">
+      <c r="A4" s="441" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="443" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="438" t="s">
+      <c r="C4" s="443" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="438" t="s">
+      <c r="D4" s="443" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="418" t="s">
+      <c r="E4" s="426" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="438" t="s">
+      <c r="F4" s="443" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="440" t="s">
+      <c r="G4" s="445" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="418" t="s">
+      <c r="H4" s="426" t="s">
         <v>235</v>
       </c>
-      <c r="I4" s="418" t="s">
+      <c r="I4" s="426" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="418"/>
-      <c r="K4" s="418" t="s">
+      <c r="J4" s="426"/>
+      <c r="K4" s="426" t="s">
         <v>185</v>
       </c>
-      <c r="L4" s="418" t="s">
+      <c r="L4" s="426" t="s">
         <v>148</v>
       </c>
-      <c r="M4" s="418" t="s">
+      <c r="M4" s="426" t="s">
         <v>187</v>
       </c>
-      <c r="N4" s="418" t="s">
+      <c r="N4" s="426" t="s">
         <v>186</v>
       </c>
-      <c r="O4" s="418" t="s">
-        <v>261</v>
-      </c>
-      <c r="P4" s="429" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q4" s="430"/>
-      <c r="R4" s="429" t="s">
-        <v>326</v>
-      </c>
-      <c r="S4" s="430"/>
-      <c r="T4" s="418" t="s">
-        <v>263</v>
+      <c r="O4" s="426" t="s">
+        <v>497</v>
+      </c>
+      <c r="P4" s="434" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q4" s="435"/>
+      <c r="R4" s="434" t="s">
+        <v>325</v>
+      </c>
+      <c r="S4" s="435"/>
+      <c r="T4" s="426" t="s">
+        <v>262</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="437"/>
-      <c r="B5" s="439"/>
-      <c r="C5" s="439"/>
-      <c r="D5" s="439"/>
-      <c r="E5" s="419"/>
-      <c r="F5" s="439"/>
-      <c r="G5" s="441"/>
-      <c r="H5" s="419"/>
-      <c r="I5" s="419"/>
-      <c r="J5" s="419"/>
-      <c r="K5" s="419"/>
-      <c r="L5" s="419"/>
-      <c r="M5" s="419"/>
-      <c r="N5" s="419"/>
-      <c r="O5" s="419"/>
-      <c r="P5" s="431" t="str">
+      <c r="A5" s="442"/>
+      <c r="B5" s="444"/>
+      <c r="C5" s="444"/>
+      <c r="D5" s="444"/>
+      <c r="E5" s="427"/>
+      <c r="F5" s="444"/>
+      <c r="G5" s="446"/>
+      <c r="H5" s="427"/>
+      <c r="I5" s="427"/>
+      <c r="J5" s="427"/>
+      <c r="K5" s="427"/>
+      <c r="L5" s="427"/>
+      <c r="M5" s="427"/>
+      <c r="N5" s="427"/>
+      <c r="O5" s="427"/>
+      <c r="P5" s="436" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  16/03</v>
       </c>
-      <c r="Q5" s="432"/>
-      <c r="R5" s="431"/>
-      <c r="S5" s="432"/>
-      <c r="T5" s="419"/>
+      <c r="Q5" s="437"/>
+      <c r="R5" s="436"/>
+      <c r="S5" s="437"/>
+      <c r="T5" s="427"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="204"/>
@@ -6043,11 +6043,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="209"/>
-      <c r="P6" s="420">
+      <c r="P6" s="447">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>1518529.01</v>
       </c>
-      <c r="Q6" s="420"/>
+      <c r="Q6" s="447"/>
       <c r="R6" s="363">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>1564586.01</v>
@@ -6112,11 +6112,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="74"/>
-      <c r="P7" s="421">
+      <c r="P7" s="418">
         <f t="shared" si="2"/>
         <v>1542558.02</v>
       </c>
-      <c r="Q7" s="421"/>
+      <c r="Q7" s="418"/>
       <c r="R7" s="363">
         <f t="shared" si="3"/>
         <v>1589344.02</v>
@@ -6180,11 +6180,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="74"/>
-      <c r="P8" s="421">
+      <c r="P8" s="418">
         <f t="shared" si="2"/>
         <v>736705.03</v>
       </c>
-      <c r="Q8" s="421"/>
+      <c r="Q8" s="418"/>
       <c r="R8" s="363">
         <f t="shared" si="3"/>
         <v>759049.03</v>
@@ -6249,11 +6249,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="74"/>
-      <c r="P9" s="421">
+      <c r="P9" s="418">
         <f t="shared" si="2"/>
         <v>3222835.04</v>
       </c>
-      <c r="Q9" s="421"/>
+      <c r="Q9" s="418"/>
       <c r="R9" s="363">
         <f t="shared" si="3"/>
         <v>3320584.04</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="U9" s="135"/>
       <c r="V9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6321,11 +6321,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="74"/>
-      <c r="P10" s="421">
+      <c r="P10" s="418">
         <f t="shared" si="2"/>
         <v>744528.05</v>
       </c>
-      <c r="Q10" s="421"/>
+      <c r="Q10" s="418"/>
       <c r="R10" s="363">
         <f t="shared" si="3"/>
         <v>767110.05</v>
@@ -6391,11 +6391,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="74"/>
-      <c r="P11" s="421">
+      <c r="P11" s="418">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="421"/>
+      <c r="Q11" s="418"/>
       <c r="R11" s="363">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6462,11 +6462,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="74"/>
-      <c r="P12" s="421">
+      <c r="P12" s="418">
         <f t="shared" si="2"/>
         <v>744299.07</v>
       </c>
-      <c r="Q12" s="421"/>
+      <c r="Q12" s="418"/>
       <c r="R12" s="363">
         <f t="shared" si="3"/>
         <v>766874.07</v>
@@ -6533,11 +6533,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="74"/>
-      <c r="P13" s="421">
+      <c r="P13" s="418">
         <f t="shared" si="2"/>
         <v>744514.08</v>
       </c>
-      <c r="Q13" s="421"/>
+      <c r="Q13" s="418"/>
       <c r="R13" s="363">
         <f t="shared" si="3"/>
         <v>767095.08</v>
@@ -6551,7 +6551,7 @@
         <v>8</v>
       </c>
       <c r="U13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6595,21 +6595,21 @@
         <v>202702.7028</v>
       </c>
       <c r="M14" s="74">
-        <v>0</v>
+        <v>75836</v>
       </c>
       <c r="N14" s="74">
         <f>I14</f>
         <v>379177.030424</v>
       </c>
       <c r="O14" s="74"/>
-      <c r="P14" s="421">
+      <c r="P14" s="418">
         <f t="shared" si="2"/>
-        <v>3509954.09</v>
-      </c>
-      <c r="Q14" s="421"/>
+        <v>3585790.09</v>
+      </c>
+      <c r="Q14" s="418"/>
       <c r="R14" s="363">
         <f t="shared" si="3"/>
-        <v>3616411.09</v>
+        <v>3694547.09</v>
       </c>
       <c r="S14" s="13">
         <f t="shared" si="4"/>
@@ -6670,11 +6670,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="74"/>
-      <c r="P15" s="421">
+      <c r="P15" s="418">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="421"/>
+      <c r="Q15" s="418"/>
       <c r="R15" s="363">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -6740,11 +6740,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="36"/>
-      <c r="P16" s="421">
+      <c r="P16" s="418">
         <f t="shared" si="2"/>
         <v>744528.11</v>
       </c>
-      <c r="Q16" s="421"/>
+      <c r="Q16" s="418"/>
       <c r="R16" s="363">
         <f t="shared" si="3"/>
         <v>767110.11</v>
@@ -6758,7 +6758,7 @@
         <v>11</v>
       </c>
       <c r="U16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6808,11 +6808,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="74"/>
-      <c r="P17" s="421">
+      <c r="P17" s="418">
         <f t="shared" si="2"/>
         <v>4420303.12</v>
       </c>
-      <c r="Q17" s="421"/>
+      <c r="Q17" s="418"/>
       <c r="R17" s="363">
         <f t="shared" si="3"/>
         <v>4554371.12</v>
@@ -6876,15 +6876,17 @@
         <v>0</v>
       </c>
       <c r="N18" s="74"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="421">
+      <c r="O18" s="74">
+        <v>91169.89</v>
+      </c>
+      <c r="P18" s="418">
         <f t="shared" si="2"/>
-        <v>759748.13</v>
-      </c>
-      <c r="Q18" s="421"/>
+        <v>850918.13</v>
+      </c>
+      <c r="Q18" s="418"/>
       <c r="R18" s="363">
         <f t="shared" si="3"/>
-        <v>782791.13</v>
+        <v>876726.13</v>
       </c>
       <c r="S18" s="13">
         <f t="shared" si="4"/>
@@ -6945,11 +6947,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="74"/>
-      <c r="P19" s="421">
+      <c r="P19" s="418">
         <f t="shared" si="2"/>
         <v>720435.14</v>
       </c>
-      <c r="Q19" s="421"/>
+      <c r="Q19" s="418"/>
       <c r="R19" s="363">
         <f t="shared" si="3"/>
         <v>742286.14</v>
@@ -6963,7 +6965,7 @@
         <v>14</v>
       </c>
       <c r="U19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6973,7 +6975,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D20" s="80">
         <v>4.4000000000000003E-3</v>
@@ -7016,11 +7018,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="74"/>
-      <c r="P20" s="421">
+      <c r="P20" s="418">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="421"/>
+      <c r="Q20" s="418"/>
       <c r="R20" s="363">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7034,7 +7036,7 @@
         <v>15</v>
       </c>
       <c r="U20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7085,11 +7087,11 @@
       </c>
       <c r="N21" s="74"/>
       <c r="O21" s="74"/>
-      <c r="P21" s="421">
+      <c r="P21" s="418">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="421"/>
+      <c r="Q21" s="418"/>
       <c r="R21" s="363">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7150,11 +7152,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="74"/>
-      <c r="P22" s="421">
+      <c r="P22" s="418">
         <f t="shared" si="2"/>
         <v>2350329.17</v>
       </c>
-      <c r="Q22" s="421"/>
+      <c r="Q22" s="418"/>
       <c r="R22" s="363">
         <f t="shared" si="3"/>
         <v>2421615.17</v>
@@ -7220,11 +7222,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="88"/>
-      <c r="P23" s="421">
+      <c r="P23" s="418">
         <f t="shared" si="2"/>
         <v>736705.18</v>
       </c>
-      <c r="Q23" s="421"/>
+      <c r="Q23" s="418"/>
       <c r="R23" s="363">
         <f t="shared" si="3"/>
         <v>759049.18</v>
@@ -7238,7 +7240,7 @@
         <v>18</v>
       </c>
       <c r="U23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7290,11 +7292,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="88"/>
-      <c r="P24" s="421">
+      <c r="P24" s="418">
         <f t="shared" si="2"/>
         <v>744528.19</v>
       </c>
-      <c r="Q24" s="421"/>
+      <c r="Q24" s="418"/>
       <c r="R24" s="363">
         <f t="shared" si="3"/>
         <v>767110.19</v>
@@ -7357,11 +7359,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="88"/>
-      <c r="P25" s="421">
+      <c r="P25" s="418">
         <f t="shared" si="2"/>
         <v>744528.2</v>
       </c>
-      <c r="Q25" s="421"/>
+      <c r="Q25" s="418"/>
       <c r="R25" s="363">
         <f t="shared" si="3"/>
         <v>767110.2</v>
@@ -7422,11 +7424,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="88"/>
-      <c r="P26" s="421">
+      <c r="P26" s="418">
         <f t="shared" si="2"/>
         <v>1559335.21</v>
       </c>
-      <c r="Q26" s="421"/>
+      <c r="Q26" s="418"/>
       <c r="R26" s="363">
         <f t="shared" si="3"/>
         <v>1606630.21</v>
@@ -7495,11 +7497,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="88"/>
-      <c r="P27" s="421">
+      <c r="P27" s="418">
         <f t="shared" si="2"/>
         <v>744528.22</v>
       </c>
-      <c r="Q27" s="421"/>
+      <c r="Q27" s="418"/>
       <c r="R27" s="363">
         <f t="shared" si="3"/>
         <v>767110.22</v>
@@ -7513,7 +7515,7 @@
         <v>22</v>
       </c>
       <c r="U27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7565,11 +7567,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="88"/>
-      <c r="P28" s="421">
+      <c r="P28" s="418">
         <f t="shared" si="2"/>
         <v>767815.23</v>
       </c>
-      <c r="Q28" s="421"/>
+      <c r="Q28" s="418"/>
       <c r="R28" s="363">
         <f t="shared" si="3"/>
         <v>791103.23</v>
@@ -7583,7 +7585,7 @@
         <v>23</v>
       </c>
       <c r="U28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7635,11 +7637,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="88"/>
-      <c r="P29" s="421">
+      <c r="P29" s="418">
         <f t="shared" si="2"/>
         <v>744528.24</v>
       </c>
-      <c r="Q29" s="421"/>
+      <c r="Q29" s="418"/>
       <c r="R29" s="363">
         <f t="shared" si="3"/>
         <v>767110.24</v>
@@ -7653,7 +7655,7 @@
         <v>24</v>
       </c>
       <c r="U29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7706,11 +7708,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="88"/>
-      <c r="P30" s="421">
+      <c r="P30" s="418">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="421"/>
+      <c r="Q30" s="418"/>
       <c r="R30" s="363">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -7724,7 +7726,7 @@
         <v>25</v>
       </c>
       <c r="V30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7776,11 +7778,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="88"/>
-      <c r="P31" s="421">
+      <c r="P31" s="418">
         <f t="shared" si="2"/>
         <v>752356.26</v>
       </c>
-      <c r="Q31" s="421"/>
+      <c r="Q31" s="418"/>
       <c r="R31" s="363">
         <f t="shared" si="3"/>
         <v>775175.26</v>
@@ -7847,11 +7849,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="88"/>
-      <c r="P32" s="421">
+      <c r="P32" s="418">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="421"/>
+      <c r="Q32" s="418"/>
       <c r="R32" s="363">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -7917,11 +7919,11 @@
         <f>I33/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P33" s="421">
+      <c r="P33" s="418">
         <f t="shared" si="2"/>
         <v>923797.28</v>
       </c>
-      <c r="Q33" s="421"/>
+      <c r="Q33" s="418"/>
       <c r="R33" s="363">
         <f t="shared" si="3"/>
         <v>951816.28</v>
@@ -7935,7 +7937,7 @@
         <v>28</v>
       </c>
       <c r="U33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7987,11 +7989,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="88"/>
-      <c r="P34" s="421">
+      <c r="P34" s="418">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="421"/>
+      <c r="Q34" s="418"/>
       <c r="R34" s="363">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8058,11 +8060,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="88"/>
-      <c r="P35" s="421">
+      <c r="P35" s="418">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="421"/>
+      <c r="Q35" s="418"/>
       <c r="R35" s="363">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8126,11 +8128,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="88"/>
-      <c r="P36" s="421">
+      <c r="P36" s="418">
         <f t="shared" si="2"/>
         <v>2643433.31</v>
       </c>
-      <c r="Q36" s="421"/>
+      <c r="Q36" s="418"/>
       <c r="R36" s="363">
         <f t="shared" si="3"/>
         <v>2723609.31</v>
@@ -8144,7 +8146,7 @@
         <v>31</v>
       </c>
       <c r="U36" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8197,11 +8199,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="88"/>
-      <c r="P37" s="421">
+      <c r="P37" s="418">
         <f t="shared" si="2"/>
         <v>573720.31999999995</v>
       </c>
-      <c r="Q37" s="421"/>
+      <c r="Q37" s="418"/>
       <c r="R37" s="363">
         <f t="shared" si="3"/>
         <v>591121.31999999995</v>
@@ -8264,11 +8266,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="88"/>
-      <c r="P38" s="421">
+      <c r="P38" s="418">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="421"/>
+      <c r="Q38" s="418"/>
       <c r="R38" s="363">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8328,11 +8330,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="88"/>
-      <c r="P39" s="421">
+      <c r="P39" s="418">
         <f t="shared" si="14"/>
         <v>2473411.34</v>
       </c>
-      <c r="Q39" s="421"/>
+      <c r="Q39" s="418"/>
       <c r="R39" s="363">
         <f t="shared" si="15"/>
         <v>2548430.34</v>
@@ -8346,7 +8348,7 @@
         <v>34</v>
       </c>
       <c r="U39" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -8399,11 +8401,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="88"/>
-      <c r="P40" s="421">
+      <c r="P40" s="418">
         <f t="shared" si="14"/>
         <v>736704.35</v>
       </c>
-      <c r="Q40" s="421"/>
+      <c r="Q40" s="418"/>
       <c r="R40" s="363">
         <f t="shared" si="15"/>
         <v>759049.35</v>
@@ -8471,11 +8473,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="88"/>
-      <c r="P41" s="421">
+      <c r="P41" s="418">
         <f t="shared" si="14"/>
         <v>748020.36</v>
       </c>
-      <c r="Q41" s="421"/>
+      <c r="Q41" s="418"/>
       <c r="R41" s="363">
         <f t="shared" si="15"/>
         <v>770708.36</v>
@@ -8538,11 +8540,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="88"/>
-      <c r="P42" s="421">
+      <c r="P42" s="418">
         <f t="shared" si="14"/>
         <v>1526106.37</v>
       </c>
-      <c r="Q42" s="421"/>
+      <c r="Q42" s="418"/>
       <c r="R42" s="363">
         <f t="shared" si="15"/>
         <v>1572393.37</v>
@@ -8608,11 +8610,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="88"/>
-      <c r="P43" s="421">
+      <c r="P43" s="418">
         <f t="shared" si="14"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="421"/>
+      <c r="Q43" s="418"/>
       <c r="R43" s="363">
         <f t="shared" si="15"/>
         <v>774480.38</v>
@@ -8680,11 +8682,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="88"/>
-      <c r="P44" s="421">
+      <c r="P44" s="418">
         <f t="shared" si="14"/>
         <v>872758.39</v>
       </c>
-      <c r="Q44" s="421"/>
+      <c r="Q44" s="418"/>
       <c r="R44" s="363">
         <f t="shared" si="15"/>
         <v>899229.39</v>
@@ -8751,11 +8753,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="88"/>
-      <c r="P45" s="421">
+      <c r="P45" s="418">
         <f t="shared" si="14"/>
         <v>728593.4</v>
       </c>
-      <c r="Q45" s="421"/>
+      <c r="Q45" s="418"/>
       <c r="R45" s="363">
         <f t="shared" si="15"/>
         <v>750692.4</v>
@@ -8819,11 +8821,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="88"/>
-      <c r="P46" s="421">
+      <c r="P46" s="418">
         <f t="shared" si="14"/>
         <v>728882.41</v>
       </c>
-      <c r="Q46" s="421"/>
+      <c r="Q46" s="418"/>
       <c r="R46" s="363">
         <f t="shared" si="15"/>
         <v>750989.41</v>
@@ -8890,11 +8892,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="88"/>
-      <c r="P47" s="421">
+      <c r="P47" s="418">
         <f t="shared" si="14"/>
         <v>728882.42</v>
       </c>
-      <c r="Q47" s="421"/>
+      <c r="Q47" s="418"/>
       <c r="R47" s="363">
         <f t="shared" si="15"/>
         <v>750989.42</v>
@@ -8908,7 +8910,7 @@
         <v>42</v>
       </c>
       <c r="U47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8962,11 +8964,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="88"/>
-      <c r="P48" s="421">
+      <c r="P48" s="418">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="421"/>
+      <c r="Q48" s="418"/>
       <c r="R48" s="363">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9030,11 +9032,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="88"/>
-      <c r="P49" s="421">
+      <c r="P49" s="418">
         <f t="shared" si="14"/>
         <v>895905.44</v>
       </c>
-      <c r="Q49" s="421"/>
+      <c r="Q49" s="418"/>
       <c r="R49" s="363">
         <f t="shared" si="15"/>
         <v>923078.44</v>
@@ -9048,7 +9050,7 @@
         <v>44</v>
       </c>
       <c r="U49" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9100,11 +9102,11 @@
         <v>395312.22320800001</v>
       </c>
       <c r="O50" s="88"/>
-      <c r="P50" s="421">
+      <c r="P50" s="418">
         <f t="shared" si="14"/>
         <v>1987415.45</v>
       </c>
-      <c r="Q50" s="421"/>
+      <c r="Q50" s="418"/>
       <c r="R50" s="363">
         <f t="shared" si="15"/>
         <v>2047694.45</v>
@@ -9168,11 +9170,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="88"/>
-      <c r="P51" s="421">
+      <c r="P51" s="418">
         <f t="shared" si="14"/>
         <v>1451367.46</v>
       </c>
-      <c r="Q51" s="421"/>
+      <c r="Q51" s="418"/>
       <c r="R51" s="363">
         <f t="shared" si="15"/>
         <v>1495387.46</v>
@@ -9237,11 +9239,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="88"/>
-      <c r="P52" s="421">
+      <c r="P52" s="418">
         <f t="shared" si="14"/>
         <v>3158183.47</v>
       </c>
-      <c r="Q52" s="421"/>
+      <c r="Q52" s="418"/>
       <c r="R52" s="363">
         <f t="shared" si="15"/>
         <v>3253971.47</v>
@@ -9255,7 +9257,7 @@
         <v>47</v>
       </c>
       <c r="U52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9302,7 +9304,7 @@
         <v>202702.7028</v>
       </c>
       <c r="M53" s="74">
-        <v>0</v>
+        <v>72609</v>
       </c>
       <c r="N53" s="74">
         <f>(I53)</f>
@@ -9312,14 +9314,14 @@
         <f>I53*0.1</f>
         <v>36304.183764000001</v>
       </c>
-      <c r="P53" s="421">
+      <c r="P53" s="418">
         <f t="shared" si="14"/>
-        <v>1053230.48</v>
-      </c>
-      <c r="Q53" s="421"/>
+        <v>1125839.48</v>
+      </c>
+      <c r="Q53" s="418"/>
       <c r="R53" s="363">
         <f t="shared" si="15"/>
-        <v>1085175.48</v>
+        <v>1159986.48</v>
       </c>
       <c r="S53" s="13">
         <f t="shared" si="16"/>
@@ -9381,11 +9383,11 @@
         <v>0</v>
       </c>
       <c r="O54" s="88"/>
-      <c r="P54" s="421">
+      <c r="P54" s="418">
         <f t="shared" si="14"/>
         <v>728882.49</v>
       </c>
-      <c r="Q54" s="421"/>
+      <c r="Q54" s="418"/>
       <c r="R54" s="363">
         <f t="shared" si="15"/>
         <v>750989.49</v>
@@ -9452,11 +9454,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="88"/>
-      <c r="P55" s="421">
+      <c r="P55" s="418">
         <f t="shared" si="14"/>
         <v>728882.5</v>
       </c>
-      <c r="Q55" s="421"/>
+      <c r="Q55" s="418"/>
       <c r="R55" s="363">
         <f t="shared" si="15"/>
         <v>750990.5</v>
@@ -9470,7 +9472,7 @@
         <v>50</v>
       </c>
       <c r="U55" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9515,21 +9517,21 @@
         <v>202702.7028</v>
       </c>
       <c r="M56" s="74">
-        <v>0</v>
+        <v>72609</v>
       </c>
       <c r="N56" s="74">
         <f>(I56)</f>
         <v>363041.83763999998</v>
       </c>
       <c r="O56" s="88"/>
-      <c r="P56" s="421">
+      <c r="P56" s="418">
         <f t="shared" si="14"/>
-        <v>2172571.5099999998</v>
-      </c>
-      <c r="Q56" s="421"/>
+        <v>2245180.5099999998</v>
+      </c>
+      <c r="Q56" s="418"/>
       <c r="R56" s="363">
         <f t="shared" si="15"/>
-        <v>2238466.5099999998</v>
+        <v>2313277.5099999998</v>
       </c>
       <c r="S56" s="13">
         <f t="shared" si="16"/>
@@ -9594,11 +9596,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="88"/>
-      <c r="P57" s="421">
+      <c r="P57" s="418">
         <f t="shared" si="14"/>
         <v>712950.52</v>
       </c>
-      <c r="Q57" s="421"/>
+      <c r="Q57" s="418"/>
       <c r="R57" s="363">
         <f t="shared" si="15"/>
         <v>734574.52</v>
@@ -9612,7 +9614,7 @@
         <v>52</v>
       </c>
       <c r="U57" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9663,11 +9665,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="88"/>
-      <c r="P58" s="421">
+      <c r="P58" s="418">
         <f t="shared" si="14"/>
         <v>3399941.53</v>
       </c>
-      <c r="Q58" s="421"/>
+      <c r="Q58" s="418"/>
       <c r="R58" s="363">
         <f t="shared" si="15"/>
         <v>3503062.53</v>
@@ -9732,11 +9734,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="88"/>
-      <c r="P59" s="421">
+      <c r="P59" s="418">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="421"/>
+      <c r="Q59" s="418"/>
       <c r="R59" s="363">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -9803,11 +9805,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="88"/>
-      <c r="P60" s="421">
+      <c r="P60" s="418">
         <f t="shared" si="14"/>
         <v>728882.55</v>
       </c>
-      <c r="Q60" s="421"/>
+      <c r="Q60" s="418"/>
       <c r="R60" s="363">
         <f t="shared" si="15"/>
         <v>750990.55</v>
@@ -9821,7 +9823,7 @@
         <v>55</v>
       </c>
       <c r="U60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9868,7 +9870,7 @@
         <v>202702.7028</v>
       </c>
       <c r="M61" s="74">
-        <v>0</v>
+        <v>72609</v>
       </c>
       <c r="N61" s="74">
         <f>(I61)</f>
@@ -9878,14 +9880,14 @@
         <f>(I61*0.1)*2</f>
         <v>72608.367528000002</v>
       </c>
-      <c r="P61" s="421">
+      <c r="P61" s="418">
         <f t="shared" si="14"/>
-        <v>1152903.56</v>
-      </c>
-      <c r="Q61" s="421"/>
+        <v>1225512.56</v>
+      </c>
+      <c r="Q61" s="418"/>
       <c r="R61" s="363">
         <f t="shared" si="15"/>
-        <v>1187871.56</v>
+        <v>1262682.56</v>
       </c>
       <c r="S61" s="13">
         <f t="shared" si="16"/>
@@ -9947,11 +9949,11 @@
         <v>0</v>
       </c>
       <c r="O62" s="88"/>
-      <c r="P62" s="421">
+      <c r="P62" s="418">
         <f t="shared" si="14"/>
         <v>1526567.57</v>
       </c>
-      <c r="Q62" s="421"/>
+      <c r="Q62" s="418"/>
       <c r="R62" s="363">
         <f t="shared" si="15"/>
         <v>1572868.57</v>
@@ -10015,11 +10017,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="88"/>
-      <c r="P63" s="421">
+      <c r="P63" s="418">
         <f t="shared" si="14"/>
         <v>728882.58</v>
       </c>
-      <c r="Q63" s="421"/>
+      <c r="Q63" s="418"/>
       <c r="R63" s="363">
         <f t="shared" si="15"/>
         <v>750990.58</v>
@@ -10083,11 +10085,11 @@
         <v>0</v>
       </c>
       <c r="O64" s="88"/>
-      <c r="P64" s="421">
+      <c r="P64" s="418">
         <f t="shared" si="14"/>
         <v>691468.59</v>
       </c>
-      <c r="Q64" s="421"/>
+      <c r="Q64" s="418"/>
       <c r="R64" s="363">
         <f t="shared" si="15"/>
         <v>712441.59</v>
@@ -10101,7 +10103,7 @@
         <v>59</v>
       </c>
       <c r="U64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10154,11 +10156,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="88"/>
-      <c r="P65" s="421">
+      <c r="P65" s="418">
         <f t="shared" si="14"/>
         <v>750827.6</v>
       </c>
-      <c r="Q65" s="421"/>
+      <c r="Q65" s="418"/>
       <c r="R65" s="363">
         <f t="shared" si="15"/>
         <v>773600.6</v>
@@ -10226,11 +10228,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="88"/>
-      <c r="P66" s="421">
+      <c r="P66" s="418">
         <f t="shared" si="14"/>
         <v>751038.61</v>
       </c>
-      <c r="Q66" s="421"/>
+      <c r="Q66" s="418"/>
       <c r="R66" s="363">
         <f t="shared" si="15"/>
         <v>773818.61</v>
@@ -10292,7 +10294,7 @@
         <v>202702.7028</v>
       </c>
       <c r="M67" s="74">
-        <v>0</v>
+        <v>66155</v>
       </c>
       <c r="N67" s="74">
         <v>0</v>
@@ -10301,14 +10303,14 @@
         <f>I67/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P67" s="421">
+      <c r="P67" s="418">
         <f t="shared" si="14"/>
-        <v>855140.62</v>
-      </c>
-      <c r="Q67" s="421"/>
+        <v>921295.62</v>
+      </c>
+      <c r="Q67" s="418"/>
       <c r="R67" s="363">
         <f t="shared" si="15"/>
-        <v>881077.62</v>
+        <v>949239.62</v>
       </c>
       <c r="S67" s="13">
         <f t="shared" si="16"/>
@@ -10370,11 +10372,11 @@
         <v>0</v>
       </c>
       <c r="O68" s="88"/>
-      <c r="P68" s="421">
+      <c r="P68" s="418">
         <f t="shared" si="14"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="421"/>
+      <c r="Q68" s="418"/>
       <c r="R68" s="363">
         <f t="shared" si="15"/>
         <v>774480.63</v>
@@ -10442,11 +10444,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="88"/>
-      <c r="P69" s="421">
+      <c r="P69" s="418">
         <f t="shared" si="14"/>
         <v>706943.64</v>
       </c>
-      <c r="Q69" s="421"/>
+      <c r="Q69" s="418"/>
       <c r="R69" s="363">
         <f t="shared" si="15"/>
         <v>728385.64</v>
@@ -10514,11 +10516,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="88"/>
-      <c r="P70" s="421">
+      <c r="P70" s="418">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="421"/>
+      <c r="Q70" s="418"/>
       <c r="R70" s="363">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10582,11 +10584,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="88"/>
-      <c r="P71" s="421">
+      <c r="P71" s="418">
         <f t="shared" si="22"/>
         <v>728882.66</v>
       </c>
-      <c r="Q71" s="421"/>
+      <c r="Q71" s="418"/>
       <c r="R71" s="363">
         <f t="shared" si="23"/>
         <v>750990.66</v>
@@ -10651,11 +10653,11 @@
         <v>0</v>
       </c>
       <c r="O72" s="88"/>
-      <c r="P72" s="421">
+      <c r="P72" s="418">
         <f t="shared" si="22"/>
         <v>1518273.67</v>
       </c>
-      <c r="Q72" s="421"/>
+      <c r="Q72" s="418"/>
       <c r="R72" s="363">
         <f t="shared" si="23"/>
         <v>1564323.67</v>
@@ -10669,7 +10671,7 @@
         <v>67</v>
       </c>
       <c r="U72" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10713,21 +10715,21 @@
         <v>202702.7028</v>
       </c>
       <c r="M73" s="74">
-        <v>0</v>
+        <v>72609</v>
       </c>
       <c r="N73" s="74">
         <f>I73</f>
         <v>363041.83763999998</v>
       </c>
       <c r="O73" s="88"/>
-      <c r="P73" s="421">
+      <c r="P73" s="418">
         <f t="shared" si="22"/>
-        <v>4486656.68</v>
-      </c>
-      <c r="Q73" s="421"/>
+        <v>4559265.68</v>
+      </c>
+      <c r="Q73" s="418"/>
       <c r="R73" s="363">
         <f t="shared" si="23"/>
-        <v>4622737.68</v>
+        <v>4697548.68</v>
       </c>
       <c r="S73" s="13">
         <f t="shared" si="24"/>
@@ -10787,11 +10789,11 @@
         <v>0</v>
       </c>
       <c r="O74" s="36"/>
-      <c r="P74" s="421">
+      <c r="P74" s="418">
         <f t="shared" si="22"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="421"/>
+      <c r="Q74" s="418"/>
       <c r="R74" s="363">
         <f t="shared" si="23"/>
         <v>678447.69</v>
@@ -10857,11 +10859,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="88"/>
-      <c r="P75" s="421">
+      <c r="P75" s="418">
         <f t="shared" si="22"/>
         <v>1372860.7</v>
       </c>
-      <c r="Q75" s="421"/>
+      <c r="Q75" s="418"/>
       <c r="R75" s="363">
         <f t="shared" si="23"/>
         <v>1414500.7</v>
@@ -10925,11 +10927,11 @@
         <v>0</v>
       </c>
       <c r="O76" s="88"/>
-      <c r="P76" s="421">
+      <c r="P76" s="418">
         <f t="shared" si="22"/>
         <v>4028209.71</v>
       </c>
-      <c r="Q76" s="421"/>
+      <c r="Q76" s="418"/>
       <c r="R76" s="363">
         <f t="shared" si="23"/>
         <v>4150385.71</v>
@@ -10943,7 +10945,7 @@
         <v>71</v>
       </c>
       <c r="U76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10995,11 +10997,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="88"/>
-      <c r="P77" s="421">
+      <c r="P77" s="418">
         <f t="shared" si="22"/>
         <v>690051.72</v>
       </c>
-      <c r="Q77" s="421"/>
+      <c r="Q77" s="418"/>
       <c r="R77" s="363">
         <f t="shared" si="23"/>
         <v>710981.72</v>
@@ -11066,11 +11068,11 @@
         <v>0</v>
       </c>
       <c r="O78" s="88"/>
-      <c r="P78" s="421">
+      <c r="P78" s="418">
         <f t="shared" si="22"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="421"/>
+      <c r="Q78" s="418"/>
       <c r="R78" s="363">
         <f t="shared" si="23"/>
         <v>732919.73</v>
@@ -11134,11 +11136,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="88"/>
-      <c r="P79" s="421">
+      <c r="P79" s="418">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="421"/>
+      <c r="Q79" s="418"/>
       <c r="R79" s="363">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11205,11 +11207,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="421">
+      <c r="P80" s="418">
         <f t="shared" si="22"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="421"/>
+      <c r="Q80" s="418"/>
       <c r="R80" s="363">
         <f t="shared" si="23"/>
         <v>911633.75</v>
@@ -11276,11 +11278,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="88"/>
-      <c r="P81" s="421">
+      <c r="P81" s="418">
         <f t="shared" si="22"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="421"/>
+      <c r="Q81" s="418"/>
       <c r="R81" s="363">
         <f t="shared" si="23"/>
         <v>774480.76</v>
@@ -11343,11 +11345,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="88"/>
-      <c r="P82" s="421">
+      <c r="P82" s="418">
         <f t="shared" si="22"/>
         <v>854048.77</v>
       </c>
-      <c r="Q82" s="421"/>
+      <c r="Q82" s="418"/>
       <c r="R82" s="363">
         <f t="shared" si="23"/>
         <v>879952.77</v>
@@ -11361,7 +11363,7 @@
         <v>77</v>
       </c>
       <c r="U82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11413,11 +11415,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="88"/>
-      <c r="P83" s="421">
+      <c r="P83" s="418">
         <f t="shared" si="22"/>
         <v>751480.78</v>
       </c>
-      <c r="Q83" s="421"/>
+      <c r="Q83" s="418"/>
       <c r="R83" s="363">
         <f t="shared" si="23"/>
         <v>774273.78</v>
@@ -11484,11 +11486,11 @@
         <v>0</v>
       </c>
       <c r="O84" s="88"/>
-      <c r="P84" s="421">
+      <c r="P84" s="418">
         <f t="shared" si="22"/>
         <v>1089017.79</v>
       </c>
-      <c r="Q84" s="421"/>
+      <c r="Q84" s="418"/>
       <c r="R84" s="363">
         <f t="shared" si="23"/>
         <v>1122048.79</v>
@@ -11502,7 +11504,7 @@
         <v>79</v>
       </c>
       <c r="U84" s="36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y84" t="s">
         <v>249</v>
@@ -11557,11 +11559,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="88"/>
-      <c r="P85" s="421">
+      <c r="P85" s="418">
         <f t="shared" si="22"/>
         <v>728063.8</v>
       </c>
-      <c r="Q85" s="421"/>
+      <c r="Q85" s="418"/>
       <c r="R85" s="363">
         <f t="shared" si="23"/>
         <v>750146.8</v>
@@ -11575,7 +11577,7 @@
         <v>80</v>
       </c>
       <c r="U85" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="86" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11628,11 +11630,11 @@
         <v>0</v>
       </c>
       <c r="O86" s="88"/>
-      <c r="P86" s="421">
+      <c r="P86" s="418">
         <f t="shared" si="22"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="421"/>
+      <c r="Q86" s="418"/>
       <c r="R86" s="363">
         <f t="shared" si="23"/>
         <v>774480.81</v>
@@ -11698,11 +11700,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="74"/>
-      <c r="P87" s="421">
+      <c r="P87" s="418">
         <f t="shared" si="22"/>
         <v>682667.82</v>
       </c>
-      <c r="Q87" s="421"/>
+      <c r="Q87" s="418"/>
       <c r="R87" s="363">
         <f t="shared" si="23"/>
         <v>703373.82</v>
@@ -11716,7 +11718,7 @@
         <v>82</v>
       </c>
       <c r="U87" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="W87" s="16"/>
     </row>
@@ -11769,11 +11771,11 @@
         <v>0</v>
       </c>
       <c r="O88" s="88"/>
-      <c r="P88" s="421">
+      <c r="P88" s="418">
         <f t="shared" si="22"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="421"/>
+      <c r="Q88" s="418"/>
       <c r="R88" s="363">
         <f t="shared" si="23"/>
         <v>775171.83</v>
@@ -11836,11 +11838,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="88"/>
-      <c r="P89" s="421">
+      <c r="P89" s="418">
         <f t="shared" si="22"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="421"/>
+      <c r="Q89" s="418"/>
       <c r="R89" s="363">
         <f t="shared" si="23"/>
         <v>775171.84</v>
@@ -11904,11 +11906,11 @@
         <v>0</v>
       </c>
       <c r="O90" s="88"/>
-      <c r="P90" s="421">
+      <c r="P90" s="418">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="421"/>
+      <c r="Q90" s="418"/>
       <c r="R90" s="363">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -11969,21 +11971,21 @@
         <v>202702.7028</v>
       </c>
       <c r="M91" s="74">
-        <v>0</v>
+        <v>77449</v>
       </c>
       <c r="N91" s="74">
         <f>I91</f>
         <v>387244.62681599997</v>
       </c>
       <c r="O91" s="88"/>
-      <c r="P91" s="421">
+      <c r="P91" s="418">
         <f t="shared" si="22"/>
-        <v>1163128.8600000001</v>
-      </c>
-      <c r="Q91" s="421"/>
+        <v>1240577.8600000001</v>
+      </c>
+      <c r="Q91" s="418"/>
       <c r="R91" s="363">
         <f t="shared" si="23"/>
-        <v>1198407.8600000001</v>
+        <v>1278205.8600000001</v>
       </c>
       <c r="S91" s="13">
         <f t="shared" si="24"/>
@@ -12043,11 +12045,11 @@
         <v>0</v>
       </c>
       <c r="O92" s="88"/>
-      <c r="P92" s="421">
+      <c r="P92" s="418">
         <f t="shared" si="22"/>
         <v>752351.87</v>
       </c>
-      <c r="Q92" s="421"/>
+      <c r="Q92" s="418"/>
       <c r="R92" s="363">
         <f t="shared" si="23"/>
         <v>775171.87</v>
@@ -12111,11 +12113,11 @@
         <v>0</v>
       </c>
       <c r="O93" s="88"/>
-      <c r="P93" s="421">
+      <c r="P93" s="418">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="421"/>
+      <c r="Q93" s="418"/>
       <c r="R93" s="363">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12178,11 +12180,11 @@
         <v>0</v>
       </c>
       <c r="O94" s="88"/>
-      <c r="P94" s="421">
+      <c r="P94" s="418">
         <f t="shared" si="22"/>
         <v>752351.89</v>
       </c>
-      <c r="Q94" s="421"/>
+      <c r="Q94" s="418"/>
       <c r="R94" s="363">
         <f t="shared" si="23"/>
         <v>775171.89</v>
@@ -12196,7 +12198,7 @@
         <v>89</v>
       </c>
       <c r="U94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="95" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12248,11 +12250,11 @@
         <v>0</v>
       </c>
       <c r="O95" s="88"/>
-      <c r="P95" s="421">
+      <c r="P95" s="418">
         <f t="shared" si="22"/>
         <v>743876.9</v>
       </c>
-      <c r="Q95" s="421"/>
+      <c r="Q95" s="418"/>
       <c r="R95" s="363">
         <f t="shared" si="23"/>
         <v>766439.9</v>
@@ -12318,11 +12320,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="88"/>
-      <c r="P96" s="421">
+      <c r="P96" s="418">
         <f t="shared" si="22"/>
         <v>752351.91</v>
       </c>
-      <c r="Q96" s="421"/>
+      <c r="Q96" s="418"/>
       <c r="R96" s="363">
         <f t="shared" si="23"/>
         <v>775171.91</v>
@@ -12346,7 +12348,7 @@
         <v>92</v>
       </c>
       <c r="C97" s="172" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D97" s="173">
         <v>4.7999999999999996E-3</v>
@@ -12391,11 +12393,11 @@
         <f>1780*100</f>
         <v>178000</v>
       </c>
-      <c r="P97" s="421">
+      <c r="P97" s="418">
         <f t="shared" si="22"/>
         <v>1840080.92</v>
       </c>
-      <c r="Q97" s="421"/>
+      <c r="Q97" s="418"/>
       <c r="R97" s="363">
         <f t="shared" si="23"/>
         <v>1895891.92</v>
@@ -12409,7 +12411,7 @@
         <v>92</v>
       </c>
       <c r="U97" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="98" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12461,11 +12463,11 @@
         <v>0</v>
       </c>
       <c r="O98" s="60"/>
-      <c r="P98" s="421">
+      <c r="P98" s="418">
         <f t="shared" si="22"/>
         <v>238871.93</v>
       </c>
-      <c r="Q98" s="421"/>
+      <c r="Q98" s="418"/>
       <c r="R98" s="363">
         <f t="shared" si="23"/>
         <v>246117.93</v>
@@ -12479,7 +12481,7 @@
         <v>93</v>
       </c>
       <c r="U98" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12532,11 +12534,11 @@
         <v>0</v>
       </c>
       <c r="O99" s="60"/>
-      <c r="P99" s="421">
+      <c r="P99" s="418">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="421"/>
+      <c r="Q99" s="418"/>
       <c r="R99" s="363">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -12602,11 +12604,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="88"/>
-      <c r="P100" s="421">
+      <c r="P100" s="418">
         <f t="shared" si="22"/>
         <v>4049080.95</v>
       </c>
-      <c r="Q100" s="421"/>
+      <c r="Q100" s="418"/>
       <c r="R100" s="363">
         <f t="shared" si="23"/>
         <v>4171890.95</v>
@@ -12669,11 +12671,11 @@
         <v>0</v>
       </c>
       <c r="O101" s="88"/>
-      <c r="P101" s="421">
+      <c r="P101" s="418">
         <f t="shared" si="22"/>
         <v>752388.96</v>
       </c>
-      <c r="Q101" s="421"/>
+      <c r="Q101" s="418"/>
       <c r="R101" s="363">
         <f t="shared" si="23"/>
         <v>775209.96</v>
@@ -12739,11 +12741,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="88"/>
-      <c r="P102" s="421">
+      <c r="P102" s="418">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752269.97</v>
       </c>
-      <c r="Q102" s="421"/>
+      <c r="Q102" s="418"/>
       <c r="R102" s="363">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775086.97</v>
@@ -12809,11 +12811,11 @@
         <v>0</v>
       </c>
       <c r="O103" s="88"/>
-      <c r="P103" s="421">
+      <c r="P103" s="418">
         <f t="shared" si="32"/>
         <v>752350.98</v>
       </c>
-      <c r="Q103" s="421"/>
+      <c r="Q103" s="418"/>
       <c r="R103" s="363">
         <f t="shared" si="33"/>
         <v>775170.98</v>
@@ -12877,11 +12879,11 @@
         <v>0</v>
       </c>
       <c r="O104" s="88"/>
-      <c r="P104" s="421">
+      <c r="P104" s="418">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="421"/>
+      <c r="Q104" s="418"/>
       <c r="R104" s="363">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -12947,11 +12949,11 @@
         <v>0</v>
       </c>
       <c r="O105" s="88"/>
-      <c r="P105" s="421">
+      <c r="P105" s="418">
         <f t="shared" si="32"/>
         <v>752351</v>
       </c>
-      <c r="Q105" s="421"/>
+      <c r="Q105" s="418"/>
       <c r="R105" s="363">
         <f t="shared" si="33"/>
         <v>775171</v>
@@ -13014,11 +13016,11 @@
         <v>0</v>
       </c>
       <c r="O106" s="88"/>
-      <c r="P106" s="421">
+      <c r="P106" s="418">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="421"/>
+      <c r="Q106" s="418"/>
       <c r="R106" s="363">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13081,11 +13083,11 @@
         <v>0</v>
       </c>
       <c r="O107" s="88"/>
-      <c r="P107" s="421">
+      <c r="P107" s="418">
         <f t="shared" si="32"/>
         <v>775118.02</v>
       </c>
-      <c r="Q107" s="421"/>
+      <c r="Q107" s="418"/>
       <c r="R107" s="363">
         <f t="shared" si="33"/>
         <v>798628.02</v>
@@ -13099,7 +13101,7 @@
         <v>102</v>
       </c>
       <c r="U107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13151,11 +13153,11 @@
         <v>0</v>
       </c>
       <c r="O108" s="88"/>
-      <c r="P108" s="421">
+      <c r="P108" s="418">
         <f t="shared" si="32"/>
         <v>728092.03</v>
       </c>
-      <c r="Q108" s="421"/>
+      <c r="Q108" s="418"/>
       <c r="R108" s="363">
         <f t="shared" si="33"/>
         <v>750176.03</v>
@@ -13219,11 +13221,11 @@
         <v>0</v>
       </c>
       <c r="O109" s="88"/>
-      <c r="P109" s="421">
+      <c r="P109" s="418">
         <f t="shared" si="32"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="421"/>
+      <c r="Q109" s="418"/>
       <c r="R109" s="363">
         <f t="shared" si="33"/>
         <v>791106.04</v>
@@ -13237,7 +13239,7 @@
         <v>104</v>
       </c>
       <c r="U109" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="110" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13289,11 +13291,11 @@
         <v>0</v>
       </c>
       <c r="O110" s="88"/>
-      <c r="P110" s="421">
+      <c r="P110" s="418">
         <f t="shared" si="32"/>
         <v>705414.05</v>
       </c>
-      <c r="Q110" s="421"/>
+      <c r="Q110" s="418"/>
       <c r="R110" s="363">
         <f t="shared" si="33"/>
         <v>726810.05</v>
@@ -13307,7 +13309,7 @@
         <v>105</v>
       </c>
       <c r="U110" s="157" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V110" s="36"/>
     </row>
@@ -13355,21 +13357,21 @@
         <v>202702.7028</v>
       </c>
       <c r="M111" s="74">
-        <v>0</v>
+        <v>70995</v>
       </c>
       <c r="N111" s="74">
         <f>(I111+K111)/2</f>
         <v>270455.26692913822</v>
       </c>
       <c r="O111" s="88"/>
-      <c r="P111" s="421">
+      <c r="P111" s="418">
         <f t="shared" si="32"/>
-        <v>1698531.06</v>
-      </c>
-      <c r="Q111" s="421"/>
+        <v>1769526.06</v>
+      </c>
+      <c r="Q111" s="418"/>
       <c r="R111" s="363">
         <f t="shared" si="33"/>
-        <v>1750049.06</v>
+        <v>1823197.06</v>
       </c>
       <c r="S111" s="82">
         <f t="shared" si="34"/>
@@ -13380,7 +13382,7 @@
         <v>106</v>
       </c>
       <c r="U111" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="112" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13432,11 +13434,11 @@
         <v>0</v>
       </c>
       <c r="O112" s="88"/>
-      <c r="P112" s="421">
+      <c r="P112" s="418">
         <f t="shared" si="32"/>
         <v>766866.07</v>
       </c>
-      <c r="Q112" s="421"/>
+      <c r="Q112" s="418"/>
       <c r="R112" s="363">
         <f t="shared" si="33"/>
         <v>790126.07</v>
@@ -13502,11 +13504,11 @@
         <v>0</v>
       </c>
       <c r="O113" s="88"/>
-      <c r="P113" s="421">
+      <c r="P113" s="418">
         <f t="shared" si="32"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="421"/>
+      <c r="Q113" s="418"/>
       <c r="R113" s="363">
         <f t="shared" si="33"/>
         <v>742930.08</v>
@@ -13569,11 +13571,11 @@
         <v>0</v>
       </c>
       <c r="O114" s="88"/>
-      <c r="P114" s="421">
+      <c r="P114" s="418">
         <f t="shared" si="32"/>
         <v>1511441.09</v>
       </c>
-      <c r="Q114" s="421"/>
+      <c r="Q114" s="418"/>
       <c r="R114" s="363">
         <f t="shared" si="33"/>
         <v>1557284.09</v>
@@ -13639,11 +13641,11 @@
         <v>0</v>
       </c>
       <c r="O115" s="88"/>
-      <c r="P115" s="421">
+      <c r="P115" s="418">
         <f t="shared" si="32"/>
         <v>1524957.1</v>
       </c>
-      <c r="Q115" s="421"/>
+      <c r="Q115" s="418"/>
       <c r="R115" s="363">
         <f t="shared" si="33"/>
         <v>1571210.1</v>
@@ -13711,11 +13713,11 @@
         <v>0</v>
       </c>
       <c r="O116" s="88"/>
-      <c r="P116" s="421">
+      <c r="P116" s="418">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="421"/>
+      <c r="Q116" s="418"/>
       <c r="R116" s="363">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -13778,11 +13780,11 @@
         <v>0</v>
       </c>
       <c r="O117" s="88"/>
-      <c r="P117" s="421">
+      <c r="P117" s="418">
         <f t="shared" si="32"/>
         <v>725114.12</v>
       </c>
-      <c r="Q117" s="421"/>
+      <c r="Q117" s="418"/>
       <c r="R117" s="363">
         <f t="shared" si="33"/>
         <v>747108.12</v>
@@ -13848,11 +13850,11 @@
         <v>0</v>
       </c>
       <c r="O118" s="88"/>
-      <c r="P118" s="421">
+      <c r="P118" s="418">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="421"/>
+      <c r="Q118" s="418"/>
       <c r="R118" s="363">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -13915,11 +13917,11 @@
         <v>0</v>
       </c>
       <c r="O119" s="88"/>
-      <c r="P119" s="421">
+      <c r="P119" s="418">
         <f t="shared" si="32"/>
         <v>728882.14</v>
       </c>
-      <c r="Q119" s="421"/>
+      <c r="Q119" s="418"/>
       <c r="R119" s="363">
         <f t="shared" si="33"/>
         <v>750990.14</v>
@@ -13983,11 +13985,11 @@
         <v>0</v>
       </c>
       <c r="O120" s="88"/>
-      <c r="P120" s="421">
+      <c r="P120" s="418">
         <f t="shared" si="32"/>
         <v>849222.15</v>
       </c>
-      <c r="Q120" s="421"/>
+      <c r="Q120" s="418"/>
       <c r="R120" s="363">
         <f t="shared" si="33"/>
         <v>874980.15</v>
@@ -14001,7 +14003,7 @@
         <v>115</v>
       </c>
       <c r="U120" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="121" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14054,11 +14056,11 @@
         <v>0</v>
       </c>
       <c r="O121" s="88"/>
-      <c r="P121" s="421">
+      <c r="P121" s="418">
         <f t="shared" si="32"/>
         <v>803799.16</v>
       </c>
-      <c r="Q121" s="421"/>
+      <c r="Q121" s="418"/>
       <c r="R121" s="363">
         <f t="shared" si="33"/>
         <v>828179.16</v>
@@ -14121,11 +14123,11 @@
         <v>0</v>
       </c>
       <c r="O122" s="88"/>
-      <c r="P122" s="421">
+      <c r="P122" s="418">
         <f t="shared" si="32"/>
         <v>854048.17</v>
       </c>
-      <c r="Q122" s="421"/>
+      <c r="Q122" s="418"/>
       <c r="R122" s="363">
         <f t="shared" si="33"/>
         <v>879952.17</v>
@@ -14139,7 +14141,7 @@
         <v>117</v>
       </c>
       <c r="U122" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="123" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14192,11 +14194,11 @@
         <v>0</v>
       </c>
       <c r="O123" s="88"/>
-      <c r="P123" s="421">
+      <c r="P123" s="418">
         <f t="shared" si="32"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="421"/>
+      <c r="Q123" s="418"/>
       <c r="R123" s="363">
         <f t="shared" si="33"/>
         <v>882540.18</v>
@@ -14210,7 +14212,7 @@
         <v>118</v>
       </c>
       <c r="U123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14262,11 +14264,11 @@
         <v>0</v>
       </c>
       <c r="O124" s="88"/>
-      <c r="P124" s="421">
+      <c r="P124" s="418">
         <f t="shared" si="32"/>
         <v>827956.19</v>
       </c>
-      <c r="Q124" s="421"/>
+      <c r="Q124" s="418"/>
       <c r="R124" s="363">
         <f t="shared" si="33"/>
         <v>853069.19</v>
@@ -14333,11 +14335,11 @@
         <v>0</v>
       </c>
       <c r="O125" s="88"/>
-      <c r="P125" s="421">
+      <c r="P125" s="418">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="421"/>
+      <c r="Q125" s="418"/>
       <c r="R125" s="363">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -14351,7 +14353,7 @@
         <v>120</v>
       </c>
       <c r="U125" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14404,11 +14406,11 @@
         <v>0</v>
       </c>
       <c r="O126" s="88"/>
-      <c r="P126" s="421">
+      <c r="P126" s="418">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="421"/>
+      <c r="Q126" s="418"/>
       <c r="R126" s="363">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -14422,7 +14424,7 @@
         <v>121</v>
       </c>
       <c r="U126" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="127" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14474,11 +14476,11 @@
         <v>0</v>
       </c>
       <c r="O127" s="74"/>
-      <c r="P127" s="421">
+      <c r="P127" s="418">
         <f t="shared" si="32"/>
         <v>736705.22</v>
       </c>
-      <c r="Q127" s="421"/>
+      <c r="Q127" s="418"/>
       <c r="R127" s="363">
         <f t="shared" si="33"/>
         <v>759050.22</v>
@@ -14542,11 +14544,11 @@
         <v>0</v>
       </c>
       <c r="O128" s="88"/>
-      <c r="P128" s="421">
+      <c r="P128" s="418">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="421"/>
+      <c r="Q128" s="418"/>
       <c r="R128" s="363">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -14560,7 +14562,7 @@
         <v>123</v>
       </c>
       <c r="U128" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="129" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14612,11 +14614,11 @@
         <v>0</v>
       </c>
       <c r="O129" s="88"/>
-      <c r="P129" s="421">
+      <c r="P129" s="418">
         <f t="shared" si="32"/>
         <v>736705.24</v>
       </c>
-      <c r="Q129" s="421"/>
+      <c r="Q129" s="418"/>
       <c r="R129" s="363">
         <f t="shared" si="33"/>
         <v>759051.24</v>
@@ -14680,11 +14682,11 @@
         <v>0</v>
       </c>
       <c r="O130" s="88"/>
-      <c r="P130" s="421">
+      <c r="P130" s="418">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="421"/>
+      <c r="Q130" s="418"/>
       <c r="R130" s="363">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -14751,11 +14753,11 @@
         <v>0</v>
       </c>
       <c r="O131" s="88"/>
-      <c r="P131" s="421">
+      <c r="P131" s="418">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="421"/>
+      <c r="Q131" s="418"/>
       <c r="R131" s="363">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -14816,11 +14818,11 @@
         <v>0</v>
       </c>
       <c r="O132" s="88"/>
-      <c r="P132" s="421">
+      <c r="P132" s="418">
         <f t="shared" si="32"/>
         <v>1680082.27</v>
       </c>
-      <c r="Q132" s="421"/>
+      <c r="Q132" s="418"/>
       <c r="R132" s="363">
         <f t="shared" si="33"/>
         <v>1731040.27</v>
@@ -14887,11 +14889,11 @@
         <v>339029.8362611382</v>
       </c>
       <c r="O133" s="88"/>
-      <c r="P133" s="421">
+      <c r="P133" s="418">
         <f t="shared" si="32"/>
         <v>9465986.2799999993</v>
       </c>
-      <c r="Q133" s="421"/>
+      <c r="Q133" s="418"/>
       <c r="R133" s="363">
         <f t="shared" si="33"/>
         <v>9753091.2799999993</v>
@@ -14954,11 +14956,11 @@
         <v>0</v>
       </c>
       <c r="O134" s="88"/>
-      <c r="P134" s="421">
+      <c r="P134" s="418">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>854048.29</v>
       </c>
-      <c r="Q134" s="421"/>
+      <c r="Q134" s="418"/>
       <c r="R134" s="363">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>879953.29</v>
@@ -15024,11 +15026,11 @@
         <v>0</v>
       </c>
       <c r="O135" s="88"/>
-      <c r="P135" s="421">
+      <c r="P135" s="418">
         <f t="shared" si="39"/>
         <v>847809.3</v>
       </c>
-      <c r="Q135" s="421"/>
+      <c r="Q135" s="418"/>
       <c r="R135" s="363">
         <f t="shared" si="40"/>
         <v>873524.3</v>
@@ -15095,11 +15097,11 @@
         <v>0</v>
       </c>
       <c r="O136" s="88"/>
-      <c r="P136" s="421">
+      <c r="P136" s="418">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="421"/>
+      <c r="Q136" s="418"/>
       <c r="R136" s="363">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15113,7 +15115,7 @@
         <v>131</v>
       </c>
       <c r="U136" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="137" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15165,11 +15167,11 @@
         <v>0</v>
       </c>
       <c r="O137" s="88"/>
-      <c r="P137" s="421">
+      <c r="P137" s="418">
         <f t="shared" si="39"/>
         <v>846226.32</v>
       </c>
-      <c r="Q137" s="421"/>
+      <c r="Q137" s="418"/>
       <c r="R137" s="363">
         <f t="shared" si="40"/>
         <v>871893.32</v>
@@ -15236,11 +15238,11 @@
         <v>0</v>
       </c>
       <c r="O138" s="88"/>
-      <c r="P138" s="421">
+      <c r="P138" s="418">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="421"/>
+      <c r="Q138" s="418"/>
       <c r="R138" s="363">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -15306,11 +15308,11 @@
         <v>0</v>
       </c>
       <c r="O139" s="88"/>
-      <c r="P139" s="421">
+      <c r="P139" s="418">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="421"/>
+      <c r="Q139" s="418"/>
       <c r="R139" s="363">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -15376,11 +15378,11 @@
         <v>0</v>
       </c>
       <c r="O140" s="88"/>
-      <c r="P140" s="421">
+      <c r="P140" s="418">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="421"/>
+      <c r="Q140" s="418"/>
       <c r="R140" s="363">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -15444,11 +15446,11 @@
         <v>0</v>
       </c>
       <c r="O141" s="88"/>
-      <c r="P141" s="421">
+      <c r="P141" s="418">
         <f t="shared" si="39"/>
         <v>3751757.36</v>
       </c>
-      <c r="Q141" s="421"/>
+      <c r="Q141" s="418"/>
       <c r="R141" s="363">
         <f t="shared" si="40"/>
         <v>3865549.36</v>
@@ -15462,7 +15464,7 @@
         <v>136</v>
       </c>
       <c r="U141" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15514,11 +15516,11 @@
         <v>0</v>
       </c>
       <c r="O142" s="88"/>
-      <c r="P142" s="421">
+      <c r="P142" s="418">
         <f t="shared" si="39"/>
         <v>799288.37</v>
       </c>
-      <c r="Q142" s="421"/>
+      <c r="Q142" s="418"/>
       <c r="R142" s="363">
         <f t="shared" si="40"/>
         <v>823532.37</v>
@@ -15581,11 +15583,11 @@
         <v>0</v>
       </c>
       <c r="O143" s="88"/>
-      <c r="P143" s="421">
+      <c r="P143" s="418">
         <f t="shared" si="39"/>
         <v>885340.38</v>
       </c>
-      <c r="Q143" s="421"/>
+      <c r="Q143" s="418"/>
       <c r="R143" s="363">
         <f t="shared" si="40"/>
         <v>912194.38</v>
@@ -15599,7 +15601,7 @@
         <v>138</v>
       </c>
       <c r="U143" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15651,11 +15653,11 @@
         <v>0</v>
       </c>
       <c r="O144" s="88"/>
-      <c r="P144" s="421">
+      <c r="P144" s="418">
         <f t="shared" si="39"/>
         <v>880691.39</v>
       </c>
-      <c r="Q144" s="421"/>
+      <c r="Q144" s="418"/>
       <c r="R144" s="363">
         <f t="shared" si="40"/>
         <v>907404.39</v>
@@ -15669,7 +15671,7 @@
         <v>139</v>
       </c>
       <c r="U144" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15695,8 +15697,8 @@
       <c r="M145" s="74"/>
       <c r="N145" s="74"/>
       <c r="O145" s="88"/>
-      <c r="P145" s="421"/>
-      <c r="Q145" s="421"/>
+      <c r="P145" s="418"/>
+      <c r="Q145" s="418"/>
       <c r="R145" s="364"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -15730,8 +15732,8 @@
       <c r="M146" s="74"/>
       <c r="N146" s="74"/>
       <c r="O146" s="88"/>
-      <c r="P146" s="421"/>
-      <c r="Q146" s="421"/>
+      <c r="P146" s="418"/>
+      <c r="Q146" s="418"/>
       <c r="R146" s="364"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -15758,8 +15760,8 @@
       <c r="M147" s="74"/>
       <c r="N147" s="74"/>
       <c r="O147" s="88"/>
-      <c r="P147" s="421"/>
-      <c r="Q147" s="421"/>
+      <c r="P147" s="418"/>
+      <c r="Q147" s="418"/>
       <c r="R147" s="364"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -15786,8 +15788,8 @@
       <c r="M148" s="74"/>
       <c r="N148" s="74"/>
       <c r="O148" s="88"/>
-      <c r="P148" s="421"/>
-      <c r="Q148" s="421"/>
+      <c r="P148" s="418"/>
+      <c r="Q148" s="418"/>
       <c r="R148" s="364"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -15847,11 +15849,11 @@
         <v>246252.47775313823</v>
       </c>
       <c r="O149" s="88"/>
-      <c r="P149" s="421">
+      <c r="P149" s="418">
         <f t="shared" ref="P149:P158" si="49">ROUND(SUM(G149:O149),0) + S149</f>
         <v>882923.46</v>
       </c>
-      <c r="Q149" s="421"/>
+      <c r="Q149" s="418"/>
       <c r="R149" s="363">
         <f t="shared" ref="R149:R158" si="50">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>909704.46</v>
@@ -15871,7 +15873,7 @@
         <v>155</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D150" s="80">
         <v>4.2300000000000003E-3</v>
@@ -15912,11 +15914,11 @@
         <v>0</v>
       </c>
       <c r="O150" s="88"/>
-      <c r="P150" s="421">
+      <c r="P150" s="418">
         <f t="shared" si="49"/>
         <v>707760.55</v>
       </c>
-      <c r="Q150" s="421"/>
+      <c r="Q150" s="418"/>
       <c r="R150" s="363">
         <f t="shared" si="50"/>
         <v>729228.55</v>
@@ -15930,7 +15932,7 @@
         <v>155</v>
       </c>
       <c r="U150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="151" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15983,11 +15985,11 @@
         <v>0</v>
       </c>
       <c r="O151" s="74"/>
-      <c r="P151" s="421">
+      <c r="P151" s="418">
         <f t="shared" si="49"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="421"/>
+      <c r="Q151" s="418"/>
       <c r="R151" s="363">
         <f t="shared" si="50"/>
         <v>782794.58</v>
@@ -16051,11 +16053,11 @@
         <v>0</v>
       </c>
       <c r="O152" s="74"/>
-      <c r="P152" s="421">
+      <c r="P152" s="418">
         <f t="shared" si="49"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="421"/>
+      <c r="Q152" s="418"/>
       <c r="R152" s="363">
         <f t="shared" si="50"/>
         <v>782794.59</v>
@@ -16119,11 +16121,11 @@
         <v>0</v>
       </c>
       <c r="O153" s="74"/>
-      <c r="P153" s="421">
+      <c r="P153" s="418">
         <f t="shared" si="49"/>
         <v>759750.63</v>
       </c>
-      <c r="Q153" s="421"/>
+      <c r="Q153" s="418"/>
       <c r="R153" s="363">
         <f t="shared" si="50"/>
         <v>782795.63</v>
@@ -16187,11 +16189,11 @@
         <v>0</v>
       </c>
       <c r="O154" s="74"/>
-      <c r="P154" s="421">
+      <c r="P154" s="418">
         <f t="shared" si="49"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="421"/>
+      <c r="Q154" s="418"/>
       <c r="R154" s="363">
         <f t="shared" si="50"/>
         <v>766170.68</v>
@@ -16254,11 +16256,11 @@
         <v>0</v>
       </c>
       <c r="O155" s="74"/>
-      <c r="P155" s="421">
+      <c r="P155" s="418">
         <f t="shared" si="49"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="421"/>
+      <c r="Q155" s="418"/>
       <c r="R155" s="363">
         <f t="shared" si="50"/>
         <v>759050.73</v>
@@ -16324,11 +16326,11 @@
         <v>0</v>
       </c>
       <c r="O156" s="74"/>
-      <c r="P156" s="421">
+      <c r="P156" s="418">
         <f t="shared" si="49"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="421"/>
+      <c r="Q156" s="418"/>
       <c r="R156" s="363">
         <f t="shared" si="50"/>
         <v>759050.75</v>
@@ -16395,11 +16397,11 @@
         <v>0</v>
       </c>
       <c r="O157" s="74"/>
-      <c r="P157" s="421">
+      <c r="P157" s="418">
         <f t="shared" si="49"/>
         <v>759750.76</v>
       </c>
-      <c r="Q157" s="421"/>
+      <c r="Q157" s="418"/>
       <c r="R157" s="363">
         <f t="shared" si="50"/>
         <v>782795.76</v>
@@ -16463,11 +16465,11 @@
         <v>0</v>
       </c>
       <c r="O158" s="74"/>
-      <c r="P158" s="421">
+      <c r="P158" s="418">
         <f t="shared" si="49"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="421"/>
+      <c r="Q158" s="418"/>
       <c r="R158" s="363">
         <f t="shared" si="50"/>
         <v>807732.04</v>
@@ -16481,7 +16483,7 @@
         <v>204</v>
       </c>
       <c r="U158" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="159" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16500,8 +16502,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="74"/>
-      <c r="P159" s="446"/>
-      <c r="Q159" s="446"/>
+      <c r="P159" s="423"/>
+      <c r="Q159" s="423"/>
       <c r="R159" s="183"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -16522,8 +16524,8 @@
       <c r="M160" s="194"/>
       <c r="N160" s="194"/>
       <c r="O160" s="360"/>
-      <c r="P160" s="447"/>
-      <c r="Q160" s="447"/>
+      <c r="P160" s="424"/>
+      <c r="Q160" s="424"/>
       <c r="R160" s="186"/>
       <c r="S160" s="13"/>
       <c r="T160" s="195"/>
@@ -16567,274 +16569,208 @@
       </c>
       <c r="M161" s="202">
         <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="N161" s="202">
+        <v>580871</v>
+      </c>
+      <c r="N161" s="473">
         <f t="shared" si="54"/>
         <v>3469638.8119514147</v>
       </c>
       <c r="O161" s="202">
         <f t="shared" si="54"/>
-        <v>799204.92218400002</v>
-      </c>
-      <c r="P161" s="444">
+        <v>890374.81218400015</v>
+      </c>
+      <c r="P161" s="421">
         <f>SUM(P6:P160)</f>
-        <v>168716264.07000002</v>
-      </c>
-      <c r="Q161" s="445"/>
+        <v>169388305.07000002</v>
+      </c>
+      <c r="Q161" s="422"/>
       <c r="R161" s="187">
         <f>SUM(R6:R160)</f>
-        <v>173833550.07000002</v>
-      </c>
-      <c r="S161" s="444"/>
-      <c r="T161" s="445"/>
+        <v>174525973.07000002</v>
+      </c>
+      <c r="S161" s="421"/>
+      <c r="T161" s="422"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="442" t="s">
-        <v>327</v>
-      </c>
-      <c r="C162" s="442"/>
-      <c r="D162" s="442"/>
-      <c r="E162" s="442"/>
-      <c r="F162" s="442"/>
-      <c r="G162" s="442"/>
-      <c r="H162" s="442"/>
-      <c r="I162" s="442"/>
-      <c r="J162" s="442"/>
-      <c r="K162" s="442"/>
-      <c r="L162" s="442"/>
-      <c r="M162" s="442"/>
-      <c r="N162" s="442"/>
-      <c r="O162" s="442"/>
-      <c r="P162" s="442"/>
-      <c r="Q162" s="442"/>
-      <c r="R162" s="442"/>
-      <c r="S162" s="442"/>
-      <c r="T162" s="442"/>
+      <c r="B162" s="419" t="s">
+        <v>326</v>
+      </c>
+      <c r="C162" s="419"/>
+      <c r="D162" s="419"/>
+      <c r="E162" s="419"/>
+      <c r="F162" s="419"/>
+      <c r="G162" s="419"/>
+      <c r="H162" s="419"/>
+      <c r="I162" s="419"/>
+      <c r="J162" s="419"/>
+      <c r="K162" s="419"/>
+      <c r="L162" s="419"/>
+      <c r="M162" s="419"/>
+      <c r="N162" s="419"/>
+      <c r="O162" s="419"/>
+      <c r="P162" s="419"/>
+      <c r="Q162" s="419"/>
+      <c r="R162" s="419"/>
+      <c r="S162" s="419"/>
+      <c r="T162" s="419"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="443"/>
-      <c r="C163" s="443"/>
-      <c r="D163" s="443"/>
-      <c r="E163" s="443"/>
-      <c r="F163" s="443"/>
-      <c r="G163" s="443"/>
-      <c r="H163" s="443"/>
-      <c r="I163" s="443"/>
-      <c r="J163" s="443"/>
-      <c r="K163" s="443"/>
-      <c r="L163" s="443"/>
-      <c r="M163" s="443"/>
-      <c r="N163" s="443"/>
-      <c r="O163" s="443"/>
-      <c r="P163" s="443"/>
-      <c r="Q163" s="443"/>
-      <c r="R163" s="443"/>
-      <c r="S163" s="443"/>
-      <c r="T163" s="443"/>
+      <c r="B163" s="420"/>
+      <c r="C163" s="420"/>
+      <c r="D163" s="420"/>
+      <c r="E163" s="420"/>
+      <c r="F163" s="420"/>
+      <c r="G163" s="420"/>
+      <c r="H163" s="420"/>
+      <c r="I163" s="420"/>
+      <c r="J163" s="420"/>
+      <c r="K163" s="420"/>
+      <c r="L163" s="420"/>
+      <c r="M163" s="420"/>
+      <c r="N163" s="420"/>
+      <c r="O163" s="420"/>
+      <c r="P163" s="420"/>
+      <c r="Q163" s="420"/>
+      <c r="R163" s="420"/>
+      <c r="S163" s="420"/>
+      <c r="T163" s="420"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="443" t="s">
-        <v>264</v>
-      </c>
-      <c r="C164" s="443"/>
-      <c r="D164" s="443"/>
-      <c r="E164" s="443"/>
-      <c r="F164" s="443"/>
-      <c r="G164" s="443"/>
-      <c r="H164" s="443"/>
-      <c r="I164" s="443"/>
-      <c r="J164" s="443"/>
-      <c r="K164" s="443"/>
-      <c r="L164" s="443"/>
-      <c r="M164" s="443"/>
-      <c r="N164" s="443"/>
-      <c r="O164" s="443"/>
-      <c r="P164" s="443"/>
-      <c r="Q164" s="443"/>
-      <c r="R164" s="443"/>
-      <c r="S164" s="443"/>
-      <c r="T164" s="443"/>
+      <c r="B164" s="420" t="s">
+        <v>263</v>
+      </c>
+      <c r="C164" s="420"/>
+      <c r="D164" s="420"/>
+      <c r="E164" s="420"/>
+      <c r="F164" s="420"/>
+      <c r="G164" s="420"/>
+      <c r="H164" s="420"/>
+      <c r="I164" s="420"/>
+      <c r="J164" s="420"/>
+      <c r="K164" s="420"/>
+      <c r="L164" s="420"/>
+      <c r="M164" s="420"/>
+      <c r="N164" s="420"/>
+      <c r="O164" s="420"/>
+      <c r="P164" s="420"/>
+      <c r="Q164" s="420"/>
+      <c r="R164" s="420"/>
+      <c r="S164" s="420"/>
+      <c r="T164" s="420"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="443"/>
-      <c r="C165" s="443"/>
-      <c r="D165" s="443"/>
-      <c r="E165" s="443"/>
-      <c r="F165" s="443"/>
-      <c r="G165" s="443"/>
-      <c r="H165" s="443"/>
-      <c r="I165" s="443"/>
-      <c r="J165" s="443"/>
-      <c r="K165" s="443"/>
-      <c r="L165" s="443"/>
-      <c r="M165" s="443"/>
-      <c r="N165" s="443"/>
-      <c r="O165" s="443"/>
-      <c r="P165" s="443"/>
-      <c r="Q165" s="443"/>
-      <c r="R165" s="443"/>
-      <c r="S165" s="443"/>
-      <c r="T165" s="443"/>
+      <c r="B165" s="420"/>
+      <c r="C165" s="420"/>
+      <c r="D165" s="420"/>
+      <c r="E165" s="420"/>
+      <c r="F165" s="420"/>
+      <c r="G165" s="420"/>
+      <c r="H165" s="420"/>
+      <c r="I165" s="420"/>
+      <c r="J165" s="420"/>
+      <c r="K165" s="420"/>
+      <c r="L165" s="420"/>
+      <c r="M165" s="420"/>
+      <c r="N165" s="420"/>
+      <c r="O165" s="420"/>
+      <c r="P165" s="420"/>
+      <c r="Q165" s="420"/>
+      <c r="R165" s="420"/>
+      <c r="S165" s="420"/>
+      <c r="T165" s="420"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="443"/>
-      <c r="C166" s="443"/>
-      <c r="D166" s="443"/>
-      <c r="E166" s="443"/>
-      <c r="F166" s="443"/>
-      <c r="G166" s="443"/>
-      <c r="H166" s="443"/>
-      <c r="I166" s="443"/>
-      <c r="J166" s="443"/>
-      <c r="K166" s="443"/>
-      <c r="L166" s="443"/>
-      <c r="M166" s="443"/>
-      <c r="N166" s="443"/>
-      <c r="O166" s="443"/>
-      <c r="P166" s="443"/>
-      <c r="Q166" s="443"/>
-      <c r="R166" s="443"/>
-      <c r="S166" s="443"/>
-      <c r="T166" s="443"/>
+      <c r="B166" s="420"/>
+      <c r="C166" s="420"/>
+      <c r="D166" s="420"/>
+      <c r="E166" s="420"/>
+      <c r="F166" s="420"/>
+      <c r="G166" s="420"/>
+      <c r="H166" s="420"/>
+      <c r="I166" s="420"/>
+      <c r="J166" s="420"/>
+      <c r="K166" s="420"/>
+      <c r="L166" s="420"/>
+      <c r="M166" s="420"/>
+      <c r="N166" s="420"/>
+      <c r="O166" s="420"/>
+      <c r="P166" s="420"/>
+      <c r="Q166" s="420"/>
+      <c r="R166" s="420"/>
+      <c r="S166" s="420"/>
+      <c r="T166" s="420"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="443"/>
-      <c r="C167" s="443"/>
-      <c r="D167" s="443"/>
-      <c r="E167" s="443"/>
-      <c r="F167" s="443"/>
-      <c r="G167" s="443"/>
-      <c r="H167" s="443"/>
-      <c r="I167" s="443"/>
-      <c r="J167" s="443"/>
-      <c r="K167" s="443"/>
-      <c r="L167" s="443"/>
-      <c r="M167" s="443"/>
-      <c r="N167" s="443"/>
-      <c r="O167" s="443"/>
-      <c r="P167" s="443"/>
-      <c r="Q167" s="443"/>
-      <c r="R167" s="443"/>
-      <c r="S167" s="443"/>
-      <c r="T167" s="443"/>
+      <c r="B167" s="420"/>
+      <c r="C167" s="420"/>
+      <c r="D167" s="420"/>
+      <c r="E167" s="420"/>
+      <c r="F167" s="420"/>
+      <c r="G167" s="420"/>
+      <c r="H167" s="420"/>
+      <c r="I167" s="420"/>
+      <c r="J167" s="420"/>
+      <c r="K167" s="420"/>
+      <c r="L167" s="420"/>
+      <c r="M167" s="420"/>
+      <c r="N167" s="420"/>
+      <c r="O167" s="420"/>
+      <c r="P167" s="420"/>
+      <c r="Q167" s="420"/>
+      <c r="R167" s="420"/>
+      <c r="S167" s="420"/>
+      <c r="T167" s="420"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="P29:Q29"/>
@@ -16859,54 +16795,120 @@
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -16942,12 +16944,12 @@
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
       <c r="J3" s="66"/>
-      <c r="K3" s="457" t="s">
-        <v>337</v>
-      </c>
-      <c r="L3" s="458"/>
-      <c r="M3" s="458"/>
-      <c r="N3" s="458"/>
+      <c r="K3" s="459" t="s">
+        <v>336</v>
+      </c>
+      <c r="L3" s="460"/>
+      <c r="M3" s="460"/>
+      <c r="N3" s="460"/>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C4" s="147" t="s">
@@ -16962,14 +16964,14 @@
         <v>166</v>
       </c>
       <c r="H4" s="90" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I4" s="67"/>
       <c r="J4" s="68"/>
-      <c r="K4" s="457"/>
-      <c r="L4" s="458"/>
-      <c r="M4" s="458"/>
-      <c r="N4" s="458"/>
+      <c r="K4" s="459"/>
+      <c r="L4" s="460"/>
+      <c r="M4" s="460"/>
+      <c r="N4" s="460"/>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C5" s="147" t="s">
@@ -16990,10 +16992,10 @@
       </c>
       <c r="I5" s="67"/>
       <c r="J5" s="68"/>
-      <c r="K5" s="457"/>
-      <c r="L5" s="458"/>
-      <c r="M5" s="458"/>
-      <c r="N5" s="458"/>
+      <c r="K5" s="459"/>
+      <c r="L5" s="460"/>
+      <c r="M5" s="460"/>
+      <c r="N5" s="460"/>
     </row>
     <row r="6" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" s="147" t="s">
@@ -17006,14 +17008,14 @@
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
       <c r="J6" s="69"/>
-      <c r="K6" s="457"/>
-      <c r="L6" s="458"/>
-      <c r="M6" s="458"/>
-      <c r="N6" s="458"/>
+      <c r="K6" s="459"/>
+      <c r="L6" s="460"/>
+      <c r="M6" s="460"/>
+      <c r="N6" s="460"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C7" s="448" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D7" s="449"/>
       <c r="E7" s="449"/>
@@ -17022,12 +17024,12 @@
       <c r="H7" s="449"/>
       <c r="I7" s="449"/>
       <c r="J7" s="450"/>
-      <c r="K7" s="459" t="s">
-        <v>362</v>
-      </c>
-      <c r="L7" s="460"/>
-      <c r="M7" s="460"/>
-      <c r="N7" s="460"/>
+      <c r="K7" s="461" t="s">
+        <v>361</v>
+      </c>
+      <c r="L7" s="462"/>
+      <c r="M7" s="462"/>
+      <c r="N7" s="462"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C8" s="451"/>
@@ -17038,10 +17040,10 @@
       <c r="H8" s="452"/>
       <c r="I8" s="452"/>
       <c r="J8" s="453"/>
-      <c r="K8" s="459"/>
-      <c r="L8" s="460"/>
-      <c r="M8" s="460"/>
-      <c r="N8" s="460"/>
+      <c r="K8" s="461"/>
+      <c r="L8" s="462"/>
+      <c r="M8" s="462"/>
+      <c r="N8" s="462"/>
     </row>
     <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="454"/>
@@ -17052,10 +17054,10 @@
       <c r="H9" s="455"/>
       <c r="I9" s="455"/>
       <c r="J9" s="456"/>
-      <c r="K9" s="459"/>
-      <c r="L9" s="460"/>
-      <c r="M9" s="460"/>
-      <c r="N9" s="460"/>
+      <c r="K9" s="461"/>
+      <c r="L9" s="462"/>
+      <c r="M9" s="462"/>
+      <c r="N9" s="462"/>
     </row>
     <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:14" x14ac:dyDescent="0.25">
@@ -17089,7 +17091,7 @@
         <v>166</v>
       </c>
       <c r="H13" s="90" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I13" s="67"/>
       <c r="J13" s="68"/>
@@ -17137,7 +17139,7 @@
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C16" s="448" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D16" s="449"/>
       <c r="E16" s="449"/>
@@ -17207,7 +17209,7 @@
         <v>166</v>
       </c>
       <c r="H22" s="90" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I22" s="67"/>
       <c r="J22" s="68"/>
@@ -17252,7 +17254,7 @@
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="448" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D25" s="449"/>
       <c r="E25" s="449"/>
@@ -17324,7 +17326,7 @@
         <v>166</v>
       </c>
       <c r="H31" s="90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I31" s="67"/>
       <c r="J31" s="68"/>
@@ -17372,7 +17374,7 @@
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C34" s="448" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D34" s="449"/>
       <c r="E34" s="449"/>
@@ -17440,7 +17442,7 @@
         <v>166</v>
       </c>
       <c r="H40" s="90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I40" s="67"/>
       <c r="J40" s="68"/>
@@ -17488,7 +17490,7 @@
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43" s="448" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D43" s="449"/>
       <c r="E43" s="449"/>
@@ -17598,7 +17600,7 @@
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C52" s="448" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D52" s="449"/>
       <c r="E52" s="449"/>
@@ -17706,7 +17708,7 @@
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C61" s="448" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D61" s="449"/>
       <c r="E61" s="449"/>
@@ -17814,7 +17816,7 @@
     </row>
     <row r="70" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C70" s="448" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D70" s="449"/>
       <c r="E70" s="449"/>
@@ -17922,7 +17924,7 @@
     </row>
     <row r="79" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C79" s="448" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D79" s="449"/>
       <c r="E79" s="449"/>
@@ -18030,7 +18032,7 @@
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C88" s="448" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D88" s="449"/>
       <c r="E88" s="449"/>
@@ -18113,7 +18115,7 @@
         <v>166</v>
       </c>
       <c r="H97" s="90" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I97" s="67"/>
       <c r="J97" s="68"/>
@@ -18158,7 +18160,7 @@
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C100" s="448" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D100" s="449"/>
       <c r="E100" s="449"/>
@@ -18243,7 +18245,7 @@
         <v>166</v>
       </c>
       <c r="H106" s="90" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I106" s="67"/>
       <c r="J106" s="68"/>
@@ -18288,7 +18290,7 @@
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C109" s="448" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D109" s="449"/>
       <c r="E109" s="449"/>
@@ -18394,7 +18396,7 @@
     </row>
     <row r="118" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C118" s="448" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D118" s="449"/>
       <c r="E118" s="449"/>
@@ -18500,7 +18502,7 @@
     </row>
     <row r="127" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C127" s="448" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D127" s="449"/>
       <c r="E127" s="449"/>
@@ -18606,7 +18608,7 @@
     </row>
     <row r="136" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C136" s="448" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D136" s="449"/>
       <c r="E136" s="449"/>
@@ -18712,7 +18714,7 @@
     </row>
     <row r="145" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C145" s="448" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D145" s="449"/>
       <c r="E145" s="449"/>
@@ -18796,11 +18798,11 @@
       <c r="G151" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H151" s="461" t="s">
-        <v>356</v>
-      </c>
-      <c r="I151" s="461"/>
-      <c r="J151" s="462"/>
+      <c r="H151" s="457" t="s">
+        <v>355</v>
+      </c>
+      <c r="I151" s="457"/>
+      <c r="J151" s="458"/>
       <c r="K151" s="347"/>
       <c r="L151" s="347"/>
     </row>
@@ -18820,7 +18822,7 @@
     </row>
     <row r="153" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C153" s="448" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D153" s="449"/>
       <c r="E153" s="449"/>
@@ -18925,11 +18927,11 @@
       <c r="G160" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H160" s="461">
+      <c r="H160" s="457">
         <v>119</v>
       </c>
-      <c r="I160" s="461"/>
-      <c r="J160" s="462"/>
+      <c r="I160" s="457"/>
+      <c r="J160" s="458"/>
       <c r="K160" s="347"/>
       <c r="L160" s="347"/>
     </row>
@@ -18949,7 +18951,7 @@
     </row>
     <row r="162" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C162" s="448" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D162" s="449"/>
       <c r="E162" s="449"/>
@@ -19052,11 +19054,11 @@
       <c r="G169" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H169" s="461">
+      <c r="H169" s="457">
         <v>80</v>
       </c>
-      <c r="I169" s="461"/>
-      <c r="J169" s="462"/>
+      <c r="I169" s="457"/>
+      <c r="J169" s="458"/>
       <c r="K169" s="347"/>
       <c r="L169" s="347"/>
     </row>
@@ -19076,7 +19078,7 @@
     </row>
     <row r="171" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C171" s="448" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D171" s="449"/>
       <c r="E171" s="449"/>
@@ -19162,11 +19164,11 @@
       <c r="G177" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H177" s="461">
+      <c r="H177" s="457">
         <v>64</v>
       </c>
-      <c r="I177" s="461"/>
-      <c r="J177" s="462"/>
+      <c r="I177" s="457"/>
+      <c r="J177" s="458"/>
       <c r="K177" s="347"/>
       <c r="L177" s="347"/>
     </row>
@@ -19186,7 +19188,7 @@
     </row>
     <row r="179" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C179" s="448" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D179" s="449"/>
       <c r="E179" s="449"/>
@@ -19272,11 +19274,11 @@
       <c r="G186" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H186" s="461">
+      <c r="H186" s="457">
         <v>28</v>
       </c>
-      <c r="I186" s="461"/>
-      <c r="J186" s="462"/>
+      <c r="I186" s="457"/>
+      <c r="J186" s="458"/>
       <c r="K186" s="347"/>
       <c r="L186" s="347"/>
     </row>
@@ -19296,7 +19298,7 @@
     </row>
     <row r="188" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C188" s="448" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D188" s="449"/>
       <c r="E188" s="449"/>
@@ -19382,11 +19384,11 @@
       <c r="G195" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H195" s="461">
+      <c r="H195" s="457">
         <v>61</v>
       </c>
-      <c r="I195" s="461"/>
-      <c r="J195" s="462"/>
+      <c r="I195" s="457"/>
+      <c r="J195" s="458"/>
       <c r="K195" s="347"/>
       <c r="L195" s="347"/>
     </row>
@@ -19406,7 +19408,7 @@
     </row>
     <row r="197" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C197" s="448" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D197" s="449"/>
       <c r="E197" s="449"/>
@@ -19489,11 +19491,11 @@
       <c r="G204" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H204" s="461">
+      <c r="H204" s="457">
         <v>97</v>
       </c>
-      <c r="I204" s="461"/>
-      <c r="J204" s="462"/>
+      <c r="I204" s="457"/>
+      <c r="J204" s="458"/>
       <c r="K204" s="347"/>
     </row>
     <row r="205" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19511,7 +19513,7 @@
     </row>
     <row r="206" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C206" s="448" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D206" s="449"/>
       <c r="E206" s="449"/>
@@ -19618,7 +19620,7 @@
     </row>
     <row r="215" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C215" s="448" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D215" s="449"/>
       <c r="E215" s="449"/>
@@ -19681,7 +19683,7 @@
         <v>166</v>
       </c>
       <c r="H221" s="90" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I221" s="67"/>
       <c r="J221" s="68"/>
@@ -19726,7 +19728,7 @@
     </row>
     <row r="224" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C224" s="448" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D224" s="449"/>
       <c r="E224" s="449"/>
@@ -19791,7 +19793,7 @@
         <v>166</v>
       </c>
       <c r="H230" s="90" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I230" s="67"/>
       <c r="J230" s="68"/>
@@ -19836,7 +19838,7 @@
     </row>
     <row r="233" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C233" s="448" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D233" s="449"/>
       <c r="E233" s="449"/>
@@ -19941,7 +19943,7 @@
     </row>
     <row r="242" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C242" s="448" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D242" s="449"/>
       <c r="E242" s="449"/>
@@ -20045,7 +20047,7 @@
     </row>
     <row r="251" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C251" s="448" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D251" s="449"/>
       <c r="E251" s="449"/>
@@ -20083,27 +20085,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C242:J244"/>
-    <mergeCell ref="C206:J208"/>
-    <mergeCell ref="C215:J217"/>
-    <mergeCell ref="C224:J226"/>
-    <mergeCell ref="H186:J186"/>
-    <mergeCell ref="C188:J190"/>
-    <mergeCell ref="H195:J195"/>
-    <mergeCell ref="C197:J199"/>
-    <mergeCell ref="H204:J204"/>
-    <mergeCell ref="C233:J235"/>
-    <mergeCell ref="H160:J160"/>
-    <mergeCell ref="C162:J164"/>
-    <mergeCell ref="H169:J169"/>
-    <mergeCell ref="C171:J173"/>
-    <mergeCell ref="H177:J177"/>
-    <mergeCell ref="C118:J120"/>
-    <mergeCell ref="C127:J129"/>
-    <mergeCell ref="C136:J138"/>
-    <mergeCell ref="C145:J147"/>
-    <mergeCell ref="C153:J155"/>
-    <mergeCell ref="H151:J151"/>
     <mergeCell ref="C251:J253"/>
     <mergeCell ref="C109:J111"/>
     <mergeCell ref="C100:J102"/>
@@ -20120,6 +20101,27 @@
     <mergeCell ref="C52:J54"/>
     <mergeCell ref="K7:N9"/>
     <mergeCell ref="C179:J181"/>
+    <mergeCell ref="C118:J120"/>
+    <mergeCell ref="C127:J129"/>
+    <mergeCell ref="C136:J138"/>
+    <mergeCell ref="C145:J147"/>
+    <mergeCell ref="C153:J155"/>
+    <mergeCell ref="H151:J151"/>
+    <mergeCell ref="H160:J160"/>
+    <mergeCell ref="C162:J164"/>
+    <mergeCell ref="H169:J169"/>
+    <mergeCell ref="C171:J173"/>
+    <mergeCell ref="H177:J177"/>
+    <mergeCell ref="C242:J244"/>
+    <mergeCell ref="C206:J208"/>
+    <mergeCell ref="C215:J217"/>
+    <mergeCell ref="C224:J226"/>
+    <mergeCell ref="H186:J186"/>
+    <mergeCell ref="C188:J190"/>
+    <mergeCell ref="H195:J195"/>
+    <mergeCell ref="C197:J199"/>
+    <mergeCell ref="H204:J204"/>
+    <mergeCell ref="C233:J235"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20139,36 +20141,36 @@
   <sheetData>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="135" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F6" s="135" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D7" s="11">
         <v>2700000</v>
       </c>
       <c r="F7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G7" s="13">
         <f>D11</f>
         <v>969506.92</v>
       </c>
       <c r="I7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J7" s="13">
         <f>G13</f>
@@ -20177,19 +20179,19 @@
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D8" s="11">
         <v>2700000</v>
       </c>
       <c r="F8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G8" s="11">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J8" s="13">
         <f>D11</f>
@@ -20198,20 +20200,20 @@
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D9" s="11">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G9" s="13">
         <f>G7</f>
         <v>969506.92</v>
       </c>
       <c r="I9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J9" s="13">
         <f>J7-J8</f>
@@ -20220,17 +20222,17 @@
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D10" s="11"/>
       <c r="F10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G10" s="11">
         <v>29928.678620400002</v>
       </c>
       <c r="I10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J10" s="11">
         <v>26537.673329999998</v>
@@ -20238,50 +20240,50 @@
     </row>
     <row r="11" spans="3:10" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D11" s="11">
         <v>969506.92</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G11" s="11">
         <f>387244.626816+185936.292610276+202702.7028</f>
         <v>775883.62222627597</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D12" s="13">
         <f>D11</f>
         <v>969506.92</v>
       </c>
       <c r="F12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G12" s="13">
         <f>G11+G10+G9</f>
         <v>1775319.220846676</v>
       </c>
       <c r="I12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J12" s="368" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G13" s="11">
         <v>1829165.92</v>
@@ -20292,11 +20294,11 @@
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F15" s="463" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G15" s="463"/>
       <c r="I15" s="463" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J15" s="463"/>
     </row>
@@ -20315,13 +20317,13 @@
     <row r="18" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="372" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D19" s="373"/>
       <c r="E19" s="373"/>
       <c r="F19" s="374"/>
       <c r="G19" s="464" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H19" s="465"/>
       <c r="I19" s="465"/>
@@ -20329,7 +20331,7 @@
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="375" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F20" s="376">
         <v>859658.99999999988</v>
@@ -20341,7 +20343,7 @@
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="375" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F21" s="376">
         <v>26537.673329999998</v>
@@ -20353,7 +20355,7 @@
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="375" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F22" s="377">
         <v>850000</v>
@@ -20373,7 +20375,7 @@
     </row>
     <row r="24" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C24" s="369" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D24" s="370"/>
       <c r="E24" s="370"/>

--- a/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
+++ b/BRISAS/EXPENSAS/2026/FEBRERO/BRISAS-FEBRERO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB875B8-CD9E-4174-895E-6040CF1BD9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5933F3BE-A291-47A1-9C23-5192A8FCE660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2919,6 +2919,13 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2931,36 +2938,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2994,50 +2982,46 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3096,7 +3080,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3124,12 +3125,6 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3141,6 +3136,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3172,7 +3173,6 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -3605,34 +3605,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="408"/>
-      <c r="B1" s="403" t="s">
+      <c r="A1" s="406"/>
+      <c r="B1" s="401" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="404"/>
-      <c r="D1" s="404"/>
-      <c r="E1" s="405"/>
+      <c r="C1" s="402"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="403"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="409"/>
-      <c r="B2" s="403" t="s">
+      <c r="A2" s="407"/>
+      <c r="B2" s="401" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="404"/>
-      <c r="D2" s="404"/>
-      <c r="E2" s="405"/>
+      <c r="C2" s="402"/>
+      <c r="D2" s="402"/>
+      <c r="E2" s="403"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="409"/>
-      <c r="B3" s="400" t="s">
+      <c r="A3" s="407"/>
+      <c r="B3" s="398" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="401"/>
-      <c r="D3" s="401"/>
-      <c r="E3" s="402"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="400"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="409"/>
+      <c r="A4" s="407"/>
       <c r="B4" s="47" t="s">
         <v>156</v>
       </c>
@@ -3641,7 +3641,7 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="409"/>
+      <c r="A5" s="407"/>
       <c r="B5" s="50" t="s">
         <v>391</v>
       </c>
@@ -3650,7 +3650,7 @@
       <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="409"/>
+      <c r="A6" s="407"/>
       <c r="B6" s="51" t="s">
         <v>286</v>
       </c>
@@ -3659,7 +3659,7 @@
       <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="409"/>
+      <c r="A7" s="407"/>
       <c r="B7" s="51" t="s">
         <v>285</v>
       </c>
@@ -3668,36 +3668,36 @@
       <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="410"/>
-      <c r="B8" s="406" t="s">
+      <c r="A8" s="408"/>
+      <c r="B8" s="404" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="406"/>
-      <c r="D8" s="406"/>
-      <c r="E8" s="407"/>
+      <c r="C8" s="404"/>
+      <c r="D8" s="404"/>
+      <c r="E8" s="405"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="411" t="s">
+      <c r="A10" s="393" t="s">
         <v>494</v>
       </c>
-      <c r="B10" s="411"/>
-      <c r="C10" s="411"/>
-      <c r="D10" s="411"/>
-      <c r="E10" s="411"/>
+      <c r="B10" s="393"/>
+      <c r="C10" s="393"/>
+      <c r="D10" s="393"/>
+      <c r="E10" s="393"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="411"/>
-      <c r="B11" s="411"/>
-      <c r="C11" s="411"/>
-      <c r="D11" s="411"/>
-      <c r="E11" s="411"/>
+      <c r="A11" s="393"/>
+      <c r="B11" s="393"/>
+      <c r="C11" s="393"/>
+      <c r="D11" s="393"/>
+      <c r="E11" s="393"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="411"/>
-      <c r="B12" s="411"/>
-      <c r="C12" s="411"/>
-      <c r="D12" s="411"/>
-      <c r="E12" s="411"/>
+      <c r="A12" s="393"/>
+      <c r="B12" s="393"/>
+      <c r="C12" s="393"/>
+      <c r="D12" s="393"/>
+      <c r="E12" s="393"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="32"/>
@@ -3714,34 +3714,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="412" t="s">
+      <c r="A15" s="394" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="412"/>
-      <c r="C15" s="412"/>
-      <c r="D15" s="412"/>
-      <c r="E15" s="412"/>
+      <c r="B15" s="394"/>
+      <c r="C15" s="394"/>
+      <c r="D15" s="394"/>
+      <c r="E15" s="394"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="412"/>
-      <c r="B16" s="412"/>
-      <c r="C16" s="412"/>
-      <c r="D16" s="412"/>
-      <c r="E16" s="412"/>
+      <c r="A16" s="394"/>
+      <c r="B16" s="394"/>
+      <c r="C16" s="394"/>
+      <c r="D16" s="394"/>
+      <c r="E16" s="394"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="412"/>
-      <c r="B17" s="412"/>
-      <c r="C17" s="412"/>
-      <c r="D17" s="412"/>
-      <c r="E17" s="412"/>
+      <c r="A17" s="394"/>
+      <c r="B17" s="394"/>
+      <c r="C17" s="394"/>
+      <c r="D17" s="394"/>
+      <c r="E17" s="394"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="412"/>
-      <c r="B18" s="412"/>
-      <c r="C18" s="412"/>
-      <c r="D18" s="412"/>
-      <c r="E18" s="412"/>
+      <c r="A18" s="394"/>
+      <c r="B18" s="394"/>
+      <c r="C18" s="394"/>
+      <c r="D18" s="394"/>
+      <c r="E18" s="394"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32"/>
@@ -3797,10 +3797,10 @@
       <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="414" t="s">
+      <c r="A25" s="396" t="s">
         <v>393</v>
       </c>
-      <c r="B25" s="415"/>
+      <c r="B25" s="397"/>
       <c r="C25" s="24"/>
       <c r="D25" s="382">
         <v>-435318.34</v>
@@ -3809,10 +3809,10 @@
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="416" t="s">
+      <c r="A26" s="387" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="417"/>
+      <c r="B26" s="388"/>
       <c r="C26" s="24"/>
       <c r="D26" s="382">
         <v>0.81</v>
@@ -3840,10 +3840,10 @@
       <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="388" t="s">
+      <c r="A28" s="391" t="s">
         <v>314</v>
       </c>
-      <c r="B28" s="389"/>
+      <c r="B28" s="392"/>
       <c r="C28" s="24"/>
       <c r="D28" s="382">
         <v>920000</v>
@@ -3976,10 +3976,10 @@
       <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="386" t="s">
+      <c r="A38" s="389" t="s">
         <v>272</v>
       </c>
-      <c r="B38" s="387"/>
+      <c r="B38" s="390"/>
       <c r="C38" s="24"/>
       <c r="D38" s="231">
         <v>148964</v>
@@ -3989,10 +3989,10 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="386" t="s">
+      <c r="A39" s="389" t="s">
         <v>273</v>
       </c>
-      <c r="B39" s="387"/>
+      <c r="B39" s="390"/>
       <c r="C39" s="24"/>
       <c r="D39" s="231">
         <v>6160</v>
@@ -4002,10 +4002,10 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="386" t="s">
+      <c r="A40" s="389" t="s">
         <v>317</v>
       </c>
-      <c r="B40" s="387"/>
+      <c r="B40" s="390"/>
       <c r="C40" s="24"/>
       <c r="D40" s="231">
         <v>23596</v>
@@ -4015,10 +4015,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="386" t="s">
+      <c r="A41" s="389" t="s">
         <v>316</v>
       </c>
-      <c r="B41" s="387"/>
+      <c r="B41" s="390"/>
       <c r="C41" s="24"/>
       <c r="D41" s="231"/>
       <c r="E41" s="85"/>
@@ -4045,10 +4045,10 @@
       <c r="E43" s="29"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="386" t="s">
+      <c r="A44" s="389" t="s">
         <v>398</v>
       </c>
-      <c r="B44" s="413"/>
+      <c r="B44" s="395"/>
       <c r="C44" s="112"/>
       <c r="D44" s="231">
         <v>44907682.960000001</v>
@@ -4060,10 +4060,10 @@
       <c r="I44" s="40"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="386" t="s">
+      <c r="A45" s="389" t="s">
         <v>399</v>
       </c>
-      <c r="B45" s="413"/>
+      <c r="B45" s="395"/>
       <c r="C45" s="112"/>
       <c r="D45" s="231">
         <v>4773198.96</v>
@@ -4097,10 +4097,10 @@
       <c r="E47" s="72"/>
     </row>
     <row r="48" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="386" t="s">
+      <c r="A48" s="389" t="s">
         <v>329</v>
       </c>
-      <c r="B48" s="413"/>
+      <c r="B48" s="395"/>
       <c r="C48" s="112"/>
       <c r="D48" s="231">
         <v>1212341.6499999999</v>
@@ -4110,10 +4110,10 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="386" t="s">
+      <c r="A49" s="389" t="s">
         <v>382</v>
       </c>
-      <c r="B49" s="413"/>
+      <c r="B49" s="395"/>
       <c r="C49" s="112"/>
       <c r="D49" s="231">
         <v>1512500</v>
@@ -4123,10 +4123,10 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="386" t="s">
+      <c r="A50" s="389" t="s">
         <v>413</v>
       </c>
-      <c r="B50" s="413"/>
+      <c r="B50" s="395"/>
       <c r="C50" s="112"/>
       <c r="D50" s="231">
         <v>5445000</v>
@@ -4136,10 +4136,10 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="386" t="s">
+      <c r="A51" s="389" t="s">
         <v>383</v>
       </c>
-      <c r="B51" s="387"/>
+      <c r="B51" s="390"/>
       <c r="C51" s="113"/>
       <c r="D51" s="231">
         <v>480000</v>
@@ -4150,10 +4150,10 @@
       <c r="G51" s="36"/>
     </row>
     <row r="52" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="386" t="s">
+      <c r="A52" s="389" t="s">
         <v>423</v>
       </c>
-      <c r="B52" s="387"/>
+      <c r="B52" s="390"/>
       <c r="C52" s="113"/>
       <c r="D52" s="231">
         <v>6300000</v>
@@ -4163,10 +4163,10 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="386" t="s">
+      <c r="A53" s="389" t="s">
         <v>384</v>
       </c>
-      <c r="B53" s="387"/>
+      <c r="B53" s="390"/>
       <c r="C53" s="113"/>
       <c r="D53" s="231">
         <v>228690</v>
@@ -4176,10 +4176,10 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="386" t="s">
+      <c r="A54" s="389" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="387"/>
+      <c r="B54" s="390"/>
       <c r="C54" s="113"/>
       <c r="D54" s="231">
         <v>228690</v>
@@ -4189,10 +4189,10 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="386" t="s">
+      <c r="A55" s="389" t="s">
         <v>409</v>
       </c>
-      <c r="B55" s="387"/>
+      <c r="B55" s="390"/>
       <c r="C55" s="113"/>
       <c r="D55" s="231">
         <v>943800</v>
@@ -4202,10 +4202,10 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="386" t="s">
+      <c r="A56" s="389" t="s">
         <v>408</v>
       </c>
-      <c r="B56" s="387"/>
+      <c r="B56" s="390"/>
       <c r="C56" s="113"/>
       <c r="D56" s="231">
         <v>943800</v>
@@ -4215,10 +4215,10 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="386" t="s">
+      <c r="A57" s="389" t="s">
         <v>375</v>
       </c>
-      <c r="B57" s="387"/>
+      <c r="B57" s="390"/>
       <c r="C57" s="113"/>
       <c r="D57" s="231">
         <v>820380</v>
@@ -4228,10 +4228,10 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="386" t="s">
+      <c r="A58" s="389" t="s">
         <v>376</v>
       </c>
-      <c r="B58" s="387"/>
+      <c r="B58" s="390"/>
       <c r="C58" s="113"/>
       <c r="D58" s="231">
         <v>820380</v>
@@ -4241,10 +4241,10 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="386" t="s">
+      <c r="A59" s="389" t="s">
         <v>378</v>
       </c>
-      <c r="B59" s="387"/>
+      <c r="B59" s="390"/>
       <c r="C59" s="113"/>
       <c r="D59" s="231">
         <v>100000</v>
@@ -4254,10 +4254,10 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="386" t="s">
+      <c r="A60" s="389" t="s">
         <v>415</v>
       </c>
-      <c r="B60" s="387"/>
+      <c r="B60" s="390"/>
       <c r="C60" s="113"/>
       <c r="D60" s="231">
         <v>100000</v>
@@ -4267,10 +4267,10 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="386" t="s">
+      <c r="A61" s="389" t="s">
         <v>428</v>
       </c>
-      <c r="B61" s="387"/>
+      <c r="B61" s="390"/>
       <c r="C61" s="24"/>
       <c r="D61" s="149">
         <v>200000</v>
@@ -4282,10 +4282,10 @@
       <c r="H61" s="97"/>
     </row>
     <row r="62" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="386" t="s">
+      <c r="A62" s="389" t="s">
         <v>403</v>
       </c>
-      <c r="B62" s="387"/>
+      <c r="B62" s="390"/>
       <c r="C62" s="24"/>
       <c r="D62" s="231">
         <v>2459883</v>
@@ -4297,10 +4297,10 @@
       <c r="H62" s="97"/>
     </row>
     <row r="63" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="386" t="s">
+      <c r="A63" s="389" t="s">
         <v>287</v>
       </c>
-      <c r="B63" s="387"/>
+      <c r="B63" s="390"/>
       <c r="C63" s="24"/>
       <c r="D63" s="231">
         <v>350000</v>
@@ -4333,10 +4333,10 @@
       <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="388" t="s">
+      <c r="A66" s="391" t="s">
         <v>427</v>
       </c>
-      <c r="B66" s="389"/>
+      <c r="B66" s="392"/>
       <c r="C66" s="24"/>
       <c r="D66" s="149">
         <v>280000</v>
@@ -4346,10 +4346,10 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="388" t="s">
+      <c r="A67" s="391" t="s">
         <v>379</v>
       </c>
-      <c r="B67" s="389"/>
+      <c r="B67" s="392"/>
       <c r="C67" s="24"/>
       <c r="D67" s="149">
         <v>250000</v>
@@ -4359,10 +4359,10 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="388" t="s">
+      <c r="A68" s="391" t="s">
         <v>381</v>
       </c>
-      <c r="B68" s="389"/>
+      <c r="B68" s="392"/>
       <c r="C68" s="24"/>
       <c r="D68" s="149">
         <v>150000</v>
@@ -4372,10 +4372,10 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="123.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="386" t="s">
+      <c r="A69" s="389" t="s">
         <v>424</v>
       </c>
-      <c r="B69" s="387"/>
+      <c r="B69" s="390"/>
       <c r="C69" s="109"/>
       <c r="D69" s="149">
         <v>2130000</v>
@@ -4385,10 +4385,10 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="386" t="s">
+      <c r="A70" s="389" t="s">
         <v>491</v>
       </c>
-      <c r="B70" s="387"/>
+      <c r="B70" s="390"/>
       <c r="C70" s="109"/>
       <c r="D70" s="149">
         <v>150000</v>
@@ -4402,10 +4402,10 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="386" t="s">
+      <c r="A71" s="389" t="s">
         <v>404</v>
       </c>
-      <c r="B71" s="387"/>
+      <c r="B71" s="390"/>
       <c r="C71" s="109"/>
       <c r="D71" s="149">
         <v>2200000</v>
@@ -4415,10 +4415,10 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="386" t="s">
+      <c r="A72" s="389" t="s">
         <v>432</v>
       </c>
-      <c r="B72" s="387"/>
+      <c r="B72" s="390"/>
       <c r="C72" s="24"/>
       <c r="D72" s="149">
         <v>320000</v>
@@ -4428,10 +4428,10 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="386" t="s">
+      <c r="A73" s="389" t="s">
         <v>425</v>
       </c>
-      <c r="B73" s="387"/>
+      <c r="B73" s="390"/>
       <c r="C73" s="109"/>
       <c r="D73" s="149">
         <v>1050000</v>
@@ -4442,10 +4442,10 @@
       <c r="F73" s="97"/>
     </row>
     <row r="74" spans="1:7" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="386" t="s">
+      <c r="A74" s="389" t="s">
         <v>426</v>
       </c>
-      <c r="B74" s="387"/>
+      <c r="B74" s="390"/>
       <c r="C74" s="109"/>
       <c r="D74" s="149">
         <v>1390000</v>
@@ -4455,10 +4455,10 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="386" t="s">
+      <c r="A75" s="389" t="s">
         <v>439</v>
       </c>
-      <c r="B75" s="387"/>
+      <c r="B75" s="390"/>
       <c r="C75" s="109"/>
       <c r="D75" s="149">
         <v>3000000</v>
@@ -4468,10 +4468,10 @@
       </c>
     </row>
     <row r="76" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="386" t="s">
+      <c r="A76" s="389" t="s">
         <v>416</v>
       </c>
-      <c r="B76" s="387"/>
+      <c r="B76" s="390"/>
       <c r="C76" s="109"/>
       <c r="D76" s="149">
         <v>319377.61</v>
@@ -4481,10 +4481,10 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="386" t="s">
+      <c r="A77" s="389" t="s">
         <v>492</v>
       </c>
-      <c r="B77" s="387"/>
+      <c r="B77" s="390"/>
       <c r="C77" s="109"/>
       <c r="D77" s="149">
         <v>112180.05</v>
@@ -4494,10 +4494,10 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="386" t="s">
+      <c r="A78" s="389" t="s">
         <v>441</v>
       </c>
-      <c r="B78" s="387"/>
+      <c r="B78" s="390"/>
       <c r="C78" s="109"/>
       <c r="D78" s="149">
         <v>73716.19</v>
@@ -4507,10 +4507,10 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="386" t="s">
+      <c r="A79" s="389" t="s">
         <v>442</v>
       </c>
-      <c r="B79" s="387"/>
+      <c r="B79" s="390"/>
       <c r="C79" s="109"/>
       <c r="D79" s="149">
         <v>588090.9</v>
@@ -4521,10 +4521,10 @@
       <c r="F79" s="97"/>
     </row>
     <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="386" t="s">
+      <c r="A80" s="389" t="s">
         <v>443</v>
       </c>
-      <c r="B80" s="387"/>
+      <c r="B80" s="390"/>
       <c r="C80" s="109"/>
       <c r="D80" s="149">
         <v>54497.599999999999</v>
@@ -4534,10 +4534,10 @@
       </c>
     </row>
     <row r="81" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="386" t="s">
+      <c r="A81" s="389" t="s">
         <v>444</v>
       </c>
-      <c r="B81" s="387"/>
+      <c r="B81" s="390"/>
       <c r="C81" s="109"/>
       <c r="D81" s="149">
         <v>160307.04</v>
@@ -4547,10 +4547,10 @@
       </c>
     </row>
     <row r="82" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="386" t="s">
+      <c r="A82" s="389" t="s">
         <v>447</v>
       </c>
-      <c r="B82" s="387"/>
+      <c r="B82" s="390"/>
       <c r="C82" s="109"/>
       <c r="D82" s="149">
         <v>12</v>
@@ -4560,10 +4560,10 @@
       </c>
     </row>
     <row r="83" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="386" t="s">
+      <c r="A83" s="389" t="s">
         <v>389</v>
       </c>
-      <c r="B83" s="387"/>
+      <c r="B83" s="390"/>
       <c r="C83" s="109"/>
       <c r="D83" s="149">
         <v>97200</v>
@@ -4573,10 +4573,10 @@
       </c>
     </row>
     <row r="84" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="386" t="s">
+      <c r="A84" s="389" t="s">
         <v>431</v>
       </c>
-      <c r="B84" s="387"/>
+      <c r="B84" s="390"/>
       <c r="C84" s="109"/>
       <c r="D84" s="149">
         <v>146099</v>
@@ -4586,10 +4586,10 @@
       </c>
     </row>
     <row r="85" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="386" t="s">
+      <c r="A85" s="389" t="s">
         <v>450</v>
       </c>
-      <c r="B85" s="387"/>
+      <c r="B85" s="390"/>
       <c r="C85" s="109"/>
       <c r="D85" s="149">
         <v>681000</v>
@@ -4599,10 +4599,10 @@
       </c>
     </row>
     <row r="86" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="386" t="s">
+      <c r="A86" s="389" t="s">
         <v>387</v>
       </c>
-      <c r="B86" s="387"/>
+      <c r="B86" s="390"/>
       <c r="C86" s="109"/>
       <c r="D86" s="149">
         <v>481000</v>
@@ -4633,19 +4633,19 @@
       <c r="E88" s="26"/>
     </row>
     <row r="89" spans="1:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="386" t="s">
+      <c r="A89" s="389" t="s">
         <v>496</v>
       </c>
-      <c r="B89" s="387"/>
+      <c r="B89" s="390"/>
       <c r="C89" s="24"/>
       <c r="D89" s="365"/>
       <c r="E89" s="96"/>
     </row>
     <row r="90" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="386" t="s">
+      <c r="A90" s="389" t="s">
         <v>410</v>
       </c>
-      <c r="B90" s="387"/>
+      <c r="B90" s="390"/>
       <c r="C90" s="24"/>
       <c r="D90" s="365">
         <v>1900000</v>
@@ -4763,10 +4763,10 @@
       <c r="E101" s="44"/>
     </row>
     <row r="102" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="386" t="s">
+      <c r="A102" s="389" t="s">
         <v>388</v>
       </c>
-      <c r="B102" s="387"/>
+      <c r="B102" s="390"/>
       <c r="C102" s="24"/>
       <c r="D102" s="231">
         <v>452107.07</v>
@@ -4776,10 +4776,10 @@
       </c>
     </row>
     <row r="103" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="386" t="s">
+      <c r="A103" s="389" t="s">
         <v>330</v>
       </c>
-      <c r="B103" s="387"/>
+      <c r="B103" s="390"/>
       <c r="C103" s="24"/>
       <c r="D103" s="231">
         <v>74126.81</v>
@@ -4789,10 +4789,10 @@
       </c>
     </row>
     <row r="104" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="386" t="s">
+      <c r="A104" s="389" t="s">
         <v>331</v>
       </c>
-      <c r="B104" s="387"/>
+      <c r="B104" s="390"/>
       <c r="C104" s="24"/>
       <c r="D104" s="231">
         <v>74126.81</v>
@@ -4803,10 +4803,10 @@
       </c>
     </row>
     <row r="105" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="386" t="s">
+      <c r="A105" s="389" t="s">
         <v>332</v>
       </c>
-      <c r="B105" s="387"/>
+      <c r="B105" s="390"/>
       <c r="C105" s="24"/>
       <c r="D105" s="231">
         <v>75556.14</v>
@@ -4817,10 +4817,10 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="388" t="s">
+      <c r="A106" s="391" t="s">
         <v>377</v>
       </c>
-      <c r="B106" s="389"/>
+      <c r="B106" s="392"/>
       <c r="C106" s="24"/>
       <c r="D106" s="231">
         <v>1114493.6200000001</v>
@@ -4830,10 +4830,10 @@
       </c>
     </row>
     <row r="107" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="388" t="s">
+      <c r="A107" s="391" t="s">
         <v>192</v>
       </c>
-      <c r="B107" s="389"/>
+      <c r="B107" s="392"/>
       <c r="C107" s="24"/>
       <c r="D107" s="231">
         <v>6056.84</v>
@@ -4844,10 +4844,10 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="388" t="s">
+      <c r="A108" s="391" t="s">
         <v>305</v>
       </c>
-      <c r="B108" s="389"/>
+      <c r="B108" s="392"/>
       <c r="C108" s="24"/>
       <c r="D108" s="231"/>
       <c r="E108" s="24" t="s">
@@ -4886,10 +4886,10 @@
       <c r="E111" s="52"/>
     </row>
     <row r="112" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="388" t="s">
+      <c r="A112" s="391" t="s">
         <v>395</v>
       </c>
-      <c r="B112" s="389"/>
+      <c r="B112" s="392"/>
       <c r="C112" s="24"/>
       <c r="D112" s="385">
         <v>5816279.9100000001</v>
@@ -4899,8 +4899,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="388"/>
-      <c r="B113" s="389"/>
+      <c r="A113" s="391"/>
+      <c r="B113" s="392"/>
       <c r="C113" s="24"/>
       <c r="D113" s="149"/>
       <c r="E113" s="86"/>
@@ -4967,10 +4967,10 @@
       <c r="E120" s="59"/>
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="397" t="s">
+      <c r="A121" s="416" t="s">
         <v>400</v>
       </c>
-      <c r="B121" s="397"/>
+      <c r="B121" s="416"/>
       <c r="C121" s="24"/>
       <c r="D121" s="231">
         <f>1500871-920000</f>
@@ -4982,10 +4982,10 @@
       </c>
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="386" t="s">
+      <c r="A122" s="389" t="s">
         <v>402</v>
       </c>
-      <c r="B122" s="387"/>
+      <c r="B122" s="390"/>
       <c r="C122" s="109"/>
       <c r="D122" s="231">
         <v>91169.89</v>
@@ -5104,24 +5104,24 @@
       <c r="E133" s="32"/>
     </row>
     <row r="134" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="390" t="s">
+      <c r="A134" s="409" t="s">
         <v>401</v>
       </c>
-      <c r="B134" s="391"/>
+      <c r="B134" s="410"/>
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32"/>
     </row>
     <row r="135" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="392"/>
-      <c r="B135" s="393"/>
+      <c r="A135" s="411"/>
+      <c r="B135" s="412"/>
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32"/>
     </row>
     <row r="136" spans="1:5" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="394"/>
-      <c r="B136" s="395"/>
+      <c r="A136" s="413"/>
+      <c r="B136" s="414"/>
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32"/>
@@ -5396,10 +5396,10 @@
       <c r="F162" s="83"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="398" t="s">
+      <c r="A163" s="417" t="s">
         <v>297</v>
       </c>
-      <c r="B163" s="399"/>
+      <c r="B163" s="418"/>
       <c r="C163" s="6"/>
       <c r="D163" s="13"/>
       <c r="E163" s="37"/>
@@ -5671,16 +5671,16 @@
       <c r="F185" s="38"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A186" s="396" t="s">
+      <c r="A186" s="415" t="s">
         <v>17</v>
       </c>
-      <c r="B186" s="396"/>
-      <c r="C186" s="396"/>
+      <c r="B186" s="415"/>
+      <c r="C186" s="415"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A187" s="396"/>
-      <c r="B187" s="396"/>
-      <c r="C187" s="396"/>
+      <c r="A187" s="415"/>
+      <c r="B187" s="415"/>
+      <c r="C187" s="415"/>
     </row>
     <row r="188" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="71"/>
@@ -5707,21 +5707,43 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A134:B136"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A186:C187"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
     <mergeCell ref="A10:E12"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A15:E18"/>
@@ -5738,44 +5760,22 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A134:B136"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A186:C187"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -5815,27 +5815,27 @@
     <row r="1" spans="1:24" ht="182.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="431" t="s">
+      <c r="C1" s="427" t="s">
         <v>463</v>
       </c>
-      <c r="D1" s="432"/>
-      <c r="E1" s="432"/>
-      <c r="F1" s="432"/>
-      <c r="G1" s="432"/>
-      <c r="H1" s="432"/>
-      <c r="I1" s="432"/>
-      <c r="J1" s="432"/>
-      <c r="K1" s="432"/>
-      <c r="L1" s="432"/>
+      <c r="D1" s="428"/>
+      <c r="E1" s="428"/>
+      <c r="F1" s="428"/>
+      <c r="G1" s="428"/>
+      <c r="H1" s="428"/>
+      <c r="I1" s="428"/>
+      <c r="J1" s="428"/>
+      <c r="K1" s="428"/>
+      <c r="L1" s="428"/>
       <c r="M1" s="155"/>
-      <c r="N1" s="433" t="s">
+      <c r="N1" s="429" t="s">
         <v>319</v>
       </c>
-      <c r="O1" s="433"/>
-      <c r="P1" s="428">
+      <c r="O1" s="429"/>
+      <c r="P1" s="424">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="428"/>
+      <c r="Q1" s="424"/>
       <c r="R1" s="184"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -5849,35 +5849,35 @@
     <row r="2" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="430" t="s">
+      <c r="C2" s="426" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="430"/>
-      <c r="E2" s="430"/>
+      <c r="D2" s="426"/>
+      <c r="E2" s="426"/>
       <c r="F2" s="155"/>
-      <c r="G2" s="425">
+      <c r="G2" s="423">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="425"/>
+      <c r="H2" s="423"/>
       <c r="I2" s="155" t="s">
         <v>278</v>
       </c>
       <c r="J2" s="155"/>
-      <c r="K2" s="425">
+      <c r="K2" s="423">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="425"/>
+      <c r="L2" s="423"/>
       <c r="M2" s="361"/>
       <c r="N2" s="362" t="s">
         <v>264</v>
       </c>
       <c r="O2" s="361"/>
-      <c r="P2" s="429">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="429"/>
+      <c r="P2" s="425">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="425"/>
       <c r="R2" s="185"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -5889,112 +5889,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="76.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="438" t="str">
+      <c r="A3" s="434" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  16/03, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="439"/>
-      <c r="C3" s="439"/>
-      <c r="D3" s="439"/>
-      <c r="E3" s="439"/>
-      <c r="F3" s="439"/>
-      <c r="G3" s="439"/>
-      <c r="H3" s="439"/>
-      <c r="I3" s="439"/>
-      <c r="J3" s="439"/>
-      <c r="K3" s="439"/>
-      <c r="L3" s="439"/>
-      <c r="M3" s="439"/>
-      <c r="N3" s="439"/>
-      <c r="O3" s="439"/>
-      <c r="P3" s="439"/>
-      <c r="Q3" s="439"/>
-      <c r="R3" s="439"/>
-      <c r="S3" s="439"/>
-      <c r="T3" s="440"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
+      <c r="I3" s="435"/>
+      <c r="J3" s="435"/>
+      <c r="K3" s="435"/>
+      <c r="L3" s="435"/>
+      <c r="M3" s="435"/>
+      <c r="N3" s="435"/>
+      <c r="O3" s="435"/>
+      <c r="P3" s="435"/>
+      <c r="Q3" s="435"/>
+      <c r="R3" s="435"/>
+      <c r="S3" s="435"/>
+      <c r="T3" s="436"/>
       <c r="X3" s="40"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="441" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="443" t="s">
+      <c r="A4" s="437" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="443" t="s">
+      <c r="C4" s="439" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="443" t="s">
+      <c r="D4" s="439" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="426" t="s">
+      <c r="E4" s="419" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="443" t="s">
+      <c r="F4" s="439" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="445" t="s">
+      <c r="G4" s="441" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="426" t="s">
+      <c r="H4" s="419" t="s">
         <v>235</v>
       </c>
-      <c r="I4" s="426" t="s">
+      <c r="I4" s="419" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="426"/>
-      <c r="K4" s="426" t="s">
+      <c r="J4" s="419"/>
+      <c r="K4" s="419" t="s">
         <v>185</v>
       </c>
-      <c r="L4" s="426" t="s">
+      <c r="L4" s="419" t="s">
         <v>148</v>
       </c>
-      <c r="M4" s="426" t="s">
+      <c r="M4" s="419" t="s">
         <v>187</v>
       </c>
-      <c r="N4" s="426" t="s">
+      <c r="N4" s="419" t="s">
         <v>186</v>
       </c>
-      <c r="O4" s="426" t="s">
+      <c r="O4" s="419" t="s">
         <v>497</v>
       </c>
-      <c r="P4" s="434" t="s">
+      <c r="P4" s="430" t="s">
         <v>338</v>
       </c>
-      <c r="Q4" s="435"/>
-      <c r="R4" s="434" t="s">
+      <c r="Q4" s="431"/>
+      <c r="R4" s="430" t="s">
         <v>325</v>
       </c>
-      <c r="S4" s="435"/>
-      <c r="T4" s="426" t="s">
+      <c r="S4" s="431"/>
+      <c r="T4" s="419" t="s">
         <v>262</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="442"/>
-      <c r="B5" s="444"/>
-      <c r="C5" s="444"/>
-      <c r="D5" s="444"/>
-      <c r="E5" s="427"/>
-      <c r="F5" s="444"/>
-      <c r="G5" s="446"/>
-      <c r="H5" s="427"/>
-      <c r="I5" s="427"/>
-      <c r="J5" s="427"/>
-      <c r="K5" s="427"/>
-      <c r="L5" s="427"/>
-      <c r="M5" s="427"/>
-      <c r="N5" s="427"/>
-      <c r="O5" s="427"/>
-      <c r="P5" s="436" t="str">
+      <c r="A5" s="438"/>
+      <c r="B5" s="440"/>
+      <c r="C5" s="440"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="420"/>
+      <c r="F5" s="440"/>
+      <c r="G5" s="442"/>
+      <c r="H5" s="420"/>
+      <c r="I5" s="420"/>
+      <c r="J5" s="420"/>
+      <c r="K5" s="420"/>
+      <c r="L5" s="420"/>
+      <c r="M5" s="420"/>
+      <c r="N5" s="420"/>
+      <c r="O5" s="420"/>
+      <c r="P5" s="432" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  16/03</v>
       </c>
-      <c r="Q5" s="437"/>
-      <c r="R5" s="436"/>
-      <c r="S5" s="437"/>
-      <c r="T5" s="427"/>
+      <c r="Q5" s="433"/>
+      <c r="R5" s="432"/>
+      <c r="S5" s="433"/>
+      <c r="T5" s="420"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="204"/>
@@ -6043,11 +6043,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="209"/>
-      <c r="P6" s="447">
+      <c r="P6" s="421">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>1518529.01</v>
       </c>
-      <c r="Q6" s="447"/>
+      <c r="Q6" s="421"/>
       <c r="R6" s="363">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>1564586.01</v>
@@ -6112,11 +6112,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="74"/>
-      <c r="P7" s="418">
+      <c r="P7" s="422">
         <f t="shared" si="2"/>
         <v>1542558.02</v>
       </c>
-      <c r="Q7" s="418"/>
+      <c r="Q7" s="422"/>
       <c r="R7" s="363">
         <f t="shared" si="3"/>
         <v>1589344.02</v>
@@ -6180,11 +6180,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="74"/>
-      <c r="P8" s="418">
+      <c r="P8" s="422">
         <f t="shared" si="2"/>
         <v>736705.03</v>
       </c>
-      <c r="Q8" s="418"/>
+      <c r="Q8" s="422"/>
       <c r="R8" s="363">
         <f t="shared" si="3"/>
         <v>759049.03</v>
@@ -6249,11 +6249,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="74"/>
-      <c r="P9" s="418">
+      <c r="P9" s="422">
         <f t="shared" si="2"/>
         <v>3222835.04</v>
       </c>
-      <c r="Q9" s="418"/>
+      <c r="Q9" s="422"/>
       <c r="R9" s="363">
         <f t="shared" si="3"/>
         <v>3320584.04</v>
@@ -6321,11 +6321,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="74"/>
-      <c r="P10" s="418">
+      <c r="P10" s="422">
         <f t="shared" si="2"/>
         <v>744528.05</v>
       </c>
-      <c r="Q10" s="418"/>
+      <c r="Q10" s="422"/>
       <c r="R10" s="363">
         <f t="shared" si="3"/>
         <v>767110.05</v>
@@ -6391,11 +6391,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="74"/>
-      <c r="P11" s="418">
+      <c r="P11" s="422">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="418"/>
+      <c r="Q11" s="422"/>
       <c r="R11" s="363">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6462,11 +6462,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="74"/>
-      <c r="P12" s="418">
+      <c r="P12" s="422">
         <f t="shared" si="2"/>
         <v>744299.07</v>
       </c>
-      <c r="Q12" s="418"/>
+      <c r="Q12" s="422"/>
       <c r="R12" s="363">
         <f t="shared" si="3"/>
         <v>766874.07</v>
@@ -6533,11 +6533,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="74"/>
-      <c r="P13" s="418">
+      <c r="P13" s="422">
         <f t="shared" si="2"/>
         <v>744514.08</v>
       </c>
-      <c r="Q13" s="418"/>
+      <c r="Q13" s="422"/>
       <c r="R13" s="363">
         <f t="shared" si="3"/>
         <v>767095.08</v>
@@ -6602,11 +6602,11 @@
         <v>379177.030424</v>
       </c>
       <c r="O14" s="74"/>
-      <c r="P14" s="418">
+      <c r="P14" s="422">
         <f t="shared" si="2"/>
         <v>3585790.09</v>
       </c>
-      <c r="Q14" s="418"/>
+      <c r="Q14" s="422"/>
       <c r="R14" s="363">
         <f t="shared" si="3"/>
         <v>3694547.09</v>
@@ -6670,11 +6670,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="74"/>
-      <c r="P15" s="418">
+      <c r="P15" s="422">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="418"/>
+      <c r="Q15" s="422"/>
       <c r="R15" s="363">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -6740,11 +6740,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="36"/>
-      <c r="P16" s="418">
+      <c r="P16" s="422">
         <f t="shared" si="2"/>
         <v>744528.11</v>
       </c>
-      <c r="Q16" s="418"/>
+      <c r="Q16" s="422"/>
       <c r="R16" s="363">
         <f t="shared" si="3"/>
         <v>767110.11</v>
@@ -6808,11 +6808,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="74"/>
-      <c r="P17" s="418">
+      <c r="P17" s="422">
         <f t="shared" si="2"/>
         <v>4420303.12</v>
       </c>
-      <c r="Q17" s="418"/>
+      <c r="Q17" s="422"/>
       <c r="R17" s="363">
         <f t="shared" si="3"/>
         <v>4554371.12</v>
@@ -6879,11 +6879,11 @@
       <c r="O18" s="74">
         <v>91169.89</v>
       </c>
-      <c r="P18" s="418">
+      <c r="P18" s="422">
         <f t="shared" si="2"/>
         <v>850918.13</v>
       </c>
-      <c r="Q18" s="418"/>
+      <c r="Q18" s="422"/>
       <c r="R18" s="363">
         <f t="shared" si="3"/>
         <v>876726.13</v>
@@ -6947,11 +6947,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="74"/>
-      <c r="P19" s="418">
+      <c r="P19" s="422">
         <f t="shared" si="2"/>
         <v>720435.14</v>
       </c>
-      <c r="Q19" s="418"/>
+      <c r="Q19" s="422"/>
       <c r="R19" s="363">
         <f t="shared" si="3"/>
         <v>742286.14</v>
@@ -7018,11 +7018,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="74"/>
-      <c r="P20" s="418">
+      <c r="P20" s="422">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="418"/>
+      <c r="Q20" s="422"/>
       <c r="R20" s="363">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7087,11 +7087,11 @@
       </c>
       <c r="N21" s="74"/>
       <c r="O21" s="74"/>
-      <c r="P21" s="418">
+      <c r="P21" s="422">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="418"/>
+      <c r="Q21" s="422"/>
       <c r="R21" s="363">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7152,11 +7152,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="74"/>
-      <c r="P22" s="418">
+      <c r="P22" s="422">
         <f t="shared" si="2"/>
         <v>2350329.17</v>
       </c>
-      <c r="Q22" s="418"/>
+      <c r="Q22" s="422"/>
       <c r="R22" s="363">
         <f t="shared" si="3"/>
         <v>2421615.17</v>
@@ -7222,11 +7222,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="88"/>
-      <c r="P23" s="418">
+      <c r="P23" s="422">
         <f t="shared" si="2"/>
         <v>736705.18</v>
       </c>
-      <c r="Q23" s="418"/>
+      <c r="Q23" s="422"/>
       <c r="R23" s="363">
         <f t="shared" si="3"/>
         <v>759049.18</v>
@@ -7292,11 +7292,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="88"/>
-      <c r="P24" s="418">
+      <c r="P24" s="422">
         <f t="shared" si="2"/>
         <v>744528.19</v>
       </c>
-      <c r="Q24" s="418"/>
+      <c r="Q24" s="422"/>
       <c r="R24" s="363">
         <f t="shared" si="3"/>
         <v>767110.19</v>
@@ -7359,11 +7359,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="88"/>
-      <c r="P25" s="418">
+      <c r="P25" s="422">
         <f t="shared" si="2"/>
         <v>744528.2</v>
       </c>
-      <c r="Q25" s="418"/>
+      <c r="Q25" s="422"/>
       <c r="R25" s="363">
         <f t="shared" si="3"/>
         <v>767110.2</v>
@@ -7424,11 +7424,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="88"/>
-      <c r="P26" s="418">
+      <c r="P26" s="422">
         <f t="shared" si="2"/>
         <v>1559335.21</v>
       </c>
-      <c r="Q26" s="418"/>
+      <c r="Q26" s="422"/>
       <c r="R26" s="363">
         <f t="shared" si="3"/>
         <v>1606630.21</v>
@@ -7497,11 +7497,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="88"/>
-      <c r="P27" s="418">
+      <c r="P27" s="422">
         <f t="shared" si="2"/>
         <v>744528.22</v>
       </c>
-      <c r="Q27" s="418"/>
+      <c r="Q27" s="422"/>
       <c r="R27" s="363">
         <f t="shared" si="3"/>
         <v>767110.22</v>
@@ -7567,11 +7567,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="88"/>
-      <c r="P28" s="418">
+      <c r="P28" s="422">
         <f t="shared" si="2"/>
         <v>767815.23</v>
       </c>
-      <c r="Q28" s="418"/>
+      <c r="Q28" s="422"/>
       <c r="R28" s="363">
         <f t="shared" si="3"/>
         <v>791103.23</v>
@@ -7637,11 +7637,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="88"/>
-      <c r="P29" s="418">
+      <c r="P29" s="422">
         <f t="shared" si="2"/>
         <v>744528.24</v>
       </c>
-      <c r="Q29" s="418"/>
+      <c r="Q29" s="422"/>
       <c r="R29" s="363">
         <f t="shared" si="3"/>
         <v>767110.24</v>
@@ -7708,11 +7708,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="88"/>
-      <c r="P30" s="418">
+      <c r="P30" s="422">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="418"/>
+      <c r="Q30" s="422"/>
       <c r="R30" s="363">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -7778,11 +7778,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="88"/>
-      <c r="P31" s="418">
+      <c r="P31" s="422">
         <f t="shared" si="2"/>
         <v>752356.26</v>
       </c>
-      <c r="Q31" s="418"/>
+      <c r="Q31" s="422"/>
       <c r="R31" s="363">
         <f t="shared" si="3"/>
         <v>775175.26</v>
@@ -7849,11 +7849,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="88"/>
-      <c r="P32" s="418">
+      <c r="P32" s="422">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="418"/>
+      <c r="Q32" s="422"/>
       <c r="R32" s="363">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -7919,11 +7919,11 @@
         <f>I33/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P33" s="418">
+      <c r="P33" s="422">
         <f t="shared" si="2"/>
         <v>923797.28</v>
       </c>
-      <c r="Q33" s="418"/>
+      <c r="Q33" s="422"/>
       <c r="R33" s="363">
         <f t="shared" si="3"/>
         <v>951816.28</v>
@@ -7989,11 +7989,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="88"/>
-      <c r="P34" s="418">
+      <c r="P34" s="422">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="418"/>
+      <c r="Q34" s="422"/>
       <c r="R34" s="363">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8060,11 +8060,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="88"/>
-      <c r="P35" s="418">
+      <c r="P35" s="422">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="418"/>
+      <c r="Q35" s="422"/>
       <c r="R35" s="363">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8128,11 +8128,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="88"/>
-      <c r="P36" s="418">
+      <c r="P36" s="422">
         <f t="shared" si="2"/>
         <v>2643433.31</v>
       </c>
-      <c r="Q36" s="418"/>
+      <c r="Q36" s="422"/>
       <c r="R36" s="363">
         <f t="shared" si="3"/>
         <v>2723609.31</v>
@@ -8199,11 +8199,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="88"/>
-      <c r="P37" s="418">
+      <c r="P37" s="422">
         <f t="shared" si="2"/>
         <v>573720.31999999995</v>
       </c>
-      <c r="Q37" s="418"/>
+      <c r="Q37" s="422"/>
       <c r="R37" s="363">
         <f t="shared" si="3"/>
         <v>591121.31999999995</v>
@@ -8266,11 +8266,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="88"/>
-      <c r="P38" s="418">
+      <c r="P38" s="422">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="418"/>
+      <c r="Q38" s="422"/>
       <c r="R38" s="363">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8330,11 +8330,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="88"/>
-      <c r="P39" s="418">
+      <c r="P39" s="422">
         <f t="shared" si="14"/>
         <v>2473411.34</v>
       </c>
-      <c r="Q39" s="418"/>
+      <c r="Q39" s="422"/>
       <c r="R39" s="363">
         <f t="shared" si="15"/>
         <v>2548430.34</v>
@@ -8401,11 +8401,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="88"/>
-      <c r="P40" s="418">
+      <c r="P40" s="422">
         <f t="shared" si="14"/>
         <v>736704.35</v>
       </c>
-      <c r="Q40" s="418"/>
+      <c r="Q40" s="422"/>
       <c r="R40" s="363">
         <f t="shared" si="15"/>
         <v>759049.35</v>
@@ -8473,11 +8473,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="88"/>
-      <c r="P41" s="418">
+      <c r="P41" s="422">
         <f t="shared" si="14"/>
         <v>748020.36</v>
       </c>
-      <c r="Q41" s="418"/>
+      <c r="Q41" s="422"/>
       <c r="R41" s="363">
         <f t="shared" si="15"/>
         <v>770708.36</v>
@@ -8540,11 +8540,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="88"/>
-      <c r="P42" s="418">
+      <c r="P42" s="422">
         <f t="shared" si="14"/>
         <v>1526106.37</v>
       </c>
-      <c r="Q42" s="418"/>
+      <c r="Q42" s="422"/>
       <c r="R42" s="363">
         <f t="shared" si="15"/>
         <v>1572393.37</v>
@@ -8610,11 +8610,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="88"/>
-      <c r="P43" s="418">
+      <c r="P43" s="422">
         <f t="shared" si="14"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="418"/>
+      <c r="Q43" s="422"/>
       <c r="R43" s="363">
         <f t="shared" si="15"/>
         <v>774480.38</v>
@@ -8682,11 +8682,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="88"/>
-      <c r="P44" s="418">
+      <c r="P44" s="422">
         <f t="shared" si="14"/>
         <v>872758.39</v>
       </c>
-      <c r="Q44" s="418"/>
+      <c r="Q44" s="422"/>
       <c r="R44" s="363">
         <f t="shared" si="15"/>
         <v>899229.39</v>
@@ -8753,11 +8753,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="88"/>
-      <c r="P45" s="418">
+      <c r="P45" s="422">
         <f t="shared" si="14"/>
         <v>728593.4</v>
       </c>
-      <c r="Q45" s="418"/>
+      <c r="Q45" s="422"/>
       <c r="R45" s="363">
         <f t="shared" si="15"/>
         <v>750692.4</v>
@@ -8821,11 +8821,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="88"/>
-      <c r="P46" s="418">
+      <c r="P46" s="422">
         <f t="shared" si="14"/>
         <v>728882.41</v>
       </c>
-      <c r="Q46" s="418"/>
+      <c r="Q46" s="422"/>
       <c r="R46" s="363">
         <f t="shared" si="15"/>
         <v>750989.41</v>
@@ -8892,11 +8892,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="88"/>
-      <c r="P47" s="418">
+      <c r="P47" s="422">
         <f t="shared" si="14"/>
         <v>728882.42</v>
       </c>
-      <c r="Q47" s="418"/>
+      <c r="Q47" s="422"/>
       <c r="R47" s="363">
         <f t="shared" si="15"/>
         <v>750989.42</v>
@@ -8964,11 +8964,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="88"/>
-      <c r="P48" s="418">
+      <c r="P48" s="422">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="418"/>
+      <c r="Q48" s="422"/>
       <c r="R48" s="363">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9032,11 +9032,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="88"/>
-      <c r="P49" s="418">
+      <c r="P49" s="422">
         <f t="shared" si="14"/>
         <v>895905.44</v>
       </c>
-      <c r="Q49" s="418"/>
+      <c r="Q49" s="422"/>
       <c r="R49" s="363">
         <f t="shared" si="15"/>
         <v>923078.44</v>
@@ -9102,11 +9102,11 @@
         <v>395312.22320800001</v>
       </c>
       <c r="O50" s="88"/>
-      <c r="P50" s="418">
+      <c r="P50" s="422">
         <f t="shared" si="14"/>
         <v>1987415.45</v>
       </c>
-      <c r="Q50" s="418"/>
+      <c r="Q50" s="422"/>
       <c r="R50" s="363">
         <f t="shared" si="15"/>
         <v>2047694.45</v>
@@ -9170,11 +9170,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="88"/>
-      <c r="P51" s="418">
+      <c r="P51" s="422">
         <f t="shared" si="14"/>
         <v>1451367.46</v>
       </c>
-      <c r="Q51" s="418"/>
+      <c r="Q51" s="422"/>
       <c r="R51" s="363">
         <f t="shared" si="15"/>
         <v>1495387.46</v>
@@ -9239,11 +9239,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="88"/>
-      <c r="P52" s="418">
+      <c r="P52" s="422">
         <f t="shared" si="14"/>
         <v>3158183.47</v>
       </c>
-      <c r="Q52" s="418"/>
+      <c r="Q52" s="422"/>
       <c r="R52" s="363">
         <f t="shared" si="15"/>
         <v>3253971.47</v>
@@ -9314,11 +9314,11 @@
         <f>I53*0.1</f>
         <v>36304.183764000001</v>
       </c>
-      <c r="P53" s="418">
+      <c r="P53" s="422">
         <f t="shared" si="14"/>
         <v>1125839.48</v>
       </c>
-      <c r="Q53" s="418"/>
+      <c r="Q53" s="422"/>
       <c r="R53" s="363">
         <f t="shared" si="15"/>
         <v>1159986.48</v>
@@ -9383,11 +9383,11 @@
         <v>0</v>
       </c>
       <c r="O54" s="88"/>
-      <c r="P54" s="418">
+      <c r="P54" s="422">
         <f t="shared" si="14"/>
         <v>728882.49</v>
       </c>
-      <c r="Q54" s="418"/>
+      <c r="Q54" s="422"/>
       <c r="R54" s="363">
         <f t="shared" si="15"/>
         <v>750989.49</v>
@@ -9454,11 +9454,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="88"/>
-      <c r="P55" s="418">
+      <c r="P55" s="422">
         <f t="shared" si="14"/>
         <v>728882.5</v>
       </c>
-      <c r="Q55" s="418"/>
+      <c r="Q55" s="422"/>
       <c r="R55" s="363">
         <f t="shared" si="15"/>
         <v>750990.5</v>
@@ -9524,11 +9524,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O56" s="88"/>
-      <c r="P56" s="418">
+      <c r="P56" s="422">
         <f t="shared" si="14"/>
         <v>2245180.5099999998</v>
       </c>
-      <c r="Q56" s="418"/>
+      <c r="Q56" s="422"/>
       <c r="R56" s="363">
         <f t="shared" si="15"/>
         <v>2313277.5099999998</v>
@@ -9596,11 +9596,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="88"/>
-      <c r="P57" s="418">
+      <c r="P57" s="422">
         <f t="shared" si="14"/>
         <v>712950.52</v>
       </c>
-      <c r="Q57" s="418"/>
+      <c r="Q57" s="422"/>
       <c r="R57" s="363">
         <f t="shared" si="15"/>
         <v>734574.52</v>
@@ -9665,11 +9665,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="88"/>
-      <c r="P58" s="418">
+      <c r="P58" s="422">
         <f t="shared" si="14"/>
         <v>3399941.53</v>
       </c>
-      <c r="Q58" s="418"/>
+      <c r="Q58" s="422"/>
       <c r="R58" s="363">
         <f t="shared" si="15"/>
         <v>3503062.53</v>
@@ -9734,11 +9734,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="88"/>
-      <c r="P59" s="418">
+      <c r="P59" s="422">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="418"/>
+      <c r="Q59" s="422"/>
       <c r="R59" s="363">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -9805,11 +9805,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="88"/>
-      <c r="P60" s="418">
+      <c r="P60" s="422">
         <f t="shared" si="14"/>
         <v>728882.55</v>
       </c>
-      <c r="Q60" s="418"/>
+      <c r="Q60" s="422"/>
       <c r="R60" s="363">
         <f t="shared" si="15"/>
         <v>750990.55</v>
@@ -9880,11 +9880,11 @@
         <f>(I61*0.1)*2</f>
         <v>72608.367528000002</v>
       </c>
-      <c r="P61" s="418">
+      <c r="P61" s="422">
         <f t="shared" si="14"/>
         <v>1225512.56</v>
       </c>
-      <c r="Q61" s="418"/>
+      <c r="Q61" s="422"/>
       <c r="R61" s="363">
         <f t="shared" si="15"/>
         <v>1262682.56</v>
@@ -9949,11 +9949,11 @@
         <v>0</v>
       </c>
       <c r="O62" s="88"/>
-      <c r="P62" s="418">
+      <c r="P62" s="422">
         <f t="shared" si="14"/>
         <v>1526567.57</v>
       </c>
-      <c r="Q62" s="418"/>
+      <c r="Q62" s="422"/>
       <c r="R62" s="363">
         <f t="shared" si="15"/>
         <v>1572868.57</v>
@@ -10017,11 +10017,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="88"/>
-      <c r="P63" s="418">
+      <c r="P63" s="422">
         <f t="shared" si="14"/>
         <v>728882.58</v>
       </c>
-      <c r="Q63" s="418"/>
+      <c r="Q63" s="422"/>
       <c r="R63" s="363">
         <f t="shared" si="15"/>
         <v>750990.58</v>
@@ -10085,11 +10085,11 @@
         <v>0</v>
       </c>
       <c r="O64" s="88"/>
-      <c r="P64" s="418">
+      <c r="P64" s="422">
         <f t="shared" si="14"/>
         <v>691468.59</v>
       </c>
-      <c r="Q64" s="418"/>
+      <c r="Q64" s="422"/>
       <c r="R64" s="363">
         <f t="shared" si="15"/>
         <v>712441.59</v>
@@ -10156,11 +10156,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="88"/>
-      <c r="P65" s="418">
+      <c r="P65" s="422">
         <f t="shared" si="14"/>
         <v>750827.6</v>
       </c>
-      <c r="Q65" s="418"/>
+      <c r="Q65" s="422"/>
       <c r="R65" s="363">
         <f t="shared" si="15"/>
         <v>773600.6</v>
@@ -10228,11 +10228,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="88"/>
-      <c r="P66" s="418">
+      <c r="P66" s="422">
         <f t="shared" si="14"/>
         <v>751038.61</v>
       </c>
-      <c r="Q66" s="418"/>
+      <c r="Q66" s="422"/>
       <c r="R66" s="363">
         <f t="shared" si="15"/>
         <v>773818.61</v>
@@ -10303,11 +10303,11 @@
         <f>I67/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P67" s="418">
+      <c r="P67" s="422">
         <f t="shared" si="14"/>
         <v>921295.62</v>
       </c>
-      <c r="Q67" s="418"/>
+      <c r="Q67" s="422"/>
       <c r="R67" s="363">
         <f t="shared" si="15"/>
         <v>949239.62</v>
@@ -10372,11 +10372,11 @@
         <v>0</v>
       </c>
       <c r="O68" s="88"/>
-      <c r="P68" s="418">
+      <c r="P68" s="422">
         <f t="shared" si="14"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="418"/>
+      <c r="Q68" s="422"/>
       <c r="R68" s="363">
         <f t="shared" si="15"/>
         <v>774480.63</v>
@@ -10444,11 +10444,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="88"/>
-      <c r="P69" s="418">
+      <c r="P69" s="422">
         <f t="shared" si="14"/>
         <v>706943.64</v>
       </c>
-      <c r="Q69" s="418"/>
+      <c r="Q69" s="422"/>
       <c r="R69" s="363">
         <f t="shared" si="15"/>
         <v>728385.64</v>
@@ -10516,11 +10516,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="88"/>
-      <c r="P70" s="418">
+      <c r="P70" s="422">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="418"/>
+      <c r="Q70" s="422"/>
       <c r="R70" s="363">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10584,11 +10584,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="88"/>
-      <c r="P71" s="418">
+      <c r="P71" s="422">
         <f t="shared" si="22"/>
         <v>728882.66</v>
       </c>
-      <c r="Q71" s="418"/>
+      <c r="Q71" s="422"/>
       <c r="R71" s="363">
         <f t="shared" si="23"/>
         <v>750990.66</v>
@@ -10653,11 +10653,11 @@
         <v>0</v>
       </c>
       <c r="O72" s="88"/>
-      <c r="P72" s="418">
+      <c r="P72" s="422">
         <f t="shared" si="22"/>
         <v>1518273.67</v>
       </c>
-      <c r="Q72" s="418"/>
+      <c r="Q72" s="422"/>
       <c r="R72" s="363">
         <f t="shared" si="23"/>
         <v>1564323.67</v>
@@ -10722,11 +10722,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O73" s="88"/>
-      <c r="P73" s="418">
+      <c r="P73" s="422">
         <f t="shared" si="22"/>
         <v>4559265.68</v>
       </c>
-      <c r="Q73" s="418"/>
+      <c r="Q73" s="422"/>
       <c r="R73" s="363">
         <f t="shared" si="23"/>
         <v>4697548.68</v>
@@ -10789,11 +10789,11 @@
         <v>0</v>
       </c>
       <c r="O74" s="36"/>
-      <c r="P74" s="418">
+      <c r="P74" s="422">
         <f t="shared" si="22"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="418"/>
+      <c r="Q74" s="422"/>
       <c r="R74" s="363">
         <f t="shared" si="23"/>
         <v>678447.69</v>
@@ -10859,11 +10859,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="88"/>
-      <c r="P75" s="418">
+      <c r="P75" s="422">
         <f t="shared" si="22"/>
         <v>1372860.7</v>
       </c>
-      <c r="Q75" s="418"/>
+      <c r="Q75" s="422"/>
       <c r="R75" s="363">
         <f t="shared" si="23"/>
         <v>1414500.7</v>
@@ -10927,11 +10927,11 @@
         <v>0</v>
       </c>
       <c r="O76" s="88"/>
-      <c r="P76" s="418">
+      <c r="P76" s="422">
         <f t="shared" si="22"/>
         <v>4028209.71</v>
       </c>
-      <c r="Q76" s="418"/>
+      <c r="Q76" s="422"/>
       <c r="R76" s="363">
         <f t="shared" si="23"/>
         <v>4150385.71</v>
@@ -10997,11 +10997,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="88"/>
-      <c r="P77" s="418">
+      <c r="P77" s="422">
         <f t="shared" si="22"/>
         <v>690051.72</v>
       </c>
-      <c r="Q77" s="418"/>
+      <c r="Q77" s="422"/>
       <c r="R77" s="363">
         <f t="shared" si="23"/>
         <v>710981.72</v>
@@ -11068,11 +11068,11 @@
         <v>0</v>
       </c>
       <c r="O78" s="88"/>
-      <c r="P78" s="418">
+      <c r="P78" s="422">
         <f t="shared" si="22"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="418"/>
+      <c r="Q78" s="422"/>
       <c r="R78" s="363">
         <f t="shared" si="23"/>
         <v>732919.73</v>
@@ -11136,11 +11136,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="88"/>
-      <c r="P79" s="418">
+      <c r="P79" s="422">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="418"/>
+      <c r="Q79" s="422"/>
       <c r="R79" s="363">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11207,11 +11207,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="418">
+      <c r="P80" s="422">
         <f t="shared" si="22"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="418"/>
+      <c r="Q80" s="422"/>
       <c r="R80" s="363">
         <f t="shared" si="23"/>
         <v>911633.75</v>
@@ -11278,11 +11278,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="88"/>
-      <c r="P81" s="418">
+      <c r="P81" s="422">
         <f t="shared" si="22"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="418"/>
+      <c r="Q81" s="422"/>
       <c r="R81" s="363">
         <f t="shared" si="23"/>
         <v>774480.76</v>
@@ -11345,11 +11345,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="88"/>
-      <c r="P82" s="418">
+      <c r="P82" s="422">
         <f t="shared" si="22"/>
         <v>854048.77</v>
       </c>
-      <c r="Q82" s="418"/>
+      <c r="Q82" s="422"/>
       <c r="R82" s="363">
         <f t="shared" si="23"/>
         <v>879952.77</v>
@@ -11415,11 +11415,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="88"/>
-      <c r="P83" s="418">
+      <c r="P83" s="422">
         <f t="shared" si="22"/>
         <v>751480.78</v>
       </c>
-      <c r="Q83" s="418"/>
+      <c r="Q83" s="422"/>
       <c r="R83" s="363">
         <f t="shared" si="23"/>
         <v>774273.78</v>
@@ -11486,11 +11486,11 @@
         <v>0</v>
       </c>
       <c r="O84" s="88"/>
-      <c r="P84" s="418">
+      <c r="P84" s="422">
         <f t="shared" si="22"/>
         <v>1089017.79</v>
       </c>
-      <c r="Q84" s="418"/>
+      <c r="Q84" s="422"/>
       <c r="R84" s="363">
         <f t="shared" si="23"/>
         <v>1122048.79</v>
@@ -11559,11 +11559,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="88"/>
-      <c r="P85" s="418">
+      <c r="P85" s="422">
         <f t="shared" si="22"/>
         <v>728063.8</v>
       </c>
-      <c r="Q85" s="418"/>
+      <c r="Q85" s="422"/>
       <c r="R85" s="363">
         <f t="shared" si="23"/>
         <v>750146.8</v>
@@ -11630,11 +11630,11 @@
         <v>0</v>
       </c>
       <c r="O86" s="88"/>
-      <c r="P86" s="418">
+      <c r="P86" s="422">
         <f t="shared" si="22"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="418"/>
+      <c r="Q86" s="422"/>
       <c r="R86" s="363">
         <f t="shared" si="23"/>
         <v>774480.81</v>
@@ -11700,11 +11700,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="74"/>
-      <c r="P87" s="418">
+      <c r="P87" s="422">
         <f t="shared" si="22"/>
         <v>682667.82</v>
       </c>
-      <c r="Q87" s="418"/>
+      <c r="Q87" s="422"/>
       <c r="R87" s="363">
         <f t="shared" si="23"/>
         <v>703373.82</v>
@@ -11771,11 +11771,11 @@
         <v>0</v>
       </c>
       <c r="O88" s="88"/>
-      <c r="P88" s="418">
+      <c r="P88" s="422">
         <f t="shared" si="22"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="418"/>
+      <c r="Q88" s="422"/>
       <c r="R88" s="363">
         <f t="shared" si="23"/>
         <v>775171.83</v>
@@ -11838,11 +11838,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="88"/>
-      <c r="P89" s="418">
+      <c r="P89" s="422">
         <f t="shared" si="22"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="418"/>
+      <c r="Q89" s="422"/>
       <c r="R89" s="363">
         <f t="shared" si="23"/>
         <v>775171.84</v>
@@ -11906,11 +11906,11 @@
         <v>0</v>
       </c>
       <c r="O90" s="88"/>
-      <c r="P90" s="418">
+      <c r="P90" s="422">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="418"/>
+      <c r="Q90" s="422"/>
       <c r="R90" s="363">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -11978,11 +11978,11 @@
         <v>387244.62681599997</v>
       </c>
       <c r="O91" s="88"/>
-      <c r="P91" s="418">
+      <c r="P91" s="422">
         <f t="shared" si="22"/>
         <v>1240577.8600000001</v>
       </c>
-      <c r="Q91" s="418"/>
+      <c r="Q91" s="422"/>
       <c r="R91" s="363">
         <f t="shared" si="23"/>
         <v>1278205.8600000001</v>
@@ -12045,11 +12045,11 @@
         <v>0</v>
       </c>
       <c r="O92" s="88"/>
-      <c r="P92" s="418">
+      <c r="P92" s="422">
         <f t="shared" si="22"/>
         <v>752351.87</v>
       </c>
-      <c r="Q92" s="418"/>
+      <c r="Q92" s="422"/>
       <c r="R92" s="363">
         <f t="shared" si="23"/>
         <v>775171.87</v>
@@ -12113,11 +12113,11 @@
         <v>0</v>
       </c>
       <c r="O93" s="88"/>
-      <c r="P93" s="418">
+      <c r="P93" s="422">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="418"/>
+      <c r="Q93" s="422"/>
       <c r="R93" s="363">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12180,11 +12180,11 @@
         <v>0</v>
       </c>
       <c r="O94" s="88"/>
-      <c r="P94" s="418">
+      <c r="P94" s="422">
         <f t="shared" si="22"/>
         <v>752351.89</v>
       </c>
-      <c r="Q94" s="418"/>
+      <c r="Q94" s="422"/>
       <c r="R94" s="363">
         <f t="shared" si="23"/>
         <v>775171.89</v>
@@ -12250,11 +12250,11 @@
         <v>0</v>
       </c>
       <c r="O95" s="88"/>
-      <c r="P95" s="418">
+      <c r="P95" s="422">
         <f t="shared" si="22"/>
         <v>743876.9</v>
       </c>
-      <c r="Q95" s="418"/>
+      <c r="Q95" s="422"/>
       <c r="R95" s="363">
         <f t="shared" si="23"/>
         <v>766439.9</v>
@@ -12320,11 +12320,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="88"/>
-      <c r="P96" s="418">
+      <c r="P96" s="422">
         <f t="shared" si="22"/>
         <v>752351.91</v>
       </c>
-      <c r="Q96" s="418"/>
+      <c r="Q96" s="422"/>
       <c r="R96" s="363">
         <f t="shared" si="23"/>
         <v>775171.91</v>
@@ -12393,11 +12393,11 @@
         <f>1780*100</f>
         <v>178000</v>
       </c>
-      <c r="P97" s="418">
+      <c r="P97" s="422">
         <f t="shared" si="22"/>
         <v>1840080.92</v>
       </c>
-      <c r="Q97" s="418"/>
+      <c r="Q97" s="422"/>
       <c r="R97" s="363">
         <f t="shared" si="23"/>
         <v>1895891.92</v>
@@ -12463,11 +12463,11 @@
         <v>0</v>
       </c>
       <c r="O98" s="60"/>
-      <c r="P98" s="418">
+      <c r="P98" s="422">
         <f t="shared" si="22"/>
         <v>238871.93</v>
       </c>
-      <c r="Q98" s="418"/>
+      <c r="Q98" s="422"/>
       <c r="R98" s="363">
         <f t="shared" si="23"/>
         <v>246117.93</v>
@@ -12534,11 +12534,11 @@
         <v>0</v>
       </c>
       <c r="O99" s="60"/>
-      <c r="P99" s="418">
+      <c r="P99" s="422">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="418"/>
+      <c r="Q99" s="422"/>
       <c r="R99" s="363">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -12604,11 +12604,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="88"/>
-      <c r="P100" s="418">
+      <c r="P100" s="422">
         <f t="shared" si="22"/>
         <v>4049080.95</v>
       </c>
-      <c r="Q100" s="418"/>
+      <c r="Q100" s="422"/>
       <c r="R100" s="363">
         <f t="shared" si="23"/>
         <v>4171890.95</v>
@@ -12671,11 +12671,11 @@
         <v>0</v>
       </c>
       <c r="O101" s="88"/>
-      <c r="P101" s="418">
+      <c r="P101" s="422">
         <f t="shared" si="22"/>
         <v>752388.96</v>
       </c>
-      <c r="Q101" s="418"/>
+      <c r="Q101" s="422"/>
       <c r="R101" s="363">
         <f t="shared" si="23"/>
         <v>775209.96</v>
@@ -12741,11 +12741,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="88"/>
-      <c r="P102" s="418">
+      <c r="P102" s="422">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752269.97</v>
       </c>
-      <c r="Q102" s="418"/>
+      <c r="Q102" s="422"/>
       <c r="R102" s="363">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775086.97</v>
@@ -12811,11 +12811,11 @@
         <v>0</v>
       </c>
       <c r="O103" s="88"/>
-      <c r="P103" s="418">
+      <c r="P103" s="422">
         <f t="shared" si="32"/>
         <v>752350.98</v>
       </c>
-      <c r="Q103" s="418"/>
+      <c r="Q103" s="422"/>
       <c r="R103" s="363">
         <f t="shared" si="33"/>
         <v>775170.98</v>
@@ -12879,11 +12879,11 @@
         <v>0</v>
       </c>
       <c r="O104" s="88"/>
-      <c r="P104" s="418">
+      <c r="P104" s="422">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="418"/>
+      <c r="Q104" s="422"/>
       <c r="R104" s="363">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -12949,11 +12949,11 @@
         <v>0</v>
       </c>
       <c r="O105" s="88"/>
-      <c r="P105" s="418">
+      <c r="P105" s="422">
         <f t="shared" si="32"/>
         <v>752351</v>
       </c>
-      <c r="Q105" s="418"/>
+      <c r="Q105" s="422"/>
       <c r="R105" s="363">
         <f t="shared" si="33"/>
         <v>775171</v>
@@ -13016,11 +13016,11 @@
         <v>0</v>
       </c>
       <c r="O106" s="88"/>
-      <c r="P106" s="418">
+      <c r="P106" s="422">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="418"/>
+      <c r="Q106" s="422"/>
       <c r="R106" s="363">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13083,11 +13083,11 @@
         <v>0</v>
       </c>
       <c r="O107" s="88"/>
-      <c r="P107" s="418">
+      <c r="P107" s="422">
         <f t="shared" si="32"/>
         <v>775118.02</v>
       </c>
-      <c r="Q107" s="418"/>
+      <c r="Q107" s="422"/>
       <c r="R107" s="363">
         <f t="shared" si="33"/>
         <v>798628.02</v>
@@ -13153,11 +13153,11 @@
         <v>0</v>
       </c>
       <c r="O108" s="88"/>
-      <c r="P108" s="418">
+      <c r="P108" s="422">
         <f t="shared" si="32"/>
         <v>728092.03</v>
       </c>
-      <c r="Q108" s="418"/>
+      <c r="Q108" s="422"/>
       <c r="R108" s="363">
         <f t="shared" si="33"/>
         <v>750176.03</v>
@@ -13221,11 +13221,11 @@
         <v>0</v>
       </c>
       <c r="O109" s="88"/>
-      <c r="P109" s="418">
+      <c r="P109" s="422">
         <f t="shared" si="32"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="418"/>
+      <c r="Q109" s="422"/>
       <c r="R109" s="363">
         <f t="shared" si="33"/>
         <v>791106.04</v>
@@ -13291,11 +13291,11 @@
         <v>0</v>
       </c>
       <c r="O110" s="88"/>
-      <c r="P110" s="418">
+      <c r="P110" s="422">
         <f t="shared" si="32"/>
         <v>705414.05</v>
       </c>
-      <c r="Q110" s="418"/>
+      <c r="Q110" s="422"/>
       <c r="R110" s="363">
         <f t="shared" si="33"/>
         <v>726810.05</v>
@@ -13364,11 +13364,11 @@
         <v>270455.26692913822</v>
       </c>
       <c r="O111" s="88"/>
-      <c r="P111" s="418">
+      <c r="P111" s="422">
         <f t="shared" si="32"/>
         <v>1769526.06</v>
       </c>
-      <c r="Q111" s="418"/>
+      <c r="Q111" s="422"/>
       <c r="R111" s="363">
         <f t="shared" si="33"/>
         <v>1823197.06</v>
@@ -13434,11 +13434,11 @@
         <v>0</v>
       </c>
       <c r="O112" s="88"/>
-      <c r="P112" s="418">
+      <c r="P112" s="422">
         <f t="shared" si="32"/>
         <v>766866.07</v>
       </c>
-      <c r="Q112" s="418"/>
+      <c r="Q112" s="422"/>
       <c r="R112" s="363">
         <f t="shared" si="33"/>
         <v>790126.07</v>
@@ -13504,11 +13504,11 @@
         <v>0</v>
       </c>
       <c r="O113" s="88"/>
-      <c r="P113" s="418">
+      <c r="P113" s="422">
         <f t="shared" si="32"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="418"/>
+      <c r="Q113" s="422"/>
       <c r="R113" s="363">
         <f t="shared" si="33"/>
         <v>742930.08</v>
@@ -13571,11 +13571,11 @@
         <v>0</v>
       </c>
       <c r="O114" s="88"/>
-      <c r="P114" s="418">
+      <c r="P114" s="422">
         <f t="shared" si="32"/>
         <v>1511441.09</v>
       </c>
-      <c r="Q114" s="418"/>
+      <c r="Q114" s="422"/>
       <c r="R114" s="363">
         <f t="shared" si="33"/>
         <v>1557284.09</v>
@@ -13641,11 +13641,11 @@
         <v>0</v>
       </c>
       <c r="O115" s="88"/>
-      <c r="P115" s="418">
+      <c r="P115" s="422">
         <f t="shared" si="32"/>
         <v>1524957.1</v>
       </c>
-      <c r="Q115" s="418"/>
+      <c r="Q115" s="422"/>
       <c r="R115" s="363">
         <f t="shared" si="33"/>
         <v>1571210.1</v>
@@ -13713,11 +13713,11 @@
         <v>0</v>
       </c>
       <c r="O116" s="88"/>
-      <c r="P116" s="418">
+      <c r="P116" s="422">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="418"/>
+      <c r="Q116" s="422"/>
       <c r="R116" s="363">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -13780,11 +13780,11 @@
         <v>0</v>
       </c>
       <c r="O117" s="88"/>
-      <c r="P117" s="418">
+      <c r="P117" s="422">
         <f t="shared" si="32"/>
         <v>725114.12</v>
       </c>
-      <c r="Q117" s="418"/>
+      <c r="Q117" s="422"/>
       <c r="R117" s="363">
         <f t="shared" si="33"/>
         <v>747108.12</v>
@@ -13850,11 +13850,11 @@
         <v>0</v>
       </c>
       <c r="O118" s="88"/>
-      <c r="P118" s="418">
+      <c r="P118" s="422">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="418"/>
+      <c r="Q118" s="422"/>
       <c r="R118" s="363">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -13917,11 +13917,11 @@
         <v>0</v>
       </c>
       <c r="O119" s="88"/>
-      <c r="P119" s="418">
+      <c r="P119" s="422">
         <f t="shared" si="32"/>
         <v>728882.14</v>
       </c>
-      <c r="Q119" s="418"/>
+      <c r="Q119" s="422"/>
       <c r="R119" s="363">
         <f t="shared" si="33"/>
         <v>750990.14</v>
@@ -13985,11 +13985,11 @@
         <v>0</v>
       </c>
       <c r="O120" s="88"/>
-      <c r="P120" s="418">
+      <c r="P120" s="422">
         <f t="shared" si="32"/>
         <v>849222.15</v>
       </c>
-      <c r="Q120" s="418"/>
+      <c r="Q120" s="422"/>
       <c r="R120" s="363">
         <f t="shared" si="33"/>
         <v>874980.15</v>
@@ -14056,11 +14056,11 @@
         <v>0</v>
       </c>
       <c r="O121" s="88"/>
-      <c r="P121" s="418">
+      <c r="P121" s="422">
         <f t="shared" si="32"/>
         <v>803799.16</v>
       </c>
-      <c r="Q121" s="418"/>
+      <c r="Q121" s="422"/>
       <c r="R121" s="363">
         <f t="shared" si="33"/>
         <v>828179.16</v>
@@ -14123,11 +14123,11 @@
         <v>0</v>
       </c>
       <c r="O122" s="88"/>
-      <c r="P122" s="418">
+      <c r="P122" s="422">
         <f t="shared" si="32"/>
         <v>854048.17</v>
       </c>
-      <c r="Q122" s="418"/>
+      <c r="Q122" s="422"/>
       <c r="R122" s="363">
         <f t="shared" si="33"/>
         <v>879952.17</v>
@@ -14194,11 +14194,11 @@
         <v>0</v>
       </c>
       <c r="O123" s="88"/>
-      <c r="P123" s="418">
+      <c r="P123" s="422">
         <f t="shared" si="32"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="418"/>
+      <c r="Q123" s="422"/>
       <c r="R123" s="363">
         <f t="shared" si="33"/>
         <v>882540.18</v>
@@ -14264,11 +14264,11 @@
         <v>0</v>
       </c>
       <c r="O124" s="88"/>
-      <c r="P124" s="418">
+      <c r="P124" s="422">
         <f t="shared" si="32"/>
         <v>827956.19</v>
       </c>
-      <c r="Q124" s="418"/>
+      <c r="Q124" s="422"/>
       <c r="R124" s="363">
         <f t="shared" si="33"/>
         <v>853069.19</v>
@@ -14335,11 +14335,11 @@
         <v>0</v>
       </c>
       <c r="O125" s="88"/>
-      <c r="P125" s="418">
+      <c r="P125" s="422">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="418"/>
+      <c r="Q125" s="422"/>
       <c r="R125" s="363">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -14406,11 +14406,11 @@
         <v>0</v>
       </c>
       <c r="O126" s="88"/>
-      <c r="P126" s="418">
+      <c r="P126" s="422">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="418"/>
+      <c r="Q126" s="422"/>
       <c r="R126" s="363">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -14476,11 +14476,11 @@
         <v>0</v>
       </c>
       <c r="O127" s="74"/>
-      <c r="P127" s="418">
+      <c r="P127" s="422">
         <f t="shared" si="32"/>
         <v>736705.22</v>
       </c>
-      <c r="Q127" s="418"/>
+      <c r="Q127" s="422"/>
       <c r="R127" s="363">
         <f t="shared" si="33"/>
         <v>759050.22</v>
@@ -14544,11 +14544,11 @@
         <v>0</v>
       </c>
       <c r="O128" s="88"/>
-      <c r="P128" s="418">
+      <c r="P128" s="422">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="418"/>
+      <c r="Q128" s="422"/>
       <c r="R128" s="363">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -14614,11 +14614,11 @@
         <v>0</v>
       </c>
       <c r="O129" s="88"/>
-      <c r="P129" s="418">
+      <c r="P129" s="422">
         <f t="shared" si="32"/>
         <v>736705.24</v>
       </c>
-      <c r="Q129" s="418"/>
+      <c r="Q129" s="422"/>
       <c r="R129" s="363">
         <f t="shared" si="33"/>
         <v>759051.24</v>
@@ -14682,11 +14682,11 @@
         <v>0</v>
       </c>
       <c r="O130" s="88"/>
-      <c r="P130" s="418">
+      <c r="P130" s="422">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="418"/>
+      <c r="Q130" s="422"/>
       <c r="R130" s="363">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -14753,11 +14753,11 @@
         <v>0</v>
       </c>
       <c r="O131" s="88"/>
-      <c r="P131" s="418">
+      <c r="P131" s="422">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="418"/>
+      <c r="Q131" s="422"/>
       <c r="R131" s="363">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -14818,11 +14818,11 @@
         <v>0</v>
       </c>
       <c r="O132" s="88"/>
-      <c r="P132" s="418">
+      <c r="P132" s="422">
         <f t="shared" si="32"/>
         <v>1680082.27</v>
       </c>
-      <c r="Q132" s="418"/>
+      <c r="Q132" s="422"/>
       <c r="R132" s="363">
         <f t="shared" si="33"/>
         <v>1731040.27</v>
@@ -14889,11 +14889,11 @@
         <v>339029.8362611382</v>
       </c>
       <c r="O133" s="88"/>
-      <c r="P133" s="418">
+      <c r="P133" s="422">
         <f t="shared" si="32"/>
         <v>9465986.2799999993</v>
       </c>
-      <c r="Q133" s="418"/>
+      <c r="Q133" s="422"/>
       <c r="R133" s="363">
         <f t="shared" si="33"/>
         <v>9753091.2799999993</v>
@@ -14956,11 +14956,11 @@
         <v>0</v>
       </c>
       <c r="O134" s="88"/>
-      <c r="P134" s="418">
+      <c r="P134" s="422">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>854048.29</v>
       </c>
-      <c r="Q134" s="418"/>
+      <c r="Q134" s="422"/>
       <c r="R134" s="363">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>879953.29</v>
@@ -15026,11 +15026,11 @@
         <v>0</v>
       </c>
       <c r="O135" s="88"/>
-      <c r="P135" s="418">
+      <c r="P135" s="422">
         <f t="shared" si="39"/>
         <v>847809.3</v>
       </c>
-      <c r="Q135" s="418"/>
+      <c r="Q135" s="422"/>
       <c r="R135" s="363">
         <f t="shared" si="40"/>
         <v>873524.3</v>
@@ -15097,11 +15097,11 @@
         <v>0</v>
       </c>
       <c r="O136" s="88"/>
-      <c r="P136" s="418">
+      <c r="P136" s="422">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="418"/>
+      <c r="Q136" s="422"/>
       <c r="R136" s="363">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15167,11 +15167,11 @@
         <v>0</v>
       </c>
       <c r="O137" s="88"/>
-      <c r="P137" s="418">
+      <c r="P137" s="422">
         <f t="shared" si="39"/>
         <v>846226.32</v>
       </c>
-      <c r="Q137" s="418"/>
+      <c r="Q137" s="422"/>
       <c r="R137" s="363">
         <f t="shared" si="40"/>
         <v>871893.32</v>
@@ -15238,11 +15238,11 @@
         <v>0</v>
       </c>
       <c r="O138" s="88"/>
-      <c r="P138" s="418">
+      <c r="P138" s="422">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="418"/>
+      <c r="Q138" s="422"/>
       <c r="R138" s="363">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -15308,11 +15308,11 @@
         <v>0</v>
       </c>
       <c r="O139" s="88"/>
-      <c r="P139" s="418">
+      <c r="P139" s="422">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="418"/>
+      <c r="Q139" s="422"/>
       <c r="R139" s="363">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -15378,11 +15378,11 @@
         <v>0</v>
       </c>
       <c r="O140" s="88"/>
-      <c r="P140" s="418">
+      <c r="P140" s="422">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="418"/>
+      <c r="Q140" s="422"/>
       <c r="R140" s="363">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -15446,11 +15446,11 @@
         <v>0</v>
       </c>
       <c r="O141" s="88"/>
-      <c r="P141" s="418">
+      <c r="P141" s="422">
         <f t="shared" si="39"/>
         <v>3751757.36</v>
       </c>
-      <c r="Q141" s="418"/>
+      <c r="Q141" s="422"/>
       <c r="R141" s="363">
         <f t="shared" si="40"/>
         <v>3865549.36</v>
@@ -15516,11 +15516,11 @@
         <v>0</v>
       </c>
       <c r="O142" s="88"/>
-      <c r="P142" s="418">
+      <c r="P142" s="422">
         <f t="shared" si="39"/>
         <v>799288.37</v>
       </c>
-      <c r="Q142" s="418"/>
+      <c r="Q142" s="422"/>
       <c r="R142" s="363">
         <f t="shared" si="40"/>
         <v>823532.37</v>
@@ -15583,11 +15583,11 @@
         <v>0</v>
       </c>
       <c r="O143" s="88"/>
-      <c r="P143" s="418">
+      <c r="P143" s="422">
         <f t="shared" si="39"/>
         <v>885340.38</v>
       </c>
-      <c r="Q143" s="418"/>
+      <c r="Q143" s="422"/>
       <c r="R143" s="363">
         <f t="shared" si="40"/>
         <v>912194.38</v>
@@ -15653,11 +15653,11 @@
         <v>0</v>
       </c>
       <c r="O144" s="88"/>
-      <c r="P144" s="418">
+      <c r="P144" s="422">
         <f t="shared" si="39"/>
         <v>880691.39</v>
       </c>
-      <c r="Q144" s="418"/>
+      <c r="Q144" s="422"/>
       <c r="R144" s="363">
         <f t="shared" si="40"/>
         <v>907404.39</v>
@@ -15697,8 +15697,8 @@
       <c r="M145" s="74"/>
       <c r="N145" s="74"/>
       <c r="O145" s="88"/>
-      <c r="P145" s="418"/>
-      <c r="Q145" s="418"/>
+      <c r="P145" s="422"/>
+      <c r="Q145" s="422"/>
       <c r="R145" s="364"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -15732,8 +15732,8 @@
       <c r="M146" s="74"/>
       <c r="N146" s="74"/>
       <c r="O146" s="88"/>
-      <c r="P146" s="418"/>
-      <c r="Q146" s="418"/>
+      <c r="P146" s="422"/>
+      <c r="Q146" s="422"/>
       <c r="R146" s="364"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -15760,8 +15760,8 @@
       <c r="M147" s="74"/>
       <c r="N147" s="74"/>
       <c r="O147" s="88"/>
-      <c r="P147" s="418"/>
-      <c r="Q147" s="418"/>
+      <c r="P147" s="422"/>
+      <c r="Q147" s="422"/>
       <c r="R147" s="364"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -15788,8 +15788,8 @@
       <c r="M148" s="74"/>
       <c r="N148" s="74"/>
       <c r="O148" s="88"/>
-      <c r="P148" s="418"/>
-      <c r="Q148" s="418"/>
+      <c r="P148" s="422"/>
+      <c r="Q148" s="422"/>
       <c r="R148" s="364"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -15849,11 +15849,11 @@
         <v>246252.47775313823</v>
       </c>
       <c r="O149" s="88"/>
-      <c r="P149" s="418">
+      <c r="P149" s="422">
         <f t="shared" ref="P149:P158" si="49">ROUND(SUM(G149:O149),0) + S149</f>
         <v>882923.46</v>
       </c>
-      <c r="Q149" s="418"/>
+      <c r="Q149" s="422"/>
       <c r="R149" s="363">
         <f t="shared" ref="R149:R158" si="50">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>909704.46</v>
@@ -15914,11 +15914,11 @@
         <v>0</v>
       </c>
       <c r="O150" s="88"/>
-      <c r="P150" s="418">
+      <c r="P150" s="422">
         <f t="shared" si="49"/>
         <v>707760.55</v>
       </c>
-      <c r="Q150" s="418"/>
+      <c r="Q150" s="422"/>
       <c r="R150" s="363">
         <f t="shared" si="50"/>
         <v>729228.55</v>
@@ -15985,11 +15985,11 @@
         <v>0</v>
       </c>
       <c r="O151" s="74"/>
-      <c r="P151" s="418">
+      <c r="P151" s="422">
         <f t="shared" si="49"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="418"/>
+      <c r="Q151" s="422"/>
       <c r="R151" s="363">
         <f t="shared" si="50"/>
         <v>782794.58</v>
@@ -16053,11 +16053,11 @@
         <v>0</v>
       </c>
       <c r="O152" s="74"/>
-      <c r="P152" s="418">
+      <c r="P152" s="422">
         <f t="shared" si="49"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="418"/>
+      <c r="Q152" s="422"/>
       <c r="R152" s="363">
         <f t="shared" si="50"/>
         <v>782794.59</v>
@@ -16121,11 +16121,11 @@
         <v>0</v>
       </c>
       <c r="O153" s="74"/>
-      <c r="P153" s="418">
+      <c r="P153" s="422">
         <f t="shared" si="49"/>
         <v>759750.63</v>
       </c>
-      <c r="Q153" s="418"/>
+      <c r="Q153" s="422"/>
       <c r="R153" s="363">
         <f t="shared" si="50"/>
         <v>782795.63</v>
@@ -16189,11 +16189,11 @@
         <v>0</v>
       </c>
       <c r="O154" s="74"/>
-      <c r="P154" s="418">
+      <c r="P154" s="422">
         <f t="shared" si="49"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="418"/>
+      <c r="Q154" s="422"/>
       <c r="R154" s="363">
         <f t="shared" si="50"/>
         <v>766170.68</v>
@@ -16256,11 +16256,11 @@
         <v>0</v>
       </c>
       <c r="O155" s="74"/>
-      <c r="P155" s="418">
+      <c r="P155" s="422">
         <f t="shared" si="49"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="418"/>
+      <c r="Q155" s="422"/>
       <c r="R155" s="363">
         <f t="shared" si="50"/>
         <v>759050.73</v>
@@ -16326,11 +16326,11 @@
         <v>0</v>
       </c>
       <c r="O156" s="74"/>
-      <c r="P156" s="418">
+      <c r="P156" s="422">
         <f t="shared" si="49"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="418"/>
+      <c r="Q156" s="422"/>
       <c r="R156" s="363">
         <f t="shared" si="50"/>
         <v>759050.75</v>
@@ -16397,11 +16397,11 @@
         <v>0</v>
       </c>
       <c r="O157" s="74"/>
-      <c r="P157" s="418">
+      <c r="P157" s="422">
         <f t="shared" si="49"/>
         <v>759750.76</v>
       </c>
-      <c r="Q157" s="418"/>
+      <c r="Q157" s="422"/>
       <c r="R157" s="363">
         <f t="shared" si="50"/>
         <v>782795.76</v>
@@ -16465,11 +16465,11 @@
         <v>0</v>
       </c>
       <c r="O158" s="74"/>
-      <c r="P158" s="418">
+      <c r="P158" s="422">
         <f t="shared" si="49"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="418"/>
+      <c r="Q158" s="422"/>
       <c r="R158" s="363">
         <f t="shared" si="50"/>
         <v>807732.04</v>
@@ -16502,8 +16502,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="74"/>
-      <c r="P159" s="423"/>
-      <c r="Q159" s="423"/>
+      <c r="P159" s="447"/>
+      <c r="Q159" s="447"/>
       <c r="R159" s="183"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -16524,8 +16524,8 @@
       <c r="M160" s="194"/>
       <c r="N160" s="194"/>
       <c r="O160" s="360"/>
-      <c r="P160" s="424"/>
-      <c r="Q160" s="424"/>
+      <c r="P160" s="448"/>
+      <c r="Q160" s="448"/>
       <c r="R160" s="186"/>
       <c r="S160" s="13"/>
       <c r="T160" s="195"/>
@@ -16571,7 +16571,7 @@
         <f t="shared" si="54"/>
         <v>580871</v>
       </c>
-      <c r="N161" s="473">
+      <c r="N161" s="386">
         <f t="shared" si="54"/>
         <v>3469638.8119514147</v>
       </c>
@@ -16579,150 +16579,312 @@
         <f t="shared" si="54"/>
         <v>890374.81218400015</v>
       </c>
-      <c r="P161" s="421">
+      <c r="P161" s="445">
         <f>SUM(P6:P160)</f>
         <v>169388305.07000002</v>
       </c>
-      <c r="Q161" s="422"/>
+      <c r="Q161" s="446"/>
       <c r="R161" s="187">
         <f>SUM(R6:R160)</f>
         <v>174525973.07000002</v>
       </c>
-      <c r="S161" s="421"/>
-      <c r="T161" s="422"/>
+      <c r="S161" s="445"/>
+      <c r="T161" s="446"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="419" t="s">
+      <c r="B162" s="443" t="s">
         <v>326</v>
       </c>
-      <c r="C162" s="419"/>
-      <c r="D162" s="419"/>
-      <c r="E162" s="419"/>
-      <c r="F162" s="419"/>
-      <c r="G162" s="419"/>
-      <c r="H162" s="419"/>
-      <c r="I162" s="419"/>
-      <c r="J162" s="419"/>
-      <c r="K162" s="419"/>
-      <c r="L162" s="419"/>
-      <c r="M162" s="419"/>
-      <c r="N162" s="419"/>
-      <c r="O162" s="419"/>
-      <c r="P162" s="419"/>
-      <c r="Q162" s="419"/>
-      <c r="R162" s="419"/>
-      <c r="S162" s="419"/>
-      <c r="T162" s="419"/>
+      <c r="C162" s="443"/>
+      <c r="D162" s="443"/>
+      <c r="E162" s="443"/>
+      <c r="F162" s="443"/>
+      <c r="G162" s="443"/>
+      <c r="H162" s="443"/>
+      <c r="I162" s="443"/>
+      <c r="J162" s="443"/>
+      <c r="K162" s="443"/>
+      <c r="L162" s="443"/>
+      <c r="M162" s="443"/>
+      <c r="N162" s="443"/>
+      <c r="O162" s="443"/>
+      <c r="P162" s="443"/>
+      <c r="Q162" s="443"/>
+      <c r="R162" s="443"/>
+      <c r="S162" s="443"/>
+      <c r="T162" s="443"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="420"/>
-      <c r="C163" s="420"/>
-      <c r="D163" s="420"/>
-      <c r="E163" s="420"/>
-      <c r="F163" s="420"/>
-      <c r="G163" s="420"/>
-      <c r="H163" s="420"/>
-      <c r="I163" s="420"/>
-      <c r="J163" s="420"/>
-      <c r="K163" s="420"/>
-      <c r="L163" s="420"/>
-      <c r="M163" s="420"/>
-      <c r="N163" s="420"/>
-      <c r="O163" s="420"/>
-      <c r="P163" s="420"/>
-      <c r="Q163" s="420"/>
-      <c r="R163" s="420"/>
-      <c r="S163" s="420"/>
-      <c r="T163" s="420"/>
+      <c r="B163" s="444"/>
+      <c r="C163" s="444"/>
+      <c r="D163" s="444"/>
+      <c r="E163" s="444"/>
+      <c r="F163" s="444"/>
+      <c r="G163" s="444"/>
+      <c r="H163" s="444"/>
+      <c r="I163" s="444"/>
+      <c r="J163" s="444"/>
+      <c r="K163" s="444"/>
+      <c r="L163" s="444"/>
+      <c r="M163" s="444"/>
+      <c r="N163" s="444"/>
+      <c r="O163" s="444"/>
+      <c r="P163" s="444"/>
+      <c r="Q163" s="444"/>
+      <c r="R163" s="444"/>
+      <c r="S163" s="444"/>
+      <c r="T163" s="444"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="420" t="s">
+      <c r="B164" s="444" t="s">
         <v>263</v>
       </c>
-      <c r="C164" s="420"/>
-      <c r="D164" s="420"/>
-      <c r="E164" s="420"/>
-      <c r="F164" s="420"/>
-      <c r="G164" s="420"/>
-      <c r="H164" s="420"/>
-      <c r="I164" s="420"/>
-      <c r="J164" s="420"/>
-      <c r="K164" s="420"/>
-      <c r="L164" s="420"/>
-      <c r="M164" s="420"/>
-      <c r="N164" s="420"/>
-      <c r="O164" s="420"/>
-      <c r="P164" s="420"/>
-      <c r="Q164" s="420"/>
-      <c r="R164" s="420"/>
-      <c r="S164" s="420"/>
-      <c r="T164" s="420"/>
+      <c r="C164" s="444"/>
+      <c r="D164" s="444"/>
+      <c r="E164" s="444"/>
+      <c r="F164" s="444"/>
+      <c r="G164" s="444"/>
+      <c r="H164" s="444"/>
+      <c r="I164" s="444"/>
+      <c r="J164" s="444"/>
+      <c r="K164" s="444"/>
+      <c r="L164" s="444"/>
+      <c r="M164" s="444"/>
+      <c r="N164" s="444"/>
+      <c r="O164" s="444"/>
+      <c r="P164" s="444"/>
+      <c r="Q164" s="444"/>
+      <c r="R164" s="444"/>
+      <c r="S164" s="444"/>
+      <c r="T164" s="444"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="420"/>
-      <c r="C165" s="420"/>
-      <c r="D165" s="420"/>
-      <c r="E165" s="420"/>
-      <c r="F165" s="420"/>
-      <c r="G165" s="420"/>
-      <c r="H165" s="420"/>
-      <c r="I165" s="420"/>
-      <c r="J165" s="420"/>
-      <c r="K165" s="420"/>
-      <c r="L165" s="420"/>
-      <c r="M165" s="420"/>
-      <c r="N165" s="420"/>
-      <c r="O165" s="420"/>
-      <c r="P165" s="420"/>
-      <c r="Q165" s="420"/>
-      <c r="R165" s="420"/>
-      <c r="S165" s="420"/>
-      <c r="T165" s="420"/>
+      <c r="B165" s="444"/>
+      <c r="C165" s="444"/>
+      <c r="D165" s="444"/>
+      <c r="E165" s="444"/>
+      <c r="F165" s="444"/>
+      <c r="G165" s="444"/>
+      <c r="H165" s="444"/>
+      <c r="I165" s="444"/>
+      <c r="J165" s="444"/>
+      <c r="K165" s="444"/>
+      <c r="L165" s="444"/>
+      <c r="M165" s="444"/>
+      <c r="N165" s="444"/>
+      <c r="O165" s="444"/>
+      <c r="P165" s="444"/>
+      <c r="Q165" s="444"/>
+      <c r="R165" s="444"/>
+      <c r="S165" s="444"/>
+      <c r="T165" s="444"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="420"/>
-      <c r="C166" s="420"/>
-      <c r="D166" s="420"/>
-      <c r="E166" s="420"/>
-      <c r="F166" s="420"/>
-      <c r="G166" s="420"/>
-      <c r="H166" s="420"/>
-      <c r="I166" s="420"/>
-      <c r="J166" s="420"/>
-      <c r="K166" s="420"/>
-      <c r="L166" s="420"/>
-      <c r="M166" s="420"/>
-      <c r="N166" s="420"/>
-      <c r="O166" s="420"/>
-      <c r="P166" s="420"/>
-      <c r="Q166" s="420"/>
-      <c r="R166" s="420"/>
-      <c r="S166" s="420"/>
-      <c r="T166" s="420"/>
+      <c r="B166" s="444"/>
+      <c r="C166" s="444"/>
+      <c r="D166" s="444"/>
+      <c r="E166" s="444"/>
+      <c r="F166" s="444"/>
+      <c r="G166" s="444"/>
+      <c r="H166" s="444"/>
+      <c r="I166" s="444"/>
+      <c r="J166" s="444"/>
+      <c r="K166" s="444"/>
+      <c r="L166" s="444"/>
+      <c r="M166" s="444"/>
+      <c r="N166" s="444"/>
+      <c r="O166" s="444"/>
+      <c r="P166" s="444"/>
+      <c r="Q166" s="444"/>
+      <c r="R166" s="444"/>
+      <c r="S166" s="444"/>
+      <c r="T166" s="444"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="420"/>
-      <c r="C167" s="420"/>
-      <c r="D167" s="420"/>
-      <c r="E167" s="420"/>
-      <c r="F167" s="420"/>
-      <c r="G167" s="420"/>
-      <c r="H167" s="420"/>
-      <c r="I167" s="420"/>
-      <c r="J167" s="420"/>
-      <c r="K167" s="420"/>
-      <c r="L167" s="420"/>
-      <c r="M167" s="420"/>
-      <c r="N167" s="420"/>
-      <c r="O167" s="420"/>
-      <c r="P167" s="420"/>
-      <c r="Q167" s="420"/>
-      <c r="R167" s="420"/>
-      <c r="S167" s="420"/>
-      <c r="T167" s="420"/>
+      <c r="B167" s="444"/>
+      <c r="C167" s="444"/>
+      <c r="D167" s="444"/>
+      <c r="E167" s="444"/>
+      <c r="F167" s="444"/>
+      <c r="G167" s="444"/>
+      <c r="H167" s="444"/>
+      <c r="I167" s="444"/>
+      <c r="J167" s="444"/>
+      <c r="K167" s="444"/>
+      <c r="L167" s="444"/>
+      <c r="M167" s="444"/>
+      <c r="N167" s="444"/>
+      <c r="O167" s="444"/>
+      <c r="P167" s="444"/>
+      <c r="Q167" s="444"/>
+      <c r="R167" s="444"/>
+      <c r="S167" s="444"/>
+      <c r="T167" s="444"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -16747,168 +16909,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -16944,12 +16944,12 @@
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
       <c r="J3" s="66"/>
-      <c r="K3" s="459" t="s">
+      <c r="K3" s="458" t="s">
         <v>336</v>
       </c>
-      <c r="L3" s="460"/>
-      <c r="M3" s="460"/>
-      <c r="N3" s="460"/>
+      <c r="L3" s="459"/>
+      <c r="M3" s="459"/>
+      <c r="N3" s="459"/>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C4" s="147" t="s">
@@ -16968,10 +16968,10 @@
       </c>
       <c r="I4" s="67"/>
       <c r="J4" s="68"/>
-      <c r="K4" s="459"/>
-      <c r="L4" s="460"/>
-      <c r="M4" s="460"/>
-      <c r="N4" s="460"/>
+      <c r="K4" s="458"/>
+      <c r="L4" s="459"/>
+      <c r="M4" s="459"/>
+      <c r="N4" s="459"/>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C5" s="147" t="s">
@@ -16992,10 +16992,10 @@
       </c>
       <c r="I5" s="67"/>
       <c r="J5" s="68"/>
-      <c r="K5" s="459"/>
-      <c r="L5" s="460"/>
-      <c r="M5" s="460"/>
-      <c r="N5" s="460"/>
+      <c r="K5" s="458"/>
+      <c r="L5" s="459"/>
+      <c r="M5" s="459"/>
+      <c r="N5" s="459"/>
     </row>
     <row r="6" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" s="147" t="s">
@@ -17008,56 +17008,56 @@
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
       <c r="J6" s="69"/>
-      <c r="K6" s="459"/>
-      <c r="L6" s="460"/>
-      <c r="M6" s="460"/>
-      <c r="N6" s="460"/>
+      <c r="K6" s="458"/>
+      <c r="L6" s="459"/>
+      <c r="M6" s="459"/>
+      <c r="N6" s="459"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="448" t="s">
+      <c r="C7" s="449" t="s">
         <v>321</v>
       </c>
-      <c r="D7" s="449"/>
-      <c r="E7" s="449"/>
-      <c r="F7" s="449"/>
-      <c r="G7" s="449"/>
-      <c r="H7" s="449"/>
-      <c r="I7" s="449"/>
-      <c r="J7" s="450"/>
-      <c r="K7" s="461" t="s">
+      <c r="D7" s="450"/>
+      <c r="E7" s="450"/>
+      <c r="F7" s="450"/>
+      <c r="G7" s="450"/>
+      <c r="H7" s="450"/>
+      <c r="I7" s="450"/>
+      <c r="J7" s="451"/>
+      <c r="K7" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="L7" s="462"/>
-      <c r="M7" s="462"/>
-      <c r="N7" s="462"/>
+      <c r="L7" s="461"/>
+      <c r="M7" s="461"/>
+      <c r="N7" s="461"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="451"/>
-      <c r="D8" s="452"/>
-      <c r="E8" s="452"/>
-      <c r="F8" s="452"/>
-      <c r="G8" s="452"/>
-      <c r="H8" s="452"/>
-      <c r="I8" s="452"/>
-      <c r="J8" s="453"/>
-      <c r="K8" s="461"/>
-      <c r="L8" s="462"/>
-      <c r="M8" s="462"/>
-      <c r="N8" s="462"/>
+      <c r="C8" s="452"/>
+      <c r="D8" s="453"/>
+      <c r="E8" s="453"/>
+      <c r="F8" s="453"/>
+      <c r="G8" s="453"/>
+      <c r="H8" s="453"/>
+      <c r="I8" s="453"/>
+      <c r="J8" s="454"/>
+      <c r="K8" s="460"/>
+      <c r="L8" s="461"/>
+      <c r="M8" s="461"/>
+      <c r="N8" s="461"/>
     </row>
     <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="454"/>
-      <c r="D9" s="455"/>
-      <c r="E9" s="455"/>
-      <c r="F9" s="455"/>
-      <c r="G9" s="455"/>
-      <c r="H9" s="455"/>
-      <c r="I9" s="455"/>
-      <c r="J9" s="456"/>
-      <c r="K9" s="461"/>
-      <c r="L9" s="462"/>
-      <c r="M9" s="462"/>
-      <c r="N9" s="462"/>
+      <c r="C9" s="455"/>
+      <c r="D9" s="456"/>
+      <c r="E9" s="456"/>
+      <c r="F9" s="456"/>
+      <c r="G9" s="456"/>
+      <c r="H9" s="456"/>
+      <c r="I9" s="456"/>
+      <c r="J9" s="457"/>
+      <c r="K9" s="460"/>
+      <c r="L9" s="461"/>
+      <c r="M9" s="461"/>
+      <c r="N9" s="461"/>
     </row>
     <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:14" x14ac:dyDescent="0.25">
@@ -17138,42 +17138,42 @@
       <c r="M15" s="347"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="448" t="s">
+      <c r="C16" s="449" t="s">
         <v>340</v>
       </c>
-      <c r="D16" s="449"/>
-      <c r="E16" s="449"/>
-      <c r="F16" s="449"/>
-      <c r="G16" s="449"/>
-      <c r="H16" s="449"/>
-      <c r="I16" s="449"/>
-      <c r="J16" s="450"/>
+      <c r="D16" s="450"/>
+      <c r="E16" s="450"/>
+      <c r="F16" s="450"/>
+      <c r="G16" s="450"/>
+      <c r="H16" s="450"/>
+      <c r="I16" s="450"/>
+      <c r="J16" s="451"/>
       <c r="K16" s="347"/>
       <c r="L16" s="347"/>
       <c r="M16" s="347"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C17" s="451"/>
-      <c r="D17" s="452"/>
-      <c r="E17" s="452"/>
-      <c r="F17" s="452"/>
-      <c r="G17" s="452"/>
-      <c r="H17" s="452"/>
-      <c r="I17" s="452"/>
-      <c r="J17" s="453"/>
+      <c r="C17" s="452"/>
+      <c r="D17" s="453"/>
+      <c r="E17" s="453"/>
+      <c r="F17" s="453"/>
+      <c r="G17" s="453"/>
+      <c r="H17" s="453"/>
+      <c r="I17" s="453"/>
+      <c r="J17" s="454"/>
       <c r="K17" s="347"/>
       <c r="L17" s="347"/>
       <c r="M17" s="347"/>
     </row>
     <row r="18" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="454"/>
-      <c r="D18" s="455"/>
-      <c r="E18" s="455"/>
-      <c r="F18" s="455"/>
-      <c r="G18" s="455"/>
-      <c r="H18" s="455"/>
-      <c r="I18" s="455"/>
-      <c r="J18" s="456"/>
+      <c r="C18" s="455"/>
+      <c r="D18" s="456"/>
+      <c r="E18" s="456"/>
+      <c r="F18" s="456"/>
+      <c r="G18" s="456"/>
+      <c r="H18" s="456"/>
+      <c r="I18" s="456"/>
+      <c r="J18" s="457"/>
     </row>
     <row r="20" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="256"/>
@@ -17253,40 +17253,40 @@
       <c r="L24" s="347"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="448" t="s">
+      <c r="C25" s="449" t="s">
         <v>370</v>
       </c>
-      <c r="D25" s="449"/>
-      <c r="E25" s="449"/>
-      <c r="F25" s="449"/>
-      <c r="G25" s="449"/>
-      <c r="H25" s="449"/>
-      <c r="I25" s="449"/>
-      <c r="J25" s="450"/>
+      <c r="D25" s="450"/>
+      <c r="E25" s="450"/>
+      <c r="F25" s="450"/>
+      <c r="G25" s="450"/>
+      <c r="H25" s="450"/>
+      <c r="I25" s="450"/>
+      <c r="J25" s="451"/>
       <c r="K25" s="347"/>
       <c r="L25" s="347"/>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="451"/>
-      <c r="D26" s="452"/>
-      <c r="E26" s="452"/>
-      <c r="F26" s="452"/>
-      <c r="G26" s="452"/>
-      <c r="H26" s="452"/>
-      <c r="I26" s="452"/>
-      <c r="J26" s="453"/>
+      <c r="C26" s="452"/>
+      <c r="D26" s="453"/>
+      <c r="E26" s="453"/>
+      <c r="F26" s="453"/>
+      <c r="G26" s="453"/>
+      <c r="H26" s="453"/>
+      <c r="I26" s="453"/>
+      <c r="J26" s="454"/>
       <c r="K26" s="347"/>
       <c r="L26" s="347"/>
     </row>
     <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="454"/>
-      <c r="D27" s="455"/>
-      <c r="E27" s="455"/>
-      <c r="F27" s="455"/>
-      <c r="G27" s="455"/>
-      <c r="H27" s="455"/>
-      <c r="I27" s="455"/>
-      <c r="J27" s="456"/>
+      <c r="C27" s="455"/>
+      <c r="D27" s="456"/>
+      <c r="E27" s="456"/>
+      <c r="F27" s="456"/>
+      <c r="G27" s="456"/>
+      <c r="H27" s="456"/>
+      <c r="I27" s="456"/>
+      <c r="J27" s="457"/>
       <c r="K27" s="347"/>
       <c r="L27" s="347"/>
     </row>
@@ -17373,42 +17373,42 @@
       <c r="M33" s="347"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C34" s="448" t="s">
+      <c r="C34" s="449" t="s">
         <v>343</v>
       </c>
-      <c r="D34" s="449"/>
-      <c r="E34" s="449"/>
-      <c r="F34" s="449"/>
-      <c r="G34" s="449"/>
-      <c r="H34" s="449"/>
-      <c r="I34" s="449"/>
-      <c r="J34" s="450"/>
+      <c r="D34" s="450"/>
+      <c r="E34" s="450"/>
+      <c r="F34" s="450"/>
+      <c r="G34" s="450"/>
+      <c r="H34" s="450"/>
+      <c r="I34" s="450"/>
+      <c r="J34" s="451"/>
       <c r="K34" s="347"/>
       <c r="L34" s="347"/>
       <c r="M34" s="347"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C35" s="451"/>
-      <c r="D35" s="452"/>
-      <c r="E35" s="452"/>
-      <c r="F35" s="452"/>
-      <c r="G35" s="452"/>
-      <c r="H35" s="452"/>
-      <c r="I35" s="452"/>
-      <c r="J35" s="453"/>
+      <c r="C35" s="452"/>
+      <c r="D35" s="453"/>
+      <c r="E35" s="453"/>
+      <c r="F35" s="453"/>
+      <c r="G35" s="453"/>
+      <c r="H35" s="453"/>
+      <c r="I35" s="453"/>
+      <c r="J35" s="454"/>
       <c r="K35" s="347"/>
       <c r="L35" s="347"/>
       <c r="M35" s="347"/>
     </row>
     <row r="36" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="454"/>
-      <c r="D36" s="455"/>
-      <c r="E36" s="455"/>
-      <c r="F36" s="455"/>
-      <c r="G36" s="455"/>
-      <c r="H36" s="455"/>
-      <c r="I36" s="455"/>
-      <c r="J36" s="456"/>
+      <c r="C36" s="455"/>
+      <c r="D36" s="456"/>
+      <c r="E36" s="456"/>
+      <c r="F36" s="456"/>
+      <c r="G36" s="456"/>
+      <c r="H36" s="456"/>
+      <c r="I36" s="456"/>
+      <c r="J36" s="457"/>
       <c r="K36" s="347"/>
       <c r="L36" s="347"/>
       <c r="M36" s="347"/>
@@ -17489,42 +17489,42 @@
       <c r="M42" s="347"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C43" s="448" t="s">
+      <c r="C43" s="449" t="s">
         <v>358</v>
       </c>
-      <c r="D43" s="449"/>
-      <c r="E43" s="449"/>
-      <c r="F43" s="449"/>
-      <c r="G43" s="449"/>
-      <c r="H43" s="449"/>
-      <c r="I43" s="449"/>
-      <c r="J43" s="450"/>
+      <c r="D43" s="450"/>
+      <c r="E43" s="450"/>
+      <c r="F43" s="450"/>
+      <c r="G43" s="450"/>
+      <c r="H43" s="450"/>
+      <c r="I43" s="450"/>
+      <c r="J43" s="451"/>
       <c r="K43" s="347"/>
       <c r="L43" s="347"/>
       <c r="M43" s="347"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="451"/>
-      <c r="D44" s="452"/>
-      <c r="E44" s="452"/>
-      <c r="F44" s="452"/>
-      <c r="G44" s="452"/>
-      <c r="H44" s="452"/>
-      <c r="I44" s="452"/>
-      <c r="J44" s="453"/>
+      <c r="C44" s="452"/>
+      <c r="D44" s="453"/>
+      <c r="E44" s="453"/>
+      <c r="F44" s="453"/>
+      <c r="G44" s="453"/>
+      <c r="H44" s="453"/>
+      <c r="I44" s="453"/>
+      <c r="J44" s="454"/>
       <c r="K44" s="347"/>
       <c r="L44" s="347"/>
       <c r="M44" s="347"/>
     </row>
     <row r="45" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="454"/>
-      <c r="D45" s="455"/>
-      <c r="E45" s="455"/>
-      <c r="F45" s="455"/>
-      <c r="G45" s="455"/>
-      <c r="H45" s="455"/>
-      <c r="I45" s="455"/>
-      <c r="J45" s="456"/>
+      <c r="C45" s="455"/>
+      <c r="D45" s="456"/>
+      <c r="E45" s="456"/>
+      <c r="F45" s="456"/>
+      <c r="G45" s="456"/>
+      <c r="H45" s="456"/>
+      <c r="I45" s="456"/>
+      <c r="J45" s="457"/>
     </row>
     <row r="47" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="3:13" x14ac:dyDescent="0.25">
@@ -17599,40 +17599,40 @@
       <c r="L51" s="347"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="448" t="s">
+      <c r="C52" s="449" t="s">
         <v>356</v>
       </c>
-      <c r="D52" s="449"/>
-      <c r="E52" s="449"/>
-      <c r="F52" s="449"/>
-      <c r="G52" s="449"/>
-      <c r="H52" s="449"/>
-      <c r="I52" s="449"/>
-      <c r="J52" s="450"/>
+      <c r="D52" s="450"/>
+      <c r="E52" s="450"/>
+      <c r="F52" s="450"/>
+      <c r="G52" s="450"/>
+      <c r="H52" s="450"/>
+      <c r="I52" s="450"/>
+      <c r="J52" s="451"/>
       <c r="K52" s="347"/>
       <c r="L52" s="347"/>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C53" s="451"/>
-      <c r="D53" s="452"/>
-      <c r="E53" s="452"/>
-      <c r="F53" s="452"/>
-      <c r="G53" s="452"/>
-      <c r="H53" s="452"/>
-      <c r="I53" s="452"/>
-      <c r="J53" s="453"/>
+      <c r="C53" s="452"/>
+      <c r="D53" s="453"/>
+      <c r="E53" s="453"/>
+      <c r="F53" s="453"/>
+      <c r="G53" s="453"/>
+      <c r="H53" s="453"/>
+      <c r="I53" s="453"/>
+      <c r="J53" s="454"/>
       <c r="K53" s="347"/>
       <c r="L53" s="347"/>
     </row>
     <row r="54" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="454"/>
-      <c r="D54" s="455"/>
-      <c r="E54" s="455"/>
-      <c r="F54" s="455"/>
-      <c r="G54" s="455"/>
-      <c r="H54" s="455"/>
-      <c r="I54" s="455"/>
-      <c r="J54" s="456"/>
+      <c r="C54" s="455"/>
+      <c r="D54" s="456"/>
+      <c r="E54" s="456"/>
+      <c r="F54" s="456"/>
+      <c r="G54" s="456"/>
+      <c r="H54" s="456"/>
+      <c r="I54" s="456"/>
+      <c r="J54" s="457"/>
       <c r="K54" s="347"/>
       <c r="L54" s="347"/>
     </row>
@@ -17707,40 +17707,40 @@
       <c r="L60" s="347"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C61" s="448" t="s">
+      <c r="C61" s="449" t="s">
         <v>357</v>
       </c>
-      <c r="D61" s="449"/>
-      <c r="E61" s="449"/>
-      <c r="F61" s="449"/>
-      <c r="G61" s="449"/>
-      <c r="H61" s="449"/>
-      <c r="I61" s="449"/>
-      <c r="J61" s="450"/>
+      <c r="D61" s="450"/>
+      <c r="E61" s="450"/>
+      <c r="F61" s="450"/>
+      <c r="G61" s="450"/>
+      <c r="H61" s="450"/>
+      <c r="I61" s="450"/>
+      <c r="J61" s="451"/>
       <c r="K61" s="347"/>
       <c r="L61" s="347"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C62" s="451"/>
-      <c r="D62" s="452"/>
-      <c r="E62" s="452"/>
-      <c r="F62" s="452"/>
-      <c r="G62" s="452"/>
-      <c r="H62" s="452"/>
-      <c r="I62" s="452"/>
-      <c r="J62" s="453"/>
+      <c r="C62" s="452"/>
+      <c r="D62" s="453"/>
+      <c r="E62" s="453"/>
+      <c r="F62" s="453"/>
+      <c r="G62" s="453"/>
+      <c r="H62" s="453"/>
+      <c r="I62" s="453"/>
+      <c r="J62" s="454"/>
       <c r="K62" s="347"/>
       <c r="L62" s="347"/>
     </row>
     <row r="63" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="454"/>
-      <c r="D63" s="455"/>
-      <c r="E63" s="455"/>
-      <c r="F63" s="455"/>
-      <c r="G63" s="455"/>
-      <c r="H63" s="455"/>
-      <c r="I63" s="455"/>
-      <c r="J63" s="456"/>
+      <c r="C63" s="455"/>
+      <c r="D63" s="456"/>
+      <c r="E63" s="456"/>
+      <c r="F63" s="456"/>
+      <c r="G63" s="456"/>
+      <c r="H63" s="456"/>
+      <c r="I63" s="456"/>
+      <c r="J63" s="457"/>
     </row>
     <row r="65" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="66" spans="3:12" x14ac:dyDescent="0.25">
@@ -17815,40 +17815,40 @@
       <c r="L69" s="347"/>
     </row>
     <row r="70" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C70" s="448" t="s">
+      <c r="C70" s="449" t="s">
         <v>345</v>
       </c>
-      <c r="D70" s="449"/>
-      <c r="E70" s="449"/>
-      <c r="F70" s="449"/>
-      <c r="G70" s="449"/>
-      <c r="H70" s="449"/>
-      <c r="I70" s="449"/>
-      <c r="J70" s="450"/>
+      <c r="D70" s="450"/>
+      <c r="E70" s="450"/>
+      <c r="F70" s="450"/>
+      <c r="G70" s="450"/>
+      <c r="H70" s="450"/>
+      <c r="I70" s="450"/>
+      <c r="J70" s="451"/>
       <c r="K70" s="347"/>
       <c r="L70" s="347"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C71" s="451"/>
-      <c r="D71" s="452"/>
-      <c r="E71" s="452"/>
-      <c r="F71" s="452"/>
-      <c r="G71" s="452"/>
-      <c r="H71" s="452"/>
-      <c r="I71" s="452"/>
-      <c r="J71" s="453"/>
+      <c r="C71" s="452"/>
+      <c r="D71" s="453"/>
+      <c r="E71" s="453"/>
+      <c r="F71" s="453"/>
+      <c r="G71" s="453"/>
+      <c r="H71" s="453"/>
+      <c r="I71" s="453"/>
+      <c r="J71" s="454"/>
       <c r="K71" s="347"/>
       <c r="L71" s="347"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="454"/>
-      <c r="D72" s="455"/>
-      <c r="E72" s="455"/>
-      <c r="F72" s="455"/>
-      <c r="G72" s="455"/>
-      <c r="H72" s="455"/>
-      <c r="I72" s="455"/>
-      <c r="J72" s="456"/>
+      <c r="C72" s="455"/>
+      <c r="D72" s="456"/>
+      <c r="E72" s="456"/>
+      <c r="F72" s="456"/>
+      <c r="G72" s="456"/>
+      <c r="H72" s="456"/>
+      <c r="I72" s="456"/>
+      <c r="J72" s="457"/>
     </row>
     <row r="74" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="3:12" x14ac:dyDescent="0.25">
@@ -17923,40 +17923,40 @@
       <c r="L78" s="347"/>
     </row>
     <row r="79" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C79" s="448" t="s">
+      <c r="C79" s="449" t="s">
         <v>346</v>
       </c>
-      <c r="D79" s="449"/>
-      <c r="E79" s="449"/>
-      <c r="F79" s="449"/>
-      <c r="G79" s="449"/>
-      <c r="H79" s="449"/>
-      <c r="I79" s="449"/>
-      <c r="J79" s="450"/>
+      <c r="D79" s="450"/>
+      <c r="E79" s="450"/>
+      <c r="F79" s="450"/>
+      <c r="G79" s="450"/>
+      <c r="H79" s="450"/>
+      <c r="I79" s="450"/>
+      <c r="J79" s="451"/>
       <c r="K79" s="347"/>
       <c r="L79" s="347"/>
     </row>
     <row r="80" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C80" s="451"/>
-      <c r="D80" s="452"/>
-      <c r="E80" s="452"/>
-      <c r="F80" s="452"/>
-      <c r="G80" s="452"/>
-      <c r="H80" s="452"/>
-      <c r="I80" s="452"/>
-      <c r="J80" s="453"/>
+      <c r="C80" s="452"/>
+      <c r="D80" s="453"/>
+      <c r="E80" s="453"/>
+      <c r="F80" s="453"/>
+      <c r="G80" s="453"/>
+      <c r="H80" s="453"/>
+      <c r="I80" s="453"/>
+      <c r="J80" s="454"/>
       <c r="K80" s="347"/>
       <c r="L80" s="347"/>
     </row>
     <row r="81" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="454"/>
-      <c r="D81" s="455"/>
-      <c r="E81" s="455"/>
-      <c r="F81" s="455"/>
-      <c r="G81" s="455"/>
-      <c r="H81" s="455"/>
-      <c r="I81" s="455"/>
-      <c r="J81" s="456"/>
+      <c r="C81" s="455"/>
+      <c r="D81" s="456"/>
+      <c r="E81" s="456"/>
+      <c r="F81" s="456"/>
+      <c r="G81" s="456"/>
+      <c r="H81" s="456"/>
+      <c r="I81" s="456"/>
+      <c r="J81" s="457"/>
       <c r="K81" s="347"/>
       <c r="L81" s="347"/>
     </row>
@@ -18031,40 +18031,40 @@
       <c r="L87" s="347"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C88" s="448" t="s">
+      <c r="C88" s="449" t="s">
         <v>347</v>
       </c>
-      <c r="D88" s="449"/>
-      <c r="E88" s="449"/>
-      <c r="F88" s="449"/>
-      <c r="G88" s="449"/>
-      <c r="H88" s="449"/>
-      <c r="I88" s="449"/>
-      <c r="J88" s="450"/>
+      <c r="D88" s="450"/>
+      <c r="E88" s="450"/>
+      <c r="F88" s="450"/>
+      <c r="G88" s="450"/>
+      <c r="H88" s="450"/>
+      <c r="I88" s="450"/>
+      <c r="J88" s="451"/>
       <c r="K88" s="347"/>
       <c r="L88" s="347"/>
     </row>
     <row r="89" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C89" s="451"/>
-      <c r="D89" s="452"/>
-      <c r="E89" s="452"/>
-      <c r="F89" s="452"/>
-      <c r="G89" s="452"/>
-      <c r="H89" s="452"/>
-      <c r="I89" s="452"/>
-      <c r="J89" s="453"/>
+      <c r="C89" s="452"/>
+      <c r="D89" s="453"/>
+      <c r="E89" s="453"/>
+      <c r="F89" s="453"/>
+      <c r="G89" s="453"/>
+      <c r="H89" s="453"/>
+      <c r="I89" s="453"/>
+      <c r="J89" s="454"/>
       <c r="K89" s="347"/>
       <c r="L89" s="347"/>
     </row>
     <row r="90" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="454"/>
-      <c r="D90" s="455"/>
-      <c r="E90" s="455"/>
-      <c r="F90" s="455"/>
-      <c r="G90" s="455"/>
-      <c r="H90" s="455"/>
-      <c r="I90" s="455"/>
-      <c r="J90" s="456"/>
+      <c r="C90" s="455"/>
+      <c r="D90" s="456"/>
+      <c r="E90" s="456"/>
+      <c r="F90" s="456"/>
+      <c r="G90" s="456"/>
+      <c r="H90" s="456"/>
+      <c r="I90" s="456"/>
+      <c r="J90" s="457"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C91" s="320"/>
@@ -18159,16 +18159,16 @@
       <c r="L99" s="347"/>
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C100" s="448" t="s">
+      <c r="C100" s="449" t="s">
         <v>359</v>
       </c>
-      <c r="D100" s="449"/>
-      <c r="E100" s="449"/>
-      <c r="F100" s="449"/>
-      <c r="G100" s="449"/>
-      <c r="H100" s="449"/>
-      <c r="I100" s="449"/>
-      <c r="J100" s="450"/>
+      <c r="D100" s="450"/>
+      <c r="E100" s="450"/>
+      <c r="F100" s="450"/>
+      <c r="G100" s="450"/>
+      <c r="H100" s="450"/>
+      <c r="I100" s="450"/>
+      <c r="J100" s="451"/>
       <c r="K100" s="347"/>
       <c r="L100" s="347"/>
       <c r="O100">
@@ -18177,14 +18177,14 @@
       </c>
     </row>
     <row r="101" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C101" s="451"/>
-      <c r="D101" s="452"/>
-      <c r="E101" s="452"/>
-      <c r="F101" s="452"/>
-      <c r="G101" s="452"/>
-      <c r="H101" s="452"/>
-      <c r="I101" s="452"/>
-      <c r="J101" s="453"/>
+      <c r="C101" s="452"/>
+      <c r="D101" s="453"/>
+      <c r="E101" s="453"/>
+      <c r="F101" s="453"/>
+      <c r="G101" s="453"/>
+      <c r="H101" s="453"/>
+      <c r="I101" s="453"/>
+      <c r="J101" s="454"/>
       <c r="K101" s="347"/>
       <c r="L101" s="347"/>
       <c r="O101">
@@ -18193,14 +18193,14 @@
       </c>
     </row>
     <row r="102" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="454"/>
-      <c r="D102" s="455"/>
-      <c r="E102" s="455"/>
-      <c r="F102" s="455"/>
-      <c r="G102" s="455"/>
-      <c r="H102" s="455"/>
-      <c r="I102" s="455"/>
-      <c r="J102" s="456"/>
+      <c r="C102" s="455"/>
+      <c r="D102" s="456"/>
+      <c r="E102" s="456"/>
+      <c r="F102" s="456"/>
+      <c r="G102" s="456"/>
+      <c r="H102" s="456"/>
+      <c r="I102" s="456"/>
+      <c r="J102" s="457"/>
       <c r="K102" s="347"/>
       <c r="L102" s="347"/>
     </row>
@@ -18289,40 +18289,40 @@
       <c r="L108" s="347"/>
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C109" s="448" t="s">
+      <c r="C109" s="449" t="s">
         <v>349</v>
       </c>
-      <c r="D109" s="449"/>
-      <c r="E109" s="449"/>
-      <c r="F109" s="449"/>
-      <c r="G109" s="449"/>
-      <c r="H109" s="449"/>
-      <c r="I109" s="449"/>
-      <c r="J109" s="450"/>
+      <c r="D109" s="450"/>
+      <c r="E109" s="450"/>
+      <c r="F109" s="450"/>
+      <c r="G109" s="450"/>
+      <c r="H109" s="450"/>
+      <c r="I109" s="450"/>
+      <c r="J109" s="451"/>
       <c r="K109" s="347"/>
       <c r="L109" s="347"/>
     </row>
     <row r="110" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C110" s="451"/>
-      <c r="D110" s="452"/>
-      <c r="E110" s="452"/>
-      <c r="F110" s="452"/>
-      <c r="G110" s="452"/>
-      <c r="H110" s="452"/>
-      <c r="I110" s="452"/>
-      <c r="J110" s="453"/>
+      <c r="C110" s="452"/>
+      <c r="D110" s="453"/>
+      <c r="E110" s="453"/>
+      <c r="F110" s="453"/>
+      <c r="G110" s="453"/>
+      <c r="H110" s="453"/>
+      <c r="I110" s="453"/>
+      <c r="J110" s="454"/>
       <c r="K110" s="347"/>
       <c r="L110" s="347"/>
     </row>
     <row r="111" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="454"/>
-      <c r="D111" s="455"/>
-      <c r="E111" s="455"/>
-      <c r="F111" s="455"/>
-      <c r="G111" s="455"/>
-      <c r="H111" s="455"/>
-      <c r="I111" s="455"/>
-      <c r="J111" s="456"/>
+      <c r="C111" s="455"/>
+      <c r="D111" s="456"/>
+      <c r="E111" s="456"/>
+      <c r="F111" s="456"/>
+      <c r="G111" s="456"/>
+      <c r="H111" s="456"/>
+      <c r="I111" s="456"/>
+      <c r="J111" s="457"/>
     </row>
     <row r="113" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="3:12" x14ac:dyDescent="0.25">
@@ -18395,40 +18395,40 @@
       <c r="L117" s="347"/>
     </row>
     <row r="118" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C118" s="448" t="s">
+      <c r="C118" s="449" t="s">
         <v>350</v>
       </c>
-      <c r="D118" s="449"/>
-      <c r="E118" s="449"/>
-      <c r="F118" s="449"/>
-      <c r="G118" s="449"/>
-      <c r="H118" s="449"/>
-      <c r="I118" s="449"/>
-      <c r="J118" s="450"/>
+      <c r="D118" s="450"/>
+      <c r="E118" s="450"/>
+      <c r="F118" s="450"/>
+      <c r="G118" s="450"/>
+      <c r="H118" s="450"/>
+      <c r="I118" s="450"/>
+      <c r="J118" s="451"/>
       <c r="K118" s="347"/>
       <c r="L118" s="347"/>
     </row>
     <row r="119" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C119" s="451"/>
-      <c r="D119" s="452"/>
-      <c r="E119" s="452"/>
-      <c r="F119" s="452"/>
-      <c r="G119" s="452"/>
-      <c r="H119" s="452"/>
-      <c r="I119" s="452"/>
-      <c r="J119" s="453"/>
+      <c r="C119" s="452"/>
+      <c r="D119" s="453"/>
+      <c r="E119" s="453"/>
+      <c r="F119" s="453"/>
+      <c r="G119" s="453"/>
+      <c r="H119" s="453"/>
+      <c r="I119" s="453"/>
+      <c r="J119" s="454"/>
       <c r="K119" s="347"/>
       <c r="L119" s="347"/>
     </row>
     <row r="120" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C120" s="454"/>
-      <c r="D120" s="455"/>
-      <c r="E120" s="455"/>
-      <c r="F120" s="455"/>
-      <c r="G120" s="455"/>
-      <c r="H120" s="455"/>
-      <c r="I120" s="455"/>
-      <c r="J120" s="456"/>
+      <c r="C120" s="455"/>
+      <c r="D120" s="456"/>
+      <c r="E120" s="456"/>
+      <c r="F120" s="456"/>
+      <c r="G120" s="456"/>
+      <c r="H120" s="456"/>
+      <c r="I120" s="456"/>
+      <c r="J120" s="457"/>
     </row>
     <row r="122" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="123" spans="3:12" x14ac:dyDescent="0.25">
@@ -18501,40 +18501,40 @@
       <c r="L126" s="347"/>
     </row>
     <row r="127" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C127" s="448" t="s">
+      <c r="C127" s="449" t="s">
         <v>351</v>
       </c>
-      <c r="D127" s="449"/>
-      <c r="E127" s="449"/>
-      <c r="F127" s="449"/>
-      <c r="G127" s="449"/>
-      <c r="H127" s="449"/>
-      <c r="I127" s="449"/>
-      <c r="J127" s="450"/>
+      <c r="D127" s="450"/>
+      <c r="E127" s="450"/>
+      <c r="F127" s="450"/>
+      <c r="G127" s="450"/>
+      <c r="H127" s="450"/>
+      <c r="I127" s="450"/>
+      <c r="J127" s="451"/>
       <c r="K127" s="347"/>
       <c r="L127" s="347"/>
     </row>
     <row r="128" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C128" s="451"/>
-      <c r="D128" s="452"/>
-      <c r="E128" s="452"/>
-      <c r="F128" s="452"/>
-      <c r="G128" s="452"/>
-      <c r="H128" s="452"/>
-      <c r="I128" s="452"/>
-      <c r="J128" s="453"/>
+      <c r="C128" s="452"/>
+      <c r="D128" s="453"/>
+      <c r="E128" s="453"/>
+      <c r="F128" s="453"/>
+      <c r="G128" s="453"/>
+      <c r="H128" s="453"/>
+      <c r="I128" s="453"/>
+      <c r="J128" s="454"/>
       <c r="K128" s="347"/>
       <c r="L128" s="347"/>
     </row>
     <row r="129" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="454"/>
-      <c r="D129" s="455"/>
-      <c r="E129" s="455"/>
-      <c r="F129" s="455"/>
-      <c r="G129" s="455"/>
-      <c r="H129" s="455"/>
-      <c r="I129" s="455"/>
-      <c r="J129" s="456"/>
+      <c r="C129" s="455"/>
+      <c r="D129" s="456"/>
+      <c r="E129" s="456"/>
+      <c r="F129" s="456"/>
+      <c r="G129" s="456"/>
+      <c r="H129" s="456"/>
+      <c r="I129" s="456"/>
+      <c r="J129" s="457"/>
     </row>
     <row r="131" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="132" spans="3:12" x14ac:dyDescent="0.25">
@@ -18607,40 +18607,40 @@
       <c r="L135" s="347"/>
     </row>
     <row r="136" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C136" s="448" t="s">
+      <c r="C136" s="449" t="s">
         <v>352</v>
       </c>
-      <c r="D136" s="449"/>
-      <c r="E136" s="449"/>
-      <c r="F136" s="449"/>
-      <c r="G136" s="449"/>
-      <c r="H136" s="449"/>
-      <c r="I136" s="449"/>
-      <c r="J136" s="450"/>
+      <c r="D136" s="450"/>
+      <c r="E136" s="450"/>
+      <c r="F136" s="450"/>
+      <c r="G136" s="450"/>
+      <c r="H136" s="450"/>
+      <c r="I136" s="450"/>
+      <c r="J136" s="451"/>
       <c r="K136" s="347"/>
       <c r="L136" s="347"/>
     </row>
     <row r="137" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C137" s="451"/>
-      <c r="D137" s="452"/>
-      <c r="E137" s="452"/>
-      <c r="F137" s="452"/>
-      <c r="G137" s="452"/>
-      <c r="H137" s="452"/>
-      <c r="I137" s="452"/>
-      <c r="J137" s="453"/>
+      <c r="C137" s="452"/>
+      <c r="D137" s="453"/>
+      <c r="E137" s="453"/>
+      <c r="F137" s="453"/>
+      <c r="G137" s="453"/>
+      <c r="H137" s="453"/>
+      <c r="I137" s="453"/>
+      <c r="J137" s="454"/>
       <c r="K137" s="347"/>
       <c r="L137" s="347"/>
     </row>
     <row r="138" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C138" s="454"/>
-      <c r="D138" s="455"/>
-      <c r="E138" s="455"/>
-      <c r="F138" s="455"/>
-      <c r="G138" s="455"/>
-      <c r="H138" s="455"/>
-      <c r="I138" s="455"/>
-      <c r="J138" s="456"/>
+      <c r="C138" s="455"/>
+      <c r="D138" s="456"/>
+      <c r="E138" s="456"/>
+      <c r="F138" s="456"/>
+      <c r="G138" s="456"/>
+      <c r="H138" s="456"/>
+      <c r="I138" s="456"/>
+      <c r="J138" s="457"/>
     </row>
     <row r="140" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="141" spans="3:12" x14ac:dyDescent="0.25">
@@ -18713,40 +18713,40 @@
       <c r="L144" s="347"/>
     </row>
     <row r="145" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C145" s="448" t="s">
+      <c r="C145" s="449" t="s">
         <v>353</v>
       </c>
-      <c r="D145" s="449"/>
-      <c r="E145" s="449"/>
-      <c r="F145" s="449"/>
-      <c r="G145" s="449"/>
-      <c r="H145" s="449"/>
-      <c r="I145" s="449"/>
-      <c r="J145" s="450"/>
+      <c r="D145" s="450"/>
+      <c r="E145" s="450"/>
+      <c r="F145" s="450"/>
+      <c r="G145" s="450"/>
+      <c r="H145" s="450"/>
+      <c r="I145" s="450"/>
+      <c r="J145" s="451"/>
       <c r="K145" s="347"/>
       <c r="L145" s="347"/>
     </row>
     <row r="146" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C146" s="451"/>
-      <c r="D146" s="452"/>
-      <c r="E146" s="452"/>
-      <c r="F146" s="452"/>
-      <c r="G146" s="452"/>
-      <c r="H146" s="452"/>
-      <c r="I146" s="452"/>
-      <c r="J146" s="453"/>
+      <c r="C146" s="452"/>
+      <c r="D146" s="453"/>
+      <c r="E146" s="453"/>
+      <c r="F146" s="453"/>
+      <c r="G146" s="453"/>
+      <c r="H146" s="453"/>
+      <c r="I146" s="453"/>
+      <c r="J146" s="454"/>
       <c r="K146" s="347"/>
       <c r="L146" s="347"/>
     </row>
     <row r="147" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="454"/>
-      <c r="D147" s="455"/>
-      <c r="E147" s="455"/>
-      <c r="F147" s="455"/>
-      <c r="G147" s="455"/>
-      <c r="H147" s="455"/>
-      <c r="I147" s="455"/>
-      <c r="J147" s="456"/>
+      <c r="C147" s="455"/>
+      <c r="D147" s="456"/>
+      <c r="E147" s="456"/>
+      <c r="F147" s="456"/>
+      <c r="G147" s="456"/>
+      <c r="H147" s="456"/>
+      <c r="I147" s="456"/>
+      <c r="J147" s="457"/>
     </row>
     <row r="148" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="149" spans="3:12" x14ac:dyDescent="0.25">
@@ -18798,11 +18798,11 @@
       <c r="G151" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H151" s="457" t="s">
+      <c r="H151" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="I151" s="457"/>
-      <c r="J151" s="458"/>
+      <c r="I151" s="462"/>
+      <c r="J151" s="463"/>
       <c r="K151" s="347"/>
       <c r="L151" s="347"/>
     </row>
@@ -18821,40 +18821,40 @@
       <c r="L152" s="347"/>
     </row>
     <row r="153" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C153" s="448" t="s">
+      <c r="C153" s="449" t="s">
         <v>354</v>
       </c>
-      <c r="D153" s="449"/>
-      <c r="E153" s="449"/>
-      <c r="F153" s="449"/>
-      <c r="G153" s="449"/>
-      <c r="H153" s="449"/>
-      <c r="I153" s="449"/>
-      <c r="J153" s="450"/>
+      <c r="D153" s="450"/>
+      <c r="E153" s="450"/>
+      <c r="F153" s="450"/>
+      <c r="G153" s="450"/>
+      <c r="H153" s="450"/>
+      <c r="I153" s="450"/>
+      <c r="J153" s="451"/>
       <c r="K153" s="347"/>
       <c r="L153" s="347"/>
     </row>
     <row r="154" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C154" s="451"/>
-      <c r="D154" s="452"/>
-      <c r="E154" s="452"/>
-      <c r="F154" s="452"/>
-      <c r="G154" s="452"/>
-      <c r="H154" s="452"/>
-      <c r="I154" s="452"/>
-      <c r="J154" s="453"/>
+      <c r="C154" s="452"/>
+      <c r="D154" s="453"/>
+      <c r="E154" s="453"/>
+      <c r="F154" s="453"/>
+      <c r="G154" s="453"/>
+      <c r="H154" s="453"/>
+      <c r="I154" s="453"/>
+      <c r="J154" s="454"/>
       <c r="K154" s="347"/>
       <c r="L154" s="347"/>
     </row>
     <row r="155" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C155" s="454"/>
-      <c r="D155" s="455"/>
-      <c r="E155" s="455"/>
-      <c r="F155" s="455"/>
-      <c r="G155" s="455"/>
-      <c r="H155" s="455"/>
-      <c r="I155" s="455"/>
-      <c r="J155" s="456"/>
+      <c r="C155" s="455"/>
+      <c r="D155" s="456"/>
+      <c r="E155" s="456"/>
+      <c r="F155" s="456"/>
+      <c r="G155" s="456"/>
+      <c r="H155" s="456"/>
+      <c r="I155" s="456"/>
+      <c r="J155" s="457"/>
       <c r="K155" s="347"/>
       <c r="L155" s="347"/>
     </row>
@@ -18927,11 +18927,11 @@
       <c r="G160" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H160" s="457">
+      <c r="H160" s="462">
         <v>119</v>
       </c>
-      <c r="I160" s="457"/>
-      <c r="J160" s="458"/>
+      <c r="I160" s="462"/>
+      <c r="J160" s="463"/>
       <c r="K160" s="347"/>
       <c r="L160" s="347"/>
     </row>
@@ -18950,40 +18950,40 @@
       <c r="L161" s="347"/>
     </row>
     <row r="162" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C162" s="448" t="s">
+      <c r="C162" s="449" t="s">
         <v>362</v>
       </c>
-      <c r="D162" s="449"/>
-      <c r="E162" s="449"/>
-      <c r="F162" s="449"/>
-      <c r="G162" s="449"/>
-      <c r="H162" s="449"/>
-      <c r="I162" s="449"/>
-      <c r="J162" s="450"/>
+      <c r="D162" s="450"/>
+      <c r="E162" s="450"/>
+      <c r="F162" s="450"/>
+      <c r="G162" s="450"/>
+      <c r="H162" s="450"/>
+      <c r="I162" s="450"/>
+      <c r="J162" s="451"/>
       <c r="K162" s="347"/>
       <c r="L162" s="347"/>
     </row>
     <row r="163" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C163" s="451"/>
-      <c r="D163" s="452"/>
-      <c r="E163" s="452"/>
-      <c r="F163" s="452"/>
-      <c r="G163" s="452"/>
-      <c r="H163" s="452"/>
-      <c r="I163" s="452"/>
-      <c r="J163" s="453"/>
+      <c r="C163" s="452"/>
+      <c r="D163" s="453"/>
+      <c r="E163" s="453"/>
+      <c r="F163" s="453"/>
+      <c r="G163" s="453"/>
+      <c r="H163" s="453"/>
+      <c r="I163" s="453"/>
+      <c r="J163" s="454"/>
       <c r="K163" s="347"/>
       <c r="L163" s="347"/>
     </row>
     <row r="164" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C164" s="454"/>
-      <c r="D164" s="455"/>
-      <c r="E164" s="455"/>
-      <c r="F164" s="455"/>
-      <c r="G164" s="455"/>
-      <c r="H164" s="455"/>
-      <c r="I164" s="455"/>
-      <c r="J164" s="456"/>
+      <c r="C164" s="455"/>
+      <c r="D164" s="456"/>
+      <c r="E164" s="456"/>
+      <c r="F164" s="456"/>
+      <c r="G164" s="456"/>
+      <c r="H164" s="456"/>
+      <c r="I164" s="456"/>
+      <c r="J164" s="457"/>
     </row>
     <row r="165" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C165" s="320"/>
@@ -19054,11 +19054,11 @@
       <c r="G169" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H169" s="457">
+      <c r="H169" s="462">
         <v>80</v>
       </c>
-      <c r="I169" s="457"/>
-      <c r="J169" s="458"/>
+      <c r="I169" s="462"/>
+      <c r="J169" s="463"/>
       <c r="K169" s="347"/>
       <c r="L169" s="347"/>
     </row>
@@ -19077,40 +19077,40 @@
       <c r="L170" s="347"/>
     </row>
     <row r="171" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C171" s="448" t="s">
+      <c r="C171" s="449" t="s">
         <v>363</v>
       </c>
-      <c r="D171" s="449"/>
-      <c r="E171" s="449"/>
-      <c r="F171" s="449"/>
-      <c r="G171" s="449"/>
-      <c r="H171" s="449"/>
-      <c r="I171" s="449"/>
-      <c r="J171" s="450"/>
+      <c r="D171" s="450"/>
+      <c r="E171" s="450"/>
+      <c r="F171" s="450"/>
+      <c r="G171" s="450"/>
+      <c r="H171" s="450"/>
+      <c r="I171" s="450"/>
+      <c r="J171" s="451"/>
       <c r="K171" s="347"/>
       <c r="L171" s="347"/>
     </row>
     <row r="172" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C172" s="451"/>
-      <c r="D172" s="452"/>
-      <c r="E172" s="452"/>
-      <c r="F172" s="452"/>
-      <c r="G172" s="452"/>
-      <c r="H172" s="452"/>
-      <c r="I172" s="452"/>
-      <c r="J172" s="453"/>
+      <c r="C172" s="452"/>
+      <c r="D172" s="453"/>
+      <c r="E172" s="453"/>
+      <c r="F172" s="453"/>
+      <c r="G172" s="453"/>
+      <c r="H172" s="453"/>
+      <c r="I172" s="453"/>
+      <c r="J172" s="454"/>
       <c r="K172" s="347"/>
       <c r="L172" s="347"/>
     </row>
     <row r="173" spans="3:12" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C173" s="454"/>
-      <c r="D173" s="455"/>
-      <c r="E173" s="455"/>
-      <c r="F173" s="455"/>
-      <c r="G173" s="455"/>
-      <c r="H173" s="455"/>
-      <c r="I173" s="455"/>
-      <c r="J173" s="456"/>
+      <c r="C173" s="455"/>
+      <c r="D173" s="456"/>
+      <c r="E173" s="456"/>
+      <c r="F173" s="456"/>
+      <c r="G173" s="456"/>
+      <c r="H173" s="456"/>
+      <c r="I173" s="456"/>
+      <c r="J173" s="457"/>
       <c r="K173" s="347"/>
       <c r="L173" s="347"/>
     </row>
@@ -19164,11 +19164,11 @@
       <c r="G177" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H177" s="457">
+      <c r="H177" s="462">
         <v>64</v>
       </c>
-      <c r="I177" s="457"/>
-      <c r="J177" s="458"/>
+      <c r="I177" s="462"/>
+      <c r="J177" s="463"/>
       <c r="K177" s="347"/>
       <c r="L177" s="347"/>
     </row>
@@ -19187,40 +19187,40 @@
       <c r="L178" s="347"/>
     </row>
     <row r="179" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C179" s="448" t="s">
+      <c r="C179" s="449" t="s">
         <v>360</v>
       </c>
-      <c r="D179" s="449"/>
-      <c r="E179" s="449"/>
-      <c r="F179" s="449"/>
-      <c r="G179" s="449"/>
-      <c r="H179" s="449"/>
-      <c r="I179" s="449"/>
-      <c r="J179" s="450"/>
+      <c r="D179" s="450"/>
+      <c r="E179" s="450"/>
+      <c r="F179" s="450"/>
+      <c r="G179" s="450"/>
+      <c r="H179" s="450"/>
+      <c r="I179" s="450"/>
+      <c r="J179" s="451"/>
       <c r="K179" s="347"/>
       <c r="L179" s="347"/>
     </row>
     <row r="180" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C180" s="451"/>
-      <c r="D180" s="452"/>
-      <c r="E180" s="452"/>
-      <c r="F180" s="452"/>
-      <c r="G180" s="452"/>
-      <c r="H180" s="452"/>
-      <c r="I180" s="452"/>
-      <c r="J180" s="453"/>
+      <c r="C180" s="452"/>
+      <c r="D180" s="453"/>
+      <c r="E180" s="453"/>
+      <c r="F180" s="453"/>
+      <c r="G180" s="453"/>
+      <c r="H180" s="453"/>
+      <c r="I180" s="453"/>
+      <c r="J180" s="454"/>
       <c r="K180" s="347"/>
       <c r="L180" s="347"/>
     </row>
     <row r="181" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C181" s="454"/>
-      <c r="D181" s="455"/>
-      <c r="E181" s="455"/>
-      <c r="F181" s="455"/>
-      <c r="G181" s="455"/>
-      <c r="H181" s="455"/>
-      <c r="I181" s="455"/>
-      <c r="J181" s="456"/>
+      <c r="C181" s="455"/>
+      <c r="D181" s="456"/>
+      <c r="E181" s="456"/>
+      <c r="F181" s="456"/>
+      <c r="G181" s="456"/>
+      <c r="H181" s="456"/>
+      <c r="I181" s="456"/>
+      <c r="J181" s="457"/>
       <c r="K181" s="347"/>
       <c r="L181" s="347"/>
     </row>
@@ -19274,11 +19274,11 @@
       <c r="G186" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H186" s="457">
+      <c r="H186" s="462">
         <v>28</v>
       </c>
-      <c r="I186" s="457"/>
-      <c r="J186" s="458"/>
+      <c r="I186" s="462"/>
+      <c r="J186" s="463"/>
       <c r="K186" s="347"/>
       <c r="L186" s="347"/>
     </row>
@@ -19297,40 +19297,40 @@
       <c r="L187" s="347"/>
     </row>
     <row r="188" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C188" s="448" t="s">
+      <c r="C188" s="449" t="s">
         <v>364</v>
       </c>
-      <c r="D188" s="449"/>
-      <c r="E188" s="449"/>
-      <c r="F188" s="449"/>
-      <c r="G188" s="449"/>
-      <c r="H188" s="449"/>
-      <c r="I188" s="449"/>
-      <c r="J188" s="450"/>
+      <c r="D188" s="450"/>
+      <c r="E188" s="450"/>
+      <c r="F188" s="450"/>
+      <c r="G188" s="450"/>
+      <c r="H188" s="450"/>
+      <c r="I188" s="450"/>
+      <c r="J188" s="451"/>
       <c r="K188" s="347"/>
       <c r="L188" s="347"/>
     </row>
     <row r="189" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C189" s="451"/>
-      <c r="D189" s="452"/>
-      <c r="E189" s="452"/>
-      <c r="F189" s="452"/>
-      <c r="G189" s="452"/>
-      <c r="H189" s="452"/>
-      <c r="I189" s="452"/>
-      <c r="J189" s="453"/>
+      <c r="C189" s="452"/>
+      <c r="D189" s="453"/>
+      <c r="E189" s="453"/>
+      <c r="F189" s="453"/>
+      <c r="G189" s="453"/>
+      <c r="H189" s="453"/>
+      <c r="I189" s="453"/>
+      <c r="J189" s="454"/>
       <c r="K189" s="347"/>
       <c r="L189" s="347"/>
     </row>
     <row r="190" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C190" s="454"/>
-      <c r="D190" s="455"/>
-      <c r="E190" s="455"/>
-      <c r="F190" s="455"/>
-      <c r="G190" s="455"/>
-      <c r="H190" s="455"/>
-      <c r="I190" s="455"/>
-      <c r="J190" s="456"/>
+      <c r="C190" s="455"/>
+      <c r="D190" s="456"/>
+      <c r="E190" s="456"/>
+      <c r="F190" s="456"/>
+      <c r="G190" s="456"/>
+      <c r="H190" s="456"/>
+      <c r="I190" s="456"/>
+      <c r="J190" s="457"/>
       <c r="K190" s="347"/>
       <c r="L190" s="347"/>
     </row>
@@ -19384,11 +19384,11 @@
       <c r="G195" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H195" s="457">
+      <c r="H195" s="462">
         <v>61</v>
       </c>
-      <c r="I195" s="457"/>
-      <c r="J195" s="458"/>
+      <c r="I195" s="462"/>
+      <c r="J195" s="463"/>
       <c r="K195" s="347"/>
       <c r="L195" s="347"/>
     </row>
@@ -19407,40 +19407,40 @@
       <c r="L196" s="347"/>
     </row>
     <row r="197" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C197" s="448" t="s">
+      <c r="C197" s="449" t="s">
         <v>365</v>
       </c>
-      <c r="D197" s="449"/>
-      <c r="E197" s="449"/>
-      <c r="F197" s="449"/>
-      <c r="G197" s="449"/>
-      <c r="H197" s="449"/>
-      <c r="I197" s="449"/>
-      <c r="J197" s="450"/>
+      <c r="D197" s="450"/>
+      <c r="E197" s="450"/>
+      <c r="F197" s="450"/>
+      <c r="G197" s="450"/>
+      <c r="H197" s="450"/>
+      <c r="I197" s="450"/>
+      <c r="J197" s="451"/>
       <c r="K197" s="347"/>
       <c r="L197" s="347"/>
     </row>
     <row r="198" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C198" s="451"/>
-      <c r="D198" s="452"/>
-      <c r="E198" s="452"/>
-      <c r="F198" s="452"/>
-      <c r="G198" s="452"/>
-      <c r="H198" s="452"/>
-      <c r="I198" s="452"/>
-      <c r="J198" s="453"/>
+      <c r="C198" s="452"/>
+      <c r="D198" s="453"/>
+      <c r="E198" s="453"/>
+      <c r="F198" s="453"/>
+      <c r="G198" s="453"/>
+      <c r="H198" s="453"/>
+      <c r="I198" s="453"/>
+      <c r="J198" s="454"/>
       <c r="K198" s="347"/>
       <c r="L198" s="347"/>
     </row>
     <row r="199" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C199" s="454"/>
-      <c r="D199" s="455"/>
-      <c r="E199" s="455"/>
-      <c r="F199" s="455"/>
-      <c r="G199" s="455"/>
-      <c r="H199" s="455"/>
-      <c r="I199" s="455"/>
-      <c r="J199" s="456"/>
+      <c r="C199" s="455"/>
+      <c r="D199" s="456"/>
+      <c r="E199" s="456"/>
+      <c r="F199" s="456"/>
+      <c r="G199" s="456"/>
+      <c r="H199" s="456"/>
+      <c r="I199" s="456"/>
+      <c r="J199" s="457"/>
       <c r="K199" s="347"/>
       <c r="L199" s="347"/>
     </row>
@@ -19491,11 +19491,11 @@
       <c r="G204" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H204" s="457">
+      <c r="H204" s="462">
         <v>97</v>
       </c>
-      <c r="I204" s="457"/>
-      <c r="J204" s="458"/>
+      <c r="I204" s="462"/>
+      <c r="J204" s="463"/>
       <c r="K204" s="347"/>
     </row>
     <row r="205" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19512,38 +19512,38 @@
       <c r="K205" s="347"/>
     </row>
     <row r="206" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C206" s="448" t="s">
+      <c r="C206" s="449" t="s">
         <v>366</v>
       </c>
-      <c r="D206" s="449"/>
-      <c r="E206" s="449"/>
-      <c r="F206" s="449"/>
-      <c r="G206" s="449"/>
-      <c r="H206" s="449"/>
-      <c r="I206" s="449"/>
-      <c r="J206" s="450"/>
+      <c r="D206" s="450"/>
+      <c r="E206" s="450"/>
+      <c r="F206" s="450"/>
+      <c r="G206" s="450"/>
+      <c r="H206" s="450"/>
+      <c r="I206" s="450"/>
+      <c r="J206" s="451"/>
       <c r="K206" s="347"/>
     </row>
     <row r="207" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C207" s="451"/>
-      <c r="D207" s="452"/>
-      <c r="E207" s="452"/>
-      <c r="F207" s="452"/>
-      <c r="G207" s="452"/>
-      <c r="H207" s="452"/>
-      <c r="I207" s="452"/>
-      <c r="J207" s="453"/>
+      <c r="C207" s="452"/>
+      <c r="D207" s="453"/>
+      <c r="E207" s="453"/>
+      <c r="F207" s="453"/>
+      <c r="G207" s="453"/>
+      <c r="H207" s="453"/>
+      <c r="I207" s="453"/>
+      <c r="J207" s="454"/>
       <c r="K207" s="347"/>
     </row>
     <row r="208" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C208" s="454"/>
-      <c r="D208" s="455"/>
-      <c r="E208" s="455"/>
-      <c r="F208" s="455"/>
-      <c r="G208" s="455"/>
-      <c r="H208" s="455"/>
-      <c r="I208" s="455"/>
-      <c r="J208" s="456"/>
+      <c r="C208" s="455"/>
+      <c r="D208" s="456"/>
+      <c r="E208" s="456"/>
+      <c r="F208" s="456"/>
+      <c r="G208" s="456"/>
+      <c r="H208" s="456"/>
+      <c r="I208" s="456"/>
+      <c r="J208" s="457"/>
     </row>
     <row r="209" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C209" s="347"/>
@@ -19619,40 +19619,40 @@
       <c r="L214" s="347"/>
     </row>
     <row r="215" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C215" s="448" t="s">
+      <c r="C215" s="449" t="s">
         <v>367</v>
       </c>
-      <c r="D215" s="449"/>
-      <c r="E215" s="449"/>
-      <c r="F215" s="449"/>
-      <c r="G215" s="449"/>
-      <c r="H215" s="449"/>
-      <c r="I215" s="449"/>
-      <c r="J215" s="450"/>
+      <c r="D215" s="450"/>
+      <c r="E215" s="450"/>
+      <c r="F215" s="450"/>
+      <c r="G215" s="450"/>
+      <c r="H215" s="450"/>
+      <c r="I215" s="450"/>
+      <c r="J215" s="451"/>
       <c r="K215" s="347"/>
       <c r="L215" s="347"/>
     </row>
     <row r="216" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C216" s="451"/>
-      <c r="D216" s="452"/>
-      <c r="E216" s="452"/>
-      <c r="F216" s="452"/>
-      <c r="G216" s="452"/>
-      <c r="H216" s="452"/>
-      <c r="I216" s="452"/>
-      <c r="J216" s="453"/>
+      <c r="C216" s="452"/>
+      <c r="D216" s="453"/>
+      <c r="E216" s="453"/>
+      <c r="F216" s="453"/>
+      <c r="G216" s="453"/>
+      <c r="H216" s="453"/>
+      <c r="I216" s="453"/>
+      <c r="J216" s="454"/>
       <c r="K216" s="347"/>
       <c r="L216" s="347"/>
     </row>
     <row r="217" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C217" s="454"/>
-      <c r="D217" s="455"/>
-      <c r="E217" s="455"/>
-      <c r="F217" s="455"/>
-      <c r="G217" s="455"/>
-      <c r="H217" s="455"/>
-      <c r="I217" s="455"/>
-      <c r="J217" s="456"/>
+      <c r="C217" s="455"/>
+      <c r="D217" s="456"/>
+      <c r="E217" s="456"/>
+      <c r="F217" s="456"/>
+      <c r="G217" s="456"/>
+      <c r="H217" s="456"/>
+      <c r="I217" s="456"/>
+      <c r="J217" s="457"/>
     </row>
     <row r="219" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="220" spans="3:12" x14ac:dyDescent="0.25">
@@ -19727,40 +19727,40 @@
       <c r="L223" s="347"/>
     </row>
     <row r="224" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C224" s="448" t="s">
+      <c r="C224" s="449" t="s">
         <v>369</v>
       </c>
-      <c r="D224" s="449"/>
-      <c r="E224" s="449"/>
-      <c r="F224" s="449"/>
-      <c r="G224" s="449"/>
-      <c r="H224" s="449"/>
-      <c r="I224" s="449"/>
-      <c r="J224" s="450"/>
+      <c r="D224" s="450"/>
+      <c r="E224" s="450"/>
+      <c r="F224" s="450"/>
+      <c r="G224" s="450"/>
+      <c r="H224" s="450"/>
+      <c r="I224" s="450"/>
+      <c r="J224" s="451"/>
       <c r="K224" s="347"/>
       <c r="L224" s="347"/>
     </row>
     <row r="225" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C225" s="451"/>
-      <c r="D225" s="452"/>
-      <c r="E225" s="452"/>
-      <c r="F225" s="452"/>
-      <c r="G225" s="452"/>
-      <c r="H225" s="452"/>
-      <c r="I225" s="452"/>
-      <c r="J225" s="453"/>
+      <c r="C225" s="452"/>
+      <c r="D225" s="453"/>
+      <c r="E225" s="453"/>
+      <c r="F225" s="453"/>
+      <c r="G225" s="453"/>
+      <c r="H225" s="453"/>
+      <c r="I225" s="453"/>
+      <c r="J225" s="454"/>
       <c r="K225" s="347"/>
       <c r="L225" s="347"/>
     </row>
     <row r="226" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C226" s="454"/>
-      <c r="D226" s="455"/>
-      <c r="E226" s="455"/>
-      <c r="F226" s="455"/>
-      <c r="G226" s="455"/>
-      <c r="H226" s="455"/>
-      <c r="I226" s="455"/>
-      <c r="J226" s="456"/>
+      <c r="C226" s="455"/>
+      <c r="D226" s="456"/>
+      <c r="E226" s="456"/>
+      <c r="F226" s="456"/>
+      <c r="G226" s="456"/>
+      <c r="H226" s="456"/>
+      <c r="I226" s="456"/>
+      <c r="J226" s="457"/>
       <c r="K226" s="347"/>
       <c r="L226" s="347"/>
     </row>
@@ -19837,40 +19837,40 @@
       <c r="L232" s="347"/>
     </row>
     <row r="233" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C233" s="448" t="s">
+      <c r="C233" s="449" t="s">
         <v>372</v>
       </c>
-      <c r="D233" s="449"/>
-      <c r="E233" s="449"/>
-      <c r="F233" s="449"/>
-      <c r="G233" s="449"/>
-      <c r="H233" s="449"/>
-      <c r="I233" s="449"/>
-      <c r="J233" s="450"/>
+      <c r="D233" s="450"/>
+      <c r="E233" s="450"/>
+      <c r="F233" s="450"/>
+      <c r="G233" s="450"/>
+      <c r="H233" s="450"/>
+      <c r="I233" s="450"/>
+      <c r="J233" s="451"/>
       <c r="K233" s="347"/>
       <c r="L233" s="347"/>
     </row>
     <row r="234" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C234" s="451"/>
-      <c r="D234" s="452"/>
-      <c r="E234" s="452"/>
-      <c r="F234" s="452"/>
-      <c r="G234" s="452"/>
-      <c r="H234" s="452"/>
-      <c r="I234" s="452"/>
-      <c r="J234" s="453"/>
+      <c r="C234" s="452"/>
+      <c r="D234" s="453"/>
+      <c r="E234" s="453"/>
+      <c r="F234" s="453"/>
+      <c r="G234" s="453"/>
+      <c r="H234" s="453"/>
+      <c r="I234" s="453"/>
+      <c r="J234" s="454"/>
       <c r="K234" s="347"/>
       <c r="L234" s="347"/>
     </row>
     <row r="235" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C235" s="454"/>
-      <c r="D235" s="455"/>
-      <c r="E235" s="455"/>
-      <c r="F235" s="455"/>
-      <c r="G235" s="455"/>
-      <c r="H235" s="455"/>
-      <c r="I235" s="455"/>
-      <c r="J235" s="456"/>
+      <c r="C235" s="455"/>
+      <c r="D235" s="456"/>
+      <c r="E235" s="456"/>
+      <c r="F235" s="456"/>
+      <c r="G235" s="456"/>
+      <c r="H235" s="456"/>
+      <c r="I235" s="456"/>
+      <c r="J235" s="457"/>
       <c r="K235" s="347"/>
       <c r="L235" s="347"/>
     </row>
@@ -19942,38 +19942,38 @@
       <c r="K241" s="347"/>
     </row>
     <row r="242" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C242" s="448" t="s">
+      <c r="C242" s="449" t="s">
         <v>373</v>
       </c>
-      <c r="D242" s="449"/>
-      <c r="E242" s="449"/>
-      <c r="F242" s="449"/>
-      <c r="G242" s="449"/>
-      <c r="H242" s="449"/>
-      <c r="I242" s="449"/>
-      <c r="J242" s="450"/>
+      <c r="D242" s="450"/>
+      <c r="E242" s="450"/>
+      <c r="F242" s="450"/>
+      <c r="G242" s="450"/>
+      <c r="H242" s="450"/>
+      <c r="I242" s="450"/>
+      <c r="J242" s="451"/>
       <c r="K242" s="347"/>
     </row>
     <row r="243" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C243" s="451"/>
-      <c r="D243" s="452"/>
-      <c r="E243" s="452"/>
-      <c r="F243" s="452"/>
-      <c r="G243" s="452"/>
-      <c r="H243" s="452"/>
-      <c r="I243" s="452"/>
-      <c r="J243" s="453"/>
+      <c r="C243" s="452"/>
+      <c r="D243" s="453"/>
+      <c r="E243" s="453"/>
+      <c r="F243" s="453"/>
+      <c r="G243" s="453"/>
+      <c r="H243" s="453"/>
+      <c r="I243" s="453"/>
+      <c r="J243" s="454"/>
       <c r="K243" s="347"/>
     </row>
     <row r="244" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C244" s="454"/>
-      <c r="D244" s="455"/>
-      <c r="E244" s="455"/>
-      <c r="F244" s="455"/>
-      <c r="G244" s="455"/>
-      <c r="H244" s="455"/>
-      <c r="I244" s="455"/>
-      <c r="J244" s="456"/>
+      <c r="C244" s="455"/>
+      <c r="D244" s="456"/>
+      <c r="E244" s="456"/>
+      <c r="F244" s="456"/>
+      <c r="G244" s="456"/>
+      <c r="H244" s="456"/>
+      <c r="I244" s="456"/>
+      <c r="J244" s="457"/>
     </row>
     <row r="246" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="247" spans="3:12" x14ac:dyDescent="0.25">
@@ -20046,45 +20046,66 @@
       <c r="L250" s="347"/>
     </row>
     <row r="251" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C251" s="448" t="s">
+      <c r="C251" s="449" t="s">
         <v>374</v>
       </c>
-      <c r="D251" s="449"/>
-      <c r="E251" s="449"/>
-      <c r="F251" s="449"/>
-      <c r="G251" s="449"/>
-      <c r="H251" s="449"/>
-      <c r="I251" s="449"/>
-      <c r="J251" s="450"/>
+      <c r="D251" s="450"/>
+      <c r="E251" s="450"/>
+      <c r="F251" s="450"/>
+      <c r="G251" s="450"/>
+      <c r="H251" s="450"/>
+      <c r="I251" s="450"/>
+      <c r="J251" s="451"/>
       <c r="K251" s="347"/>
       <c r="L251" s="347"/>
     </row>
     <row r="252" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C252" s="451"/>
-      <c r="D252" s="452"/>
-      <c r="E252" s="452"/>
-      <c r="F252" s="452"/>
-      <c r="G252" s="452"/>
-      <c r="H252" s="452"/>
-      <c r="I252" s="452"/>
-      <c r="J252" s="453"/>
+      <c r="C252" s="452"/>
+      <c r="D252" s="453"/>
+      <c r="E252" s="453"/>
+      <c r="F252" s="453"/>
+      <c r="G252" s="453"/>
+      <c r="H252" s="453"/>
+      <c r="I252" s="453"/>
+      <c r="J252" s="454"/>
       <c r="K252" s="347"/>
       <c r="L252" s="347"/>
     </row>
     <row r="253" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C253" s="454"/>
-      <c r="D253" s="455"/>
-      <c r="E253" s="455"/>
-      <c r="F253" s="455"/>
-      <c r="G253" s="455"/>
-      <c r="H253" s="455"/>
-      <c r="I253" s="455"/>
-      <c r="J253" s="456"/>
+      <c r="C253" s="455"/>
+      <c r="D253" s="456"/>
+      <c r="E253" s="456"/>
+      <c r="F253" s="456"/>
+      <c r="G253" s="456"/>
+      <c r="H253" s="456"/>
+      <c r="I253" s="456"/>
+      <c r="J253" s="457"/>
       <c r="K253" s="347"/>
       <c r="L253" s="347"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C242:J244"/>
+    <mergeCell ref="C206:J208"/>
+    <mergeCell ref="C215:J217"/>
+    <mergeCell ref="C224:J226"/>
+    <mergeCell ref="H186:J186"/>
+    <mergeCell ref="C188:J190"/>
+    <mergeCell ref="H195:J195"/>
+    <mergeCell ref="C197:J199"/>
+    <mergeCell ref="H204:J204"/>
+    <mergeCell ref="C233:J235"/>
+    <mergeCell ref="H160:J160"/>
+    <mergeCell ref="C162:J164"/>
+    <mergeCell ref="H169:J169"/>
+    <mergeCell ref="C171:J173"/>
+    <mergeCell ref="H177:J177"/>
+    <mergeCell ref="C118:J120"/>
+    <mergeCell ref="C127:J129"/>
+    <mergeCell ref="C136:J138"/>
+    <mergeCell ref="C145:J147"/>
+    <mergeCell ref="C153:J155"/>
+    <mergeCell ref="H151:J151"/>
     <mergeCell ref="C251:J253"/>
     <mergeCell ref="C109:J111"/>
     <mergeCell ref="C100:J102"/>
@@ -20101,27 +20122,6 @@
     <mergeCell ref="C52:J54"/>
     <mergeCell ref="K7:N9"/>
     <mergeCell ref="C179:J181"/>
-    <mergeCell ref="C118:J120"/>
-    <mergeCell ref="C127:J129"/>
-    <mergeCell ref="C136:J138"/>
-    <mergeCell ref="C145:J147"/>
-    <mergeCell ref="C153:J155"/>
-    <mergeCell ref="H151:J151"/>
-    <mergeCell ref="H160:J160"/>
-    <mergeCell ref="C162:J164"/>
-    <mergeCell ref="H169:J169"/>
-    <mergeCell ref="C171:J173"/>
-    <mergeCell ref="H177:J177"/>
-    <mergeCell ref="C242:J244"/>
-    <mergeCell ref="C206:J208"/>
-    <mergeCell ref="C215:J217"/>
-    <mergeCell ref="C224:J226"/>
-    <mergeCell ref="H186:J186"/>
-    <mergeCell ref="C188:J190"/>
-    <mergeCell ref="H195:J195"/>
-    <mergeCell ref="C197:J199"/>
-    <mergeCell ref="H204:J204"/>
-    <mergeCell ref="C233:J235"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20293,26 +20293,26 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="463" t="s">
+      <c r="F15" s="464" t="s">
         <v>474</v>
       </c>
-      <c r="G15" s="463"/>
-      <c r="I15" s="463" t="s">
+      <c r="G15" s="464"/>
+      <c r="I15" s="464" t="s">
         <v>480</v>
       </c>
-      <c r="J15" s="463"/>
+      <c r="J15" s="464"/>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F16" s="463"/>
-      <c r="G16" s="463"/>
-      <c r="I16" s="463"/>
-      <c r="J16" s="463"/>
+      <c r="F16" s="464"/>
+      <c r="G16" s="464"/>
+      <c r="I16" s="464"/>
+      <c r="J16" s="464"/>
     </row>
     <row r="17" spans="3:10" ht="37.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="463"/>
-      <c r="G17" s="463"/>
-      <c r="I17" s="463"/>
-      <c r="J17" s="463"/>
+      <c r="F17" s="464"/>
+      <c r="G17" s="464"/>
+      <c r="I17" s="464"/>
+      <c r="J17" s="464"/>
     </row>
     <row r="18" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
@@ -20322,12 +20322,12 @@
       <c r="D19" s="373"/>
       <c r="E19" s="373"/>
       <c r="F19" s="374"/>
-      <c r="G19" s="464" t="s">
+      <c r="G19" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="H19" s="465"/>
-      <c r="I19" s="465"/>
-      <c r="J19" s="466"/>
+      <c r="H19" s="466"/>
+      <c r="I19" s="466"/>
+      <c r="J19" s="467"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="375" t="s">
@@ -20336,10 +20336,10 @@
       <c r="F20" s="376">
         <v>859658.99999999988</v>
       </c>
-      <c r="G20" s="467"/>
-      <c r="H20" s="468"/>
-      <c r="I20" s="468"/>
-      <c r="J20" s="469"/>
+      <c r="G20" s="468"/>
+      <c r="H20" s="469"/>
+      <c r="I20" s="469"/>
+      <c r="J20" s="470"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="375" t="s">
@@ -20348,10 +20348,10 @@
       <c r="F21" s="376">
         <v>26537.673329999998</v>
       </c>
-      <c r="G21" s="467"/>
-      <c r="H21" s="468"/>
-      <c r="I21" s="468"/>
-      <c r="J21" s="469"/>
+      <c r="G21" s="468"/>
+      <c r="H21" s="469"/>
+      <c r="I21" s="469"/>
+      <c r="J21" s="470"/>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="375" t="s">
@@ -20360,18 +20360,18 @@
       <c r="F22" s="377">
         <v>850000</v>
       </c>
-      <c r="G22" s="467"/>
-      <c r="H22" s="468"/>
-      <c r="I22" s="468"/>
-      <c r="J22" s="469"/>
+      <c r="G22" s="468"/>
+      <c r="H22" s="469"/>
+      <c r="I22" s="469"/>
+      <c r="J22" s="470"/>
     </row>
     <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="375"/>
       <c r="F23" s="378"/>
-      <c r="G23" s="467"/>
-      <c r="H23" s="468"/>
-      <c r="I23" s="468"/>
-      <c r="J23" s="469"/>
+      <c r="G23" s="468"/>
+      <c r="H23" s="469"/>
+      <c r="I23" s="469"/>
+      <c r="J23" s="470"/>
     </row>
     <row r="24" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C24" s="369" t="s">
@@ -20383,10 +20383,10 @@
         <f>SUM(F20:F23)</f>
         <v>1736196.6733299999</v>
       </c>
-      <c r="G24" s="470"/>
-      <c r="H24" s="471"/>
-      <c r="I24" s="471"/>
-      <c r="J24" s="472"/>
+      <c r="G24" s="471"/>
+      <c r="H24" s="472"/>
+      <c r="I24" s="472"/>
+      <c r="J24" s="473"/>
     </row>
   </sheetData>
   <mergeCells count="3">
